--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="459">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -1388,6 +1388,9 @@
   </si>
   <si>
     <t>FUCHS TITAN ATF 6400 (ATF FZ) 1L</t>
+  </si>
+  <si>
+    <t>RAV SOL PARBRIZ IARNA 1L</t>
   </si>
 </sst>
 </file>
@@ -1832,7 +1835,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D438"/>
+  <dimension ref="A1:D439"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="49.85546875" customWidth="1"/>
@@ -2433,7 +2436,7 @@
         <v>13</v>
       </c>
       <c r="B43" s="3">
-        <v>1873</v>
+        <v>1861</v>
       </c>
       <c r="C43" s="3">
         <v>13</v>
@@ -3049,7 +3052,7 @@
         <v>45</v>
       </c>
       <c r="B87" s="3">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C87" s="3">
         <v>18.37</v>
@@ -3679,7 +3682,7 @@
         <v>88</v>
       </c>
       <c r="B132" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C132" s="3">
         <v>207.31</v>
@@ -5233,7 +5236,7 @@
         <v>191</v>
       </c>
       <c r="B243" s="3">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C243" s="3">
         <v>33.479999999999997</v>
@@ -5863,7 +5866,7 @@
         <v>232</v>
       </c>
       <c r="B288" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C288" s="3">
         <v>44.93</v>
@@ -5919,7 +5922,7 @@
         <v>235</v>
       </c>
       <c r="B292" s="3">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C292" s="3">
         <v>222.62</v>
@@ -6056,10 +6059,10 @@
     </row>
     <row r="302" spans="1:4">
       <c r="A302" t="s">
-        <v>245</v>
+        <v>458</v>
       </c>
       <c r="B302" s="3">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C302" s="3">
         <v>13.72</v>
@@ -6070,13 +6073,13 @@
     </row>
     <row r="303" spans="1:4">
       <c r="A303" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B303" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C303" s="3">
-        <v>31.95</v>
+        <v>13.72</v>
       </c>
       <c r="D303" s="4" t="s">
         <v>366</v>
@@ -6084,13 +6087,13 @@
     </row>
     <row r="304" spans="1:4">
       <c r="A304" t="s">
-        <v>370</v>
+        <v>246</v>
       </c>
       <c r="B304" s="3">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="C304" s="3">
-        <v>16.2</v>
+        <v>31.95</v>
       </c>
       <c r="D304" s="4" t="s">
         <v>366</v>
@@ -6098,13 +6101,13 @@
     </row>
     <row r="305" spans="1:4">
       <c r="A305" t="s">
-        <v>247</v>
+        <v>370</v>
       </c>
       <c r="B305" s="3">
-        <v>6</v>
+        <v>105</v>
       </c>
       <c r="C305" s="3">
-        <v>36.869999999999997</v>
+        <v>16.2</v>
       </c>
       <c r="D305" s="4" t="s">
         <v>366</v>
@@ -6112,13 +6115,13 @@
     </row>
     <row r="306" spans="1:4">
       <c r="A306" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B306" s="3">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C306" s="3">
-        <v>31.48</v>
+        <v>36.869999999999997</v>
       </c>
       <c r="D306" s="4" t="s">
         <v>366</v>
@@ -6126,13 +6129,13 @@
     </row>
     <row r="307" spans="1:4">
       <c r="A307" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B307" s="3">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C307" s="3">
-        <v>21.9</v>
+        <v>31.48</v>
       </c>
       <c r="D307" s="4" t="s">
         <v>366</v>
@@ -6140,13 +6143,13 @@
     </row>
     <row r="308" spans="1:4">
       <c r="A308" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B308" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C308" s="3">
-        <v>23.19</v>
+        <v>21.9</v>
       </c>
       <c r="D308" s="4" t="s">
         <v>366</v>
@@ -6154,13 +6157,13 @@
     </row>
     <row r="309" spans="1:4">
       <c r="A309" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B309" s="3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C309" s="3">
-        <v>19.55</v>
+        <v>23.19</v>
       </c>
       <c r="D309" s="4" t="s">
         <v>366</v>
@@ -6168,13 +6171,13 @@
     </row>
     <row r="310" spans="1:4">
       <c r="A310" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B310" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C310" s="3">
-        <v>19.07</v>
+        <v>19.55</v>
       </c>
       <c r="D310" s="4" t="s">
         <v>366</v>
@@ -6182,13 +6185,13 @@
     </row>
     <row r="311" spans="1:4">
       <c r="A311" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B311" s="3">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C311" s="3">
-        <v>21.9</v>
+        <v>19.07</v>
       </c>
       <c r="D311" s="4" t="s">
         <v>366</v>
@@ -6196,27 +6199,27 @@
     </row>
     <row r="312" spans="1:4">
       <c r="A312" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B312" s="3">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C312" s="3">
-        <v>79.349999999999994</v>
+        <v>21.9</v>
       </c>
       <c r="D312" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="313" spans="1:4">
       <c r="A313" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B313" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C313" s="3">
-        <v>862.7</v>
+        <v>79.349999999999994</v>
       </c>
       <c r="D313" s="4" t="s">
         <v>367</v>
@@ -6224,13 +6227,13 @@
     </row>
     <row r="314" spans="1:4">
       <c r="A314" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B314" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C314" s="3">
-        <v>56.93</v>
+        <v>862.7</v>
       </c>
       <c r="D314" s="4" t="s">
         <v>367</v>
@@ -6238,13 +6241,13 @@
     </row>
     <row r="315" spans="1:4">
       <c r="A315" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B315" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C315" s="3">
-        <v>1265</v>
+        <v>56.93</v>
       </c>
       <c r="D315" s="4" t="s">
         <v>367</v>
@@ -6252,27 +6255,27 @@
     </row>
     <row r="316" spans="1:4">
       <c r="A316" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B316" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C316" s="3">
-        <v>76</v>
+        <v>1265</v>
       </c>
       <c r="D316" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="317" spans="1:4">
       <c r="A317" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B317" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C317" s="3">
-        <v>267.85000000000002</v>
+        <v>76</v>
       </c>
       <c r="D317" s="4" t="s">
         <v>364</v>
@@ -6280,13 +6283,13 @@
     </row>
     <row r="318" spans="1:4">
       <c r="A318" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B318" s="3">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C318" s="3">
-        <v>74.7</v>
+        <v>267.85000000000002</v>
       </c>
       <c r="D318" s="4" t="s">
         <v>364</v>
@@ -6294,13 +6297,13 @@
     </row>
     <row r="319" spans="1:4">
       <c r="A319" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B319" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C319" s="3">
-        <v>327.3</v>
+        <v>74.7</v>
       </c>
       <c r="D319" s="4" t="s">
         <v>364</v>
@@ -6308,13 +6311,13 @@
     </row>
     <row r="320" spans="1:4">
       <c r="A320" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B320" s="3">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C320" s="3">
-        <v>72.13</v>
+        <v>327.3</v>
       </c>
       <c r="D320" s="4" t="s">
         <v>364</v>
@@ -6322,13 +6325,13 @@
     </row>
     <row r="321" spans="1:4">
       <c r="A321" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B321" s="3">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="C321" s="3">
-        <v>302.39999999999998</v>
+        <v>72.13</v>
       </c>
       <c r="D321" s="4" t="s">
         <v>364</v>
@@ -6336,41 +6339,41 @@
     </row>
     <row r="322" spans="1:4">
       <c r="A322" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B322" s="3">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C322" s="3">
-        <v>36.799999999999997</v>
+        <v>302.39999999999998</v>
       </c>
       <c r="D322" s="4" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="323" spans="1:4">
       <c r="A323" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B323" s="3">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C323" s="3">
-        <v>428.5</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D323" s="4" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="324" spans="1:4">
       <c r="A324" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B324" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C324" s="3">
-        <v>450.22</v>
+        <v>428.5</v>
       </c>
       <c r="D324" s="4" t="s">
         <v>364</v>
@@ -6378,13 +6381,13 @@
     </row>
     <row r="325" spans="1:4">
       <c r="A325" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B325" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C325" s="3">
-        <v>465.7</v>
+        <v>450.22</v>
       </c>
       <c r="D325" s="4" t="s">
         <v>364</v>
@@ -6392,13 +6395,13 @@
     </row>
     <row r="326" spans="1:4">
       <c r="A326" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B326" s="3">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C326" s="3">
-        <v>38.25</v>
+        <v>465.7</v>
       </c>
       <c r="D326" s="4" t="s">
         <v>364</v>
@@ -6406,13 +6409,13 @@
     </row>
     <row r="327" spans="1:4">
       <c r="A327" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B327" s="3">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C327" s="3">
-        <v>87.49</v>
+        <v>38.25</v>
       </c>
       <c r="D327" s="4" t="s">
         <v>364</v>
@@ -6420,13 +6423,13 @@
     </row>
     <row r="328" spans="1:4">
       <c r="A328" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B328" s="3">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C328" s="3">
-        <v>63.13</v>
+        <v>87.49</v>
       </c>
       <c r="D328" s="4" t="s">
         <v>364</v>
@@ -6434,27 +6437,27 @@
     </row>
     <row r="329" spans="1:4">
       <c r="A329" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B329" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C329" s="3">
-        <v>377.78</v>
+        <v>63.13</v>
       </c>
       <c r="D329" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="330" spans="1:4">
       <c r="A330" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B330" s="3">
         <v>2</v>
       </c>
       <c r="C330" s="3">
-        <v>3333.85</v>
+        <v>377.78</v>
       </c>
       <c r="D330" s="4" t="s">
         <v>368</v>
@@ -6462,13 +6465,13 @@
     </row>
     <row r="331" spans="1:4">
       <c r="A331" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B331" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C331" s="3">
-        <v>374.67</v>
+        <v>3333.85</v>
       </c>
       <c r="D331" s="4" t="s">
         <v>368</v>
@@ -6476,13 +6479,13 @@
     </row>
     <row r="332" spans="1:4">
       <c r="A332" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B332" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C332" s="3">
-        <v>120.06</v>
+        <v>374.67</v>
       </c>
       <c r="D332" s="4" t="s">
         <v>368</v>
@@ -6490,41 +6493,41 @@
     </row>
     <row r="333" spans="1:4">
       <c r="A333" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B333" s="3">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="C333" s="3">
-        <v>54.2</v>
+        <v>120.06</v>
       </c>
       <c r="D333" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="334" spans="1:4">
       <c r="A334" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B334" s="3">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="C334" s="3">
-        <v>31.5</v>
+        <v>54.2</v>
       </c>
       <c r="D334" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="335" spans="1:4">
       <c r="A335" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B335" s="3">
         <v>0</v>
       </c>
       <c r="C335" s="3">
-        <v>114.09</v>
+        <v>31.5</v>
       </c>
       <c r="D335" s="4" t="s">
         <v>364</v>
@@ -6532,13 +6535,13 @@
     </row>
     <row r="336" spans="1:4">
       <c r="A336" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B336" s="3">
         <v>0</v>
       </c>
       <c r="C336" s="3">
-        <v>139.9</v>
+        <v>114.09</v>
       </c>
       <c r="D336" s="4" t="s">
         <v>364</v>
@@ -6546,13 +6549,13 @@
     </row>
     <row r="337" spans="1:4">
       <c r="A337" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B337" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C337" s="3">
-        <v>50.13</v>
+        <v>139.9</v>
       </c>
       <c r="D337" s="4" t="s">
         <v>364</v>
@@ -6560,13 +6563,13 @@
     </row>
     <row r="338" spans="1:4">
       <c r="A338" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B338" s="3">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C338" s="3">
-        <v>140.26</v>
+        <v>50.13</v>
       </c>
       <c r="D338" s="4" t="s">
         <v>364</v>
@@ -6574,55 +6577,55 @@
     </row>
     <row r="339" spans="1:4">
       <c r="A339" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B339" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C339" s="3">
-        <v>370.53</v>
+        <v>140.26</v>
       </c>
       <c r="D339" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="340" spans="1:4">
       <c r="A340" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B340" s="3">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C340" s="3">
-        <v>30.9</v>
+        <v>370.53</v>
       </c>
       <c r="D340" s="4" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
     </row>
     <row r="341" spans="1:4">
       <c r="A341" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B341" s="3">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C341" s="3">
-        <v>5746.5</v>
+        <v>30.9</v>
       </c>
       <c r="D341" s="4" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="342" spans="1:4">
       <c r="A342" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B342" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C342" s="3">
-        <v>516.46</v>
+        <v>5746.5</v>
       </c>
       <c r="D342" s="4" t="s">
         <v>364</v>
@@ -6630,13 +6633,13 @@
     </row>
     <row r="343" spans="1:4">
       <c r="A343" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B343" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C343" s="3">
-        <v>185.15</v>
+        <v>516.46</v>
       </c>
       <c r="D343" s="4" t="s">
         <v>364</v>
@@ -6644,58 +6647,58 @@
     </row>
     <row r="344" spans="1:4">
       <c r="A344" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B344" s="3">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="C344" s="3">
-        <v>11.5</v>
+        <v>185.15</v>
       </c>
       <c r="D344" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="345" spans="1:4">
       <c r="A345" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B345" s="3">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C345" s="3">
-        <v>724.5</v>
+        <v>11.5</v>
       </c>
       <c r="D345" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="346" spans="1:4">
       <c r="A346" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B346" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C346" s="3">
-        <v>450.22</v>
+        <v>724.5</v>
       </c>
       <c r="D346" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="347" spans="1:4">
       <c r="A347" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B347" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C347" s="3">
-        <v>461.23</v>
+        <v>450.22</v>
       </c>
       <c r="D347" s="4" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -6706,7 +6709,7 @@
         <v>1</v>
       </c>
       <c r="C348" s="3">
-        <v>518.41999999999996</v>
+        <v>461.23</v>
       </c>
       <c r="D348" s="4" t="s">
         <v>357</v>
@@ -6714,13 +6717,13 @@
     </row>
     <row r="349" spans="1:4">
       <c r="A349" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B349" s="3">
         <v>1</v>
       </c>
       <c r="C349" s="3">
-        <v>348.08</v>
+        <v>518.41999999999996</v>
       </c>
       <c r="D349" s="4" t="s">
         <v>357</v>
@@ -6728,13 +6731,13 @@
     </row>
     <row r="350" spans="1:4">
       <c r="A350" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B350" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C350" s="3">
-        <v>33.479999999999997</v>
+        <v>348.08</v>
       </c>
       <c r="D350" s="4" t="s">
         <v>357</v>
@@ -6742,13 +6745,13 @@
     </row>
     <row r="351" spans="1:4">
       <c r="A351" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B351" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C351" s="3">
-        <v>35.79</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D351" s="4" t="s">
         <v>357</v>
@@ -6756,13 +6759,13 @@
     </row>
     <row r="352" spans="1:4">
       <c r="A352" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B352" s="3">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C352" s="3">
-        <v>377.7</v>
+        <v>35.79</v>
       </c>
       <c r="D352" s="4" t="s">
         <v>357</v>
@@ -6770,13 +6773,13 @@
     </row>
     <row r="353" spans="1:4">
       <c r="A353" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B353" s="3">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C353" s="3">
-        <v>33.21</v>
+        <v>377.7</v>
       </c>
       <c r="D353" s="4" t="s">
         <v>357</v>
@@ -6784,13 +6787,13 @@
     </row>
     <row r="354" spans="1:4">
       <c r="A354" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B354" s="3">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C354" s="3">
-        <v>27.16</v>
+        <v>33.21</v>
       </c>
       <c r="D354" s="4" t="s">
         <v>357</v>
@@ -6798,13 +6801,13 @@
     </row>
     <row r="355" spans="1:4">
       <c r="A355" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B355" s="3">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C355" s="3">
-        <v>361.41</v>
+        <v>27.16</v>
       </c>
       <c r="D355" s="4" t="s">
         <v>357</v>
@@ -6812,13 +6815,13 @@
     </row>
     <row r="356" spans="1:4">
       <c r="A356" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B356" s="3">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="C356" s="3">
-        <v>29.25</v>
+        <v>361.41</v>
       </c>
       <c r="D356" s="4" t="s">
         <v>357</v>
@@ -6826,13 +6829,13 @@
     </row>
     <row r="357" spans="1:4">
       <c r="A357" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B357" s="3">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="C357" s="3">
-        <v>304.54000000000002</v>
+        <v>29.25</v>
       </c>
       <c r="D357" s="4" t="s">
         <v>357</v>
@@ -6840,13 +6843,13 @@
     </row>
     <row r="358" spans="1:4">
       <c r="A358" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B358" s="3">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C358" s="3">
-        <v>34.049999999999997</v>
+        <v>304.54000000000002</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>357</v>
@@ -6854,55 +6857,55 @@
     </row>
     <row r="359" spans="1:4">
       <c r="A359" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B359" s="3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C359" s="3">
-        <v>57.7</v>
+        <v>34.049999999999997</v>
       </c>
       <c r="D359" s="4" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
     </row>
     <row r="360" spans="1:4">
       <c r="A360" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B360" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C360" s="3">
-        <v>90.9</v>
+        <v>57.7</v>
       </c>
       <c r="D360" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="361" spans="1:4">
       <c r="A361" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B361" s="3">
-        <v>273</v>
+        <v>10</v>
       </c>
       <c r="C361" s="3">
-        <v>47.62</v>
+        <v>90.9</v>
       </c>
       <c r="D361" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="362" spans="1:4">
       <c r="A362" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B362" s="3">
-        <v>1</v>
+        <v>266</v>
       </c>
       <c r="C362" s="3">
-        <v>7173.59</v>
+        <v>47.62</v>
       </c>
       <c r="D362" s="4" t="s">
         <v>364</v>
@@ -6910,13 +6913,13 @@
     </row>
     <row r="363" spans="1:4">
       <c r="A363" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B363" s="3">
         <v>1</v>
       </c>
       <c r="C363" s="3">
-        <v>677.79</v>
+        <v>7173.59</v>
       </c>
       <c r="D363" s="4" t="s">
         <v>364</v>
@@ -6924,13 +6927,13 @@
     </row>
     <row r="364" spans="1:4">
       <c r="A364" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B364" s="3">
-        <v>12</v>
-      </c>
-      <c r="C364" s="8">
-        <v>171.47</v>
+        <v>1</v>
+      </c>
+      <c r="C364" s="3">
+        <v>677.79</v>
       </c>
       <c r="D364" s="4" t="s">
         <v>364</v>
@@ -6938,13 +6941,13 @@
     </row>
     <row r="365" spans="1:4">
       <c r="A365" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B365" s="3">
-        <v>104</v>
-      </c>
-      <c r="C365" s="3">
-        <v>212.75</v>
+        <v>12</v>
+      </c>
+      <c r="C365" s="8">
+        <v>171.47</v>
       </c>
       <c r="D365" s="4" t="s">
         <v>364</v>
@@ -6952,13 +6955,13 @@
     </row>
     <row r="366" spans="1:4">
       <c r="A366" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B366" s="3">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="C366" s="3">
-        <v>2335.67</v>
+        <v>212.75</v>
       </c>
       <c r="D366" s="4" t="s">
         <v>364</v>
@@ -6966,13 +6969,13 @@
     </row>
     <row r="367" spans="1:4">
       <c r="A367" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B367" s="3">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="C367" s="3">
-        <v>66.180000000000007</v>
+        <v>2335.67</v>
       </c>
       <c r="D367" s="4" t="s">
         <v>364</v>
@@ -6980,13 +6983,13 @@
     </row>
     <row r="368" spans="1:4">
       <c r="A368" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B368" s="3">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="C368" s="3">
-        <v>8139.6</v>
+        <v>66.180000000000007</v>
       </c>
       <c r="D368" s="4" t="s">
         <v>364</v>
@@ -6994,13 +6997,13 @@
     </row>
     <row r="369" spans="1:4">
       <c r="A369" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B369" s="3">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="C369" s="3">
-        <v>259.81</v>
+        <v>8139.6</v>
       </c>
       <c r="D369" s="4" t="s">
         <v>364</v>
@@ -7008,13 +7011,13 @@
     </row>
     <row r="370" spans="1:4">
       <c r="A370" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B370" s="3">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C370" s="3">
-        <v>259.8</v>
+        <v>259.81</v>
       </c>
       <c r="D370" s="4" t="s">
         <v>364</v>
@@ -7022,13 +7025,13 @@
     </row>
     <row r="371" spans="1:4">
       <c r="A371" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B371" s="3">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="C371" s="3">
-        <v>310.2</v>
+        <v>259.8</v>
       </c>
       <c r="D371" s="4" t="s">
         <v>364</v>
@@ -7036,13 +7039,13 @@
     </row>
     <row r="372" spans="1:4">
       <c r="A372" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B372" s="3">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C372" s="3">
-        <v>36.43</v>
+        <v>310.2</v>
       </c>
       <c r="D372" s="4" t="s">
         <v>364</v>
@@ -7050,13 +7053,13 @@
     </row>
     <row r="373" spans="1:4">
       <c r="A373" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B373" s="3">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C373" s="3">
-        <v>87.22</v>
+        <v>36.43</v>
       </c>
       <c r="D373" s="4" t="s">
         <v>364</v>
@@ -7064,13 +7067,13 @@
     </row>
     <row r="374" spans="1:4">
       <c r="A374" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B374" s="3">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C374" s="3">
-        <v>319.60000000000002</v>
+        <v>87.22</v>
       </c>
       <c r="D374" s="4" t="s">
         <v>364</v>
@@ -7078,13 +7081,13 @@
     </row>
     <row r="375" spans="1:4">
       <c r="A375" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B375" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C375" s="3">
-        <v>62.6</v>
+        <v>319.60000000000002</v>
       </c>
       <c r="D375" s="4" t="s">
         <v>364</v>
@@ -7092,13 +7095,13 @@
     </row>
     <row r="376" spans="1:4">
       <c r="A376" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B376" s="3">
-        <v>8</v>
-      </c>
-      <c r="C376" s="8">
-        <v>385.25</v>
+        <v>14</v>
+      </c>
+      <c r="C376" s="3">
+        <v>62.6</v>
       </c>
       <c r="D376" s="4" t="s">
         <v>364</v>
@@ -7106,27 +7109,27 @@
     </row>
     <row r="377" spans="1:4">
       <c r="A377" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B377" s="3">
-        <v>29</v>
-      </c>
-      <c r="C377" s="3">
-        <v>67.28</v>
+        <v>8</v>
+      </c>
+      <c r="C377" s="8">
+        <v>385.25</v>
       </c>
       <c r="D377" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="378" spans="1:4">
       <c r="A378" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B378" s="3">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C378" s="3">
-        <v>1138.5</v>
+        <v>67.28</v>
       </c>
       <c r="D378" s="4" t="s">
         <v>367</v>
@@ -7134,27 +7137,27 @@
     </row>
     <row r="379" spans="1:4">
       <c r="A379" t="s">
-        <v>350</v>
+        <v>319</v>
       </c>
       <c r="B379" s="3">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C379" s="3">
-        <v>58.69</v>
+        <v>1138.5</v>
       </c>
       <c r="D379" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="380" spans="1:4">
       <c r="A380" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B380" s="3">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C380" s="3">
-        <v>289.33999999999997</v>
+        <v>58.69</v>
       </c>
       <c r="D380" s="4" t="s">
         <v>364</v>
@@ -7162,13 +7165,13 @@
     </row>
     <row r="381" spans="1:4">
       <c r="A381" t="s">
-        <v>320</v>
+        <v>351</v>
       </c>
       <c r="B381" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C381" s="3">
-        <v>48.76</v>
+        <v>289.33999999999997</v>
       </c>
       <c r="D381" s="4" t="s">
         <v>364</v>
@@ -7176,13 +7179,13 @@
     </row>
     <row r="382" spans="1:4">
       <c r="A382" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B382" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C382" s="3">
-        <v>242.34</v>
+        <v>48.76</v>
       </c>
       <c r="D382" s="4" t="s">
         <v>364</v>
@@ -7190,13 +7193,13 @@
     </row>
     <row r="383" spans="1:4">
       <c r="A383" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B383" s="3">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="C383" s="3">
-        <v>65.599999999999994</v>
+        <v>242.34</v>
       </c>
       <c r="D383" s="4" t="s">
         <v>364</v>
@@ -7204,13 +7207,13 @@
     </row>
     <row r="384" spans="1:4">
       <c r="A384" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B384" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C384" s="3">
-        <v>255.03</v>
+        <v>65.599999999999994</v>
       </c>
       <c r="D384" s="4" t="s">
         <v>364</v>
@@ -7218,13 +7221,13 @@
     </row>
     <row r="385" spans="1:4">
       <c r="A385" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B385" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C385" s="3">
-        <v>220.8</v>
+        <v>255.03</v>
       </c>
       <c r="D385" s="4" t="s">
         <v>364</v>
@@ -7232,13 +7235,13 @@
     </row>
     <row r="386" spans="1:4">
       <c r="A386" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B386" s="3">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C386" s="3">
-        <v>255.02</v>
+        <v>220.8</v>
       </c>
       <c r="D386" s="4" t="s">
         <v>364</v>
@@ -7246,13 +7249,13 @@
     </row>
     <row r="387" spans="1:4">
       <c r="A387" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B387" s="3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C387" s="3">
-        <v>68.86</v>
+        <v>255.02</v>
       </c>
       <c r="D387" s="4" t="s">
         <v>364</v>
@@ -7260,13 +7263,13 @@
     </row>
     <row r="388" spans="1:4">
       <c r="A388" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B388" s="3">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C388" s="3">
-        <v>344.28</v>
+        <v>68.86</v>
       </c>
       <c r="D388" s="4" t="s">
         <v>364</v>
@@ -7274,13 +7277,13 @@
     </row>
     <row r="389" spans="1:4">
       <c r="A389" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B389" s="3">
         <v>2</v>
       </c>
       <c r="C389" s="3">
-        <v>60.29</v>
+        <v>344.28</v>
       </c>
       <c r="D389" s="4" t="s">
         <v>364</v>
@@ -7288,13 +7291,13 @@
     </row>
     <row r="390" spans="1:4">
       <c r="A390" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B390" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C390" s="3">
-        <v>261.8</v>
+        <v>60.29</v>
       </c>
       <c r="D390" s="4" t="s">
         <v>364</v>
@@ -7302,55 +7305,55 @@
     </row>
     <row r="391" spans="1:4">
       <c r="A391" t="s">
-        <v>382</v>
+        <v>329</v>
       </c>
       <c r="B391" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C391" s="3">
-        <v>30.58</v>
+        <v>261.8</v>
       </c>
       <c r="D391" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="392" spans="1:4">
       <c r="A392" t="s">
-        <v>330</v>
+        <v>382</v>
       </c>
       <c r="B392" s="3">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="C392" s="3">
-        <v>16.95</v>
+        <v>30.58</v>
       </c>
       <c r="D392" s="4" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
     </row>
     <row r="393" spans="1:4">
       <c r="A393" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B393" s="3">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="C393" s="3">
-        <v>24.95</v>
+        <v>16.95</v>
       </c>
       <c r="D393" s="4" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
     </row>
     <row r="394" spans="1:4">
       <c r="A394" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B394" s="3">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="C394" s="3">
-        <v>641.49</v>
+        <v>24.95</v>
       </c>
       <c r="D394" s="4" t="s">
         <v>367</v>
@@ -7358,13 +7361,13 @@
     </row>
     <row r="395" spans="1:4">
       <c r="A395" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B395" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C395" s="3">
-        <v>39.57</v>
+        <v>641.49</v>
       </c>
       <c r="D395" s="4" t="s">
         <v>367</v>
@@ -7372,13 +7375,13 @@
     </row>
     <row r="396" spans="1:4">
       <c r="A396" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B396" s="3">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C396" s="3">
-        <v>51.83</v>
+        <v>39.57</v>
       </c>
       <c r="D396" s="4" t="s">
         <v>367</v>
@@ -7386,27 +7389,27 @@
     </row>
     <row r="397" spans="1:4">
       <c r="A397" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B397" s="3">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C397" s="3">
-        <v>33.840000000000003</v>
+        <v>51.83</v>
       </c>
       <c r="D397" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="398" spans="1:4">
       <c r="A398" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B398" s="3">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="C398" s="3">
-        <v>150.15</v>
+        <v>33.840000000000003</v>
       </c>
       <c r="D398" s="4" t="s">
         <v>364</v>
@@ -7414,13 +7417,13 @@
     </row>
     <row r="399" spans="1:4">
       <c r="A399" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B399" s="3">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C399" s="3">
-        <v>144.5</v>
+        <v>150.15</v>
       </c>
       <c r="D399" s="4" t="s">
         <v>364</v>
@@ -7428,13 +7431,13 @@
     </row>
     <row r="400" spans="1:4">
       <c r="A400" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B400" s="3">
         <v>25</v>
       </c>
       <c r="C400" s="3">
-        <v>100.93</v>
+        <v>144.5</v>
       </c>
       <c r="D400" s="4" t="s">
         <v>364</v>
@@ -7442,13 +7445,13 @@
     </row>
     <row r="401" spans="1:4">
       <c r="A401" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B401" s="3">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C401" s="3">
-        <v>124.5</v>
+        <v>100.93</v>
       </c>
       <c r="D401" s="4" t="s">
         <v>364</v>
@@ -7456,13 +7459,13 @@
     </row>
     <row r="402" spans="1:4">
       <c r="A402" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B402" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C402" s="3">
-        <v>27.21</v>
+        <v>124.5</v>
       </c>
       <c r="D402" s="4" t="s">
         <v>364</v>
@@ -7470,41 +7473,41 @@
     </row>
     <row r="403" spans="1:4">
       <c r="A403" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B403" s="3">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="C403" s="3">
-        <v>24.79</v>
+        <v>27.21</v>
       </c>
       <c r="D403" s="4" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
     </row>
     <row r="404" spans="1:4">
       <c r="A404" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B404" s="3">
-        <v>6</v>
+        <v>94</v>
       </c>
       <c r="C404" s="3">
-        <v>37.1</v>
+        <v>24.79</v>
       </c>
       <c r="D404" s="4" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
     </row>
     <row r="405" spans="1:4">
       <c r="A405" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B405" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C405" s="3">
-        <v>178.04</v>
+        <v>37.1</v>
       </c>
       <c r="D405" s="4" t="s">
         <v>364</v>
@@ -7512,41 +7515,41 @@
     </row>
     <row r="406" spans="1:4">
       <c r="A406" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B406" s="3">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="C406" s="3">
-        <v>23.88</v>
+        <v>178.04</v>
       </c>
       <c r="D406" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="407" spans="1:4">
       <c r="A407" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B407" s="3">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="C407" s="3">
-        <v>20.68</v>
+        <v>23.88</v>
       </c>
       <c r="D407" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="408" spans="1:4">
       <c r="A408" t="s">
-        <v>372</v>
+        <v>345</v>
       </c>
       <c r="B408" s="3">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="C408" s="3">
-        <v>97.54</v>
+        <v>20.68</v>
       </c>
       <c r="D408" s="4" t="s">
         <v>364</v>
@@ -7554,13 +7557,13 @@
     </row>
     <row r="409" spans="1:4">
       <c r="A409" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B409" s="3">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C409" s="3">
-        <v>304.02999999999997</v>
+        <v>97.54</v>
       </c>
       <c r="D409" s="4" t="s">
         <v>364</v>
@@ -7568,27 +7571,27 @@
     </row>
     <row r="410" spans="1:4">
       <c r="A410" t="s">
-        <v>346</v>
+        <v>373</v>
       </c>
       <c r="B410" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C410" s="3">
-        <v>1934.56</v>
+        <v>304.02999999999997</v>
       </c>
       <c r="D410" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="411" spans="1:4">
       <c r="A411" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B411" s="3">
         <v>0</v>
       </c>
       <c r="C411" s="3">
-        <v>230.99</v>
+        <v>1934.56</v>
       </c>
       <c r="D411" s="4" t="s">
         <v>368</v>
@@ -7596,55 +7599,55 @@
     </row>
     <row r="412" spans="1:4">
       <c r="A412" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B412" s="3">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="C412" s="3">
-        <v>33.39</v>
+        <v>230.99</v>
       </c>
       <c r="D412" s="4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="413" spans="1:4">
       <c r="A413" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B413" s="3">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="C413" s="3">
-        <v>20.66</v>
+        <v>33.39</v>
       </c>
       <c r="D413" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="414" spans="1:4">
       <c r="A414" t="s">
-        <v>375</v>
+        <v>349</v>
       </c>
       <c r="B414" s="3">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="C414" s="3">
-        <v>97.5</v>
+        <v>20.66</v>
       </c>
       <c r="D414" s="4" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
     </row>
     <row r="415" spans="1:4">
       <c r="A415" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B415" s="3">
-        <v>443</v>
+        <v>78</v>
       </c>
       <c r="C415" s="3">
-        <v>24.7</v>
+        <v>97.5</v>
       </c>
       <c r="D415" s="4" t="s">
         <v>374</v>
@@ -7652,13 +7655,13 @@
     </row>
     <row r="416" spans="1:4">
       <c r="A416" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B416" s="3">
-        <v>477</v>
+        <v>443</v>
       </c>
       <c r="C416" s="3">
-        <v>35.75</v>
+        <v>24.7</v>
       </c>
       <c r="D416" s="4" t="s">
         <v>374</v>
@@ -7666,13 +7669,13 @@
     </row>
     <row r="417" spans="1:4">
       <c r="A417" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B417" s="3">
-        <v>153</v>
+        <v>477</v>
       </c>
       <c r="C417" s="3">
-        <v>9.1</v>
+        <v>35.75</v>
       </c>
       <c r="D417" s="4" t="s">
         <v>374</v>
@@ -7680,13 +7683,13 @@
     </row>
     <row r="418" spans="1:4">
       <c r="A418" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B418" s="3">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C418" s="3">
-        <v>5.43</v>
+        <v>9.1</v>
       </c>
       <c r="D418" s="4" t="s">
         <v>374</v>
@@ -7694,13 +7697,13 @@
     </row>
     <row r="419" spans="1:4">
       <c r="A419" t="s">
-        <v>432</v>
+        <v>379</v>
       </c>
       <c r="B419" s="3">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="C419" s="3">
-        <v>11.99</v>
+        <v>5.43</v>
       </c>
       <c r="D419" s="4" t="s">
         <v>374</v>
@@ -7708,27 +7711,27 @@
     </row>
     <row r="420" spans="1:4">
       <c r="A420" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
       <c r="B420" s="3">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="C420" s="3">
-        <v>9.75</v>
+        <v>11.99</v>
       </c>
       <c r="D420" s="4" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="421" spans="1:4">
       <c r="A421" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B421" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C421" s="3">
-        <v>6.37</v>
+        <v>9.75</v>
       </c>
       <c r="D421" s="4" t="s">
         <v>380</v>
@@ -7736,13 +7739,13 @@
     </row>
     <row r="422" spans="1:4">
       <c r="A422" t="s">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="B422" s="3">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C422" s="3">
-        <v>10.53</v>
+        <v>6.37</v>
       </c>
       <c r="D422" s="4" t="s">
         <v>380</v>
@@ -7750,27 +7753,27 @@
     </row>
     <row r="423" spans="1:4">
       <c r="A423" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="B423" s="3">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="C423" s="3">
-        <v>11.59</v>
+        <v>10.53</v>
       </c>
       <c r="D423" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="424" spans="1:4">
       <c r="A424" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="B424" s="3">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C424" s="3">
-        <v>12.09</v>
+        <v>11.59</v>
       </c>
       <c r="D424" s="4" t="s">
         <v>381</v>
@@ -7778,10 +7781,10 @@
     </row>
     <row r="425" spans="1:4">
       <c r="A425" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B425" s="3">
-        <v>230</v>
+        <v>36</v>
       </c>
       <c r="C425" s="3">
         <v>12.09</v>
@@ -7792,13 +7795,13 @@
     </row>
     <row r="426" spans="1:4">
       <c r="A426" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B426" s="3">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="C426" s="3">
-        <v>6.5</v>
+        <v>12.09</v>
       </c>
       <c r="D426" s="4" t="s">
         <v>381</v>
@@ -7806,10 +7809,10 @@
     </row>
     <row r="427" spans="1:4">
       <c r="A427" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B427" s="3">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C427" s="3">
         <v>6.5</v>
@@ -7820,27 +7823,27 @@
     </row>
     <row r="428" spans="1:4">
       <c r="A428" t="s">
-        <v>453</v>
+        <v>437</v>
       </c>
       <c r="B428" s="3">
-        <v>2</v>
+        <v>214</v>
       </c>
       <c r="C428" s="3">
-        <v>5017</v>
+        <v>6.5</v>
       </c>
       <c r="D428" s="4" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
     </row>
     <row r="429" spans="1:4">
       <c r="A429" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B429" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C429" s="3">
-        <v>4437.1499999999996</v>
+        <v>5017</v>
       </c>
       <c r="D429" s="4" t="s">
         <v>364</v>
@@ -7848,13 +7851,13 @@
     </row>
     <row r="430" spans="1:4">
       <c r="A430" t="s">
-        <v>429</v>
+        <v>454</v>
       </c>
       <c r="B430" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C430" s="3">
-        <v>6239.83</v>
+        <v>4437.1499999999996</v>
       </c>
       <c r="D430" s="4" t="s">
         <v>364</v>
@@ -7862,13 +7865,13 @@
     </row>
     <row r="431" spans="1:4">
       <c r="A431" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="B431" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C431" s="3">
-        <v>5980</v>
+        <v>6239.83</v>
       </c>
       <c r="D431" s="4" t="s">
         <v>364</v>
@@ -7876,13 +7879,13 @@
     </row>
     <row r="432" spans="1:4">
       <c r="A432" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="B432" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C432" s="3">
-        <v>3556.4</v>
+        <v>5980</v>
       </c>
       <c r="D432" s="4" t="s">
         <v>364</v>
@@ -7890,13 +7893,13 @@
     </row>
     <row r="433" spans="1:4">
       <c r="A433" t="s">
-        <v>451</v>
+        <v>428</v>
       </c>
       <c r="B433" s="3">
         <v>2</v>
       </c>
       <c r="C433" s="3">
-        <v>6463</v>
+        <v>3556.4</v>
       </c>
       <c r="D433" s="4" t="s">
         <v>364</v>
@@ -7904,13 +7907,13 @@
     </row>
     <row r="434" spans="1:4">
       <c r="A434" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B434" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C434" s="3">
-        <v>5199</v>
+        <v>6463</v>
       </c>
       <c r="D434" s="4" t="s">
         <v>364</v>
@@ -7918,27 +7921,27 @@
     </row>
     <row r="435" spans="1:4">
       <c r="A435" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="B435" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C435" s="3">
-        <v>58.68</v>
+        <v>5199</v>
       </c>
       <c r="D435" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="436" spans="1:4">
       <c r="A436" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="B436" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C436" s="3">
-        <v>65</v>
+        <v>58.68</v>
       </c>
       <c r="D436" s="4" t="s">
         <v>367</v>
@@ -7946,13 +7949,13 @@
     </row>
     <row r="437" spans="1:4">
       <c r="A437" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="B437" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C437" s="3">
-        <v>70.25</v>
+        <v>65</v>
       </c>
       <c r="D437" s="4" t="s">
         <v>367</v>
@@ -7960,15 +7963,29 @@
     </row>
     <row r="438" spans="1:4">
       <c r="A438" t="s">
+        <v>449</v>
+      </c>
+      <c r="B438" s="3">
+        <v>10</v>
+      </c>
+      <c r="C438" s="3">
+        <v>70.25</v>
+      </c>
+      <c r="D438" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4">
+      <c r="A439" t="s">
         <v>456</v>
       </c>
-      <c r="B438" s="3">
+      <c r="B439" s="3">
         <v>13</v>
       </c>
-      <c r="C438" s="3">
+      <c r="C439" s="3">
         <v>45</v>
       </c>
-      <c r="D438" s="4" t="s">
+      <c r="D439" s="4" t="s">
         <v>455</v>
       </c>
     </row>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -2296,7 +2296,7 @@
         <v>423</v>
       </c>
       <c r="B33" s="3">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C33" s="3">
         <v>207.95</v>
@@ -2436,7 +2436,7 @@
         <v>13</v>
       </c>
       <c r="B43" s="3">
-        <v>1861</v>
+        <v>1825</v>
       </c>
       <c r="C43" s="3">
         <v>13</v>
@@ -2450,7 +2450,7 @@
         <v>14</v>
       </c>
       <c r="B44" s="3">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C44" s="3">
         <v>23.37</v>
@@ -2758,7 +2758,7 @@
         <v>31</v>
       </c>
       <c r="B66" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C66" s="3">
         <v>70.47</v>
@@ -2772,7 +2772,7 @@
         <v>32</v>
       </c>
       <c r="B67" s="3">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C67" s="3">
         <v>87.12</v>
@@ -2912,7 +2912,7 @@
         <v>443</v>
       </c>
       <c r="B77" s="3">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C77" s="3">
         <v>19.48</v>
@@ -3052,7 +3052,7 @@
         <v>45</v>
       </c>
       <c r="B87" s="3">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C87" s="3">
         <v>18.37</v>
@@ -3066,7 +3066,7 @@
         <v>46</v>
       </c>
       <c r="B88" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C88" s="3">
         <v>82.88</v>
@@ -3108,7 +3108,7 @@
         <v>49</v>
       </c>
       <c r="B91" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C91" s="3">
         <v>65.83</v>
@@ -4074,7 +4074,7 @@
         <v>113</v>
       </c>
       <c r="B160" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C160" s="3">
         <v>32.200000000000003</v>
@@ -4466,7 +4466,7 @@
         <v>140</v>
       </c>
       <c r="B188" s="3">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C188" s="3">
         <v>35.81</v>
@@ -4578,7 +4578,7 @@
         <v>147</v>
       </c>
       <c r="B196" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C196" s="3">
         <v>44.5</v>
@@ -4592,7 +4592,7 @@
         <v>148</v>
       </c>
       <c r="B197" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C197" s="10">
         <v>210.88</v>
@@ -4788,7 +4788,7 @@
         <v>161</v>
       </c>
       <c r="B211" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C211" s="3">
         <v>48.13</v>
@@ -4942,7 +4942,7 @@
         <v>172</v>
       </c>
       <c r="B222" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C222" s="3">
         <v>37.299999999999997</v>
@@ -5180,7 +5180,7 @@
         <v>187</v>
       </c>
       <c r="B239" s="3">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C239" s="3">
         <v>67.28</v>
@@ -5208,7 +5208,7 @@
         <v>189</v>
       </c>
       <c r="B241" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C241" s="8">
         <v>75.88</v>
@@ -5348,7 +5348,7 @@
         <v>198</v>
       </c>
       <c r="B251" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C251" s="3">
         <v>32.200000000000003</v>
@@ -5432,7 +5432,7 @@
         <v>204</v>
       </c>
       <c r="B257" s="3">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C257" s="3">
         <v>56</v>
@@ -5866,7 +5866,7 @@
         <v>232</v>
       </c>
       <c r="B288" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C288" s="3">
         <v>44.93</v>
@@ -5894,7 +5894,7 @@
         <v>233</v>
       </c>
       <c r="B290" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C290" s="3">
         <v>6591.8</v>
@@ -5908,7 +5908,7 @@
         <v>234</v>
       </c>
       <c r="B291" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C291" s="3">
         <v>182.42</v>
@@ -5922,7 +5922,7 @@
         <v>235</v>
       </c>
       <c r="B292" s="3">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C292" s="3">
         <v>222.62</v>
@@ -6510,7 +6510,7 @@
         <v>275</v>
       </c>
       <c r="B334" s="3">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C334" s="3">
         <v>54.2</v>
@@ -6902,7 +6902,7 @@
         <v>302</v>
       </c>
       <c r="B362" s="3">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="C362" s="3">
         <v>47.62</v>
@@ -6944,7 +6944,7 @@
         <v>305</v>
       </c>
       <c r="B365" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C365" s="8">
         <v>171.47</v>
@@ -6958,7 +6958,7 @@
         <v>306</v>
       </c>
       <c r="B366" s="3">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C366" s="3">
         <v>212.75</v>
@@ -6986,7 +6986,7 @@
         <v>308</v>
       </c>
       <c r="B368" s="3">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C368" s="3">
         <v>66.180000000000007</v>
@@ -7014,7 +7014,7 @@
         <v>310</v>
       </c>
       <c r="B370" s="3">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C370" s="3">
         <v>259.81</v>
@@ -7028,7 +7028,7 @@
         <v>311</v>
       </c>
       <c r="B371" s="3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C371" s="3">
         <v>259.8</v>
@@ -7042,7 +7042,7 @@
         <v>312</v>
       </c>
       <c r="B372" s="3">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C372" s="3">
         <v>310.2</v>
@@ -7210,7 +7210,7 @@
         <v>322</v>
       </c>
       <c r="B384" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C384" s="3">
         <v>65.599999999999994</v>
@@ -7224,7 +7224,7 @@
         <v>323</v>
       </c>
       <c r="B385" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C385" s="3">
         <v>255.03</v>
@@ -7672,7 +7672,7 @@
         <v>377</v>
       </c>
       <c r="B417" s="3">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="C417" s="3">
         <v>35.75</v>
@@ -7826,7 +7826,7 @@
         <v>437</v>
       </c>
       <c r="B428" s="3">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="C428" s="3">
         <v>6.5</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -2758,7 +2758,7 @@
         <v>31</v>
       </c>
       <c r="B66" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C66" s="3">
         <v>70.47</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -2002,7 +2002,7 @@
         <v>413</v>
       </c>
       <c r="B12" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12" s="3">
         <v>535.12</v>
@@ -2240,7 +2240,7 @@
         <v>405</v>
       </c>
       <c r="B29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" s="3">
         <v>478.19</v>
@@ -2436,7 +2436,7 @@
         <v>13</v>
       </c>
       <c r="B43" s="3">
-        <v>1825</v>
+        <v>1813</v>
       </c>
       <c r="C43" s="3">
         <v>13</v>
@@ -2590,7 +2590,7 @@
         <v>417</v>
       </c>
       <c r="B54" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C54" s="3">
         <v>144.84</v>
@@ -2618,7 +2618,7 @@
         <v>23</v>
       </c>
       <c r="B56" s="3">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C56" s="3">
         <v>255</v>
@@ -2772,7 +2772,7 @@
         <v>32</v>
       </c>
       <c r="B67" s="3">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C67" s="3">
         <v>87.12</v>
@@ -2814,7 +2814,7 @@
         <v>34</v>
       </c>
       <c r="B70" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C70" s="3">
         <v>73.13</v>
@@ -2828,7 +2828,7 @@
         <v>35</v>
       </c>
       <c r="B71" s="3">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C71" s="3">
         <v>89.38</v>
@@ -2856,7 +2856,7 @@
         <v>37</v>
       </c>
       <c r="B73" s="3">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C73" s="3">
         <v>73.13</v>
@@ -2912,7 +2912,7 @@
         <v>443</v>
       </c>
       <c r="B77" s="3">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="C77" s="3">
         <v>19.48</v>
@@ -2926,7 +2926,7 @@
         <v>444</v>
       </c>
       <c r="B78" s="3">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C78" s="3">
         <v>70.72</v>
@@ -3206,7 +3206,7 @@
         <v>56</v>
       </c>
       <c r="B98" s="3">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C98" s="3">
         <v>69.55</v>
@@ -3794,7 +3794,7 @@
         <v>94</v>
       </c>
       <c r="B140" s="3">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C140" s="3">
         <v>66.98</v>
@@ -3934,7 +3934,7 @@
         <v>104</v>
       </c>
       <c r="B150" s="3">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C150" s="8">
         <v>77.63</v>
@@ -3948,7 +3948,7 @@
         <v>105</v>
       </c>
       <c r="B151" s="3">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C151" s="3">
         <v>93.35</v>
@@ -4228,7 +4228,7 @@
         <v>124</v>
       </c>
       <c r="B171" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C171" s="3">
         <v>58.68</v>
@@ -4564,7 +4564,7 @@
         <v>385</v>
       </c>
       <c r="B195" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C195" s="3">
         <v>168.7</v>
@@ -4578,7 +4578,7 @@
         <v>147</v>
       </c>
       <c r="B196" s="3">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C196" s="3">
         <v>44.5</v>
@@ -4704,7 +4704,7 @@
         <v>156</v>
       </c>
       <c r="B205" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C205" s="3">
         <v>199.77</v>
@@ -4718,7 +4718,7 @@
         <v>157</v>
       </c>
       <c r="B206" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C206" s="3">
         <v>2060</v>
@@ -4760,7 +4760,7 @@
         <v>352</v>
       </c>
       <c r="B209" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C209" s="8">
         <v>257.70999999999998</v>
@@ -4774,7 +4774,7 @@
         <v>160</v>
       </c>
       <c r="B210" s="3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C210" s="3">
         <v>33.479999999999997</v>
@@ -4802,7 +4802,7 @@
         <v>162</v>
       </c>
       <c r="B212" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C212" s="3">
         <v>5400</v>
@@ -4858,7 +4858,7 @@
         <v>166</v>
       </c>
       <c r="B216" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C216" s="3">
         <v>265.05</v>
@@ -4942,7 +4942,7 @@
         <v>172</v>
       </c>
       <c r="B222" s="3">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="C222" s="3">
         <v>37.299999999999997</v>
@@ -4956,7 +4956,7 @@
         <v>173</v>
       </c>
       <c r="B223" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C223" s="3">
         <v>126.24</v>
@@ -4970,7 +4970,7 @@
         <v>174</v>
       </c>
       <c r="B224" s="3">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C224" s="3">
         <v>154.62</v>
@@ -5208,7 +5208,7 @@
         <v>189</v>
       </c>
       <c r="B241" s="3">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C241" s="8">
         <v>75.88</v>
@@ -5222,7 +5222,7 @@
         <v>190</v>
       </c>
       <c r="B242" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C242" s="3">
         <v>109.08</v>
@@ -5866,7 +5866,7 @@
         <v>232</v>
       </c>
       <c r="B288" s="3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C288" s="3">
         <v>44.93</v>
@@ -5922,7 +5922,7 @@
         <v>235</v>
       </c>
       <c r="B292" s="3">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C292" s="3">
         <v>222.62</v>
@@ -5936,7 +5936,7 @@
         <v>236</v>
       </c>
       <c r="B293" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C293" s="3">
         <v>2314.8000000000002</v>
@@ -6902,7 +6902,7 @@
         <v>302</v>
       </c>
       <c r="B362" s="3">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C362" s="3">
         <v>47.62</v>
@@ -6916,7 +6916,7 @@
         <v>303</v>
       </c>
       <c r="B363" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C363" s="3">
         <v>7173.59</v>
@@ -6944,7 +6944,7 @@
         <v>305</v>
       </c>
       <c r="B365" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C365" s="8">
         <v>171.47</v>
@@ -6958,7 +6958,7 @@
         <v>306</v>
       </c>
       <c r="B366" s="3">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C366" s="3">
         <v>212.75</v>
@@ -6986,7 +6986,7 @@
         <v>308</v>
       </c>
       <c r="B368" s="3">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C368" s="3">
         <v>66.180000000000007</v>
@@ -7014,7 +7014,7 @@
         <v>310</v>
       </c>
       <c r="B370" s="3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C370" s="3">
         <v>259.81</v>
@@ -7042,7 +7042,7 @@
         <v>312</v>
       </c>
       <c r="B372" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C372" s="3">
         <v>310.2</v>
@@ -7224,7 +7224,7 @@
         <v>323</v>
       </c>
       <c r="B385" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C385" s="3">
         <v>255.03</v>
@@ -7280,7 +7280,7 @@
         <v>327</v>
       </c>
       <c r="B389" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C389" s="3">
         <v>344.28</v>
@@ -7658,7 +7658,7 @@
         <v>376</v>
       </c>
       <c r="B416" s="3">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="C416" s="3">
         <v>24.7</v>
@@ -7672,7 +7672,7 @@
         <v>377</v>
       </c>
       <c r="B417" s="3">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="C417" s="3">
         <v>35.75</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -2226,7 +2226,7 @@
         <v>404</v>
       </c>
       <c r="B28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" s="3">
         <v>491.37</v>
@@ -2436,7 +2436,7 @@
         <v>13</v>
       </c>
       <c r="B43" s="3">
-        <v>1813</v>
+        <v>1801</v>
       </c>
       <c r="C43" s="3">
         <v>13</v>
@@ -2772,7 +2772,7 @@
         <v>32</v>
       </c>
       <c r="B67" s="3">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C67" s="3">
         <v>87.12</v>
@@ -2870,7 +2870,7 @@
         <v>38</v>
       </c>
       <c r="B74" s="3">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C74" s="3">
         <v>103.51</v>
@@ -2912,7 +2912,7 @@
         <v>443</v>
       </c>
       <c r="B77" s="3">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="C77" s="3">
         <v>19.48</v>
@@ -2954,7 +2954,7 @@
         <v>446</v>
       </c>
       <c r="B80" s="3">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C80" s="3">
         <v>22.21</v>
@@ -3248,7 +3248,7 @@
         <v>59</v>
       </c>
       <c r="B101" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C101" s="3">
         <v>40.54</v>
@@ -3570,7 +3570,7 @@
         <v>80</v>
       </c>
       <c r="B124" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C124" s="3">
         <v>52.17</v>
@@ -4676,7 +4676,7 @@
         <v>154</v>
       </c>
       <c r="B203" s="3">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C203" s="3">
         <v>44.51</v>
@@ -4690,7 +4690,7 @@
         <v>155</v>
       </c>
       <c r="B204" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C204" s="3">
         <v>145.94</v>
@@ -4704,7 +4704,7 @@
         <v>156</v>
       </c>
       <c r="B205" s="3">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C205" s="3">
         <v>199.77</v>
@@ -4830,7 +4830,7 @@
         <v>164</v>
       </c>
       <c r="B214" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C214" s="3">
         <v>216.3</v>
@@ -4942,7 +4942,7 @@
         <v>172</v>
       </c>
       <c r="B222" s="3">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C222" s="3">
         <v>37.299999999999997</v>
@@ -5180,7 +5180,7 @@
         <v>187</v>
       </c>
       <c r="B239" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C239" s="3">
         <v>67.28</v>
@@ -5432,7 +5432,7 @@
         <v>204</v>
       </c>
       <c r="B257" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C257" s="3">
         <v>56</v>
@@ -5670,7 +5670,7 @@
         <v>219</v>
       </c>
       <c r="B274" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C274" s="3">
         <v>83.84</v>
@@ -5866,7 +5866,7 @@
         <v>232</v>
       </c>
       <c r="B288" s="3">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C288" s="3">
         <v>44.93</v>
@@ -5908,7 +5908,7 @@
         <v>234</v>
       </c>
       <c r="B291" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C291" s="3">
         <v>182.42</v>
@@ -5922,7 +5922,7 @@
         <v>235</v>
       </c>
       <c r="B292" s="3">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C292" s="3">
         <v>222.62</v>
@@ -6216,7 +6216,7 @@
         <v>254</v>
       </c>
       <c r="B313" s="3">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C313" s="3">
         <v>79.349999999999994</v>
@@ -6510,7 +6510,7 @@
         <v>275</v>
       </c>
       <c r="B334" s="3">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C334" s="3">
         <v>54.2</v>
@@ -6902,7 +6902,7 @@
         <v>302</v>
       </c>
       <c r="B362" s="3">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="C362" s="3">
         <v>47.62</v>
@@ -6958,7 +6958,7 @@
         <v>306</v>
       </c>
       <c r="B366" s="3">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C366" s="3">
         <v>212.75</v>
@@ -6986,7 +6986,7 @@
         <v>308</v>
       </c>
       <c r="B368" s="3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C368" s="3">
         <v>66.180000000000007</v>
@@ -7028,7 +7028,7 @@
         <v>311</v>
       </c>
       <c r="B371" s="3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C371" s="3">
         <v>259.8</v>
@@ -7350,7 +7350,7 @@
         <v>331</v>
       </c>
       <c r="B394" s="3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C394" s="3">
         <v>24.95</v>
@@ -7644,7 +7644,7 @@
         <v>375</v>
       </c>
       <c r="B415" s="3">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C415" s="3">
         <v>97.5</v>
@@ -7658,7 +7658,7 @@
         <v>376</v>
       </c>
       <c r="B416" s="3">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C416" s="3">
         <v>24.7</v>
@@ -7672,7 +7672,7 @@
         <v>377</v>
       </c>
       <c r="B417" s="3">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C417" s="3">
         <v>35.75</v>
@@ -7742,7 +7742,7 @@
         <v>415</v>
       </c>
       <c r="B422" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C422" s="3">
         <v>6.37</v>
@@ -7812,7 +7812,7 @@
         <v>436</v>
       </c>
       <c r="B427" s="3">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C427" s="3">
         <v>6.5</v>
@@ -7826,7 +7826,7 @@
         <v>437</v>
       </c>
       <c r="B428" s="3">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C428" s="3">
         <v>6.5</v>
@@ -7980,7 +7980,7 @@
         <v>456</v>
       </c>
       <c r="B439" s="3">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C439" s="3">
         <v>45</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="466">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -1391,6 +1391,27 @@
   </si>
   <si>
     <t>RAV SOL PARBRIZ IARNA 1L</t>
+  </si>
+  <si>
+    <t>FUCHS TITAN ATF 4134 1L M9 G SERIE</t>
+  </si>
+  <si>
+    <t>FUCHS TITAN ATF 6006 1L ulei 6 HP</t>
+  </si>
+  <si>
+    <t>FUCHS TITAN ATF 6008 1L ulei 8HP</t>
+  </si>
+  <si>
+    <t>FUCHS TITAN ATF 6400 1L ulei T-WS</t>
+  </si>
+  <si>
+    <t>FUCHS TITAN ATF 7134 FE 1L ulei M9-FE</t>
+  </si>
+  <si>
+    <t>FUCHS TITAN FFL-2 60L ulei DCT-HV</t>
+  </si>
+  <si>
+    <t>FUCHS TITAN FFL-52529 20L ulei DCT-HV</t>
   </si>
 </sst>
 </file>
@@ -1835,7 +1856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D439"/>
+  <dimension ref="A1:D446"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="49.85546875" customWidth="1"/>
@@ -7989,6 +8010,104 @@
         <v>455</v>
       </c>
     </row>
+    <row r="440" spans="1:4">
+      <c r="A440" t="s">
+        <v>459</v>
+      </c>
+      <c r="B440" s="3">
+        <v>10</v>
+      </c>
+      <c r="C440" s="3">
+        <v>70.25</v>
+      </c>
+      <c r="D440" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="441" spans="1:4">
+      <c r="A441" t="s">
+        <v>460</v>
+      </c>
+      <c r="B441" s="3">
+        <v>36</v>
+      </c>
+      <c r="C441" s="3">
+        <v>58.9</v>
+      </c>
+      <c r="D441" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4">
+      <c r="A442" t="s">
+        <v>461</v>
+      </c>
+      <c r="B442" s="3">
+        <v>60</v>
+      </c>
+      <c r="C442" s="3">
+        <v>89.21</v>
+      </c>
+      <c r="D442" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4">
+      <c r="A443" t="s">
+        <v>462</v>
+      </c>
+      <c r="B443" s="3">
+        <v>60</v>
+      </c>
+      <c r="C443" s="3">
+        <v>59.18</v>
+      </c>
+      <c r="D443" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4">
+      <c r="A444" t="s">
+        <v>463</v>
+      </c>
+      <c r="B444" s="3">
+        <v>36</v>
+      </c>
+      <c r="C444" s="3">
+        <v>60.62</v>
+      </c>
+      <c r="D444" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4">
+      <c r="A445" t="s">
+        <v>464</v>
+      </c>
+      <c r="B445" s="3">
+        <v>3</v>
+      </c>
+      <c r="C445" s="3">
+        <v>3431.7</v>
+      </c>
+      <c r="D445" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4">
+      <c r="A446" t="s">
+        <v>465</v>
+      </c>
+      <c r="B446" s="3">
+        <v>3</v>
+      </c>
+      <c r="C446" s="3">
+        <v>1260.2</v>
+      </c>
+      <c r="D446" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -1411,7 +1411,7 @@
     <t>FUCHS TITAN FFL-2 60L ulei DCT-HV</t>
   </si>
   <si>
-    <t>FUCHS TITAN FFL-52529 20L ulei DCT-HV</t>
+    <t>FUCHS TITAN FFL-52529 20L ulei DCT-LV</t>
   </si>
 </sst>
 </file>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="467">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -1412,6 +1412,9 @@
   </si>
   <si>
     <t>FUCHS TITAN FFL-52529 20L ulei DCT-LV</t>
+  </si>
+  <si>
+    <t>FUCHS SINTOFLUID FE 75W 1L ulei MTF-3</t>
   </si>
 </sst>
 </file>
@@ -1856,7 +1859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D446"/>
+  <dimension ref="A1:D447"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="49.85546875" customWidth="1"/>
@@ -8108,6 +8111,20 @@
         <v>367</v>
       </c>
     </row>
+    <row r="447" spans="1:4">
+      <c r="A447" t="s">
+        <v>466</v>
+      </c>
+      <c r="B447" s="3">
+        <v>60</v>
+      </c>
+      <c r="C447" s="3">
+        <v>47.2</v>
+      </c>
+      <c r="D447" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -1984,7 +1984,7 @@
         <v>394</v>
       </c>
       <c r="B9" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="3">
         <v>309.52</v>
@@ -2460,7 +2460,7 @@
         <v>13</v>
       </c>
       <c r="B43" s="3">
-        <v>1801</v>
+        <v>1789</v>
       </c>
       <c r="C43" s="3">
         <v>13</v>
@@ -2796,7 +2796,7 @@
         <v>32</v>
       </c>
       <c r="B67" s="3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C67" s="3">
         <v>87.12</v>
@@ -2838,7 +2838,7 @@
         <v>34</v>
       </c>
       <c r="B70" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C70" s="3">
         <v>73.13</v>
@@ -2852,7 +2852,7 @@
         <v>35</v>
       </c>
       <c r="B71" s="3">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C71" s="3">
         <v>89.38</v>
@@ -2936,7 +2936,7 @@
         <v>443</v>
       </c>
       <c r="B77" s="3">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C77" s="3">
         <v>19.48</v>
@@ -2950,7 +2950,7 @@
         <v>444</v>
       </c>
       <c r="B78" s="3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C78" s="3">
         <v>70.72</v>
@@ -3818,7 +3818,7 @@
         <v>94</v>
       </c>
       <c r="B140" s="3">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C140" s="3">
         <v>66.98</v>
@@ -4126,7 +4126,7 @@
         <v>115</v>
       </c>
       <c r="B162" s="3">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C162" s="3">
         <v>32.200000000000003</v>
@@ -4252,7 +4252,7 @@
         <v>124</v>
       </c>
       <c r="B171" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C171" s="3">
         <v>58.68</v>
@@ -4546,7 +4546,7 @@
         <v>144</v>
       </c>
       <c r="B192" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C192" s="3">
         <v>248.77</v>
@@ -4784,7 +4784,7 @@
         <v>352</v>
       </c>
       <c r="B209" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C209" s="8">
         <v>257.70999999999998</v>
@@ -4798,7 +4798,7 @@
         <v>160</v>
       </c>
       <c r="B210" s="3">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C210" s="3">
         <v>33.479999999999997</v>
@@ -4826,7 +4826,7 @@
         <v>162</v>
       </c>
       <c r="B212" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C212" s="3">
         <v>5400</v>
@@ -4854,7 +4854,7 @@
         <v>164</v>
       </c>
       <c r="B214" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C214" s="3">
         <v>216.3</v>
@@ -4896,7 +4896,7 @@
         <v>167</v>
       </c>
       <c r="B217" s="3">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C217" s="3">
         <v>36.799999999999997</v>
@@ -5456,7 +5456,7 @@
         <v>204</v>
       </c>
       <c r="B257" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C257" s="3">
         <v>56</v>
@@ -5890,7 +5890,7 @@
         <v>232</v>
       </c>
       <c r="B288" s="3">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C288" s="3">
         <v>44.93</v>
@@ -5932,7 +5932,7 @@
         <v>234</v>
       </c>
       <c r="B291" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C291" s="3">
         <v>182.42</v>
@@ -5946,7 +5946,7 @@
         <v>235</v>
       </c>
       <c r="B292" s="3">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C292" s="3">
         <v>222.62</v>
@@ -6982,7 +6982,7 @@
         <v>306</v>
       </c>
       <c r="B366" s="3">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C366" s="3">
         <v>212.75</v>
@@ -7010,7 +7010,7 @@
         <v>308</v>
       </c>
       <c r="B368" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C368" s="3">
         <v>66.180000000000007</v>
@@ -7234,7 +7234,7 @@
         <v>322</v>
       </c>
       <c r="B384" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C384" s="3">
         <v>65.599999999999994</v>
@@ -7262,7 +7262,7 @@
         <v>324</v>
       </c>
       <c r="B386" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C386" s="3">
         <v>220.8</v>
@@ -7668,7 +7668,7 @@
         <v>375</v>
       </c>
       <c r="B415" s="3">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C415" s="3">
         <v>97.5</v>
@@ -7794,7 +7794,7 @@
         <v>416</v>
       </c>
       <c r="B424" s="3">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C424" s="3">
         <v>11.59</v>
@@ -7836,7 +7836,7 @@
         <v>436</v>
       </c>
       <c r="B427" s="3">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C427" s="3">
         <v>6.5</v>
@@ -7850,7 +7850,7 @@
         <v>437</v>
       </c>
       <c r="B428" s="3">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C428" s="3">
         <v>6.5</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -4980,7 +4980,7 @@
         <v>173</v>
       </c>
       <c r="B223" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C223" s="3">
         <v>126.24</v>
@@ -6982,7 +6982,7 @@
         <v>306</v>
       </c>
       <c r="B366" s="3">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C366" s="3">
         <v>212.75</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="470">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -1415,6 +1415,15 @@
   </si>
   <si>
     <t>FUCHS SINTOFLUID FE 75W 1L ulei MTF-3</t>
+  </si>
+  <si>
+    <t>CEMSA sol curatare discuri 60L</t>
+  </si>
+  <si>
+    <t>CEMSA sol curatare discuri 30L</t>
+  </si>
+  <si>
+    <t>CEMSA robinet 3/4</t>
   </si>
 </sst>
 </file>
@@ -1859,7 +1868,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D447"/>
+  <dimension ref="A1:D450"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="49.85546875" customWidth="1"/>
@@ -2278,7 +2287,7 @@
         <v>422</v>
       </c>
       <c r="B30" s="3">
-        <v>461</v>
+        <v>437</v>
       </c>
       <c r="C30" s="3">
         <v>45.19</v>
@@ -2443,27 +2452,27 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>12</v>
+        <v>467</v>
       </c>
       <c r="B42" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C42" s="3">
-        <v>36.4</v>
+        <v>907.2</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>13</v>
+        <v>468</v>
       </c>
       <c r="B43" s="3">
-        <v>1789</v>
+        <v>6</v>
       </c>
       <c r="C43" s="3">
-        <v>13</v>
+        <v>465.75</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>366</v>
@@ -2471,55 +2480,55 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>14</v>
+        <v>469</v>
       </c>
       <c r="B44" s="3">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="C44" s="3">
-        <v>23.37</v>
+        <v>10.8</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B45" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C45" s="3">
-        <v>361.92</v>
+        <v>36.4</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>439</v>
+        <v>13</v>
       </c>
       <c r="B46" s="3">
-        <v>2</v>
+        <v>1789</v>
       </c>
       <c r="C46" s="3">
-        <v>1844.7</v>
+        <v>13</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B47" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C47" s="3">
-        <v>21</v>
+        <v>23.37</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>367</v>
@@ -2527,13 +2536,13 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B48" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C48" s="3">
-        <v>357.53</v>
+        <v>361.92</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>367</v>
@@ -2541,27 +2550,27 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>18</v>
+        <v>439</v>
       </c>
       <c r="B49" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C49" s="3">
-        <v>19.3</v>
+        <v>1844.7</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B50" s="3">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C50" s="3">
-        <v>337.5</v>
+        <v>21</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>367</v>
@@ -2569,13 +2578,13 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B51" s="3">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C51" s="3">
-        <v>33.64</v>
+        <v>357.53</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>367</v>
@@ -2583,69 +2592,69 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B52" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C52" s="3">
-        <v>298.12</v>
+        <v>19.3</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>390</v>
+        <v>367</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B53" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C53" s="3">
-        <v>1982.77</v>
+        <v>337.5</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>417</v>
+        <v>20</v>
       </c>
       <c r="B54" s="3">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C54" s="3">
-        <v>144.84</v>
+        <v>33.64</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B55" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C55" s="3">
-        <v>280.12</v>
+        <v>298.12</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>368</v>
+        <v>390</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B56" s="3">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C56" s="3">
-        <v>255</v>
+        <v>1982.77</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>368</v>
@@ -2653,167 +2662,167 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>24</v>
+        <v>417</v>
       </c>
       <c r="B57" s="3">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="C57" s="3">
-        <v>24.51</v>
+        <v>144.84</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>389</v>
+        <v>368</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>440</v>
+        <v>23</v>
       </c>
       <c r="B58" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C58" s="3">
-        <v>135.29</v>
+        <v>280.12</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>389</v>
+        <v>368</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B59" s="3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C59" s="3">
-        <v>26.21</v>
+        <v>255</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>388</v>
+        <v>368</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B60" s="3">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="C60" s="3">
-        <v>101.08</v>
+        <v>24.51</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B61" s="3">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C61" s="3">
-        <v>1557.7</v>
+        <v>135.29</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B62" s="3">
         <v>60</v>
       </c>
       <c r="C62" s="3">
-        <v>29.13</v>
+        <v>26.21</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B63" s="3">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="C63" s="3">
-        <v>102.31</v>
+        <v>101.08</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>29</v>
+        <v>441</v>
       </c>
       <c r="B64" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C64" s="3">
-        <v>168.07</v>
+        <v>1557.7</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B65" s="3">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="C65" s="3">
-        <v>16.600000000000001</v>
+        <v>29.13</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B66" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C66" s="3">
-        <v>70.47</v>
+        <v>102.31</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B67" s="3">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="C67" s="3">
-        <v>87.12</v>
+        <v>168.07</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>418</v>
+        <v>30</v>
       </c>
       <c r="B68" s="3">
         <v>0</v>
       </c>
       <c r="C68" s="3">
-        <v>1041.71</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>386</v>
@@ -2821,13 +2830,13 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B69" s="3">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="C69" s="3">
-        <v>18.96</v>
+        <v>70.47</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>386</v>
@@ -2835,13 +2844,13 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B70" s="3">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="C70" s="3">
-        <v>73.13</v>
+        <v>87.12</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>386</v>
@@ -2849,13 +2858,13 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>35</v>
+        <v>418</v>
       </c>
       <c r="B71" s="3">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="C71" s="3">
-        <v>89.38</v>
+        <v>1041.71</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>386</v>
@@ -2863,10 +2872,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B72" s="3">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="C72" s="3">
         <v>18.96</v>
@@ -2877,10 +2886,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B73" s="3">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="C73" s="3">
         <v>73.13</v>
@@ -2891,13 +2900,13 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B74" s="3">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="C74" s="3">
-        <v>103.51</v>
+        <v>89.38</v>
       </c>
       <c r="D74" s="4" t="s">
         <v>386</v>
@@ -2905,13 +2914,13 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>442</v>
+        <v>36</v>
       </c>
       <c r="B75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C75" s="3">
-        <v>1180.5999999999999</v>
+        <v>18.96</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>386</v>
@@ -2919,13 +2928,13 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B76" s="3">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="C76" s="3">
-        <v>3173.52</v>
+        <v>73.13</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>386</v>
@@ -2933,55 +2942,55 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>443</v>
+        <v>38</v>
       </c>
       <c r="B77" s="3">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="C77" s="3">
-        <v>19.48</v>
+        <v>103.51</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>447</v>
+        <v>386</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B78" s="3">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="C78" s="3">
-        <v>70.72</v>
+        <v>1180.5999999999999</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>447</v>
+        <v>386</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>445</v>
+        <v>39</v>
       </c>
       <c r="B79" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C79" s="3">
-        <v>1045.3</v>
+        <v>3173.52</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>447</v>
+        <v>386</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B80" s="3">
-        <v>58</v>
+        <v>738</v>
       </c>
       <c r="C80" s="3">
-        <v>22.21</v>
+        <v>19.48</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>447</v>
@@ -2989,55 +2998,55 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>40</v>
+        <v>444</v>
       </c>
       <c r="B81" s="3">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C81" s="3">
-        <v>25.4</v>
+        <v>70.72</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>366</v>
+        <v>447</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>41</v>
+        <v>445</v>
       </c>
       <c r="B82" s="3">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C82" s="3">
-        <v>40.92</v>
+        <v>1045.3</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>366</v>
+        <v>447</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>42</v>
+        <v>446</v>
       </c>
       <c r="B83" s="3">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="C83" s="3">
-        <v>25.4</v>
+        <v>22.21</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>366</v>
+        <v>447</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B84" s="3">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C84" s="3">
-        <v>28.07</v>
+        <v>25.4</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>366</v>
@@ -3045,13 +3054,13 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>384</v>
+        <v>41</v>
       </c>
       <c r="B85" s="3">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C85" s="3">
-        <v>23.33</v>
+        <v>40.92</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>366</v>
@@ -3059,69 +3068,69 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B86" s="3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C86" s="3">
-        <v>34.630000000000003</v>
+        <v>25.4</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B87" s="3">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="C87" s="3">
-        <v>18.37</v>
+        <v>28.07</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>46</v>
+        <v>384</v>
       </c>
       <c r="B88" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C88" s="3">
-        <v>82.88</v>
+        <v>23.33</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B89" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C89" s="3">
-        <v>161.01</v>
+        <v>34.630000000000003</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B90" s="3">
-        <v>4</v>
+        <v>79</v>
       </c>
       <c r="C90" s="3">
-        <v>50.23</v>
+        <v>18.37</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>369</v>
@@ -3129,83 +3138,83 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B91" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C91" s="3">
-        <v>65.83</v>
+        <v>82.88</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B92" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C92" s="3">
-        <v>46.76</v>
+        <v>161.01</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B93" s="3">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C93" s="3">
-        <v>62.11</v>
+        <v>50.23</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B94" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C94" s="3">
-        <v>47.61</v>
+        <v>65.83</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B95" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C95" s="3">
-        <v>63.76</v>
+        <v>46.76</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B96" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C96" s="3">
-        <v>1159.2</v>
+        <v>62.11</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>367</v>
@@ -3213,13 +3222,13 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B97" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C97" s="3">
-        <v>255</v>
+        <v>47.61</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>367</v>
@@ -3227,13 +3236,13 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B98" s="3">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C98" s="3">
-        <v>69.55</v>
+        <v>63.76</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>367</v>
@@ -3241,13 +3250,13 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B99" s="3">
         <v>1</v>
       </c>
       <c r="C99" s="3">
-        <v>1391.04</v>
+        <v>1159.2</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>367</v>
@@ -3255,13 +3264,13 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B100" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C100" s="3">
-        <v>87.1</v>
+        <v>255</v>
       </c>
       <c r="D100" s="4" t="s">
         <v>367</v>
@@ -3269,13 +3278,13 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B101" s="3">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C101" s="3">
-        <v>40.54</v>
+        <v>69.55</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>367</v>
@@ -3283,13 +3292,13 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B102" s="3">
         <v>1</v>
       </c>
       <c r="C102" s="3">
-        <v>460.01</v>
+        <v>1391.04</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>367</v>
@@ -3297,13 +3306,13 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B103" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C103" s="3">
-        <v>639.4</v>
+        <v>87.1</v>
       </c>
       <c r="D103" s="4" t="s">
         <v>367</v>
@@ -3311,13 +3320,13 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B104" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C104" s="3">
-        <v>103.89</v>
+        <v>40.54</v>
       </c>
       <c r="D104" s="4" t="s">
         <v>367</v>
@@ -3325,13 +3334,13 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B105" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C105" s="3">
-        <v>58.48</v>
+        <v>460.01</v>
       </c>
       <c r="D105" s="4" t="s">
         <v>367</v>
@@ -3339,13 +3348,13 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B106" s="3">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="C106" s="3">
-        <v>56.93</v>
+        <v>639.4</v>
       </c>
       <c r="D106" s="4" t="s">
         <v>367</v>
@@ -3353,13 +3362,13 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B107" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C107" s="3">
-        <v>63.76</v>
+        <v>103.89</v>
       </c>
       <c r="D107" s="4" t="s">
         <v>367</v>
@@ -3367,13 +3376,13 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B108" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C108" s="3">
-        <v>61.92</v>
+        <v>58.48</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>367</v>
@@ -3381,13 +3390,13 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B109" s="3">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C109" s="3">
-        <v>63.76</v>
+        <v>56.93</v>
       </c>
       <c r="D109" s="4" t="s">
         <v>367</v>
@@ -3395,13 +3404,13 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B110" s="3">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C110" s="3">
-        <v>69.56</v>
+        <v>63.76</v>
       </c>
       <c r="D110" s="4" t="s">
         <v>367</v>
@@ -3409,13 +3418,13 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B111" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C111" s="3">
-        <v>59.68</v>
+        <v>61.92</v>
       </c>
       <c r="D111" s="4" t="s">
         <v>367</v>
@@ -3423,13 +3432,13 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B112" s="3">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C112" s="3">
-        <v>56.93</v>
+        <v>63.76</v>
       </c>
       <c r="D112" s="4" t="s">
         <v>367</v>
@@ -3437,13 +3446,13 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B113" s="3">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C113" s="3">
-        <v>80.73</v>
+        <v>69.56</v>
       </c>
       <c r="D113" s="4" t="s">
         <v>367</v>
@@ -3451,13 +3460,13 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B114" s="3">
         <v>4</v>
       </c>
       <c r="C114" s="3">
-        <v>98.95</v>
+        <v>59.68</v>
       </c>
       <c r="D114" s="4" t="s">
         <v>367</v>
@@ -3465,13 +3474,13 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B115" s="3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="C115" s="3">
-        <v>93.25</v>
+        <v>56.93</v>
       </c>
       <c r="D115" s="4" t="s">
         <v>367</v>
@@ -3479,13 +3488,13 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B116" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C116" s="3">
-        <v>63.76</v>
+        <v>80.73</v>
       </c>
       <c r="D116" s="4" t="s">
         <v>367</v>
@@ -3493,13 +3502,13 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B117" s="3">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C117" s="3">
-        <v>63.76</v>
+        <v>98.95</v>
       </c>
       <c r="D117" s="4" t="s">
         <v>367</v>
@@ -3507,13 +3516,13 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B118" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C118" s="3">
-        <v>81.150000000000006</v>
+        <v>93.25</v>
       </c>
       <c r="D118" s="4" t="s">
         <v>367</v>
@@ -3521,10 +3530,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B119" s="3">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C119" s="3">
         <v>63.76</v>
@@ -3535,13 +3544,13 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B120" s="3">
         <v>18</v>
       </c>
       <c r="C120" s="3">
-        <v>69.87</v>
+        <v>63.76</v>
       </c>
       <c r="D120" s="4" t="s">
         <v>367</v>
@@ -3549,13 +3558,13 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B121" s="3">
         <v>14</v>
       </c>
       <c r="C121" s="3">
-        <v>63.76</v>
+        <v>81.150000000000006</v>
       </c>
       <c r="D121" s="4" t="s">
         <v>367</v>
@@ -3563,13 +3572,13 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B122" s="3">
-        <v>6</v>
-      </c>
-      <c r="C122" s="8">
-        <v>79.91</v>
+        <v>27</v>
+      </c>
+      <c r="C122" s="3">
+        <v>63.76</v>
       </c>
       <c r="D122" s="4" t="s">
         <v>367</v>
@@ -3577,13 +3586,13 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B123" s="3">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C123" s="3">
-        <v>69.56</v>
+        <v>69.87</v>
       </c>
       <c r="D123" s="4" t="s">
         <v>367</v>
@@ -3591,13 +3600,13 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B124" s="3">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="C124" s="3">
-        <v>52.17</v>
+        <v>63.76</v>
       </c>
       <c r="D124" s="4" t="s">
         <v>367</v>
@@ -3605,13 +3614,13 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B125" s="3">
-        <v>8</v>
-      </c>
-      <c r="C125" s="3">
-        <v>208.66</v>
+        <v>6</v>
+      </c>
+      <c r="C125" s="8">
+        <v>79.91</v>
       </c>
       <c r="D125" s="4" t="s">
         <v>367</v>
@@ -3619,13 +3628,13 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B126" s="3">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C126" s="3">
-        <v>88.87</v>
+        <v>69.56</v>
       </c>
       <c r="D126" s="4" t="s">
         <v>367</v>
@@ -3633,13 +3642,13 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B127" s="3">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="C127" s="3">
-        <v>67.27</v>
+        <v>52.17</v>
       </c>
       <c r="D127" s="4" t="s">
         <v>367</v>
@@ -3647,13 +3656,13 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B128" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C128" s="3">
-        <v>69.55</v>
+        <v>208.66</v>
       </c>
       <c r="D128" s="4" t="s">
         <v>367</v>
@@ -3661,13 +3670,13 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B129" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C129" s="3">
-        <v>63.89</v>
+        <v>88.87</v>
       </c>
       <c r="D129" s="4" t="s">
         <v>367</v>
@@ -3675,13 +3684,13 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B130" s="3">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C130" s="3">
-        <v>149.91</v>
+        <v>67.27</v>
       </c>
       <c r="D130" s="4" t="s">
         <v>367</v>
@@ -3689,13 +3698,13 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B131" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C131" s="3">
-        <v>38.57</v>
+        <v>69.55</v>
       </c>
       <c r="D131" s="4" t="s">
         <v>367</v>
@@ -3703,13 +3712,13 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B132" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C132" s="3">
-        <v>207.31</v>
+        <v>63.89</v>
       </c>
       <c r="D132" s="4" t="s">
         <v>367</v>
@@ -3717,55 +3726,55 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B133" s="3">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C133" s="3">
-        <v>58.24</v>
+        <v>149.91</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B134" s="3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C134" s="3">
-        <v>65.23</v>
+        <v>38.57</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B135" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C135" s="3">
-        <v>290.95</v>
+        <v>207.31</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B136" s="3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C136" s="3">
-        <v>325.87</v>
+        <v>58.24</v>
       </c>
       <c r="D136" s="4" t="s">
         <v>364</v>
@@ -3773,69 +3782,69 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B137" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C137" s="3">
-        <v>5165.8</v>
+        <v>65.23</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="138" spans="1:4">
       <c r="A138" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B138" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C138" s="3">
-        <v>511.75</v>
+        <v>290.95</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B139" s="3">
         <v>4</v>
       </c>
       <c r="C139" s="3">
-        <v>572.70000000000005</v>
+        <v>325.87</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B140" s="3">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="C140" s="3">
-        <v>66.98</v>
+        <v>5165.8</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B141" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C141" s="3">
-        <v>367.42</v>
+        <v>511.75</v>
       </c>
       <c r="D141" s="4" t="s">
         <v>367</v>
@@ -3843,97 +3852,97 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B142" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C142" s="3">
-        <v>51.52</v>
+        <v>572.70000000000005</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="143" spans="1:4">
       <c r="A143" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B143" s="3">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="C143" s="3">
-        <v>23.19</v>
+        <v>66.98</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B144" s="3">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C144" s="3">
-        <v>23.19</v>
+        <v>367.42</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B145" s="3">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C145" s="3">
-        <v>69.55</v>
+        <v>51.52</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B146" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C146" s="3">
-        <v>3169.7</v>
+        <v>23.19</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B147" s="3">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C147" s="3">
-        <v>81.14</v>
+        <v>23.19</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B148" s="3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C148" s="3">
-        <v>81.14</v>
+        <v>69.55</v>
       </c>
       <c r="D148" s="4" t="s">
         <v>367</v>
@@ -3941,27 +3950,27 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B149" s="3">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="C149" s="3">
-        <v>66.98</v>
+        <v>3169.7</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B150" s="3">
-        <v>30</v>
-      </c>
-      <c r="C150" s="8">
-        <v>77.63</v>
+        <v>12</v>
+      </c>
+      <c r="C150" s="3">
+        <v>81.14</v>
       </c>
       <c r="D150" s="4" t="s">
         <v>367</v>
@@ -3969,13 +3978,13 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B151" s="3">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C151" s="3">
-        <v>93.35</v>
+        <v>81.14</v>
       </c>
       <c r="D151" s="4" t="s">
         <v>367</v>
@@ -3983,27 +3992,27 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B152" s="3">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="C152" s="3">
-        <v>1217.1600000000001</v>
+        <v>66.98</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B153" s="3">
-        <v>0</v>
-      </c>
-      <c r="C153" s="3">
-        <v>3079</v>
+        <v>30</v>
+      </c>
+      <c r="C153" s="8">
+        <v>77.63</v>
       </c>
       <c r="D153" s="4" t="s">
         <v>367</v>
@@ -4011,122 +4020,122 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B154" s="3">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C154" s="3">
-        <v>43.7</v>
+        <v>93.35</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B155" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C155" s="3">
-        <v>48.95</v>
+        <v>1217.1600000000001</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B156" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C156" s="3">
-        <v>72.33</v>
+        <v>3079</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B157" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C157" s="3">
-        <v>284.19</v>
+        <v>43.7</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="158" spans="1:4">
       <c r="A158" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B158" s="3">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C158" s="3">
-        <v>101.5</v>
+        <v>48.95</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="159" spans="1:4">
       <c r="A159" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B159" s="3">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="C159" s="3">
-        <v>32.200000000000003</v>
+        <v>72.33</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B160" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C160" s="3">
-        <v>32.200000000000003</v>
+        <v>284.19</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
     </row>
     <row r="161" spans="1:4">
       <c r="A161" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B161" s="3">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C161" s="3">
-        <v>37.43</v>
+        <v>101.5</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
     </row>
     <row r="162" spans="1:4">
       <c r="A162" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B162" s="3">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="C162" s="3">
         <v>32.200000000000003</v>
@@ -4137,111 +4146,111 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B163" s="3">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C163" s="3">
-        <v>115.01</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B164" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C164" s="3">
-        <v>38.39</v>
+        <v>37.43</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B165" s="3">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C165" s="3">
-        <v>151.47999999999999</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B166" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C166" s="3">
-        <v>181.68</v>
+        <v>115.01</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B167" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C167" s="3">
-        <v>20.059999999999999</v>
+        <v>38.39</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B168" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C168" s="3">
-        <v>12.88</v>
+        <v>151.47999999999999</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
     </row>
     <row r="169" spans="1:4">
       <c r="A169" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B169" s="3">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C169" s="3">
-        <v>26.73</v>
+        <v>181.68</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B170" s="3">
         <v>12</v>
       </c>
       <c r="C170" s="3">
-        <v>29.95</v>
+        <v>20.059999999999999</v>
       </c>
       <c r="D170" s="4" t="s">
         <v>355</v>
@@ -4249,13 +4258,13 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B171" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C171" s="3">
-        <v>58.68</v>
+        <v>12.88</v>
       </c>
       <c r="D171" s="4" t="s">
         <v>355</v>
@@ -4263,13 +4272,13 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B172" s="3">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C172" s="3">
-        <v>79.98</v>
+        <v>26.73</v>
       </c>
       <c r="D172" s="4" t="s">
         <v>355</v>
@@ -4277,69 +4286,69 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B173" s="3">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C173" s="3">
-        <v>38.770000000000003</v>
+        <v>29.95</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="174" spans="1:4">
       <c r="A174" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B174" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C174" s="3">
-        <v>107.35</v>
+        <v>58.68</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
     </row>
     <row r="175" spans="1:4">
       <c r="A175" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B175" s="3">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="C175" s="3">
-        <v>61.83</v>
+        <v>79.98</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
     </row>
     <row r="176" spans="1:4">
       <c r="A176" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B176" s="3">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C176" s="3">
-        <v>243.16</v>
+        <v>38.770000000000003</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
     </row>
     <row r="177" spans="1:4">
       <c r="A177" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B177" s="3">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="C177" s="3">
-        <v>63.78</v>
+        <v>107.35</v>
       </c>
       <c r="D177" s="4" t="s">
         <v>367</v>
@@ -4347,13 +4356,13 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B178" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C178" s="3">
-        <v>75.989999999999995</v>
+        <v>61.83</v>
       </c>
       <c r="D178" s="4" t="s">
         <v>364</v>
@@ -4361,13 +4370,13 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B179" s="3">
         <v>1</v>
       </c>
       <c r="C179" s="3">
-        <v>297.64999999999998</v>
+        <v>243.16</v>
       </c>
       <c r="D179" s="4" t="s">
         <v>364</v>
@@ -4375,24 +4384,24 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B180" s="3">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C180" s="3">
-        <v>77.28</v>
+        <v>63.78</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="181" spans="1:4">
       <c r="A181" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B181" s="3">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C181" s="3">
         <v>75.989999999999995</v>
@@ -4403,13 +4412,13 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B182" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C182" s="3">
-        <v>342.24</v>
+        <v>297.64999999999998</v>
       </c>
       <c r="D182" s="4" t="s">
         <v>364</v>
@@ -4417,55 +4426,55 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B183" s="3">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C183" s="3">
-        <v>633.75</v>
+        <v>77.28</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="184" spans="1:4">
       <c r="A184" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B184" s="3">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="C184" s="3">
-        <v>50.51</v>
+        <v>75.989999999999995</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="185" spans="1:4">
       <c r="A185" t="s">
-        <v>430</v>
+        <v>135</v>
       </c>
       <c r="B185" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C185" s="3">
-        <v>581.9</v>
+        <v>342.24</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="186" spans="1:4">
       <c r="A186" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B186" s="3">
         <v>2</v>
       </c>
       <c r="C186" s="3">
-        <v>579.13</v>
+        <v>633.75</v>
       </c>
       <c r="D186" s="4" t="s">
         <v>367</v>
@@ -4473,83 +4482,83 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B187" s="3">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="C187" s="3">
-        <v>122.36</v>
+        <v>50.51</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="188" spans="1:4">
       <c r="A188" t="s">
-        <v>140</v>
+        <v>430</v>
       </c>
       <c r="B188" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C188" s="3">
-        <v>35.81</v>
+        <v>581.9</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
     </row>
     <row r="189" spans="1:4">
       <c r="A189" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B189" s="3">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C189" s="3">
-        <v>59.25</v>
+        <v>579.13</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="190" spans="1:4">
       <c r="A190" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B190" s="3">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C190" s="3">
-        <v>260</v>
+        <v>122.36</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="191" spans="1:4">
       <c r="A191" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B191" s="3">
-        <v>22</v>
-      </c>
-      <c r="C191" s="7">
-        <v>59.62</v>
+        <v>25</v>
+      </c>
+      <c r="C191" s="3">
+        <v>35.81</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="192" spans="1:4">
       <c r="A192" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B192" s="3">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C192" s="3">
-        <v>248.77</v>
+        <v>59.25</v>
       </c>
       <c r="D192" s="4" t="s">
         <v>364</v>
@@ -4557,13 +4566,13 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B193" s="3">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C193" s="3">
-        <v>74.7</v>
+        <v>260</v>
       </c>
       <c r="D193" s="4" t="s">
         <v>364</v>
@@ -4571,13 +4580,13 @@
     </row>
     <row r="194" spans="1:4">
       <c r="A194" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B194" s="3">
-        <v>15</v>
-      </c>
-      <c r="C194" s="3">
-        <v>296.3</v>
+        <v>22</v>
+      </c>
+      <c r="C194" s="7">
+        <v>59.62</v>
       </c>
       <c r="D194" s="4" t="s">
         <v>364</v>
@@ -4585,13 +4594,13 @@
     </row>
     <row r="195" spans="1:4">
       <c r="A195" t="s">
-        <v>385</v>
+        <v>144</v>
       </c>
       <c r="B195" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C195" s="3">
-        <v>168.7</v>
+        <v>248.77</v>
       </c>
       <c r="D195" s="4" t="s">
         <v>364</v>
@@ -4599,13 +4608,13 @@
     </row>
     <row r="196" spans="1:4">
       <c r="A196" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B196" s="3">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C196" s="3">
-        <v>44.5</v>
+        <v>74.7</v>
       </c>
       <c r="D196" s="4" t="s">
         <v>364</v>
@@ -4613,13 +4622,13 @@
     </row>
     <row r="197" spans="1:4">
       <c r="A197" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B197" s="3">
-        <v>10</v>
-      </c>
-      <c r="C197" s="10">
-        <v>210.88</v>
+        <v>15</v>
+      </c>
+      <c r="C197" s="3">
+        <v>296.3</v>
       </c>
       <c r="D197" s="4" t="s">
         <v>364</v>
@@ -4627,13 +4636,13 @@
     </row>
     <row r="198" spans="1:4">
       <c r="A198" t="s">
-        <v>149</v>
+        <v>385</v>
       </c>
       <c r="B198" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C198" s="3">
-        <v>2189.02</v>
+        <v>168.7</v>
       </c>
       <c r="D198" s="4" t="s">
         <v>364</v>
@@ -4641,13 +4650,13 @@
     </row>
     <row r="199" spans="1:4">
       <c r="A199" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B199" s="3">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C199" s="3">
-        <v>453.22</v>
+        <v>44.5</v>
       </c>
       <c r="D199" s="4" t="s">
         <v>364</v>
@@ -4655,13 +4664,13 @@
     </row>
     <row r="200" spans="1:4">
       <c r="A200" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B200" s="3">
-        <v>20</v>
-      </c>
-      <c r="C200" s="3">
-        <v>48.64</v>
+        <v>10</v>
+      </c>
+      <c r="C200" s="10">
+        <v>210.88</v>
       </c>
       <c r="D200" s="4" t="s">
         <v>364</v>
@@ -4669,13 +4678,13 @@
     </row>
     <row r="201" spans="1:4">
       <c r="A201" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B201" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C201" s="3">
-        <v>126.63</v>
+        <v>2189.02</v>
       </c>
       <c r="D201" s="4" t="s">
         <v>364</v>
@@ -4683,27 +4692,27 @@
     </row>
     <row r="202" spans="1:4">
       <c r="A202" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B202" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C202" s="3">
-        <v>69.56</v>
+        <v>453.22</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="203" spans="1:4">
       <c r="A203" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B203" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C203" s="3">
-        <v>44.51</v>
+        <v>48.64</v>
       </c>
       <c r="D203" s="4" t="s">
         <v>364</v>
@@ -4711,13 +4720,13 @@
     </row>
     <row r="204" spans="1:4">
       <c r="A204" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B204" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C204" s="3">
-        <v>145.94</v>
+        <v>126.63</v>
       </c>
       <c r="D204" s="4" t="s">
         <v>364</v>
@@ -4725,27 +4734,27 @@
     </row>
     <row r="205" spans="1:4">
       <c r="A205" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B205" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C205" s="3">
-        <v>199.77</v>
+        <v>69.56</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="206" spans="1:4">
       <c r="A206" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B206" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C206" s="3">
-        <v>2060</v>
+        <v>44.51</v>
       </c>
       <c r="D206" s="4" t="s">
         <v>364</v>
@@ -4753,13 +4762,13 @@
     </row>
     <row r="207" spans="1:4">
       <c r="A207" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B207" s="3">
-        <v>14</v>
-      </c>
-      <c r="C207" s="8">
-        <v>58.32</v>
+        <v>3</v>
+      </c>
+      <c r="C207" s="3">
+        <v>145.94</v>
       </c>
       <c r="D207" s="4" t="s">
         <v>364</v>
@@ -4767,13 +4776,13 @@
     </row>
     <row r="208" spans="1:4">
       <c r="A208" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B208" s="3">
         <v>2</v>
       </c>
       <c r="C208" s="3">
-        <v>183.41</v>
+        <v>199.77</v>
       </c>
       <c r="D208" s="4" t="s">
         <v>364</v>
@@ -4781,13 +4790,13 @@
     </row>
     <row r="209" spans="1:4">
       <c r="A209" t="s">
-        <v>352</v>
+        <v>157</v>
       </c>
       <c r="B209" s="3">
-        <v>7</v>
-      </c>
-      <c r="C209" s="8">
-        <v>257.70999999999998</v>
+        <v>0</v>
+      </c>
+      <c r="C209" s="3">
+        <v>2060</v>
       </c>
       <c r="D209" s="4" t="s">
         <v>364</v>
@@ -4795,27 +4804,27 @@
     </row>
     <row r="210" spans="1:4">
       <c r="A210" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B210" s="3">
-        <v>37</v>
-      </c>
-      <c r="C210" s="3">
-        <v>33.479999999999997</v>
+        <v>12</v>
+      </c>
+      <c r="C210" s="8">
+        <v>58.32</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="211" spans="1:4">
       <c r="A211" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B211" s="3">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C211" s="3">
-        <v>48.13</v>
+        <v>183.41</v>
       </c>
       <c r="D211" s="4" t="s">
         <v>364</v>
@@ -4823,13 +4832,13 @@
     </row>
     <row r="212" spans="1:4">
       <c r="A212" t="s">
-        <v>162</v>
+        <v>352</v>
       </c>
       <c r="B212" s="3">
-        <v>3</v>
-      </c>
-      <c r="C212" s="3">
-        <v>5400</v>
+        <v>7</v>
+      </c>
+      <c r="C212" s="8">
+        <v>257.70999999999998</v>
       </c>
       <c r="D212" s="4" t="s">
         <v>364</v>
@@ -4837,27 +4846,27 @@
     </row>
     <row r="213" spans="1:4">
       <c r="A213" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B213" s="3">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="C213" s="3">
-        <v>170.78</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="214" spans="1:4">
       <c r="A214" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B214" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C214" s="3">
-        <v>216.3</v>
+        <v>48.13</v>
       </c>
       <c r="D214" s="4" t="s">
         <v>364</v>
@@ -4865,13 +4874,13 @@
     </row>
     <row r="215" spans="1:4">
       <c r="A215" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B215" s="3">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C215" s="3">
-        <v>59.7</v>
+        <v>5400</v>
       </c>
       <c r="D215" s="4" t="s">
         <v>364</v>
@@ -4879,13 +4888,13 @@
     </row>
     <row r="216" spans="1:4">
       <c r="A216" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B216" s="3">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C216" s="3">
-        <v>265.05</v>
+        <v>170.78</v>
       </c>
       <c r="D216" s="4" t="s">
         <v>364</v>
@@ -4893,69 +4902,69 @@
     </row>
     <row r="217" spans="1:4">
       <c r="A217" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B217" s="3">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="C217" s="3">
-        <v>36.799999999999997</v>
+        <v>216.3</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="218" spans="1:4">
       <c r="A218" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B218" s="3">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C218" s="3">
-        <v>103.04</v>
+        <v>59.7</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="219" spans="1:4">
       <c r="A219" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B219" s="3">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="C219" s="3">
-        <v>36.75</v>
+        <v>265.05</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="220" spans="1:4">
       <c r="A220" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B220" s="3">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C220" s="3">
-        <v>47.16</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
     </row>
     <row r="221" spans="1:4">
       <c r="A221" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B221" s="3">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C221" s="3">
-        <v>16.809999999999999</v>
+        <v>103.04</v>
       </c>
       <c r="D221" s="4" t="s">
         <v>366</v>
@@ -4963,55 +4972,55 @@
     </row>
     <row r="222" spans="1:4">
       <c r="A222" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B222" s="3">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C222" s="3">
-        <v>37.299999999999997</v>
+        <v>36.75</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="223" spans="1:4">
       <c r="A223" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B223" s="3">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C223" s="3">
-        <v>126.24</v>
+        <v>47.16</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="224" spans="1:4">
       <c r="A224" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B224" s="3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C224" s="3">
-        <v>154.62</v>
+        <v>16.809999999999999</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="225" spans="1:4">
       <c r="A225" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B225" s="3">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="C225" s="3">
-        <v>508.2</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="D225" s="4" t="s">
         <v>364</v>
@@ -5019,13 +5028,13 @@
     </row>
     <row r="226" spans="1:4">
       <c r="A226" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B226" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C226" s="3">
-        <v>5069</v>
+        <v>126.24</v>
       </c>
       <c r="D226" s="4" t="s">
         <v>364</v>
@@ -5033,13 +5042,13 @@
     </row>
     <row r="227" spans="1:4">
       <c r="A227" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B227" s="3">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C227" s="3">
-        <v>466.78</v>
+        <v>154.62</v>
       </c>
       <c r="D227" s="4" t="s">
         <v>364</v>
@@ -5047,55 +5056,55 @@
     </row>
     <row r="228" spans="1:4">
       <c r="A228" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B228" s="3">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C228" s="3">
-        <v>57.5</v>
+        <v>508.2</v>
       </c>
       <c r="D228" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="229" spans="1:4">
       <c r="A229" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B229" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C229" s="3">
-        <v>63.13</v>
+        <v>5069</v>
       </c>
       <c r="D229" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="230" spans="1:4">
       <c r="A230" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B230" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C230" s="3">
-        <v>20789.41</v>
+        <v>466.78</v>
       </c>
       <c r="D230" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="231" spans="1:4">
       <c r="A231" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B231" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C231" s="3">
-        <v>33057.85</v>
+        <v>57.5</v>
       </c>
       <c r="D231" s="4" t="s">
         <v>367</v>
@@ -5103,13 +5112,13 @@
     </row>
     <row r="232" spans="1:4">
       <c r="A232" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B232" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C232" s="3">
-        <v>83.5</v>
+        <v>63.13</v>
       </c>
       <c r="D232" s="4" t="s">
         <v>367</v>
@@ -5117,55 +5126,55 @@
     </row>
     <row r="233" spans="1:4">
       <c r="A233" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B233" s="3">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C233" s="3">
-        <v>81.650000000000006</v>
+        <v>20789.41</v>
       </c>
       <c r="D233" s="4" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
     </row>
     <row r="234" spans="1:4">
       <c r="A234" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B234" s="3">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C234" s="3">
-        <v>50.71</v>
+        <v>33057.85</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
     </row>
     <row r="235" spans="1:4">
       <c r="A235" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B235" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C235" s="3">
-        <v>51.75</v>
+        <v>83.5</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
     </row>
     <row r="236" spans="1:4">
       <c r="A236" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B236" s="3">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C236" s="3">
-        <v>36.799999999999997</v>
+        <v>81.650000000000006</v>
       </c>
       <c r="D236" s="4" t="s">
         <v>419</v>
@@ -5173,13 +5182,13 @@
     </row>
     <row r="237" spans="1:4">
       <c r="A237" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B237" s="3">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C237" s="3">
-        <v>36.799999999999997</v>
+        <v>50.71</v>
       </c>
       <c r="D237" s="4" t="s">
         <v>419</v>
@@ -5187,13 +5196,13 @@
     </row>
     <row r="238" spans="1:4">
       <c r="A238" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B238" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C238" s="3">
-        <v>79.58</v>
+        <v>51.75</v>
       </c>
       <c r="D238" s="4" t="s">
         <v>419</v>
@@ -5201,55 +5210,55 @@
     </row>
     <row r="239" spans="1:4">
       <c r="A239" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B239" s="3">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C239" s="3">
-        <v>67.28</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D239" s="4" t="s">
-        <v>367</v>
+        <v>419</v>
       </c>
     </row>
     <row r="240" spans="1:4">
       <c r="A240" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B240" s="3">
-        <v>29</v>
-      </c>
-      <c r="C240" s="8">
-        <v>79.599999999999994</v>
+        <v>12</v>
+      </c>
+      <c r="C240" s="3">
+        <v>36.799999999999997</v>
       </c>
       <c r="D240" s="4" t="s">
-        <v>367</v>
+        <v>419</v>
       </c>
     </row>
     <row r="241" spans="1:4">
       <c r="A241" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B241" s="3">
-        <v>32</v>
-      </c>
-      <c r="C241" s="8">
-        <v>75.88</v>
+        <v>12</v>
+      </c>
+      <c r="C241" s="3">
+        <v>79.58</v>
       </c>
       <c r="D241" s="4" t="s">
-        <v>367</v>
+        <v>419</v>
       </c>
     </row>
     <row r="242" spans="1:4">
       <c r="A242" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B242" s="3">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C242" s="3">
-        <v>109.08</v>
+        <v>67.28</v>
       </c>
       <c r="D242" s="4" t="s">
         <v>367</v>
@@ -5257,164 +5266,164 @@
     </row>
     <row r="243" spans="1:4">
       <c r="A243" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B243" s="3">
-        <v>74</v>
-      </c>
-      <c r="C243" s="3">
-        <v>33.479999999999997</v>
+        <v>29</v>
+      </c>
+      <c r="C243" s="8">
+        <v>79.599999999999994</v>
       </c>
       <c r="D243" s="4" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
     </row>
     <row r="244" spans="1:4">
       <c r="A244" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B244" s="3">
-        <v>5</v>
-      </c>
-      <c r="C244" s="3">
-        <v>422.09</v>
+        <v>27</v>
+      </c>
+      <c r="C244" s="8">
+        <v>75.88</v>
       </c>
       <c r="D244" s="4" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
     </row>
     <row r="245" spans="1:4">
       <c r="A245" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B245" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C245" s="3">
-        <v>1277.7</v>
+        <v>109.08</v>
       </c>
       <c r="D245" s="4" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
     </row>
     <row r="246" spans="1:4">
       <c r="A246" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B246" s="3">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="C246" s="3">
-        <v>6.44</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D246" s="4" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
     </row>
     <row r="247" spans="1:4">
       <c r="A247" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B247" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C247" s="3">
-        <v>108.2</v>
+        <v>422.09</v>
       </c>
       <c r="D247" s="4" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
     </row>
     <row r="248" spans="1:4">
       <c r="A248" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B248" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C248" s="3">
-        <v>4456.4799999999996</v>
+        <v>1277.7</v>
       </c>
       <c r="D248" s="4" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="249" spans="1:4">
       <c r="A249" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B249" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C249" s="3">
-        <v>7429</v>
+        <v>6.44</v>
       </c>
       <c r="D249" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="250" spans="1:4">
       <c r="A250" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B250" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C250" s="3">
-        <v>609.5</v>
+        <v>108.2</v>
       </c>
       <c r="D250" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="251" spans="1:4">
       <c r="A251" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B251" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C251" s="3">
-        <v>32.200000000000003</v>
+        <v>4456.4799999999996</v>
       </c>
       <c r="D251" s="4" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
     </row>
     <row r="252" spans="1:4">
       <c r="A252" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B252" s="3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C252" s="3">
-        <v>32.200000000000003</v>
+        <v>7429</v>
       </c>
       <c r="D252" s="4" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
     </row>
     <row r="253" spans="1:4">
       <c r="A253" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B253" s="3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="C253" s="3">
-        <v>32.200000000000003</v>
+        <v>609.5</v>
       </c>
       <c r="D253" s="4" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
     </row>
     <row r="254" spans="1:4">
       <c r="A254" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B254" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C254" s="3">
         <v>32.200000000000003</v>
@@ -5425,13 +5434,13 @@
     </row>
     <row r="255" spans="1:4">
       <c r="A255" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B255" s="3">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C255" s="3">
-        <v>40.4</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D255" s="4" t="s">
         <v>354</v>
@@ -5439,13 +5448,13 @@
     </row>
     <row r="256" spans="1:4">
       <c r="A256" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B256" s="3">
-        <v>178</v>
+        <v>36</v>
       </c>
       <c r="C256" s="3">
-        <v>36.06</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D256" s="4" t="s">
         <v>354</v>
@@ -5453,153 +5462,153 @@
     </row>
     <row r="257" spans="1:4">
       <c r="A257" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B257" s="3">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C257" s="3">
-        <v>56</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D257" s="4" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
     </row>
     <row r="258" spans="1:4">
       <c r="A258" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B258" s="3">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C258" s="3">
-        <v>57.63</v>
+        <v>40.4</v>
       </c>
       <c r="D258" s="4" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
     </row>
     <row r="259" spans="1:4">
       <c r="A259" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B259" s="3">
-        <v>4</v>
+        <v>178</v>
       </c>
       <c r="C259" s="3">
-        <v>60.78</v>
+        <v>36.06</v>
       </c>
       <c r="D259" s="4" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
     </row>
     <row r="260" spans="1:4">
       <c r="A260" t="s">
-        <v>420</v>
+        <v>204</v>
       </c>
       <c r="B260" s="3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C260" s="3">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D260" s="4" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
     </row>
     <row r="261" spans="1:4">
       <c r="A261" t="s">
-        <v>421</v>
+        <v>205</v>
       </c>
       <c r="B261" s="3">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C261" s="3">
-        <v>29.63</v>
+        <v>57.63</v>
       </c>
       <c r="D261" s="4" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
     </row>
     <row r="262" spans="1:4">
       <c r="A262" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B262" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C262" s="3">
-        <v>42.49</v>
+        <v>60.78</v>
       </c>
       <c r="D262" s="4" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
     </row>
     <row r="263" spans="1:4">
       <c r="A263" t="s">
-        <v>208</v>
-      </c>
-      <c r="B263" s="4">
-        <v>19</v>
-      </c>
-      <c r="C263" s="8">
-        <v>86.95</v>
+        <v>420</v>
+      </c>
+      <c r="B263" s="3">
+        <v>4</v>
+      </c>
+      <c r="C263" s="3">
+        <v>65</v>
       </c>
       <c r="D263" s="4" t="s">
-        <v>364</v>
+        <v>419</v>
       </c>
     </row>
     <row r="264" spans="1:4">
       <c r="A264" t="s">
-        <v>209</v>
+        <v>421</v>
       </c>
       <c r="B264" s="3">
-        <v>3</v>
-      </c>
-      <c r="C264" s="8">
-        <v>312.57</v>
+        <v>12</v>
+      </c>
+      <c r="C264" s="3">
+        <v>29.63</v>
       </c>
       <c r="D264" s="4" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
     </row>
     <row r="265" spans="1:4">
       <c r="A265" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B265" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C265" s="3">
-        <v>71.709999999999994</v>
+        <v>42.49</v>
       </c>
       <c r="D265" s="4" t="s">
-        <v>364</v>
+        <v>419</v>
       </c>
     </row>
     <row r="266" spans="1:4">
       <c r="A266" t="s">
-        <v>211</v>
-      </c>
-      <c r="B266" s="3">
-        <v>1</v>
-      </c>
-      <c r="C266" s="3">
-        <v>77.760000000000005</v>
+        <v>208</v>
+      </c>
+      <c r="B266" s="4">
+        <v>19</v>
+      </c>
+      <c r="C266" s="8">
+        <v>86.95</v>
       </c>
       <c r="D266" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="267" spans="1:4">
       <c r="A267" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B267" s="3">
-        <v>13</v>
-      </c>
-      <c r="C267" s="3">
-        <v>54.7</v>
+        <v>3</v>
+      </c>
+      <c r="C267" s="8">
+        <v>312.57</v>
       </c>
       <c r="D267" s="4" t="s">
         <v>364</v>
@@ -5607,13 +5616,13 @@
     </row>
     <row r="268" spans="1:4">
       <c r="A268" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B268" s="3">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C268" s="3">
-        <v>67.28</v>
+        <v>71.709999999999994</v>
       </c>
       <c r="D268" s="4" t="s">
         <v>364</v>
@@ -5621,27 +5630,27 @@
     </row>
     <row r="269" spans="1:4">
       <c r="A269" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B269" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C269" s="3">
-        <v>334.36</v>
+        <v>77.760000000000005</v>
       </c>
       <c r="D269" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="270" spans="1:4">
       <c r="A270" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B270" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C270" s="3">
-        <v>78.87</v>
+        <v>54.7</v>
       </c>
       <c r="D270" s="4" t="s">
         <v>364</v>
@@ -5649,13 +5658,13 @@
     </row>
     <row r="271" spans="1:4">
       <c r="A271" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B271" s="3">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C271" s="3">
-        <v>83.84</v>
+        <v>67.28</v>
       </c>
       <c r="D271" s="4" t="s">
         <v>364</v>
@@ -5663,13 +5672,13 @@
     </row>
     <row r="272" spans="1:4">
       <c r="A272" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B272" s="3">
         <v>4</v>
       </c>
       <c r="C272" s="3">
-        <v>331.2</v>
+        <v>334.36</v>
       </c>
       <c r="D272" s="4" t="s">
         <v>364</v>
@@ -5677,13 +5686,13 @@
     </row>
     <row r="273" spans="1:4">
       <c r="A273" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B273" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C273" s="3">
-        <v>79.75</v>
+        <v>78.87</v>
       </c>
       <c r="D273" s="4" t="s">
         <v>364</v>
@@ -5691,10 +5700,10 @@
     </row>
     <row r="274" spans="1:4">
       <c r="A274" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B274" s="3">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C274" s="3">
         <v>83.84</v>
@@ -5705,13 +5714,13 @@
     </row>
     <row r="275" spans="1:4">
       <c r="A275" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B275" s="3">
-        <v>2</v>
-      </c>
-      <c r="C275" s="8">
-        <v>347.3</v>
+        <v>4</v>
+      </c>
+      <c r="C275" s="3">
+        <v>331.2</v>
       </c>
       <c r="D275" s="4" t="s">
         <v>364</v>
@@ -5719,13 +5728,13 @@
     </row>
     <row r="276" spans="1:4">
       <c r="A276" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B276" s="3">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C276" s="3">
-        <v>284</v>
+        <v>79.75</v>
       </c>
       <c r="D276" s="4" t="s">
         <v>364</v>
@@ -5733,83 +5742,83 @@
     </row>
     <row r="277" spans="1:4">
       <c r="A277" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B277" s="3">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C277" s="3">
-        <v>28.15</v>
+        <v>83.84</v>
       </c>
       <c r="D277" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="278" spans="1:4">
       <c r="A278" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B278" s="3">
-        <v>1</v>
-      </c>
-      <c r="C278" s="3">
-        <v>45.08</v>
+        <v>2</v>
+      </c>
+      <c r="C278" s="8">
+        <v>347.3</v>
       </c>
       <c r="D278" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="279" spans="1:4">
       <c r="A279" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B279" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C279" s="3">
-        <v>51.52</v>
+        <v>284</v>
       </c>
       <c r="D279" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="280" spans="1:4">
       <c r="A280" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B280" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C280" s="3">
-        <v>40.57</v>
+        <v>28.15</v>
       </c>
       <c r="D280" s="4" t="s">
-        <v>419</v>
+        <v>366</v>
       </c>
     </row>
     <row r="281" spans="1:4">
       <c r="A281" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B281" s="3">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="C281" s="3">
-        <v>36.229999999999997</v>
+        <v>45.08</v>
       </c>
       <c r="D281" s="4" t="s">
-        <v>419</v>
+        <v>366</v>
       </c>
     </row>
     <row r="282" spans="1:4">
       <c r="A282" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B282" s="3">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C282" s="3">
-        <v>54.12</v>
+        <v>51.52</v>
       </c>
       <c r="D282" s="4" t="s">
         <v>366</v>
@@ -5817,41 +5826,41 @@
     </row>
     <row r="283" spans="1:4">
       <c r="A283" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B283" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C283" s="3">
-        <v>69.55</v>
+        <v>40.57</v>
       </c>
       <c r="D283" s="4" t="s">
-        <v>364</v>
+        <v>419</v>
       </c>
     </row>
     <row r="284" spans="1:4">
       <c r="A284" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B284" s="3">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C284" s="3">
-        <v>295.14999999999998</v>
+        <v>36.229999999999997</v>
       </c>
       <c r="D284" s="4" t="s">
-        <v>364</v>
+        <v>419</v>
       </c>
     </row>
     <row r="285" spans="1:4">
       <c r="A285" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B285" s="3">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C285" s="3">
-        <v>38.56</v>
+        <v>54.12</v>
       </c>
       <c r="D285" s="4" t="s">
         <v>366</v>
@@ -5859,83 +5868,83 @@
     </row>
     <row r="286" spans="1:4">
       <c r="A286" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B286" s="3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C286" s="3">
-        <v>60.95</v>
+        <v>69.55</v>
       </c>
       <c r="D286" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="287" spans="1:4">
       <c r="A287" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B287" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C287" s="3">
-        <v>78.209999999999994</v>
+        <v>295.14999999999998</v>
       </c>
       <c r="D287" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="288" spans="1:4">
       <c r="A288" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B288" s="3">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="C288" s="3">
-        <v>44.93</v>
+        <v>38.56</v>
       </c>
       <c r="D288" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="289" spans="1:4">
       <c r="A289" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B289" s="3">
-        <v>240</v>
+        <v>7</v>
       </c>
       <c r="C289" s="3">
-        <v>51.15</v>
+        <v>60.95</v>
       </c>
       <c r="D289" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="290" spans="1:4">
       <c r="A290" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B290" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C290" s="3">
-        <v>6591.8</v>
+        <v>78.209999999999994</v>
       </c>
       <c r="D290" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="291" spans="1:4">
       <c r="A291" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B291" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C291" s="3">
-        <v>182.42</v>
+        <v>44.93</v>
       </c>
       <c r="D291" s="4" t="s">
         <v>364</v>
@@ -5943,13 +5952,13 @@
     </row>
     <row r="292" spans="1:4">
       <c r="A292" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B292" s="3">
-        <v>138</v>
+        <v>240</v>
       </c>
       <c r="C292" s="3">
-        <v>222.62</v>
+        <v>51.15</v>
       </c>
       <c r="D292" s="4" t="s">
         <v>364</v>
@@ -5957,13 +5966,13 @@
     </row>
     <row r="293" spans="1:4">
       <c r="A293" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B293" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C293" s="3">
-        <v>2314.8000000000002</v>
+        <v>6591.8</v>
       </c>
       <c r="D293" s="4" t="s">
         <v>364</v>
@@ -5971,13 +5980,13 @@
     </row>
     <row r="294" spans="1:4">
       <c r="A294" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B294" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C294" s="3">
-        <v>894.8</v>
+        <v>182.42</v>
       </c>
       <c r="D294" s="4" t="s">
         <v>364</v>
@@ -5985,55 +5994,55 @@
     </row>
     <row r="295" spans="1:4">
       <c r="A295" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B295" s="3">
-        <v>26</v>
+        <v>126</v>
       </c>
       <c r="C295" s="3">
-        <v>31.6</v>
+        <v>222.62</v>
       </c>
       <c r="D295" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="296" spans="1:4">
       <c r="A296" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B296" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C296" s="3">
-        <v>77.28</v>
+        <v>2314.8000000000002</v>
       </c>
       <c r="D296" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="297" spans="1:4">
       <c r="A297" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B297" s="3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C297" s="3">
-        <v>43.8</v>
+        <v>894.8</v>
       </c>
       <c r="D297" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="298" spans="1:4">
       <c r="A298" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B298" s="3">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C298" s="3">
-        <v>21.9</v>
+        <v>31.6</v>
       </c>
       <c r="D298" s="4" t="s">
         <v>366</v>
@@ -6041,13 +6050,13 @@
     </row>
     <row r="299" spans="1:4">
       <c r="A299" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B299" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C299" s="3">
-        <v>798.6</v>
+        <v>77.28</v>
       </c>
       <c r="D299" s="4" t="s">
         <v>366</v>
@@ -6055,13 +6064,13 @@
     </row>
     <row r="300" spans="1:4">
       <c r="A300" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B300" s="3">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="C300" s="3">
-        <v>23.19</v>
+        <v>43.8</v>
       </c>
       <c r="D300" s="4" t="s">
         <v>366</v>
@@ -6069,13 +6078,13 @@
     </row>
     <row r="301" spans="1:4">
       <c r="A301" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B301" s="3">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="C301" s="3">
-        <v>8.24</v>
+        <v>21.9</v>
       </c>
       <c r="D301" s="4" t="s">
         <v>366</v>
@@ -6083,13 +6092,13 @@
     </row>
     <row r="302" spans="1:4">
       <c r="A302" t="s">
-        <v>458</v>
+        <v>242</v>
       </c>
       <c r="B302" s="3">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C302" s="3">
-        <v>13.72</v>
+        <v>798.6</v>
       </c>
       <c r="D302" s="4" t="s">
         <v>366</v>
@@ -6097,13 +6106,13 @@
     </row>
     <row r="303" spans="1:4">
       <c r="A303" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B303" s="3">
-        <v>4</v>
+        <v>85</v>
       </c>
       <c r="C303" s="3">
-        <v>13.72</v>
+        <v>23.19</v>
       </c>
       <c r="D303" s="4" t="s">
         <v>366</v>
@@ -6111,13 +6120,13 @@
     </row>
     <row r="304" spans="1:4">
       <c r="A304" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B304" s="3">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="C304" s="3">
-        <v>31.95</v>
+        <v>8.24</v>
       </c>
       <c r="D304" s="4" t="s">
         <v>366</v>
@@ -6125,13 +6134,13 @@
     </row>
     <row r="305" spans="1:4">
       <c r="A305" t="s">
-        <v>370</v>
+        <v>458</v>
       </c>
       <c r="B305" s="3">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="C305" s="3">
-        <v>16.2</v>
+        <v>13.72</v>
       </c>
       <c r="D305" s="4" t="s">
         <v>366</v>
@@ -6139,13 +6148,13 @@
     </row>
     <row r="306" spans="1:4">
       <c r="A306" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B306" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C306" s="3">
-        <v>36.869999999999997</v>
+        <v>13.72</v>
       </c>
       <c r="D306" s="4" t="s">
         <v>366</v>
@@ -6153,13 +6162,13 @@
     </row>
     <row r="307" spans="1:4">
       <c r="A307" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B307" s="3">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C307" s="3">
-        <v>31.48</v>
+        <v>31.95</v>
       </c>
       <c r="D307" s="4" t="s">
         <v>366</v>
@@ -6167,13 +6176,13 @@
     </row>
     <row r="308" spans="1:4">
       <c r="A308" t="s">
-        <v>249</v>
+        <v>370</v>
       </c>
       <c r="B308" s="3">
-        <v>7</v>
+        <v>105</v>
       </c>
       <c r="C308" s="3">
-        <v>21.9</v>
+        <v>16.2</v>
       </c>
       <c r="D308" s="4" t="s">
         <v>366</v>
@@ -6181,13 +6190,13 @@
     </row>
     <row r="309" spans="1:4">
       <c r="A309" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B309" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C309" s="3">
-        <v>23.19</v>
+        <v>36.869999999999997</v>
       </c>
       <c r="D309" s="4" t="s">
         <v>366</v>
@@ -6195,13 +6204,13 @@
     </row>
     <row r="310" spans="1:4">
       <c r="A310" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B310" s="3">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C310" s="3">
-        <v>19.55</v>
+        <v>31.48</v>
       </c>
       <c r="D310" s="4" t="s">
         <v>366</v>
@@ -6209,13 +6218,13 @@
     </row>
     <row r="311" spans="1:4">
       <c r="A311" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B311" s="3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C311" s="3">
-        <v>19.07</v>
+        <v>21.9</v>
       </c>
       <c r="D311" s="4" t="s">
         <v>366</v>
@@ -6223,13 +6232,13 @@
     </row>
     <row r="312" spans="1:4">
       <c r="A312" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B312" s="3">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="C312" s="3">
-        <v>21.9</v>
+        <v>23.19</v>
       </c>
       <c r="D312" s="4" t="s">
         <v>366</v>
@@ -6237,55 +6246,55 @@
     </row>
     <row r="313" spans="1:4">
       <c r="A313" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B313" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C313" s="3">
-        <v>79.349999999999994</v>
+        <v>19.55</v>
       </c>
       <c r="D313" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="314" spans="1:4">
       <c r="A314" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B314" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C314" s="3">
-        <v>862.7</v>
+        <v>19.07</v>
       </c>
       <c r="D314" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="315" spans="1:4">
       <c r="A315" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B315" s="3">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C315" s="3">
-        <v>56.93</v>
+        <v>21.9</v>
       </c>
       <c r="D315" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="316" spans="1:4">
       <c r="A316" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B316" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C316" s="3">
-        <v>1265</v>
+        <v>79.349999999999994</v>
       </c>
       <c r="D316" s="4" t="s">
         <v>367</v>
@@ -6293,55 +6302,55 @@
     </row>
     <row r="317" spans="1:4">
       <c r="A317" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B317" s="3">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C317" s="3">
-        <v>76</v>
+        <v>862.7</v>
       </c>
       <c r="D317" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="318" spans="1:4">
       <c r="A318" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B318" s="3">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C318" s="3">
-        <v>267.85000000000002</v>
+        <v>56.93</v>
       </c>
       <c r="D318" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="319" spans="1:4">
       <c r="A319" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B319" s="3">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C319" s="3">
-        <v>74.7</v>
+        <v>1265</v>
       </c>
       <c r="D319" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="320" spans="1:4">
       <c r="A320" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B320" s="3">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C320" s="3">
-        <v>327.3</v>
+        <v>76</v>
       </c>
       <c r="D320" s="4" t="s">
         <v>364</v>
@@ -6349,13 +6358,13 @@
     </row>
     <row r="321" spans="1:4">
       <c r="A321" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B321" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C321" s="3">
-        <v>72.13</v>
+        <v>267.85000000000002</v>
       </c>
       <c r="D321" s="4" t="s">
         <v>364</v>
@@ -6363,13 +6372,13 @@
     </row>
     <row r="322" spans="1:4">
       <c r="A322" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B322" s="3">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="C322" s="3">
-        <v>302.39999999999998</v>
+        <v>74.7</v>
       </c>
       <c r="D322" s="4" t="s">
         <v>364</v>
@@ -6377,27 +6386,27 @@
     </row>
     <row r="323" spans="1:4">
       <c r="A323" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B323" s="3">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="C323" s="3">
-        <v>36.799999999999997</v>
+        <v>327.3</v>
       </c>
       <c r="D323" s="4" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="324" spans="1:4">
       <c r="A324" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B324" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C324" s="3">
-        <v>428.5</v>
+        <v>72.13</v>
       </c>
       <c r="D324" s="4" t="s">
         <v>364</v>
@@ -6405,13 +6414,13 @@
     </row>
     <row r="325" spans="1:4">
       <c r="A325" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B325" s="3">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="C325" s="3">
-        <v>450.22</v>
+        <v>302.39999999999998</v>
       </c>
       <c r="D325" s="4" t="s">
         <v>364</v>
@@ -6419,27 +6428,27 @@
     </row>
     <row r="326" spans="1:4">
       <c r="A326" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B326" s="3">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="C326" s="3">
-        <v>465.7</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D326" s="4" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="327" spans="1:4">
       <c r="A327" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B327" s="3">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="C327" s="3">
-        <v>38.25</v>
+        <v>428.5</v>
       </c>
       <c r="D327" s="4" t="s">
         <v>364</v>
@@ -6447,13 +6456,13 @@
     </row>
     <row r="328" spans="1:4">
       <c r="A328" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B328" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C328" s="3">
-        <v>87.49</v>
+        <v>450.22</v>
       </c>
       <c r="D328" s="4" t="s">
         <v>364</v>
@@ -6461,13 +6470,13 @@
     </row>
     <row r="329" spans="1:4">
       <c r="A329" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B329" s="3">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C329" s="3">
-        <v>63.13</v>
+        <v>465.7</v>
       </c>
       <c r="D329" s="4" t="s">
         <v>364</v>
@@ -6475,55 +6484,55 @@
     </row>
     <row r="330" spans="1:4">
       <c r="A330" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B330" s="3">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C330" s="3">
-        <v>377.78</v>
+        <v>38.25</v>
       </c>
       <c r="D330" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="331" spans="1:4">
       <c r="A331" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B331" s="3">
         <v>2</v>
       </c>
       <c r="C331" s="3">
-        <v>3333.85</v>
+        <v>87.49</v>
       </c>
       <c r="D331" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="332" spans="1:4">
       <c r="A332" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B332" s="3">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="C332" s="3">
-        <v>374.67</v>
+        <v>63.13</v>
       </c>
       <c r="D332" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="333" spans="1:4">
       <c r="A333" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B333" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C333" s="3">
-        <v>120.06</v>
+        <v>377.78</v>
       </c>
       <c r="D333" s="4" t="s">
         <v>368</v>
@@ -6531,69 +6540,69 @@
     </row>
     <row r="334" spans="1:4">
       <c r="A334" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B334" s="3">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C334" s="3">
-        <v>54.2</v>
+        <v>3333.85</v>
       </c>
       <c r="D334" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="335" spans="1:4">
       <c r="A335" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B335" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C335" s="3">
-        <v>31.5</v>
+        <v>374.67</v>
       </c>
       <c r="D335" s="4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="336" spans="1:4">
       <c r="A336" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B336" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C336" s="3">
-        <v>114.09</v>
+        <v>120.06</v>
       </c>
       <c r="D336" s="4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="337" spans="1:4">
       <c r="A337" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B337" s="3">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="C337" s="3">
-        <v>139.9</v>
+        <v>54.2</v>
       </c>
       <c r="D337" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="338" spans="1:4">
       <c r="A338" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B338" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C338" s="3">
-        <v>50.13</v>
+        <v>31.5</v>
       </c>
       <c r="D338" s="4" t="s">
         <v>364</v>
@@ -6601,13 +6610,13 @@
     </row>
     <row r="339" spans="1:4">
       <c r="A339" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B339" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C339" s="3">
-        <v>140.26</v>
+        <v>114.09</v>
       </c>
       <c r="D339" s="4" t="s">
         <v>364</v>
@@ -6615,41 +6624,41 @@
     </row>
     <row r="340" spans="1:4">
       <c r="A340" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B340" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C340" s="3">
-        <v>370.53</v>
+        <v>139.9</v>
       </c>
       <c r="D340" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="341" spans="1:4">
       <c r="A341" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B341" s="3">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C341" s="3">
-        <v>30.9</v>
+        <v>50.13</v>
       </c>
       <c r="D341" s="4" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="342" spans="1:4">
       <c r="A342" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B342" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C342" s="3">
-        <v>5746.5</v>
+        <v>140.26</v>
       </c>
       <c r="D342" s="4" t="s">
         <v>364</v>
@@ -6657,55 +6666,55 @@
     </row>
     <row r="343" spans="1:4">
       <c r="A343" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B343" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C343" s="3">
-        <v>516.46</v>
+        <v>370.53</v>
       </c>
       <c r="D343" s="4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="344" spans="1:4">
       <c r="A344" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B344" s="3">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C344" s="3">
-        <v>185.15</v>
+        <v>30.9</v>
       </c>
       <c r="D344" s="4" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="345" spans="1:4">
       <c r="A345" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B345" s="3">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="C345" s="3">
-        <v>11.5</v>
+        <v>5746.5</v>
       </c>
       <c r="D345" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="346" spans="1:4">
       <c r="A346" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B346" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C346" s="3">
-        <v>724.5</v>
+        <v>516.46</v>
       </c>
       <c r="D346" s="4" t="s">
         <v>364</v>
@@ -6713,69 +6722,69 @@
     </row>
     <row r="347" spans="1:4">
       <c r="A347" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B347" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C347" s="3">
-        <v>450.22</v>
+        <v>185.15</v>
       </c>
       <c r="D347" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="348" spans="1:4">
       <c r="A348" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B348" s="3">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="C348" s="3">
-        <v>461.23</v>
+        <v>11.5</v>
       </c>
       <c r="D348" s="4" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
     </row>
     <row r="349" spans="1:4">
       <c r="A349" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B349" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C349" s="3">
-        <v>518.41999999999996</v>
+        <v>724.5</v>
       </c>
       <c r="D349" s="4" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
     </row>
     <row r="350" spans="1:4">
       <c r="A350" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B350" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C350" s="3">
-        <v>348.08</v>
+        <v>450.22</v>
       </c>
       <c r="D350" s="4" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
     </row>
     <row r="351" spans="1:4">
       <c r="A351" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B351" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C351" s="3">
-        <v>33.479999999999997</v>
+        <v>461.23</v>
       </c>
       <c r="D351" s="4" t="s">
         <v>357</v>
@@ -6783,13 +6792,13 @@
     </row>
     <row r="352" spans="1:4">
       <c r="A352" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B352" s="3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C352" s="3">
-        <v>35.79</v>
+        <v>518.41999999999996</v>
       </c>
       <c r="D352" s="4" t="s">
         <v>357</v>
@@ -6797,13 +6806,13 @@
     </row>
     <row r="353" spans="1:4">
       <c r="A353" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B353" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C353" s="3">
-        <v>377.7</v>
+        <v>348.08</v>
       </c>
       <c r="D353" s="4" t="s">
         <v>357</v>
@@ -6811,13 +6820,13 @@
     </row>
     <row r="354" spans="1:4">
       <c r="A354" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B354" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C354" s="3">
-        <v>33.21</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D354" s="4" t="s">
         <v>357</v>
@@ -6825,13 +6834,13 @@
     </row>
     <row r="355" spans="1:4">
       <c r="A355" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B355" s="3">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C355" s="3">
-        <v>27.16</v>
+        <v>35.79</v>
       </c>
       <c r="D355" s="4" t="s">
         <v>357</v>
@@ -6839,13 +6848,13 @@
     </row>
     <row r="356" spans="1:4">
       <c r="A356" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B356" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C356" s="3">
-        <v>361.41</v>
+        <v>377.7</v>
       </c>
       <c r="D356" s="4" t="s">
         <v>357</v>
@@ -6853,13 +6862,13 @@
     </row>
     <row r="357" spans="1:4">
       <c r="A357" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B357" s="3">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="C357" s="3">
-        <v>29.25</v>
+        <v>33.21</v>
       </c>
       <c r="D357" s="4" t="s">
         <v>357</v>
@@ -6867,13 +6876,13 @@
     </row>
     <row r="358" spans="1:4">
       <c r="A358" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B358" s="3">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C358" s="3">
-        <v>304.54000000000002</v>
+        <v>27.16</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>357</v>
@@ -6881,13 +6890,13 @@
     </row>
     <row r="359" spans="1:4">
       <c r="A359" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B359" s="3">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C359" s="3">
-        <v>34.049999999999997</v>
+        <v>361.41</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>357</v>
@@ -6895,55 +6904,55 @@
     </row>
     <row r="360" spans="1:4">
       <c r="A360" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B360" s="3">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="C360" s="3">
-        <v>57.7</v>
+        <v>29.25</v>
       </c>
       <c r="D360" s="4" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
     </row>
     <row r="361" spans="1:4">
       <c r="A361" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B361" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C361" s="3">
-        <v>90.9</v>
+        <v>304.54000000000002</v>
       </c>
       <c r="D361" s="4" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
     </row>
     <row r="362" spans="1:4">
       <c r="A362" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B362" s="3">
-        <v>250</v>
+        <v>17</v>
       </c>
       <c r="C362" s="3">
-        <v>47.62</v>
+        <v>34.049999999999997</v>
       </c>
       <c r="D362" s="4" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
     </row>
     <row r="363" spans="1:4">
       <c r="A363" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B363" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C363" s="3">
-        <v>7173.59</v>
+        <v>57.7</v>
       </c>
       <c r="D363" s="4" t="s">
         <v>364</v>
@@ -6951,27 +6960,27 @@
     </row>
     <row r="364" spans="1:4">
       <c r="A364" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B364" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C364" s="3">
-        <v>677.79</v>
+        <v>90.9</v>
       </c>
       <c r="D364" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="365" spans="1:4">
       <c r="A365" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B365" s="3">
-        <v>9</v>
-      </c>
-      <c r="C365" s="8">
-        <v>171.47</v>
+        <v>225</v>
+      </c>
+      <c r="C365" s="3">
+        <v>47.62</v>
       </c>
       <c r="D365" s="4" t="s">
         <v>364</v>
@@ -6979,13 +6988,13 @@
     </row>
     <row r="366" spans="1:4">
       <c r="A366" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B366" s="3">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="C366" s="3">
-        <v>212.75</v>
+        <v>7173.59</v>
       </c>
       <c r="D366" s="4" t="s">
         <v>364</v>
@@ -6993,13 +7002,13 @@
     </row>
     <row r="367" spans="1:4">
       <c r="A367" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B367" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C367" s="3">
-        <v>2335.67</v>
+        <v>677.79</v>
       </c>
       <c r="D367" s="4" t="s">
         <v>364</v>
@@ -7007,13 +7016,13 @@
     </row>
     <row r="368" spans="1:4">
       <c r="A368" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B368" s="3">
-        <v>28</v>
-      </c>
-      <c r="C368" s="3">
-        <v>66.180000000000007</v>
+        <v>3</v>
+      </c>
+      <c r="C368" s="8">
+        <v>171.47</v>
       </c>
       <c r="D368" s="4" t="s">
         <v>364</v>
@@ -7021,13 +7030,13 @@
     </row>
     <row r="369" spans="1:4">
       <c r="A369" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B369" s="3">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="C369" s="3">
-        <v>8139.6</v>
+        <v>212.75</v>
       </c>
       <c r="D369" s="4" t="s">
         <v>364</v>
@@ -7035,13 +7044,13 @@
     </row>
     <row r="370" spans="1:4">
       <c r="A370" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B370" s="3">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C370" s="3">
-        <v>259.81</v>
+        <v>2335.67</v>
       </c>
       <c r="D370" s="4" t="s">
         <v>364</v>
@@ -7049,13 +7058,13 @@
     </row>
     <row r="371" spans="1:4">
       <c r="A371" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B371" s="3">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C371" s="3">
-        <v>259.8</v>
+        <v>66.180000000000007</v>
       </c>
       <c r="D371" s="4" t="s">
         <v>364</v>
@@ -7063,13 +7072,13 @@
     </row>
     <row r="372" spans="1:4">
       <c r="A372" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B372" s="3">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C372" s="3">
-        <v>310.2</v>
+        <v>8139.6</v>
       </c>
       <c r="D372" s="4" t="s">
         <v>364</v>
@@ -7077,13 +7086,13 @@
     </row>
     <row r="373" spans="1:4">
       <c r="A373" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B373" s="3">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C373" s="3">
-        <v>36.43</v>
+        <v>259.81</v>
       </c>
       <c r="D373" s="4" t="s">
         <v>364</v>
@@ -7091,13 +7100,13 @@
     </row>
     <row r="374" spans="1:4">
       <c r="A374" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B374" s="3">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C374" s="3">
-        <v>87.22</v>
+        <v>259.8</v>
       </c>
       <c r="D374" s="4" t="s">
         <v>364</v>
@@ -7105,13 +7114,13 @@
     </row>
     <row r="375" spans="1:4">
       <c r="A375" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B375" s="3">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C375" s="3">
-        <v>319.60000000000002</v>
+        <v>310.2</v>
       </c>
       <c r="D375" s="4" t="s">
         <v>364</v>
@@ -7119,13 +7128,13 @@
     </row>
     <row r="376" spans="1:4">
       <c r="A376" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B376" s="3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C376" s="3">
-        <v>62.6</v>
+        <v>36.43</v>
       </c>
       <c r="D376" s="4" t="s">
         <v>364</v>
@@ -7133,13 +7142,13 @@
     </row>
     <row r="377" spans="1:4">
       <c r="A377" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B377" s="3">
-        <v>8</v>
-      </c>
-      <c r="C377" s="8">
-        <v>385.25</v>
+        <v>16</v>
+      </c>
+      <c r="C377" s="3">
+        <v>87.22</v>
       </c>
       <c r="D377" s="4" t="s">
         <v>364</v>
@@ -7147,41 +7156,41 @@
     </row>
     <row r="378" spans="1:4">
       <c r="A378" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B378" s="3">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="C378" s="3">
-        <v>67.28</v>
+        <v>319.60000000000002</v>
       </c>
       <c r="D378" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="379" spans="1:4">
       <c r="A379" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B379" s="3">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C379" s="3">
-        <v>1138.5</v>
+        <v>62.6</v>
       </c>
       <c r="D379" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="380" spans="1:4">
       <c r="A380" t="s">
-        <v>350</v>
+        <v>317</v>
       </c>
       <c r="B380" s="3">
-        <v>22</v>
-      </c>
-      <c r="C380" s="3">
-        <v>58.69</v>
+        <v>8</v>
+      </c>
+      <c r="C380" s="8">
+        <v>385.25</v>
       </c>
       <c r="D380" s="4" t="s">
         <v>364</v>
@@ -7189,41 +7198,41 @@
     </row>
     <row r="381" spans="1:4">
       <c r="A381" t="s">
-        <v>351</v>
+        <v>318</v>
       </c>
       <c r="B381" s="3">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C381" s="3">
-        <v>289.33999999999997</v>
+        <v>67.28</v>
       </c>
       <c r="D381" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="382" spans="1:4">
       <c r="A382" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B382" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C382" s="3">
-        <v>48.76</v>
+        <v>1138.5</v>
       </c>
       <c r="D382" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="383" spans="1:4">
       <c r="A383" t="s">
-        <v>321</v>
+        <v>350</v>
       </c>
       <c r="B383" s="3">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="C383" s="3">
-        <v>242.34</v>
+        <v>58.69</v>
       </c>
       <c r="D383" s="4" t="s">
         <v>364</v>
@@ -7231,13 +7240,13 @@
     </row>
     <row r="384" spans="1:4">
       <c r="A384" t="s">
-        <v>322</v>
+        <v>351</v>
       </c>
       <c r="B384" s="3">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C384" s="3">
-        <v>65.599999999999994</v>
+        <v>289.33999999999997</v>
       </c>
       <c r="D384" s="4" t="s">
         <v>364</v>
@@ -7245,13 +7254,13 @@
     </row>
     <row r="385" spans="1:4">
       <c r="A385" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B385" s="3">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C385" s="3">
-        <v>255.03</v>
+        <v>48.76</v>
       </c>
       <c r="D385" s="4" t="s">
         <v>364</v>
@@ -7259,13 +7268,13 @@
     </row>
     <row r="386" spans="1:4">
       <c r="A386" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B386" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C386" s="3">
-        <v>220.8</v>
+        <v>242.34</v>
       </c>
       <c r="D386" s="4" t="s">
         <v>364</v>
@@ -7273,13 +7282,13 @@
     </row>
     <row r="387" spans="1:4">
       <c r="A387" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B387" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C387" s="3">
-        <v>255.02</v>
+        <v>65.599999999999994</v>
       </c>
       <c r="D387" s="4" t="s">
         <v>364</v>
@@ -7287,13 +7296,13 @@
     </row>
     <row r="388" spans="1:4">
       <c r="A388" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B388" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C388" s="3">
-        <v>68.86</v>
+        <v>255.03</v>
       </c>
       <c r="D388" s="4" t="s">
         <v>364</v>
@@ -7301,13 +7310,13 @@
     </row>
     <row r="389" spans="1:4">
       <c r="A389" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B389" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C389" s="3">
-        <v>344.28</v>
+        <v>220.8</v>
       </c>
       <c r="D389" s="4" t="s">
         <v>364</v>
@@ -7315,13 +7324,13 @@
     </row>
     <row r="390" spans="1:4">
       <c r="A390" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B390" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C390" s="3">
-        <v>60.29</v>
+        <v>255.02</v>
       </c>
       <c r="D390" s="4" t="s">
         <v>364</v>
@@ -7329,13 +7338,13 @@
     </row>
     <row r="391" spans="1:4">
       <c r="A391" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B391" s="3">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C391" s="3">
-        <v>261.8</v>
+        <v>68.86</v>
       </c>
       <c r="D391" s="4" t="s">
         <v>364</v>
@@ -7343,83 +7352,83 @@
     </row>
     <row r="392" spans="1:4">
       <c r="A392" t="s">
-        <v>382</v>
+        <v>327</v>
       </c>
       <c r="B392" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C392" s="3">
-        <v>30.58</v>
+        <v>344.28</v>
       </c>
       <c r="D392" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="393" spans="1:4">
       <c r="A393" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B393" s="3">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="C393" s="3">
-        <v>16.95</v>
+        <v>60.29</v>
       </c>
       <c r="D393" s="4" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="394" spans="1:4">
       <c r="A394" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B394" s="3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="C394" s="3">
-        <v>24.95</v>
+        <v>261.8</v>
       </c>
       <c r="D394" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="395" spans="1:4">
       <c r="A395" t="s">
-        <v>332</v>
+        <v>382</v>
       </c>
       <c r="B395" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C395" s="3">
-        <v>641.49</v>
+        <v>30.58</v>
       </c>
       <c r="D395" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="396" spans="1:4">
       <c r="A396" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B396" s="3">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="C396" s="3">
-        <v>39.57</v>
+        <v>16.95</v>
       </c>
       <c r="D396" s="4" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
     </row>
     <row r="397" spans="1:4">
       <c r="A397" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B397" s="3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C397" s="3">
-        <v>51.83</v>
+        <v>24.95</v>
       </c>
       <c r="D397" s="4" t="s">
         <v>367</v>
@@ -7427,55 +7436,55 @@
     </row>
     <row r="398" spans="1:4">
       <c r="A398" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B398" s="3">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="C398" s="3">
-        <v>33.840000000000003</v>
+        <v>641.49</v>
       </c>
       <c r="D398" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="399" spans="1:4">
       <c r="A399" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B399" s="3">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C399" s="3">
-        <v>150.15</v>
+        <v>39.57</v>
       </c>
       <c r="D399" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="400" spans="1:4">
       <c r="A400" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B400" s="3">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="C400" s="3">
-        <v>144.5</v>
+        <v>51.83</v>
       </c>
       <c r="D400" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="401" spans="1:4">
       <c r="A401" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B401" s="3">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C401" s="3">
-        <v>100.93</v>
+        <v>33.840000000000003</v>
       </c>
       <c r="D401" s="4" t="s">
         <v>364</v>
@@ -7483,13 +7492,13 @@
     </row>
     <row r="402" spans="1:4">
       <c r="A402" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B402" s="3">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C402" s="3">
-        <v>124.5</v>
+        <v>150.15</v>
       </c>
       <c r="D402" s="4" t="s">
         <v>364</v>
@@ -7497,13 +7506,13 @@
     </row>
     <row r="403" spans="1:4">
       <c r="A403" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B403" s="3">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C403" s="3">
-        <v>27.21</v>
+        <v>144.5</v>
       </c>
       <c r="D403" s="4" t="s">
         <v>364</v>
@@ -7511,27 +7520,27 @@
     </row>
     <row r="404" spans="1:4">
       <c r="A404" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B404" s="3">
-        <v>94</v>
+        <v>25</v>
       </c>
       <c r="C404" s="3">
-        <v>24.79</v>
+        <v>100.93</v>
       </c>
       <c r="D404" s="4" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
     </row>
     <row r="405" spans="1:4">
       <c r="A405" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B405" s="3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C405" s="3">
-        <v>37.1</v>
+        <v>124.5</v>
       </c>
       <c r="D405" s="4" t="s">
         <v>364</v>
@@ -7539,13 +7548,13 @@
     </row>
     <row r="406" spans="1:4">
       <c r="A406" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B406" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C406" s="3">
-        <v>178.04</v>
+        <v>27.21</v>
       </c>
       <c r="D406" s="4" t="s">
         <v>364</v>
@@ -7553,27 +7562,27 @@
     </row>
     <row r="407" spans="1:4">
       <c r="A407" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B407" s="3">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="C407" s="3">
-        <v>23.88</v>
+        <v>24.79</v>
       </c>
       <c r="D407" s="4" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="408" spans="1:4">
       <c r="A408" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B408" s="3">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="C408" s="3">
-        <v>20.68</v>
+        <v>37.1</v>
       </c>
       <c r="D408" s="4" t="s">
         <v>364</v>
@@ -7581,13 +7590,13 @@
     </row>
     <row r="409" spans="1:4">
       <c r="A409" t="s">
-        <v>372</v>
+        <v>343</v>
       </c>
       <c r="B409" s="3">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C409" s="3">
-        <v>97.54</v>
+        <v>178.04</v>
       </c>
       <c r="D409" s="4" t="s">
         <v>364</v>
@@ -7595,55 +7604,55 @@
     </row>
     <row r="410" spans="1:4">
       <c r="A410" t="s">
-        <v>373</v>
+        <v>344</v>
       </c>
       <c r="B410" s="3">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="C410" s="3">
-        <v>304.02999999999997</v>
+        <v>23.88</v>
       </c>
       <c r="D410" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="411" spans="1:4">
       <c r="A411" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B411" s="3">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="C411" s="3">
-        <v>1934.56</v>
+        <v>20.68</v>
       </c>
       <c r="D411" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="412" spans="1:4">
       <c r="A412" t="s">
-        <v>347</v>
+        <v>372</v>
       </c>
       <c r="B412" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C412" s="3">
-        <v>230.99</v>
+        <v>97.54</v>
       </c>
       <c r="D412" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="413" spans="1:4">
       <c r="A413" t="s">
-        <v>348</v>
+        <v>373</v>
       </c>
       <c r="B413" s="3">
-        <v>96</v>
+        <v>7</v>
       </c>
       <c r="C413" s="3">
-        <v>33.39</v>
+        <v>304.02999999999997</v>
       </c>
       <c r="D413" s="4" t="s">
         <v>364</v>
@@ -7651,69 +7660,69 @@
     </row>
     <row r="414" spans="1:4">
       <c r="A414" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B414" s="3">
         <v>0</v>
       </c>
       <c r="C414" s="3">
-        <v>20.66</v>
+        <v>1934.56</v>
       </c>
       <c r="D414" s="4" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="415" spans="1:4">
       <c r="A415" t="s">
-        <v>375</v>
+        <v>347</v>
       </c>
       <c r="B415" s="3">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="C415" s="3">
-        <v>97.5</v>
+        <v>230.99</v>
       </c>
       <c r="D415" s="4" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
     </row>
     <row r="416" spans="1:4">
       <c r="A416" t="s">
-        <v>376</v>
+        <v>348</v>
       </c>
       <c r="B416" s="3">
-        <v>430</v>
+        <v>96</v>
       </c>
       <c r="C416" s="3">
-        <v>24.7</v>
+        <v>33.39</v>
       </c>
       <c r="D416" s="4" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
     </row>
     <row r="417" spans="1:4">
       <c r="A417" t="s">
-        <v>377</v>
+        <v>349</v>
       </c>
       <c r="B417" s="3">
-        <v>455</v>
+        <v>0</v>
       </c>
       <c r="C417" s="3">
-        <v>35.75</v>
+        <v>20.66</v>
       </c>
       <c r="D417" s="4" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
     </row>
     <row r="418" spans="1:4">
       <c r="A418" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B418" s="3">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c r="C418" s="3">
-        <v>9.1</v>
+        <v>97.5</v>
       </c>
       <c r="D418" s="4" t="s">
         <v>374</v>
@@ -7721,13 +7730,13 @@
     </row>
     <row r="419" spans="1:4">
       <c r="A419" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B419" s="3">
-        <v>152</v>
+        <v>410</v>
       </c>
       <c r="C419" s="3">
-        <v>5.43</v>
+        <v>24.7</v>
       </c>
       <c r="D419" s="4" t="s">
         <v>374</v>
@@ -7735,13 +7744,13 @@
     </row>
     <row r="420" spans="1:4">
       <c r="A420" t="s">
-        <v>432</v>
+        <v>377</v>
       </c>
       <c r="B420" s="3">
-        <v>140</v>
+        <v>448</v>
       </c>
       <c r="C420" s="3">
-        <v>11.99</v>
+        <v>35.75</v>
       </c>
       <c r="D420" s="4" t="s">
         <v>374</v>
@@ -7749,97 +7758,97 @@
     </row>
     <row r="421" spans="1:4">
       <c r="A421" t="s">
-        <v>414</v>
+        <v>378</v>
       </c>
       <c r="B421" s="3">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="C421" s="3">
-        <v>9.75</v>
+        <v>9.1</v>
       </c>
       <c r="D421" s="4" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="422" spans="1:4">
       <c r="A422" t="s">
-        <v>415</v>
+        <v>379</v>
       </c>
       <c r="B422" s="3">
-        <v>19</v>
+        <v>152</v>
       </c>
       <c r="C422" s="3">
-        <v>6.37</v>
+        <v>5.43</v>
       </c>
       <c r="D422" s="4" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="423" spans="1:4">
       <c r="A423" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B423" s="3">
-        <v>12</v>
+        <v>140</v>
       </c>
       <c r="C423" s="3">
-        <v>10.53</v>
+        <v>11.99</v>
       </c>
       <c r="D423" s="4" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="424" spans="1:4">
       <c r="A424" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B424" s="3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C424" s="3">
-        <v>11.59</v>
+        <v>9.75</v>
       </c>
       <c r="D424" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="425" spans="1:4">
       <c r="A425" t="s">
-        <v>434</v>
+        <v>415</v>
       </c>
       <c r="B425" s="3">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="C425" s="3">
-        <v>12.09</v>
+        <v>6.37</v>
       </c>
       <c r="D425" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="426" spans="1:4">
       <c r="A426" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B426" s="3">
-        <v>230</v>
+        <v>12</v>
       </c>
       <c r="C426" s="3">
-        <v>12.09</v>
+        <v>10.53</v>
       </c>
       <c r="D426" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="427" spans="1:4">
       <c r="A427" t="s">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="B427" s="3">
-        <v>201</v>
+        <v>24</v>
       </c>
       <c r="C427" s="3">
-        <v>6.5</v>
+        <v>11.59</v>
       </c>
       <c r="D427" s="4" t="s">
         <v>381</v>
@@ -7847,13 +7856,13 @@
     </row>
     <row r="428" spans="1:4">
       <c r="A428" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B428" s="3">
-        <v>188</v>
+        <v>36</v>
       </c>
       <c r="C428" s="3">
-        <v>6.5</v>
+        <v>12.09</v>
       </c>
       <c r="D428" s="4" t="s">
         <v>381</v>
@@ -7861,55 +7870,55 @@
     </row>
     <row r="429" spans="1:4">
       <c r="A429" t="s">
-        <v>453</v>
+        <v>435</v>
       </c>
       <c r="B429" s="3">
-        <v>2</v>
+        <v>230</v>
       </c>
       <c r="C429" s="3">
-        <v>5017</v>
+        <v>12.09</v>
       </c>
       <c r="D429" s="4" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
     </row>
     <row r="430" spans="1:4">
       <c r="A430" t="s">
-        <v>454</v>
+        <v>436</v>
       </c>
       <c r="B430" s="3">
-        <v>8</v>
+        <v>201</v>
       </c>
       <c r="C430" s="3">
-        <v>4437.1499999999996</v>
+        <v>6.5</v>
       </c>
       <c r="D430" s="4" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
     </row>
     <row r="431" spans="1:4">
       <c r="A431" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="B431" s="3">
-        <v>7</v>
+        <v>188</v>
       </c>
       <c r="C431" s="3">
-        <v>6239.83</v>
+        <v>6.5</v>
       </c>
       <c r="D431" s="4" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
     </row>
     <row r="432" spans="1:4">
       <c r="A432" t="s">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="B432" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C432" s="3">
-        <v>5980</v>
+        <v>5017</v>
       </c>
       <c r="D432" s="4" t="s">
         <v>364</v>
@@ -7917,13 +7926,13 @@
     </row>
     <row r="433" spans="1:4">
       <c r="A433" t="s">
-        <v>428</v>
+        <v>454</v>
       </c>
       <c r="B433" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C433" s="3">
-        <v>3556.4</v>
+        <v>4437.1499999999996</v>
       </c>
       <c r="D433" s="4" t="s">
         <v>364</v>
@@ -7931,13 +7940,13 @@
     </row>
     <row r="434" spans="1:4">
       <c r="A434" t="s">
-        <v>451</v>
+        <v>429</v>
       </c>
       <c r="B434" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C434" s="3">
-        <v>6463</v>
+        <v>6239.83</v>
       </c>
       <c r="D434" s="4" t="s">
         <v>364</v>
@@ -7945,13 +7954,13 @@
     </row>
     <row r="435" spans="1:4">
       <c r="A435" t="s">
-        <v>452</v>
+        <v>438</v>
       </c>
       <c r="B435" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C435" s="3">
-        <v>5199</v>
+        <v>5980</v>
       </c>
       <c r="D435" s="4" t="s">
         <v>364</v>
@@ -7959,69 +7968,69 @@
     </row>
     <row r="436" spans="1:4">
       <c r="A436" t="s">
-        <v>448</v>
+        <v>428</v>
       </c>
       <c r="B436" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C436" s="3">
-        <v>58.68</v>
+        <v>3556.4</v>
       </c>
       <c r="D436" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="437" spans="1:4">
       <c r="A437" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="B437" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C437" s="3">
-        <v>65</v>
+        <v>6463</v>
       </c>
       <c r="D437" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="438" spans="1:4">
       <c r="A438" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B438" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C438" s="3">
-        <v>70.25</v>
+        <v>5199</v>
       </c>
       <c r="D438" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="439" spans="1:4">
       <c r="A439" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="B439" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C439" s="3">
-        <v>45</v>
+        <v>58.68</v>
       </c>
       <c r="D439" s="4" t="s">
-        <v>455</v>
+        <v>367</v>
       </c>
     </row>
     <row r="440" spans="1:4">
       <c r="A440" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B440" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C440" s="3">
-        <v>70.25</v>
+        <v>65</v>
       </c>
       <c r="D440" s="4" t="s">
         <v>367</v>
@@ -8029,13 +8038,13 @@
     </row>
     <row r="441" spans="1:4">
       <c r="A441" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="B441" s="3">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C441" s="3">
-        <v>58.9</v>
+        <v>70.25</v>
       </c>
       <c r="D441" s="4" t="s">
         <v>367</v>
@@ -8043,27 +8052,27 @@
     </row>
     <row r="442" spans="1:4">
       <c r="A442" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="B442" s="3">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="C442" s="3">
-        <v>89.21</v>
+        <v>45</v>
       </c>
       <c r="D442" s="4" t="s">
-        <v>367</v>
+        <v>455</v>
       </c>
     </row>
     <row r="443" spans="1:4">
       <c r="A443" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B443" s="3">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="C443" s="3">
-        <v>59.18</v>
+        <v>70.25</v>
       </c>
       <c r="D443" s="4" t="s">
         <v>367</v>
@@ -8071,13 +8080,13 @@
     </row>
     <row r="444" spans="1:4">
       <c r="A444" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B444" s="3">
         <v>36</v>
       </c>
       <c r="C444" s="3">
-        <v>60.62</v>
+        <v>58.9</v>
       </c>
       <c r="D444" s="4" t="s">
         <v>367</v>
@@ -8085,13 +8094,13 @@
     </row>
     <row r="445" spans="1:4">
       <c r="A445" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B445" s="3">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="C445" s="3">
-        <v>3431.7</v>
+        <v>89.21</v>
       </c>
       <c r="D445" s="4" t="s">
         <v>367</v>
@@ -8099,13 +8108,13 @@
     </row>
     <row r="446" spans="1:4">
       <c r="A446" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B446" s="3">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="C446" s="3">
-        <v>1260.2</v>
+        <v>59.18</v>
       </c>
       <c r="D446" s="4" t="s">
         <v>367</v>
@@ -8113,15 +8122,57 @@
     </row>
     <row r="447" spans="1:4">
       <c r="A447" t="s">
+        <v>463</v>
+      </c>
+      <c r="B447" s="3">
+        <v>36</v>
+      </c>
+      <c r="C447" s="3">
+        <v>60.62</v>
+      </c>
+      <c r="D447" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4">
+      <c r="A448" t="s">
+        <v>464</v>
+      </c>
+      <c r="B448" s="3">
+        <v>3</v>
+      </c>
+      <c r="C448" s="3">
+        <v>3431.7</v>
+      </c>
+      <c r="D448" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4">
+      <c r="A449" t="s">
+        <v>465</v>
+      </c>
+      <c r="B449" s="3">
+        <v>3</v>
+      </c>
+      <c r="C449" s="3">
+        <v>1260.2</v>
+      </c>
+      <c r="D449" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4">
+      <c r="A450" t="s">
         <v>466</v>
       </c>
-      <c r="B447" s="3">
+      <c r="B450" s="3">
         <v>60</v>
       </c>
-      <c r="C447" s="3">
+      <c r="C450" s="3">
         <v>47.2</v>
       </c>
-      <c r="D447" s="4" t="s">
+      <c r="D450" s="4" t="s">
         <v>367</v>
       </c>
     </row>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -2511,7 +2511,7 @@
         <v>13</v>
       </c>
       <c r="B46" s="3">
-        <v>1789</v>
+        <v>1777</v>
       </c>
       <c r="C46" s="3">
         <v>13</v>
@@ -2875,7 +2875,7 @@
         <v>33</v>
       </c>
       <c r="B72" s="3">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C72" s="3">
         <v>18.96</v>
@@ -2987,7 +2987,7 @@
         <v>443</v>
       </c>
       <c r="B80" s="3">
-        <v>738</v>
+        <v>726</v>
       </c>
       <c r="C80" s="3">
         <v>19.48</v>
@@ -3127,7 +3127,7 @@
         <v>45</v>
       </c>
       <c r="B90" s="3">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C90" s="3">
         <v>18.37</v>
@@ -3645,7 +3645,7 @@
         <v>80</v>
       </c>
       <c r="B127" s="3">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C127" s="3">
         <v>52.17</v>
@@ -3659,7 +3659,7 @@
         <v>81</v>
       </c>
       <c r="B128" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C128" s="3">
         <v>208.66</v>
@@ -3995,7 +3995,7 @@
         <v>103</v>
       </c>
       <c r="B152" s="3">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C152" s="3">
         <v>66.98</v>
@@ -4807,7 +4807,7 @@
         <v>158</v>
       </c>
       <c r="B210" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C210" s="8">
         <v>58.32</v>
@@ -4835,7 +4835,7 @@
         <v>352</v>
       </c>
       <c r="B212" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C212" s="8">
         <v>257.70999999999998</v>
@@ -4947,7 +4947,7 @@
         <v>167</v>
       </c>
       <c r="B220" s="3">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C220" s="3">
         <v>36.799999999999997</v>
@@ -5311,7 +5311,7 @@
         <v>191</v>
       </c>
       <c r="B246" s="3">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C246" s="3">
         <v>33.479999999999997</v>
@@ -5493,7 +5493,7 @@
         <v>203</v>
       </c>
       <c r="B259" s="3">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C259" s="3">
         <v>36.06</v>
@@ -5591,7 +5591,7 @@
         <v>208</v>
       </c>
       <c r="B266" s="4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C266" s="8">
         <v>86.95</v>
@@ -5605,7 +5605,7 @@
         <v>209</v>
       </c>
       <c r="B267" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C267" s="8">
         <v>312.57</v>
@@ -5997,7 +5997,7 @@
         <v>235</v>
       </c>
       <c r="B295" s="3">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C295" s="3">
         <v>222.62</v>
@@ -6585,7 +6585,7 @@
         <v>275</v>
       </c>
       <c r="B337" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C337" s="3">
         <v>54.2</v>
@@ -7033,7 +7033,7 @@
         <v>306</v>
       </c>
       <c r="B369" s="3">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C369" s="3">
         <v>212.75</v>
@@ -7061,7 +7061,7 @@
         <v>308</v>
       </c>
       <c r="B371" s="3">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C371" s="3">
         <v>66.180000000000007</v>
@@ -7089,7 +7089,7 @@
         <v>310</v>
       </c>
       <c r="B373" s="3">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C373" s="3">
         <v>259.81</v>
@@ -8167,7 +8167,7 @@
         <v>466</v>
       </c>
       <c r="B450" s="3">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C450" s="3">
         <v>47.2</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -2217,7 +2217,7 @@
         <v>401</v>
       </c>
       <c r="B25" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25" s="3">
         <v>376.62</v>
@@ -2399,7 +2399,7 @@
         <v>11</v>
       </c>
       <c r="B38" s="3">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C38" s="3">
         <v>189</v>
@@ -2427,7 +2427,7 @@
         <v>426</v>
       </c>
       <c r="B40" s="3">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="C40" s="3">
         <v>26.29</v>
@@ -2511,7 +2511,7 @@
         <v>13</v>
       </c>
       <c r="B46" s="3">
-        <v>1777</v>
+        <v>1753</v>
       </c>
       <c r="C46" s="3">
         <v>13</v>
@@ -2847,7 +2847,7 @@
         <v>32</v>
       </c>
       <c r="B70" s="3">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C70" s="3">
         <v>87.12</v>
@@ -2875,7 +2875,7 @@
         <v>33</v>
       </c>
       <c r="B72" s="3">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C72" s="3">
         <v>18.96</v>
@@ -2987,7 +2987,7 @@
         <v>443</v>
       </c>
       <c r="B80" s="3">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="C80" s="3">
         <v>19.48</v>
@@ -3029,7 +3029,7 @@
         <v>446</v>
       </c>
       <c r="B83" s="3">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C83" s="3">
         <v>22.21</v>
@@ -3127,7 +3127,7 @@
         <v>45</v>
       </c>
       <c r="B90" s="3">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C90" s="3">
         <v>18.37</v>
@@ -3323,7 +3323,7 @@
         <v>59</v>
       </c>
       <c r="B104" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C104" s="3">
         <v>40.54</v>
@@ -3869,7 +3869,7 @@
         <v>94</v>
       </c>
       <c r="B143" s="3">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C143" s="3">
         <v>66.98</v>
@@ -4177,7 +4177,7 @@
         <v>115</v>
       </c>
       <c r="B165" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C165" s="3">
         <v>32.200000000000003</v>
@@ -4751,7 +4751,7 @@
         <v>154</v>
       </c>
       <c r="B206" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C206" s="3">
         <v>44.51</v>
@@ -4779,7 +4779,7 @@
         <v>156</v>
       </c>
       <c r="B208" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C208" s="3">
         <v>199.77</v>
@@ -4835,7 +4835,7 @@
         <v>352</v>
       </c>
       <c r="B212" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C212" s="8">
         <v>257.70999999999998</v>
@@ -4849,7 +4849,7 @@
         <v>160</v>
       </c>
       <c r="B213" s="3">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C213" s="3">
         <v>33.479999999999997</v>
@@ -5017,7 +5017,7 @@
         <v>172</v>
       </c>
       <c r="B225" s="3">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C225" s="3">
         <v>37.299999999999997</v>
@@ -5031,7 +5031,7 @@
         <v>173</v>
       </c>
       <c r="B226" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C226" s="3">
         <v>126.24</v>
@@ -5045,7 +5045,7 @@
         <v>174</v>
       </c>
       <c r="B227" s="3">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C227" s="3">
         <v>154.62</v>
@@ -5311,7 +5311,7 @@
         <v>191</v>
       </c>
       <c r="B246" s="3">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C246" s="3">
         <v>33.479999999999997</v>
@@ -5493,7 +5493,7 @@
         <v>203</v>
       </c>
       <c r="B259" s="3">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C259" s="3">
         <v>36.06</v>
@@ -5507,7 +5507,7 @@
         <v>204</v>
       </c>
       <c r="B260" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C260" s="3">
         <v>56</v>
@@ -5941,7 +5941,7 @@
         <v>232</v>
       </c>
       <c r="B291" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C291" s="3">
         <v>44.93</v>
@@ -5955,7 +5955,7 @@
         <v>232</v>
       </c>
       <c r="B292" s="3">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C292" s="3">
         <v>51.15</v>
@@ -5997,7 +5997,7 @@
         <v>235</v>
       </c>
       <c r="B295" s="3">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C295" s="3">
         <v>222.62</v>
@@ -6977,7 +6977,7 @@
         <v>302</v>
       </c>
       <c r="B365" s="3">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C365" s="3">
         <v>47.62</v>
@@ -7033,7 +7033,7 @@
         <v>306</v>
       </c>
       <c r="B369" s="3">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C369" s="3">
         <v>212.75</v>
@@ -7061,7 +7061,7 @@
         <v>308</v>
       </c>
       <c r="B371" s="3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C371" s="3">
         <v>66.180000000000007</v>
@@ -7117,7 +7117,7 @@
         <v>312</v>
       </c>
       <c r="B375" s="3">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C375" s="3">
         <v>310.2</v>
@@ -7299,7 +7299,7 @@
         <v>323</v>
       </c>
       <c r="B388" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C388" s="3">
         <v>255.03</v>
@@ -7341,7 +7341,7 @@
         <v>326</v>
       </c>
       <c r="B391" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C391" s="3">
         <v>68.86</v>
@@ -7355,7 +7355,7 @@
         <v>327</v>
       </c>
       <c r="B392" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C392" s="3">
         <v>344.28</v>
@@ -7621,7 +7621,7 @@
         <v>345</v>
       </c>
       <c r="B411" s="3">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C411" s="3">
         <v>20.68</v>
@@ -7635,7 +7635,7 @@
         <v>372</v>
       </c>
       <c r="B412" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C412" s="3">
         <v>97.54</v>
@@ -7929,7 +7929,7 @@
         <v>454</v>
       </c>
       <c r="B433" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C433" s="3">
         <v>4437.1499999999996</v>
@@ -8055,7 +8055,7 @@
         <v>456</v>
       </c>
       <c r="B442" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C442" s="3">
         <v>45</v>
@@ -8167,7 +8167,7 @@
         <v>466</v>
       </c>
       <c r="B450" s="3">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C450" s="3">
         <v>47.2</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -4779,7 +4779,7 @@
         <v>156</v>
       </c>
       <c r="B208" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C208" s="3">
         <v>199.77</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="469">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -1385,9 +1385,6 @@
   </si>
   <si>
     <t>FEBI 06161 ULEI SERVODIRECTIE</t>
-  </si>
-  <si>
-    <t>FUCHS TITAN ATF 6400 (ATF FZ) 1L</t>
   </si>
   <si>
     <t>RAV SOL PARBRIZ IARNA 1L</t>
@@ -1868,7 +1865,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D450"/>
+  <dimension ref="A1:D448"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="49.85546875" customWidth="1"/>
@@ -2452,7 +2449,7 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B42" s="3">
         <v>6</v>
@@ -2466,7 +2463,7 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B43" s="3">
         <v>6</v>
@@ -2480,7 +2477,7 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B44" s="3">
         <v>6</v>
@@ -2651,7 +2648,7 @@
         <v>22</v>
       </c>
       <c r="B56" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C56" s="3">
         <v>1982.77</v>
@@ -2847,7 +2844,7 @@
         <v>32</v>
       </c>
       <c r="B70" s="3">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C70" s="3">
         <v>87.12</v>
@@ -2875,7 +2872,7 @@
         <v>33</v>
       </c>
       <c r="B72" s="3">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C72" s="3">
         <v>18.96</v>
@@ -2987,7 +2984,7 @@
         <v>443</v>
       </c>
       <c r="B80" s="3">
-        <v>720</v>
+        <v>708</v>
       </c>
       <c r="C80" s="3">
         <v>19.48</v>
@@ -3029,7 +3026,7 @@
         <v>446</v>
       </c>
       <c r="B83" s="3">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C83" s="3">
         <v>22.21</v>
@@ -3995,7 +3992,7 @@
         <v>103</v>
       </c>
       <c r="B152" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C152" s="3">
         <v>66.98</v>
@@ -4149,7 +4146,7 @@
         <v>113</v>
       </c>
       <c r="B163" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C163" s="3">
         <v>32.200000000000003</v>
@@ -4541,7 +4538,7 @@
         <v>140</v>
       </c>
       <c r="B191" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C191" s="3">
         <v>35.81</v>
@@ -4555,7 +4552,7 @@
         <v>141</v>
       </c>
       <c r="B192" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C192" s="3">
         <v>59.25</v>
@@ -4569,7 +4566,7 @@
         <v>142</v>
       </c>
       <c r="B193" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C193" s="3">
         <v>260</v>
@@ -4765,7 +4762,7 @@
         <v>155</v>
       </c>
       <c r="B207" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C207" s="3">
         <v>145.94</v>
@@ -4891,7 +4888,7 @@
         <v>163</v>
       </c>
       <c r="B216" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C216" s="3">
         <v>170.78</v>
@@ -5017,7 +5014,7 @@
         <v>172</v>
       </c>
       <c r="B225" s="3">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C225" s="3">
         <v>37.299999999999997</v>
@@ -5045,7 +5042,7 @@
         <v>174</v>
       </c>
       <c r="B227" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C227" s="3">
         <v>154.62</v>
@@ -5311,7 +5308,7 @@
         <v>191</v>
       </c>
       <c r="B246" s="3">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C246" s="3">
         <v>33.479999999999997</v>
@@ -5423,7 +5420,7 @@
         <v>198</v>
       </c>
       <c r="B254" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C254" s="3">
         <v>32.200000000000003</v>
@@ -5941,10 +5938,10 @@
         <v>232</v>
       </c>
       <c r="B291" s="3">
-        <v>4</v>
+        <v>230</v>
       </c>
       <c r="C291" s="3">
-        <v>44.93</v>
+        <v>51.15</v>
       </c>
       <c r="D291" s="4" t="s">
         <v>364</v>
@@ -5952,13 +5949,13 @@
     </row>
     <row r="292" spans="1:4">
       <c r="A292" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B292" s="3">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="C292" s="3">
-        <v>51.15</v>
+        <v>6591.8</v>
       </c>
       <c r="D292" s="4" t="s">
         <v>364</v>
@@ -5966,13 +5963,13 @@
     </row>
     <row r="293" spans="1:4">
       <c r="A293" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B293" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C293" s="3">
-        <v>6591.8</v>
+        <v>182.42</v>
       </c>
       <c r="D293" s="4" t="s">
         <v>364</v>
@@ -5980,13 +5977,13 @@
     </row>
     <row r="294" spans="1:4">
       <c r="A294" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B294" s="3">
-        <v>1</v>
+        <v>116</v>
       </c>
       <c r="C294" s="3">
-        <v>182.42</v>
+        <v>222.62</v>
       </c>
       <c r="D294" s="4" t="s">
         <v>364</v>
@@ -5994,13 +5991,13 @@
     </row>
     <row r="295" spans="1:4">
       <c r="A295" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B295" s="3">
-        <v>118</v>
+        <v>1</v>
       </c>
       <c r="C295" s="3">
-        <v>222.62</v>
+        <v>2314.8000000000002</v>
       </c>
       <c r="D295" s="4" t="s">
         <v>364</v>
@@ -6008,13 +6005,13 @@
     </row>
     <row r="296" spans="1:4">
       <c r="A296" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B296" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C296" s="3">
-        <v>2314.8000000000002</v>
+        <v>894.8</v>
       </c>
       <c r="D296" s="4" t="s">
         <v>364</v>
@@ -6022,27 +6019,27 @@
     </row>
     <row r="297" spans="1:4">
       <c r="A297" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B297" s="3">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C297" s="3">
-        <v>894.8</v>
+        <v>31.6</v>
       </c>
       <c r="D297" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="298" spans="1:4">
       <c r="A298" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B298" s="3">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C298" s="3">
-        <v>31.6</v>
+        <v>77.28</v>
       </c>
       <c r="D298" s="4" t="s">
         <v>366</v>
@@ -6050,13 +6047,13 @@
     </row>
     <row r="299" spans="1:4">
       <c r="A299" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B299" s="3">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C299" s="3">
-        <v>77.28</v>
+        <v>43.8</v>
       </c>
       <c r="D299" s="4" t="s">
         <v>366</v>
@@ -6064,13 +6061,13 @@
     </row>
     <row r="300" spans="1:4">
       <c r="A300" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B300" s="3">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="C300" s="3">
-        <v>43.8</v>
+        <v>21.9</v>
       </c>
       <c r="D300" s="4" t="s">
         <v>366</v>
@@ -6078,13 +6075,13 @@
     </row>
     <row r="301" spans="1:4">
       <c r="A301" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B301" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C301" s="3">
-        <v>21.9</v>
+        <v>798.6</v>
       </c>
       <c r="D301" s="4" t="s">
         <v>366</v>
@@ -6092,13 +6089,13 @@
     </row>
     <row r="302" spans="1:4">
       <c r="A302" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B302" s="3">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="C302" s="3">
-        <v>798.6</v>
+        <v>23.19</v>
       </c>
       <c r="D302" s="4" t="s">
         <v>366</v>
@@ -6106,13 +6103,13 @@
     </row>
     <row r="303" spans="1:4">
       <c r="A303" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B303" s="3">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="C303" s="3">
-        <v>23.19</v>
+        <v>8.24</v>
       </c>
       <c r="D303" s="4" t="s">
         <v>366</v>
@@ -6120,13 +6117,13 @@
     </row>
     <row r="304" spans="1:4">
       <c r="A304" t="s">
-        <v>244</v>
+        <v>457</v>
       </c>
       <c r="B304" s="3">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="C304" s="3">
-        <v>8.24</v>
+        <v>13.72</v>
       </c>
       <c r="D304" s="4" t="s">
         <v>366</v>
@@ -6134,10 +6131,10 @@
     </row>
     <row r="305" spans="1:4">
       <c r="A305" t="s">
-        <v>458</v>
+        <v>245</v>
       </c>
       <c r="B305" s="3">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C305" s="3">
         <v>13.72</v>
@@ -6148,13 +6145,13 @@
     </row>
     <row r="306" spans="1:4">
       <c r="A306" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B306" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C306" s="3">
-        <v>13.72</v>
+        <v>31.95</v>
       </c>
       <c r="D306" s="4" t="s">
         <v>366</v>
@@ -6162,13 +6159,13 @@
     </row>
     <row r="307" spans="1:4">
       <c r="A307" t="s">
-        <v>246</v>
+        <v>370</v>
       </c>
       <c r="B307" s="3">
-        <v>7</v>
+        <v>105</v>
       </c>
       <c r="C307" s="3">
-        <v>31.95</v>
+        <v>16.2</v>
       </c>
       <c r="D307" s="4" t="s">
         <v>366</v>
@@ -6176,13 +6173,13 @@
     </row>
     <row r="308" spans="1:4">
       <c r="A308" t="s">
-        <v>370</v>
+        <v>247</v>
       </c>
       <c r="B308" s="3">
-        <v>105</v>
+        <v>6</v>
       </c>
       <c r="C308" s="3">
-        <v>16.2</v>
+        <v>36.869999999999997</v>
       </c>
       <c r="D308" s="4" t="s">
         <v>366</v>
@@ -6190,13 +6187,13 @@
     </row>
     <row r="309" spans="1:4">
       <c r="A309" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B309" s="3">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C309" s="3">
-        <v>36.869999999999997</v>
+        <v>31.48</v>
       </c>
       <c r="D309" s="4" t="s">
         <v>366</v>
@@ -6204,13 +6201,13 @@
     </row>
     <row r="310" spans="1:4">
       <c r="A310" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B310" s="3">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C310" s="3">
-        <v>31.48</v>
+        <v>21.9</v>
       </c>
       <c r="D310" s="4" t="s">
         <v>366</v>
@@ -6218,13 +6215,13 @@
     </row>
     <row r="311" spans="1:4">
       <c r="A311" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B311" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C311" s="3">
-        <v>21.9</v>
+        <v>23.19</v>
       </c>
       <c r="D311" s="4" t="s">
         <v>366</v>
@@ -6232,13 +6229,13 @@
     </row>
     <row r="312" spans="1:4">
       <c r="A312" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B312" s="3">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C312" s="3">
-        <v>23.19</v>
+        <v>19.55</v>
       </c>
       <c r="D312" s="4" t="s">
         <v>366</v>
@@ -6246,13 +6243,13 @@
     </row>
     <row r="313" spans="1:4">
       <c r="A313" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B313" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C313" s="3">
-        <v>19.55</v>
+        <v>19.07</v>
       </c>
       <c r="D313" s="4" t="s">
         <v>366</v>
@@ -6260,13 +6257,13 @@
     </row>
     <row r="314" spans="1:4">
       <c r="A314" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B314" s="3">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C314" s="3">
-        <v>19.07</v>
+        <v>21.9</v>
       </c>
       <c r="D314" s="4" t="s">
         <v>366</v>
@@ -6274,27 +6271,27 @@
     </row>
     <row r="315" spans="1:4">
       <c r="A315" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B315" s="3">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C315" s="3">
-        <v>21.9</v>
+        <v>79.349999999999994</v>
       </c>
       <c r="D315" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="316" spans="1:4">
       <c r="A316" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B316" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C316" s="3">
-        <v>79.349999999999994</v>
+        <v>862.7</v>
       </c>
       <c r="D316" s="4" t="s">
         <v>367</v>
@@ -6302,13 +6299,13 @@
     </row>
     <row r="317" spans="1:4">
       <c r="A317" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B317" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C317" s="3">
-        <v>862.7</v>
+        <v>56.93</v>
       </c>
       <c r="D317" s="4" t="s">
         <v>367</v>
@@ -6316,13 +6313,13 @@
     </row>
     <row r="318" spans="1:4">
       <c r="A318" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B318" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C318" s="3">
-        <v>56.93</v>
+        <v>1265</v>
       </c>
       <c r="D318" s="4" t="s">
         <v>367</v>
@@ -6330,27 +6327,27 @@
     </row>
     <row r="319" spans="1:4">
       <c r="A319" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B319" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C319" s="3">
-        <v>1265</v>
+        <v>76</v>
       </c>
       <c r="D319" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="320" spans="1:4">
       <c r="A320" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B320" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C320" s="3">
-        <v>76</v>
+        <v>267.85000000000002</v>
       </c>
       <c r="D320" s="4" t="s">
         <v>364</v>
@@ -6358,13 +6355,13 @@
     </row>
     <row r="321" spans="1:4">
       <c r="A321" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B321" s="3">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C321" s="3">
-        <v>267.85000000000002</v>
+        <v>74.7</v>
       </c>
       <c r="D321" s="4" t="s">
         <v>364</v>
@@ -6372,13 +6369,13 @@
     </row>
     <row r="322" spans="1:4">
       <c r="A322" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B322" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C322" s="3">
-        <v>74.7</v>
+        <v>327.3</v>
       </c>
       <c r="D322" s="4" t="s">
         <v>364</v>
@@ -6386,13 +6383,13 @@
     </row>
     <row r="323" spans="1:4">
       <c r="A323" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B323" s="3">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C323" s="3">
-        <v>327.3</v>
+        <v>72.13</v>
       </c>
       <c r="D323" s="4" t="s">
         <v>364</v>
@@ -6400,13 +6397,13 @@
     </row>
     <row r="324" spans="1:4">
       <c r="A324" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B324" s="3">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="C324" s="3">
-        <v>72.13</v>
+        <v>302.39999999999998</v>
       </c>
       <c r="D324" s="4" t="s">
         <v>364</v>
@@ -6414,41 +6411,41 @@
     </row>
     <row r="325" spans="1:4">
       <c r="A325" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B325" s="3">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C325" s="3">
-        <v>302.39999999999998</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D325" s="4" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="326" spans="1:4">
       <c r="A326" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B326" s="3">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C326" s="3">
-        <v>36.799999999999997</v>
+        <v>428.5</v>
       </c>
       <c r="D326" s="4" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="327" spans="1:4">
       <c r="A327" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B327" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C327" s="3">
-        <v>428.5</v>
+        <v>450.22</v>
       </c>
       <c r="D327" s="4" t="s">
         <v>364</v>
@@ -6456,13 +6453,13 @@
     </row>
     <row r="328" spans="1:4">
       <c r="A328" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B328" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C328" s="3">
-        <v>450.22</v>
+        <v>465.7</v>
       </c>
       <c r="D328" s="4" t="s">
         <v>364</v>
@@ -6470,13 +6467,13 @@
     </row>
     <row r="329" spans="1:4">
       <c r="A329" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B329" s="3">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C329" s="3">
-        <v>465.7</v>
+        <v>38.25</v>
       </c>
       <c r="D329" s="4" t="s">
         <v>364</v>
@@ -6484,13 +6481,13 @@
     </row>
     <row r="330" spans="1:4">
       <c r="A330" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B330" s="3">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C330" s="3">
-        <v>38.25</v>
+        <v>87.49</v>
       </c>
       <c r="D330" s="4" t="s">
         <v>364</v>
@@ -6498,13 +6495,13 @@
     </row>
     <row r="331" spans="1:4">
       <c r="A331" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B331" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C331" s="3">
-        <v>87.49</v>
+        <v>63.13</v>
       </c>
       <c r="D331" s="4" t="s">
         <v>364</v>
@@ -6512,27 +6509,27 @@
     </row>
     <row r="332" spans="1:4">
       <c r="A332" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B332" s="3">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C332" s="3">
-        <v>63.13</v>
+        <v>377.78</v>
       </c>
       <c r="D332" s="4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="333" spans="1:4">
       <c r="A333" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B333" s="3">
         <v>2</v>
       </c>
       <c r="C333" s="3">
-        <v>377.78</v>
+        <v>3333.85</v>
       </c>
       <c r="D333" s="4" t="s">
         <v>368</v>
@@ -6540,13 +6537,13 @@
     </row>
     <row r="334" spans="1:4">
       <c r="A334" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B334" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C334" s="3">
-        <v>3333.85</v>
+        <v>374.67</v>
       </c>
       <c r="D334" s="4" t="s">
         <v>368</v>
@@ -6554,13 +6551,13 @@
     </row>
     <row r="335" spans="1:4">
       <c r="A335" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B335" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C335" s="3">
-        <v>374.67</v>
+        <v>120.06</v>
       </c>
       <c r="D335" s="4" t="s">
         <v>368</v>
@@ -6568,41 +6565,41 @@
     </row>
     <row r="336" spans="1:4">
       <c r="A336" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B336" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C336" s="3">
-        <v>120.06</v>
+        <v>54.2</v>
       </c>
       <c r="D336" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="337" spans="1:4">
       <c r="A337" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B337" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C337" s="3">
-        <v>54.2</v>
+        <v>31.5</v>
       </c>
       <c r="D337" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="338" spans="1:4">
       <c r="A338" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B338" s="3">
         <v>0</v>
       </c>
       <c r="C338" s="3">
-        <v>31.5</v>
+        <v>114.09</v>
       </c>
       <c r="D338" s="4" t="s">
         <v>364</v>
@@ -6610,13 +6607,13 @@
     </row>
     <row r="339" spans="1:4">
       <c r="A339" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B339" s="3">
         <v>0</v>
       </c>
       <c r="C339" s="3">
-        <v>114.09</v>
+        <v>139.9</v>
       </c>
       <c r="D339" s="4" t="s">
         <v>364</v>
@@ -6624,13 +6621,13 @@
     </row>
     <row r="340" spans="1:4">
       <c r="A340" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B340" s="3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C340" s="3">
-        <v>139.9</v>
+        <v>50.13</v>
       </c>
       <c r="D340" s="4" t="s">
         <v>364</v>
@@ -6638,13 +6635,13 @@
     </row>
     <row r="341" spans="1:4">
       <c r="A341" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B341" s="3">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C341" s="3">
-        <v>50.13</v>
+        <v>140.26</v>
       </c>
       <c r="D341" s="4" t="s">
         <v>364</v>
@@ -6652,55 +6649,55 @@
     </row>
     <row r="342" spans="1:4">
       <c r="A342" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B342" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C342" s="3">
-        <v>140.26</v>
+        <v>370.53</v>
       </c>
       <c r="D342" s="4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="343" spans="1:4">
       <c r="A343" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B343" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C343" s="3">
-        <v>370.53</v>
+        <v>30.9</v>
       </c>
       <c r="D343" s="4" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
     </row>
     <row r="344" spans="1:4">
       <c r="A344" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B344" s="3">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="C344" s="3">
-        <v>30.9</v>
+        <v>5746.5</v>
       </c>
       <c r="D344" s="4" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="345" spans="1:4">
       <c r="A345" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B345" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C345" s="3">
-        <v>5746.5</v>
+        <v>516.46</v>
       </c>
       <c r="D345" s="4" t="s">
         <v>364</v>
@@ -6708,13 +6705,13 @@
     </row>
     <row r="346" spans="1:4">
       <c r="A346" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B346" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C346" s="3">
-        <v>516.46</v>
+        <v>185.15</v>
       </c>
       <c r="D346" s="4" t="s">
         <v>364</v>
@@ -6722,58 +6719,58 @@
     </row>
     <row r="347" spans="1:4">
       <c r="A347" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B347" s="3">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C347" s="3">
-        <v>185.15</v>
+        <v>11.5</v>
       </c>
       <c r="D347" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="348" spans="1:4">
       <c r="A348" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B348" s="3">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="C348" s="3">
-        <v>11.5</v>
+        <v>724.5</v>
       </c>
       <c r="D348" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="349" spans="1:4">
       <c r="A349" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B349" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C349" s="3">
-        <v>724.5</v>
+        <v>450.22</v>
       </c>
       <c r="D349" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="350" spans="1:4">
       <c r="A350" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B350" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C350" s="3">
-        <v>450.22</v>
+        <v>461.23</v>
       </c>
       <c r="D350" s="4" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -6784,7 +6781,7 @@
         <v>1</v>
       </c>
       <c r="C351" s="3">
-        <v>461.23</v>
+        <v>518.41999999999996</v>
       </c>
       <c r="D351" s="4" t="s">
         <v>357</v>
@@ -6792,13 +6789,13 @@
     </row>
     <row r="352" spans="1:4">
       <c r="A352" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B352" s="3">
         <v>1</v>
       </c>
       <c r="C352" s="3">
-        <v>518.41999999999996</v>
+        <v>348.08</v>
       </c>
       <c r="D352" s="4" t="s">
         <v>357</v>
@@ -6806,13 +6803,13 @@
     </row>
     <row r="353" spans="1:4">
       <c r="A353" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B353" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C353" s="3">
-        <v>348.08</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D353" s="4" t="s">
         <v>357</v>
@@ -6820,13 +6817,13 @@
     </row>
     <row r="354" spans="1:4">
       <c r="A354" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B354" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C354" s="3">
-        <v>33.479999999999997</v>
+        <v>35.79</v>
       </c>
       <c r="D354" s="4" t="s">
         <v>357</v>
@@ -6834,13 +6831,13 @@
     </row>
     <row r="355" spans="1:4">
       <c r="A355" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B355" s="3">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C355" s="3">
-        <v>35.79</v>
+        <v>377.7</v>
       </c>
       <c r="D355" s="4" t="s">
         <v>357</v>
@@ -6848,13 +6845,13 @@
     </row>
     <row r="356" spans="1:4">
       <c r="A356" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B356" s="3">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C356" s="3">
-        <v>377.7</v>
+        <v>33.21</v>
       </c>
       <c r="D356" s="4" t="s">
         <v>357</v>
@@ -6862,13 +6859,13 @@
     </row>
     <row r="357" spans="1:4">
       <c r="A357" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B357" s="3">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C357" s="3">
-        <v>33.21</v>
+        <v>27.16</v>
       </c>
       <c r="D357" s="4" t="s">
         <v>357</v>
@@ -6876,13 +6873,13 @@
     </row>
     <row r="358" spans="1:4">
       <c r="A358" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B358" s="3">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="C358" s="3">
-        <v>27.16</v>
+        <v>361.41</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>357</v>
@@ -6890,13 +6887,13 @@
     </row>
     <row r="359" spans="1:4">
       <c r="A359" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B359" s="3">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="C359" s="3">
-        <v>361.41</v>
+        <v>29.25</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>357</v>
@@ -6904,13 +6901,13 @@
     </row>
     <row r="360" spans="1:4">
       <c r="A360" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B360" s="3">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="C360" s="3">
-        <v>29.25</v>
+        <v>304.54000000000002</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>357</v>
@@ -6918,13 +6915,13 @@
     </row>
     <row r="361" spans="1:4">
       <c r="A361" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B361" s="3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C361" s="3">
-        <v>304.54000000000002</v>
+        <v>34.049999999999997</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>357</v>
@@ -6932,55 +6929,55 @@
     </row>
     <row r="362" spans="1:4">
       <c r="A362" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B362" s="3">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C362" s="3">
-        <v>34.049999999999997</v>
+        <v>57.7</v>
       </c>
       <c r="D362" s="4" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
     </row>
     <row r="363" spans="1:4">
       <c r="A363" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B363" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C363" s="3">
-        <v>57.7</v>
+        <v>90.9</v>
       </c>
       <c r="D363" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="364" spans="1:4">
       <c r="A364" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B364" s="3">
-        <v>10</v>
+        <v>221</v>
       </c>
       <c r="C364" s="3">
-        <v>90.9</v>
+        <v>47.62</v>
       </c>
       <c r="D364" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="365" spans="1:4">
       <c r="A365" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B365" s="3">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="C365" s="3">
-        <v>47.62</v>
+        <v>7173.59</v>
       </c>
       <c r="D365" s="4" t="s">
         <v>364</v>
@@ -6988,13 +6985,13 @@
     </row>
     <row r="366" spans="1:4">
       <c r="A366" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B366" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C366" s="3">
-        <v>7173.59</v>
+        <v>677.79</v>
       </c>
       <c r="D366" s="4" t="s">
         <v>364</v>
@@ -7002,13 +6999,13 @@
     </row>
     <row r="367" spans="1:4">
       <c r="A367" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B367" s="3">
-        <v>1</v>
-      </c>
-      <c r="C367" s="3">
-        <v>677.79</v>
+        <v>3</v>
+      </c>
+      <c r="C367" s="8">
+        <v>171.47</v>
       </c>
       <c r="D367" s="4" t="s">
         <v>364</v>
@@ -7016,13 +7013,13 @@
     </row>
     <row r="368" spans="1:4">
       <c r="A368" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B368" s="3">
-        <v>3</v>
-      </c>
-      <c r="C368" s="8">
-        <v>171.47</v>
+        <v>70</v>
+      </c>
+      <c r="C368" s="3">
+        <v>212.75</v>
       </c>
       <c r="D368" s="4" t="s">
         <v>364</v>
@@ -7030,13 +7027,13 @@
     </row>
     <row r="369" spans="1:4">
       <c r="A369" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B369" s="3">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="C369" s="3">
-        <v>212.75</v>
+        <v>2335.67</v>
       </c>
       <c r="D369" s="4" t="s">
         <v>364</v>
@@ -7044,13 +7041,13 @@
     </row>
     <row r="370" spans="1:4">
       <c r="A370" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B370" s="3">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C370" s="3">
-        <v>2335.67</v>
+        <v>66.180000000000007</v>
       </c>
       <c r="D370" s="4" t="s">
         <v>364</v>
@@ -7058,13 +7055,13 @@
     </row>
     <row r="371" spans="1:4">
       <c r="A371" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B371" s="3">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C371" s="3">
-        <v>66.180000000000007</v>
+        <v>8139.6</v>
       </c>
       <c r="D371" s="4" t="s">
         <v>364</v>
@@ -7072,13 +7069,13 @@
     </row>
     <row r="372" spans="1:4">
       <c r="A372" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B372" s="3">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C372" s="3">
-        <v>8139.6</v>
+        <v>259.81</v>
       </c>
       <c r="D372" s="4" t="s">
         <v>364</v>
@@ -7086,13 +7083,13 @@
     </row>
     <row r="373" spans="1:4">
       <c r="A373" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B373" s="3">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="C373" s="3">
-        <v>259.81</v>
+        <v>259.8</v>
       </c>
       <c r="D373" s="4" t="s">
         <v>364</v>
@@ -7100,13 +7097,13 @@
     </row>
     <row r="374" spans="1:4">
       <c r="A374" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B374" s="3">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="C374" s="3">
-        <v>259.8</v>
+        <v>310.2</v>
       </c>
       <c r="D374" s="4" t="s">
         <v>364</v>
@@ -7114,13 +7111,13 @@
     </row>
     <row r="375" spans="1:4">
       <c r="A375" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B375" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C375" s="3">
-        <v>310.2</v>
+        <v>36.43</v>
       </c>
       <c r="D375" s="4" t="s">
         <v>364</v>
@@ -7128,13 +7125,13 @@
     </row>
     <row r="376" spans="1:4">
       <c r="A376" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B376" s="3">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C376" s="3">
-        <v>36.43</v>
+        <v>87.22</v>
       </c>
       <c r="D376" s="4" t="s">
         <v>364</v>
@@ -7142,13 +7139,13 @@
     </row>
     <row r="377" spans="1:4">
       <c r="A377" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B377" s="3">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C377" s="3">
-        <v>87.22</v>
+        <v>319.60000000000002</v>
       </c>
       <c r="D377" s="4" t="s">
         <v>364</v>
@@ -7156,13 +7153,13 @@
     </row>
     <row r="378" spans="1:4">
       <c r="A378" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B378" s="3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C378" s="3">
-        <v>319.60000000000002</v>
+        <v>62.6</v>
       </c>
       <c r="D378" s="4" t="s">
         <v>364</v>
@@ -7170,13 +7167,13 @@
     </row>
     <row r="379" spans="1:4">
       <c r="A379" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B379" s="3">
-        <v>14</v>
-      </c>
-      <c r="C379" s="3">
-        <v>62.6</v>
+        <v>8</v>
+      </c>
+      <c r="C379" s="8">
+        <v>385.25</v>
       </c>
       <c r="D379" s="4" t="s">
         <v>364</v>
@@ -7184,27 +7181,27 @@
     </row>
     <row r="380" spans="1:4">
       <c r="A380" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B380" s="3">
-        <v>8</v>
-      </c>
-      <c r="C380" s="8">
-        <v>385.25</v>
+        <v>28</v>
+      </c>
+      <c r="C380" s="3">
+        <v>67.28</v>
       </c>
       <c r="D380" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="381" spans="1:4">
       <c r="A381" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B381" s="3">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="C381" s="3">
-        <v>67.28</v>
+        <v>1138.5</v>
       </c>
       <c r="D381" s="4" t="s">
         <v>367</v>
@@ -7212,27 +7209,27 @@
     </row>
     <row r="382" spans="1:4">
       <c r="A382" t="s">
-        <v>319</v>
+        <v>350</v>
       </c>
       <c r="B382" s="3">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C382" s="3">
-        <v>1138.5</v>
+        <v>58.69</v>
       </c>
       <c r="D382" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="383" spans="1:4">
       <c r="A383" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B383" s="3">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C383" s="3">
-        <v>58.69</v>
+        <v>289.33999999999997</v>
       </c>
       <c r="D383" s="4" t="s">
         <v>364</v>
@@ -7240,13 +7237,13 @@
     </row>
     <row r="384" spans="1:4">
       <c r="A384" t="s">
-        <v>351</v>
+        <v>320</v>
       </c>
       <c r="B384" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C384" s="3">
-        <v>289.33999999999997</v>
+        <v>48.76</v>
       </c>
       <c r="D384" s="4" t="s">
         <v>364</v>
@@ -7254,13 +7251,13 @@
     </row>
     <row r="385" spans="1:4">
       <c r="A385" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B385" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C385" s="3">
-        <v>48.76</v>
+        <v>242.34</v>
       </c>
       <c r="D385" s="4" t="s">
         <v>364</v>
@@ -7268,13 +7265,13 @@
     </row>
     <row r="386" spans="1:4">
       <c r="A386" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B386" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C386" s="3">
-        <v>242.34</v>
+        <v>65.599999999999994</v>
       </c>
       <c r="D386" s="4" t="s">
         <v>364</v>
@@ -7282,13 +7279,13 @@
     </row>
     <row r="387" spans="1:4">
       <c r="A387" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B387" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C387" s="3">
-        <v>65.599999999999994</v>
+        <v>255.03</v>
       </c>
       <c r="D387" s="4" t="s">
         <v>364</v>
@@ -7296,13 +7293,13 @@
     </row>
     <row r="388" spans="1:4">
       <c r="A388" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B388" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C388" s="3">
-        <v>255.03</v>
+        <v>220.8</v>
       </c>
       <c r="D388" s="4" t="s">
         <v>364</v>
@@ -7310,13 +7307,13 @@
     </row>
     <row r="389" spans="1:4">
       <c r="A389" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B389" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C389" s="3">
-        <v>220.8</v>
+        <v>255.02</v>
       </c>
       <c r="D389" s="4" t="s">
         <v>364</v>
@@ -7324,13 +7321,13 @@
     </row>
     <row r="390" spans="1:4">
       <c r="A390" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B390" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C390" s="3">
-        <v>255.02</v>
+        <v>68.86</v>
       </c>
       <c r="D390" s="4" t="s">
         <v>364</v>
@@ -7338,13 +7335,13 @@
     </row>
     <row r="391" spans="1:4">
       <c r="A391" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B391" s="3">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C391" s="3">
-        <v>68.86</v>
+        <v>344.28</v>
       </c>
       <c r="D391" s="4" t="s">
         <v>364</v>
@@ -7352,13 +7349,13 @@
     </row>
     <row r="392" spans="1:4">
       <c r="A392" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B392" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C392" s="3">
-        <v>344.28</v>
+        <v>60.29</v>
       </c>
       <c r="D392" s="4" t="s">
         <v>364</v>
@@ -7366,13 +7363,13 @@
     </row>
     <row r="393" spans="1:4">
       <c r="A393" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B393" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C393" s="3">
-        <v>60.29</v>
+        <v>261.8</v>
       </c>
       <c r="D393" s="4" t="s">
         <v>364</v>
@@ -7380,55 +7377,55 @@
     </row>
     <row r="394" spans="1:4">
       <c r="A394" t="s">
-        <v>329</v>
+        <v>382</v>
       </c>
       <c r="B394" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C394" s="3">
-        <v>261.8</v>
+        <v>30.58</v>
       </c>
       <c r="D394" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="395" spans="1:4">
       <c r="A395" t="s">
-        <v>382</v>
+        <v>330</v>
       </c>
       <c r="B395" s="3">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="C395" s="3">
-        <v>30.58</v>
+        <v>16.95</v>
       </c>
       <c r="D395" s="4" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
     </row>
     <row r="396" spans="1:4">
       <c r="A396" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B396" s="3">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="C396" s="3">
-        <v>16.95</v>
+        <v>24.95</v>
       </c>
       <c r="D396" s="4" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
     </row>
     <row r="397" spans="1:4">
       <c r="A397" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B397" s="3">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="C397" s="3">
-        <v>24.95</v>
+        <v>641.49</v>
       </c>
       <c r="D397" s="4" t="s">
         <v>367</v>
@@ -7436,13 +7433,13 @@
     </row>
     <row r="398" spans="1:4">
       <c r="A398" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B398" s="3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C398" s="3">
-        <v>641.49</v>
+        <v>39.57</v>
       </c>
       <c r="D398" s="4" t="s">
         <v>367</v>
@@ -7450,13 +7447,13 @@
     </row>
     <row r="399" spans="1:4">
       <c r="A399" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B399" s="3">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C399" s="3">
-        <v>39.57</v>
+        <v>51.83</v>
       </c>
       <c r="D399" s="4" t="s">
         <v>367</v>
@@ -7464,27 +7461,27 @@
     </row>
     <row r="400" spans="1:4">
       <c r="A400" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B400" s="3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C400" s="3">
-        <v>51.83</v>
+        <v>33.840000000000003</v>
       </c>
       <c r="D400" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="401" spans="1:4">
       <c r="A401" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B401" s="3">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="C401" s="3">
-        <v>33.840000000000003</v>
+        <v>150.15</v>
       </c>
       <c r="D401" s="4" t="s">
         <v>364</v>
@@ -7492,13 +7489,13 @@
     </row>
     <row r="402" spans="1:4">
       <c r="A402" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B402" s="3">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C402" s="3">
-        <v>150.15</v>
+        <v>144.5</v>
       </c>
       <c r="D402" s="4" t="s">
         <v>364</v>
@@ -7506,13 +7503,13 @@
     </row>
     <row r="403" spans="1:4">
       <c r="A403" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B403" s="3">
         <v>25</v>
       </c>
       <c r="C403" s="3">
-        <v>144.5</v>
+        <v>100.93</v>
       </c>
       <c r="D403" s="4" t="s">
         <v>364</v>
@@ -7520,13 +7517,13 @@
     </row>
     <row r="404" spans="1:4">
       <c r="A404" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B404" s="3">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C404" s="3">
-        <v>100.93</v>
+        <v>124.5</v>
       </c>
       <c r="D404" s="4" t="s">
         <v>364</v>
@@ -7534,13 +7531,13 @@
     </row>
     <row r="405" spans="1:4">
       <c r="A405" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B405" s="3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C405" s="3">
-        <v>124.5</v>
+        <v>27.21</v>
       </c>
       <c r="D405" s="4" t="s">
         <v>364</v>
@@ -7548,41 +7545,41 @@
     </row>
     <row r="406" spans="1:4">
       <c r="A406" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B406" s="3">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="C406" s="3">
-        <v>27.21</v>
+        <v>24.79</v>
       </c>
       <c r="D406" s="4" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
     </row>
     <row r="407" spans="1:4">
       <c r="A407" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B407" s="3">
-        <v>94</v>
+        <v>6</v>
       </c>
       <c r="C407" s="3">
-        <v>24.79</v>
+        <v>37.1</v>
       </c>
       <c r="D407" s="4" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
     </row>
     <row r="408" spans="1:4">
       <c r="A408" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B408" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C408" s="3">
-        <v>37.1</v>
+        <v>178.04</v>
       </c>
       <c r="D408" s="4" t="s">
         <v>364</v>
@@ -7590,41 +7587,41 @@
     </row>
     <row r="409" spans="1:4">
       <c r="A409" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B409" s="3">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="C409" s="3">
-        <v>178.04</v>
+        <v>23.88</v>
       </c>
       <c r="D409" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="410" spans="1:4">
       <c r="A410" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B410" s="3">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="C410" s="3">
-        <v>23.88</v>
+        <v>20.68</v>
       </c>
       <c r="D410" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="411" spans="1:4">
       <c r="A411" t="s">
-        <v>345</v>
+        <v>372</v>
       </c>
       <c r="B411" s="3">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="C411" s="3">
-        <v>20.68</v>
+        <v>97.54</v>
       </c>
       <c r="D411" s="4" t="s">
         <v>364</v>
@@ -7632,13 +7629,13 @@
     </row>
     <row r="412" spans="1:4">
       <c r="A412" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B412" s="3">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C412" s="3">
-        <v>97.54</v>
+        <v>304.02999999999997</v>
       </c>
       <c r="D412" s="4" t="s">
         <v>364</v>
@@ -7646,27 +7643,27 @@
     </row>
     <row r="413" spans="1:4">
       <c r="A413" t="s">
-        <v>373</v>
+        <v>346</v>
       </c>
       <c r="B413" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C413" s="3">
-        <v>304.02999999999997</v>
+        <v>1934.56</v>
       </c>
       <c r="D413" s="4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="414" spans="1:4">
       <c r="A414" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B414" s="3">
         <v>0</v>
       </c>
       <c r="C414" s="3">
-        <v>1934.56</v>
+        <v>230.99</v>
       </c>
       <c r="D414" s="4" t="s">
         <v>368</v>
@@ -7674,55 +7671,55 @@
     </row>
     <row r="415" spans="1:4">
       <c r="A415" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B415" s="3">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="C415" s="3">
-        <v>230.99</v>
+        <v>33.39</v>
       </c>
       <c r="D415" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="416" spans="1:4">
       <c r="A416" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B416" s="3">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="C416" s="3">
-        <v>33.39</v>
+        <v>20.66</v>
       </c>
       <c r="D416" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="417" spans="1:4">
       <c r="A417" t="s">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="B417" s="3">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="C417" s="3">
-        <v>20.66</v>
+        <v>97.5</v>
       </c>
       <c r="D417" s="4" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
     </row>
     <row r="418" spans="1:4">
       <c r="A418" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B418" s="3">
-        <v>76</v>
+        <v>410</v>
       </c>
       <c r="C418" s="3">
-        <v>97.5</v>
+        <v>24.7</v>
       </c>
       <c r="D418" s="4" t="s">
         <v>374</v>
@@ -7730,13 +7727,13 @@
     </row>
     <row r="419" spans="1:4">
       <c r="A419" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B419" s="3">
-        <v>410</v>
+        <v>448</v>
       </c>
       <c r="C419" s="3">
-        <v>24.7</v>
+        <v>35.75</v>
       </c>
       <c r="D419" s="4" t="s">
         <v>374</v>
@@ -7744,13 +7741,13 @@
     </row>
     <row r="420" spans="1:4">
       <c r="A420" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B420" s="3">
-        <v>448</v>
+        <v>150</v>
       </c>
       <c r="C420" s="3">
-        <v>35.75</v>
+        <v>9.1</v>
       </c>
       <c r="D420" s="4" t="s">
         <v>374</v>
@@ -7758,13 +7755,13 @@
     </row>
     <row r="421" spans="1:4">
       <c r="A421" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B421" s="3">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C421" s="3">
-        <v>9.1</v>
+        <v>5.43</v>
       </c>
       <c r="D421" s="4" t="s">
         <v>374</v>
@@ -7772,13 +7769,13 @@
     </row>
     <row r="422" spans="1:4">
       <c r="A422" t="s">
-        <v>379</v>
+        <v>432</v>
       </c>
       <c r="B422" s="3">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="C422" s="3">
-        <v>5.43</v>
+        <v>11.99</v>
       </c>
       <c r="D422" s="4" t="s">
         <v>374</v>
@@ -7786,27 +7783,27 @@
     </row>
     <row r="423" spans="1:4">
       <c r="A423" t="s">
-        <v>432</v>
+        <v>414</v>
       </c>
       <c r="B423" s="3">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="C423" s="3">
-        <v>11.99</v>
+        <v>9.75</v>
       </c>
       <c r="D423" s="4" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
     </row>
     <row r="424" spans="1:4">
       <c r="A424" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B424" s="3">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C424" s="3">
-        <v>9.75</v>
+        <v>6.37</v>
       </c>
       <c r="D424" s="4" t="s">
         <v>380</v>
@@ -7814,13 +7811,13 @@
     </row>
     <row r="425" spans="1:4">
       <c r="A425" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="B425" s="3">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C425" s="3">
-        <v>6.37</v>
+        <v>10.53</v>
       </c>
       <c r="D425" s="4" t="s">
         <v>380</v>
@@ -7828,27 +7825,27 @@
     </row>
     <row r="426" spans="1:4">
       <c r="A426" t="s">
-        <v>433</v>
+        <v>416</v>
       </c>
       <c r="B426" s="3">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C426" s="3">
-        <v>10.53</v>
+        <v>11.59</v>
       </c>
       <c r="D426" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="427" spans="1:4">
       <c r="A427" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="B427" s="3">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C427" s="3">
-        <v>11.59</v>
+        <v>12.09</v>
       </c>
       <c r="D427" s="4" t="s">
         <v>381</v>
@@ -7856,10 +7853,10 @@
     </row>
     <row r="428" spans="1:4">
       <c r="A428" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B428" s="3">
-        <v>36</v>
+        <v>230</v>
       </c>
       <c r="C428" s="3">
         <v>12.09</v>
@@ -7870,13 +7867,13 @@
     </row>
     <row r="429" spans="1:4">
       <c r="A429" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B429" s="3">
-        <v>230</v>
+        <v>201</v>
       </c>
       <c r="C429" s="3">
-        <v>12.09</v>
+        <v>6.5</v>
       </c>
       <c r="D429" s="4" t="s">
         <v>381</v>
@@ -7884,10 +7881,10 @@
     </row>
     <row r="430" spans="1:4">
       <c r="A430" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B430" s="3">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="C430" s="3">
         <v>6.5</v>
@@ -7898,27 +7895,27 @@
     </row>
     <row r="431" spans="1:4">
       <c r="A431" t="s">
-        <v>437</v>
+        <v>453</v>
       </c>
       <c r="B431" s="3">
-        <v>188</v>
+        <v>2</v>
       </c>
       <c r="C431" s="3">
-        <v>6.5</v>
+        <v>5017</v>
       </c>
       <c r="D431" s="4" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
     </row>
     <row r="432" spans="1:4">
       <c r="A432" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B432" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C432" s="3">
-        <v>5017</v>
+        <v>4437.1499999999996</v>
       </c>
       <c r="D432" s="4" t="s">
         <v>364</v>
@@ -7926,13 +7923,13 @@
     </row>
     <row r="433" spans="1:4">
       <c r="A433" t="s">
-        <v>454</v>
+        <v>429</v>
       </c>
       <c r="B433" s="3">
         <v>7</v>
       </c>
       <c r="C433" s="3">
-        <v>4437.1499999999996</v>
+        <v>6239.83</v>
       </c>
       <c r="D433" s="4" t="s">
         <v>364</v>
@@ -7940,13 +7937,13 @@
     </row>
     <row r="434" spans="1:4">
       <c r="A434" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="B434" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C434" s="3">
-        <v>6239.83</v>
+        <v>5980</v>
       </c>
       <c r="D434" s="4" t="s">
         <v>364</v>
@@ -7954,13 +7951,13 @@
     </row>
     <row r="435" spans="1:4">
       <c r="A435" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="B435" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C435" s="3">
-        <v>5980</v>
+        <v>3556.4</v>
       </c>
       <c r="D435" s="4" t="s">
         <v>364</v>
@@ -7968,13 +7965,13 @@
     </row>
     <row r="436" spans="1:4">
       <c r="A436" t="s">
-        <v>428</v>
+        <v>451</v>
       </c>
       <c r="B436" s="3">
         <v>2</v>
       </c>
       <c r="C436" s="3">
-        <v>3556.4</v>
+        <v>6463</v>
       </c>
       <c r="D436" s="4" t="s">
         <v>364</v>
@@ -7982,13 +7979,13 @@
     </row>
     <row r="437" spans="1:4">
       <c r="A437" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B437" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C437" s="3">
-        <v>6463</v>
+        <v>5199</v>
       </c>
       <c r="D437" s="4" t="s">
         <v>364</v>
@@ -7996,27 +7993,27 @@
     </row>
     <row r="438" spans="1:4">
       <c r="A438" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="B438" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C438" s="3">
-        <v>5199</v>
+        <v>58.68</v>
       </c>
       <c r="D438" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="439" spans="1:4">
       <c r="A439" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B439" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C439" s="3">
-        <v>58.68</v>
+        <v>70.25</v>
       </c>
       <c r="D439" s="4" t="s">
         <v>367</v>
@@ -8024,21 +8021,21 @@
     </row>
     <row r="440" spans="1:4">
       <c r="A440" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B440" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C440" s="3">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="D440" s="4" t="s">
-        <v>367</v>
+        <v>455</v>
       </c>
     </row>
     <row r="441" spans="1:4">
       <c r="A441" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="B441" s="3">
         <v>10</v>
@@ -8052,27 +8049,27 @@
     </row>
     <row r="442" spans="1:4">
       <c r="A442" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B442" s="3">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="C442" s="3">
-        <v>45</v>
+        <v>58.9</v>
       </c>
       <c r="D442" s="4" t="s">
-        <v>455</v>
+        <v>367</v>
       </c>
     </row>
     <row r="443" spans="1:4">
       <c r="A443" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B443" s="3">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="C443" s="3">
-        <v>70.25</v>
+        <v>89.21</v>
       </c>
       <c r="D443" s="4" t="s">
         <v>367</v>
@@ -8080,13 +8077,13 @@
     </row>
     <row r="444" spans="1:4">
       <c r="A444" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B444" s="3">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C444" s="3">
-        <v>58.9</v>
+        <v>59.18</v>
       </c>
       <c r="D444" s="4" t="s">
         <v>367</v>
@@ -8094,13 +8091,13 @@
     </row>
     <row r="445" spans="1:4">
       <c r="A445" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B445" s="3">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C445" s="3">
-        <v>89.21</v>
+        <v>60.62</v>
       </c>
       <c r="D445" s="4" t="s">
         <v>367</v>
@@ -8108,13 +8105,13 @@
     </row>
     <row r="446" spans="1:4">
       <c r="A446" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B446" s="3">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="C446" s="3">
-        <v>59.18</v>
+        <v>3431.7</v>
       </c>
       <c r="D446" s="4" t="s">
         <v>367</v>
@@ -8122,13 +8119,13 @@
     </row>
     <row r="447" spans="1:4">
       <c r="A447" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B447" s="3">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="C447" s="3">
-        <v>60.62</v>
+        <v>1260.2</v>
       </c>
       <c r="D447" s="4" t="s">
         <v>367</v>
@@ -8136,43 +8133,15 @@
     </row>
     <row r="448" spans="1:4">
       <c r="A448" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B448" s="3">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C448" s="3">
-        <v>3431.7</v>
+        <v>47.2</v>
       </c>
       <c r="D448" s="4" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="449" spans="1:4">
-      <c r="A449" t="s">
-        <v>465</v>
-      </c>
-      <c r="B449" s="3">
-        <v>3</v>
-      </c>
-      <c r="C449" s="3">
-        <v>1260.2</v>
-      </c>
-      <c r="D449" s="4" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="450" spans="1:4">
-      <c r="A450" t="s">
-        <v>466</v>
-      </c>
-      <c r="B450" s="3">
-        <v>56</v>
-      </c>
-      <c r="C450" s="3">
-        <v>47.2</v>
-      </c>
-      <c r="D450" s="4" t="s">
         <v>367</v>
       </c>
     </row>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -5966,7 +5966,7 @@
         <v>234</v>
       </c>
       <c r="B293" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C293" s="3">
         <v>182.42</v>
@@ -7100,7 +7100,7 @@
         <v>312</v>
       </c>
       <c r="B374" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C374" s="3">
         <v>310.2</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -2214,7 +2214,7 @@
         <v>401</v>
       </c>
       <c r="B25" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C25" s="3">
         <v>376.62</v>
@@ -2242,7 +2242,7 @@
         <v>403</v>
       </c>
       <c r="B27" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C27" s="3">
         <v>442.81</v>
@@ -2620,7 +2620,7 @@
         <v>20</v>
       </c>
       <c r="B54" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C54" s="3">
         <v>33.64</v>
@@ -4146,7 +4146,7 @@
         <v>113</v>
       </c>
       <c r="B163" s="3">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C163" s="3">
         <v>32.200000000000003</v>
@@ -4328,7 +4328,7 @@
         <v>126</v>
       </c>
       <c r="B176" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C176" s="3">
         <v>38.770000000000003</v>
@@ -4538,7 +4538,7 @@
         <v>140</v>
       </c>
       <c r="B191" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C191" s="3">
         <v>35.81</v>
@@ -5014,7 +5014,7 @@
         <v>172</v>
       </c>
       <c r="B225" s="3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C225" s="3">
         <v>37.299999999999997</v>
@@ -5028,7 +5028,7 @@
         <v>173</v>
       </c>
       <c r="B226" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C226" s="3">
         <v>126.24</v>
@@ -5980,7 +5980,7 @@
         <v>235</v>
       </c>
       <c r="B294" s="3">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C294" s="3">
         <v>222.62</v>
@@ -7002,7 +7002,7 @@
         <v>305</v>
       </c>
       <c r="B367" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C367" s="8">
         <v>171.47</v>
@@ -7016,7 +7016,7 @@
         <v>306</v>
       </c>
       <c r="B368" s="3">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C368" s="3">
         <v>212.75</v>
@@ -7100,7 +7100,7 @@
         <v>312</v>
       </c>
       <c r="B374" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C374" s="3">
         <v>310.2</v>
@@ -8024,7 +8024,7 @@
         <v>456</v>
       </c>
       <c r="B440" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C440" s="3">
         <v>45</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -4762,7 +4762,7 @@
         <v>155</v>
       </c>
       <c r="B207" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C207" s="3">
         <v>145.94</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="470">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -1421,6 +1421,9 @@
   </si>
   <si>
     <t>CEMSA robinet 3/4</t>
+  </si>
+  <si>
+    <t>FUCHS TITAN FFL-52529 1L ulei DCT-LV</t>
   </si>
 </sst>
 </file>
@@ -1865,7 +1868,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D448"/>
+  <dimension ref="A1:D449"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="49.85546875" customWidth="1"/>
@@ -8145,6 +8148,20 @@
         <v>367</v>
       </c>
     </row>
+    <row r="449" spans="1:4">
+      <c r="A449" t="s">
+        <v>469</v>
+      </c>
+      <c r="B449" s="3">
+        <v>60</v>
+      </c>
+      <c r="C449" s="3">
+        <v>71.760000000000005</v>
+      </c>
+      <c r="D449" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -1965,7 +1965,7 @@
         <v>393</v>
       </c>
       <c r="B7" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="3">
         <v>407.86</v>
@@ -2105,7 +2105,7 @@
         <v>7</v>
       </c>
       <c r="B17" s="3">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C17" s="3">
         <v>909.67</v>
@@ -2287,7 +2287,7 @@
         <v>422</v>
       </c>
       <c r="B30" s="3">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="C30" s="3">
         <v>45.19</v>
@@ -2329,7 +2329,7 @@
         <v>423</v>
       </c>
       <c r="B33" s="3">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="C33" s="3">
         <v>207.95</v>
@@ -2511,7 +2511,7 @@
         <v>13</v>
       </c>
       <c r="B46" s="3">
-        <v>1753</v>
+        <v>1741</v>
       </c>
       <c r="C46" s="3">
         <v>13</v>
@@ -2721,7 +2721,7 @@
         <v>440</v>
       </c>
       <c r="B61" s="3">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C61" s="3">
         <v>135.29</v>
@@ -2749,7 +2749,7 @@
         <v>26</v>
       </c>
       <c r="B63" s="3">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C63" s="3">
         <v>101.08</v>
@@ -2847,7 +2847,7 @@
         <v>32</v>
       </c>
       <c r="B70" s="3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C70" s="3">
         <v>87.12</v>
@@ -2875,7 +2875,7 @@
         <v>33</v>
       </c>
       <c r="B72" s="3">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C72" s="3">
         <v>18.96</v>
@@ -2987,7 +2987,7 @@
         <v>443</v>
       </c>
       <c r="B80" s="3">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C80" s="3">
         <v>19.48</v>
@@ -3001,7 +3001,7 @@
         <v>444</v>
       </c>
       <c r="B81" s="3">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C81" s="3">
         <v>70.72</v>
@@ -3029,7 +3029,7 @@
         <v>446</v>
       </c>
       <c r="B83" s="3">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C83" s="3">
         <v>22.21</v>
@@ -3183,7 +3183,7 @@
         <v>49</v>
       </c>
       <c r="B94" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C94" s="3">
         <v>65.83</v>
@@ -3687,7 +3687,7 @@
         <v>83</v>
       </c>
       <c r="B130" s="3">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C130" s="3">
         <v>67.27</v>
@@ -4401,7 +4401,7 @@
         <v>131</v>
       </c>
       <c r="B181" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C181" s="3">
         <v>75.989999999999995</v>
@@ -4415,7 +4415,7 @@
         <v>132</v>
       </c>
       <c r="B182" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C182" s="3">
         <v>297.64999999999998</v>
@@ -4555,7 +4555,7 @@
         <v>141</v>
       </c>
       <c r="B192" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C192" s="3">
         <v>59.25</v>
@@ -4863,7 +4863,7 @@
         <v>161</v>
       </c>
       <c r="B214" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C214" s="3">
         <v>48.13</v>
@@ -5017,7 +5017,7 @@
         <v>172</v>
       </c>
       <c r="B225" s="3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C225" s="3">
         <v>37.299999999999997</v>
@@ -5031,7 +5031,7 @@
         <v>173</v>
       </c>
       <c r="B226" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C226" s="3">
         <v>126.24</v>
@@ -5269,7 +5269,7 @@
         <v>188</v>
       </c>
       <c r="B243" s="3">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C243" s="8">
         <v>79.599999999999994</v>
@@ -5563,7 +5563,7 @@
         <v>421</v>
       </c>
       <c r="B264" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C264" s="3">
         <v>29.63</v>
@@ -5941,7 +5941,7 @@
         <v>232</v>
       </c>
       <c r="B291" s="3">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C291" s="3">
         <v>51.15</v>
@@ -5997,7 +5997,7 @@
         <v>236</v>
       </c>
       <c r="B295" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C295" s="3">
         <v>2314.8000000000002</v>
@@ -6655,7 +6655,7 @@
         <v>281</v>
       </c>
       <c r="B342" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C342" s="3">
         <v>370.53</v>
@@ -6963,7 +6963,7 @@
         <v>302</v>
       </c>
       <c r="B364" s="3">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C364" s="3">
         <v>47.62</v>
@@ -7019,7 +7019,7 @@
         <v>306</v>
       </c>
       <c r="B368" s="3">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C368" s="3">
         <v>212.75</v>
@@ -7411,7 +7411,7 @@
         <v>331</v>
       </c>
       <c r="B396" s="3">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C396" s="3">
         <v>24.95</v>
@@ -7705,7 +7705,7 @@
         <v>375</v>
       </c>
       <c r="B417" s="3">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C417" s="3">
         <v>97.5</v>
@@ -7719,7 +7719,7 @@
         <v>376</v>
       </c>
       <c r="B418" s="3">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C418" s="3">
         <v>24.7</v>
@@ -7733,7 +7733,7 @@
         <v>377</v>
       </c>
       <c r="B419" s="3">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="C419" s="3">
         <v>35.75</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -4751,7 +4751,7 @@
         <v>154</v>
       </c>
       <c r="B206" s="3">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C206" s="3">
         <v>44.51</v>
@@ -4765,7 +4765,7 @@
         <v>155</v>
       </c>
       <c r="B207" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C207" s="3">
         <v>145.94</v>
@@ -4779,7 +4779,7 @@
         <v>156</v>
       </c>
       <c r="B208" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C208" s="3">
         <v>199.77</v>
@@ -4807,7 +4807,7 @@
         <v>158</v>
       </c>
       <c r="B210" s="3">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C210" s="8">
         <v>58.32</v>
@@ -4835,7 +4835,7 @@
         <v>352</v>
       </c>
       <c r="B212" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C212" s="8">
         <v>257.70999999999998</v>
@@ -5031,7 +5031,7 @@
         <v>173</v>
       </c>
       <c r="B226" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C226" s="3">
         <v>126.24</v>
@@ -7005,7 +7005,7 @@
         <v>305</v>
       </c>
       <c r="B367" s="3">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C367" s="8">
         <v>171.47</v>
@@ -7103,7 +7103,7 @@
         <v>312</v>
       </c>
       <c r="B374" s="3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C374" s="3">
         <v>310.2</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="469">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -1358,9 +1358,6 @@
   </si>
   <si>
     <t>MAX X-100</t>
-  </si>
-  <si>
-    <t>FUCHS TITAN ATF 6006 (6HP) 1L</t>
   </si>
   <si>
     <t>FUCHS TITAN ATF 4134 (M9-G) 1L</t>
@@ -1868,7 +1865,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D449"/>
+  <dimension ref="A1:D448"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="49.85546875" customWidth="1"/>
@@ -1993,7 +1990,7 @@
         <v>394</v>
       </c>
       <c r="B9" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C9" s="3">
         <v>309.52</v>
@@ -2007,7 +2004,7 @@
         <v>395</v>
       </c>
       <c r="B10" s="3">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C10" s="3">
         <v>343.45</v>
@@ -2217,7 +2214,7 @@
         <v>401</v>
       </c>
       <c r="B25" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C25" s="3">
         <v>376.62</v>
@@ -2287,7 +2284,7 @@
         <v>422</v>
       </c>
       <c r="B30" s="3">
-        <v>425</v>
+        <v>401</v>
       </c>
       <c r="C30" s="3">
         <v>45.19</v>
@@ -2301,7 +2298,7 @@
         <v>8</v>
       </c>
       <c r="B31" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C31" s="3">
         <v>5899.25</v>
@@ -2329,7 +2326,7 @@
         <v>423</v>
       </c>
       <c r="B33" s="3">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C33" s="3">
         <v>207.95</v>
@@ -2357,7 +2354,7 @@
         <v>425</v>
       </c>
       <c r="B35" s="3">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="C35" s="3">
         <v>42.7</v>
@@ -2410,7 +2407,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B39" s="3">
         <v>82</v>
@@ -2452,7 +2449,7 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B42" s="3">
         <v>6</v>
@@ -2466,7 +2463,7 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B43" s="3">
         <v>6</v>
@@ -2480,7 +2477,7 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B44" s="3">
         <v>6</v>
@@ -2511,7 +2508,7 @@
         <v>13</v>
       </c>
       <c r="B46" s="3">
-        <v>1741</v>
+        <v>1729</v>
       </c>
       <c r="C46" s="3">
         <v>13</v>
@@ -2567,7 +2564,7 @@
         <v>16</v>
       </c>
       <c r="B50" s="3">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C50" s="3">
         <v>21</v>
@@ -2665,7 +2662,7 @@
         <v>417</v>
       </c>
       <c r="B57" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C57" s="3">
         <v>144.84</v>
@@ -2693,7 +2690,7 @@
         <v>23</v>
       </c>
       <c r="B59" s="3">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C59" s="3">
         <v>255</v>
@@ -2721,7 +2718,7 @@
         <v>440</v>
       </c>
       <c r="B61" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C61" s="3">
         <v>135.29</v>
@@ -2735,7 +2732,7 @@
         <v>25</v>
       </c>
       <c r="B62" s="3">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C62" s="3">
         <v>26.21</v>
@@ -2749,7 +2746,7 @@
         <v>26</v>
       </c>
       <c r="B63" s="3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C63" s="3">
         <v>101.08</v>
@@ -2847,7 +2844,7 @@
         <v>32</v>
       </c>
       <c r="B70" s="3">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C70" s="3">
         <v>87.12</v>
@@ -2903,7 +2900,7 @@
         <v>35</v>
       </c>
       <c r="B74" s="3">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C74" s="3">
         <v>89.38</v>
@@ -2987,7 +2984,7 @@
         <v>443</v>
       </c>
       <c r="B80" s="3">
-        <v>706</v>
+        <v>670</v>
       </c>
       <c r="C80" s="3">
         <v>19.48</v>
@@ -3001,7 +2998,7 @@
         <v>444</v>
       </c>
       <c r="B81" s="3">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C81" s="3">
         <v>70.72</v>
@@ -3029,7 +3026,7 @@
         <v>446</v>
       </c>
       <c r="B83" s="3">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C83" s="3">
         <v>22.21</v>
@@ -4457,7 +4454,7 @@
         <v>135</v>
       </c>
       <c r="B185" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C185" s="3">
         <v>342.24</v>
@@ -4485,7 +4482,7 @@
         <v>137</v>
       </c>
       <c r="B187" s="3">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C187" s="3">
         <v>50.51</v>
@@ -4905,7 +4902,7 @@
         <v>164</v>
       </c>
       <c r="B217" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C217" s="3">
         <v>216.3</v>
@@ -4961,7 +4958,7 @@
         <v>168</v>
       </c>
       <c r="B221" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C221" s="3">
         <v>103.04</v>
@@ -5423,7 +5420,7 @@
         <v>198</v>
       </c>
       <c r="B254" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C254" s="3">
         <v>32.200000000000003</v>
@@ -5731,7 +5728,7 @@
         <v>218</v>
       </c>
       <c r="B276" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C276" s="3">
         <v>79.75</v>
@@ -5969,7 +5966,7 @@
         <v>234</v>
       </c>
       <c r="B293" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C293" s="3">
         <v>182.42</v>
@@ -5983,7 +5980,7 @@
         <v>235</v>
       </c>
       <c r="B294" s="3">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C294" s="3">
         <v>222.62</v>
@@ -6120,7 +6117,7 @@
     </row>
     <row r="304" spans="1:4">
       <c r="A304" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B304" s="3">
         <v>21</v>
@@ -6963,7 +6960,7 @@
         <v>302</v>
       </c>
       <c r="B364" s="3">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C364" s="3">
         <v>47.62</v>
@@ -7075,7 +7072,7 @@
         <v>310</v>
       </c>
       <c r="B372" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C372" s="3">
         <v>259.81</v>
@@ -7705,7 +7702,7 @@
         <v>375</v>
       </c>
       <c r="B417" s="3">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C417" s="3">
         <v>97.5</v>
@@ -7719,7 +7716,7 @@
         <v>376</v>
       </c>
       <c r="B418" s="3">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C418" s="3">
         <v>24.7</v>
@@ -7859,7 +7856,7 @@
         <v>435</v>
       </c>
       <c r="B428" s="3">
-        <v>230</v>
+        <v>195</v>
       </c>
       <c r="C428" s="3">
         <v>12.09</v>
@@ -7873,7 +7870,7 @@
         <v>436</v>
       </c>
       <c r="B429" s="3">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C429" s="3">
         <v>6.5</v>
@@ -7887,7 +7884,7 @@
         <v>437</v>
       </c>
       <c r="B430" s="3">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C430" s="3">
         <v>6.5</v>
@@ -7898,7 +7895,7 @@
     </row>
     <row r="431" spans="1:4">
       <c r="A431" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B431" s="3">
         <v>2</v>
@@ -7912,7 +7909,7 @@
     </row>
     <row r="432" spans="1:4">
       <c r="A432" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B432" s="3">
         <v>7</v>
@@ -7968,7 +7965,7 @@
     </row>
     <row r="436" spans="1:4">
       <c r="A436" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B436" s="3">
         <v>2</v>
@@ -7982,7 +7979,7 @@
     </row>
     <row r="437" spans="1:4">
       <c r="A437" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B437" s="3">
         <v>1</v>
@@ -7999,10 +7996,10 @@
         <v>448</v>
       </c>
       <c r="B438" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C438" s="3">
-        <v>58.68</v>
+        <v>70.25</v>
       </c>
       <c r="D438" s="4" t="s">
         <v>367</v>
@@ -8010,30 +8007,30 @@
     </row>
     <row r="439" spans="1:4">
       <c r="A439" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="B439" s="3">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C439" s="3">
-        <v>70.25</v>
+        <v>45</v>
       </c>
       <c r="D439" s="4" t="s">
-        <v>367</v>
+        <v>454</v>
       </c>
     </row>
     <row r="440" spans="1:4">
       <c r="A440" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B440" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C440" s="3">
-        <v>45</v>
+        <v>70.25</v>
       </c>
       <c r="D440" s="4" t="s">
-        <v>455</v>
+        <v>367</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -8041,10 +8038,10 @@
         <v>458</v>
       </c>
       <c r="B441" s="3">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C441" s="3">
-        <v>70.25</v>
+        <v>58.9</v>
       </c>
       <c r="D441" s="4" t="s">
         <v>367</v>
@@ -8055,10 +8052,10 @@
         <v>459</v>
       </c>
       <c r="B442" s="3">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C442" s="3">
-        <v>58.9</v>
+        <v>89.21</v>
       </c>
       <c r="D442" s="4" t="s">
         <v>367</v>
@@ -8072,7 +8069,7 @@
         <v>60</v>
       </c>
       <c r="C443" s="3">
-        <v>89.21</v>
+        <v>59.18</v>
       </c>
       <c r="D443" s="4" t="s">
         <v>367</v>
@@ -8083,10 +8080,10 @@
         <v>461</v>
       </c>
       <c r="B444" s="3">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C444" s="3">
-        <v>59.18</v>
+        <v>60.62</v>
       </c>
       <c r="D444" s="4" t="s">
         <v>367</v>
@@ -8097,10 +8094,10 @@
         <v>462</v>
       </c>
       <c r="B445" s="3">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="C445" s="3">
-        <v>60.62</v>
+        <v>3431.7</v>
       </c>
       <c r="D445" s="4" t="s">
         <v>367</v>
@@ -8114,7 +8111,7 @@
         <v>3</v>
       </c>
       <c r="C446" s="3">
-        <v>3431.7</v>
+        <v>1260.2</v>
       </c>
       <c r="D446" s="4" t="s">
         <v>367</v>
@@ -8125,10 +8122,10 @@
         <v>464</v>
       </c>
       <c r="B447" s="3">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C447" s="3">
-        <v>1260.2</v>
+        <v>47.2</v>
       </c>
       <c r="D447" s="4" t="s">
         <v>367</v>
@@ -8136,29 +8133,15 @@
     </row>
     <row r="448" spans="1:4">
       <c r="A448" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B448" s="3">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C448" s="3">
-        <v>47.2</v>
+        <v>71.760000000000005</v>
       </c>
       <c r="D448" s="4" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="449" spans="1:4">
-      <c r="A449" t="s">
-        <v>469</v>
-      </c>
-      <c r="B449" s="3">
-        <v>60</v>
-      </c>
-      <c r="C449" s="3">
-        <v>71.760000000000005</v>
-      </c>
-      <c r="D449" s="4" t="s">
         <v>367</v>
       </c>
     </row>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="469">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -1865,7 +1865,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D448"/>
+  <dimension ref="A1:D449"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="49.85546875" customWidth="1"/>
@@ -5168,10 +5168,10 @@
         <v>182</v>
       </c>
       <c r="B236" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C236" s="3">
-        <v>81.650000000000006</v>
+        <v>45.72</v>
       </c>
       <c r="D236" s="4" t="s">
         <v>419</v>
@@ -5179,13 +5179,13 @@
     </row>
     <row r="237" spans="1:4">
       <c r="A237" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B237" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C237" s="3">
-        <v>50.71</v>
+        <v>81.650000000000006</v>
       </c>
       <c r="D237" s="4" t="s">
         <v>419</v>
@@ -5193,13 +5193,13 @@
     </row>
     <row r="238" spans="1:4">
       <c r="A238" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B238" s="3">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C238" s="3">
-        <v>51.75</v>
+        <v>50.71</v>
       </c>
       <c r="D238" s="4" t="s">
         <v>419</v>
@@ -5207,13 +5207,13 @@
     </row>
     <row r="239" spans="1:4">
       <c r="A239" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B239" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C239" s="3">
-        <v>36.799999999999997</v>
+        <v>51.75</v>
       </c>
       <c r="D239" s="4" t="s">
         <v>419</v>
@@ -5221,13 +5221,13 @@
     </row>
     <row r="240" spans="1:4">
       <c r="A240" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B240" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C240" s="3">
-        <v>36.799999999999997</v>
+        <v>36.94</v>
       </c>
       <c r="D240" s="4" t="s">
         <v>419</v>
@@ -5241,7 +5241,7 @@
         <v>12</v>
       </c>
       <c r="C241" s="3">
-        <v>79.58</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D241" s="4" t="s">
         <v>419</v>
@@ -5249,27 +5249,27 @@
     </row>
     <row r="242" spans="1:4">
       <c r="A242" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B242" s="3">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C242" s="3">
-        <v>67.28</v>
+        <v>79.58</v>
       </c>
       <c r="D242" s="4" t="s">
-        <v>367</v>
+        <v>419</v>
       </c>
     </row>
     <row r="243" spans="1:4">
       <c r="A243" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B243" s="3">
-        <v>27</v>
-      </c>
-      <c r="C243" s="8">
-        <v>79.599999999999994</v>
+        <v>30</v>
+      </c>
+      <c r="C243" s="3">
+        <v>67.28</v>
       </c>
       <c r="D243" s="4" t="s">
         <v>367</v>
@@ -5277,13 +5277,13 @@
     </row>
     <row r="244" spans="1:4">
       <c r="A244" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B244" s="3">
         <v>27</v>
       </c>
       <c r="C244" s="8">
-        <v>75.88</v>
+        <v>79.599999999999994</v>
       </c>
       <c r="D244" s="4" t="s">
         <v>367</v>
@@ -5291,13 +5291,13 @@
     </row>
     <row r="245" spans="1:4">
       <c r="A245" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B245" s="3">
-        <v>21</v>
-      </c>
-      <c r="C245" s="3">
-        <v>109.08</v>
+        <v>27</v>
+      </c>
+      <c r="C245" s="8">
+        <v>75.88</v>
       </c>
       <c r="D245" s="4" t="s">
         <v>367</v>
@@ -5305,27 +5305,27 @@
     </row>
     <row r="246" spans="1:4">
       <c r="A246" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B246" s="3">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="C246" s="3">
-        <v>33.479999999999997</v>
+        <v>109.08</v>
       </c>
       <c r="D246" s="4" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
     </row>
     <row r="247" spans="1:4">
       <c r="A247" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B247" s="3">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="C247" s="3">
-        <v>422.09</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D247" s="4" t="s">
         <v>356</v>
@@ -5333,13 +5333,13 @@
     </row>
     <row r="248" spans="1:4">
       <c r="A248" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B248" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C248" s="3">
-        <v>1277.7</v>
+        <v>422.09</v>
       </c>
       <c r="D248" s="4" t="s">
         <v>356</v>
@@ -5347,27 +5347,27 @@
     </row>
     <row r="249" spans="1:4">
       <c r="A249" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B249" s="3">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C249" s="3">
-        <v>6.44</v>
+        <v>1277.7</v>
       </c>
       <c r="D249" s="4" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
     </row>
     <row r="250" spans="1:4">
       <c r="A250" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B250" s="3">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C250" s="3">
-        <v>108.2</v>
+        <v>6.44</v>
       </c>
       <c r="D250" s="4" t="s">
         <v>366</v>
@@ -5375,16 +5375,16 @@
     </row>
     <row r="251" spans="1:4">
       <c r="A251" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B251" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C251" s="3">
-        <v>4456.4799999999996</v>
+        <v>108.2</v>
       </c>
       <c r="D251" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5392,10 +5392,10 @@
         <v>196</v>
       </c>
       <c r="B252" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C252" s="3">
-        <v>7429</v>
+        <v>4456.4799999999996</v>
       </c>
       <c r="D252" s="4" t="s">
         <v>364</v>
@@ -5403,13 +5403,13 @@
     </row>
     <row r="253" spans="1:4">
       <c r="A253" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B253" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C253" s="3">
-        <v>609.5</v>
+        <v>7429</v>
       </c>
       <c r="D253" s="4" t="s">
         <v>364</v>
@@ -5417,24 +5417,24 @@
     </row>
     <row r="254" spans="1:4">
       <c r="A254" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B254" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C254" s="3">
-        <v>32.200000000000003</v>
+        <v>609.5</v>
       </c>
       <c r="D254" s="4" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
     </row>
     <row r="255" spans="1:4">
       <c r="A255" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B255" s="3">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C255" s="3">
         <v>32.200000000000003</v>
@@ -5445,10 +5445,10 @@
     </row>
     <row r="256" spans="1:4">
       <c r="A256" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B256" s="3">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C256" s="3">
         <v>32.200000000000003</v>
@@ -5459,10 +5459,10 @@
     </row>
     <row r="257" spans="1:4">
       <c r="A257" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B257" s="3">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="C257" s="3">
         <v>32.200000000000003</v>
@@ -5473,13 +5473,13 @@
     </row>
     <row r="258" spans="1:4">
       <c r="A258" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B258" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C258" s="3">
-        <v>40.4</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D258" s="4" t="s">
         <v>354</v>
@@ -5487,13 +5487,13 @@
     </row>
     <row r="259" spans="1:4">
       <c r="A259" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B259" s="3">
-        <v>175</v>
+        <v>3</v>
       </c>
       <c r="C259" s="3">
-        <v>36.06</v>
+        <v>40.4</v>
       </c>
       <c r="D259" s="4" t="s">
         <v>354</v>
@@ -5501,27 +5501,27 @@
     </row>
     <row r="260" spans="1:4">
       <c r="A260" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B260" s="3">
-        <v>10</v>
+        <v>175</v>
       </c>
       <c r="C260" s="3">
-        <v>56</v>
+        <v>36.06</v>
       </c>
       <c r="D260" s="4" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
     </row>
     <row r="261" spans="1:4">
       <c r="A261" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B261" s="3">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C261" s="3">
-        <v>57.63</v>
+        <v>56</v>
       </c>
       <c r="D261" s="4" t="s">
         <v>367</v>
@@ -5529,13 +5529,13 @@
     </row>
     <row r="262" spans="1:4">
       <c r="A262" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B262" s="3">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C262" s="3">
-        <v>60.78</v>
+        <v>57.63</v>
       </c>
       <c r="D262" s="4" t="s">
         <v>367</v>
@@ -5543,69 +5543,69 @@
     </row>
     <row r="263" spans="1:4">
       <c r="A263" t="s">
-        <v>420</v>
+        <v>206</v>
       </c>
       <c r="B263" s="3">
         <v>4</v>
       </c>
       <c r="C263" s="3">
-        <v>65</v>
+        <v>60.78</v>
       </c>
       <c r="D263" s="4" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
     </row>
     <row r="264" spans="1:4">
       <c r="A264" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B264" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C264" s="3">
-        <v>29.63</v>
+        <v>65</v>
       </c>
       <c r="D264" s="4" t="s">
-        <v>354</v>
+        <v>419</v>
       </c>
     </row>
     <row r="265" spans="1:4">
       <c r="A265" t="s">
-        <v>207</v>
+        <v>421</v>
       </c>
       <c r="B265" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C265" s="3">
-        <v>42.49</v>
+        <v>29.63</v>
       </c>
       <c r="D265" s="4" t="s">
-        <v>419</v>
+        <v>354</v>
       </c>
     </row>
     <row r="266" spans="1:4">
       <c r="A266" t="s">
-        <v>208</v>
-      </c>
-      <c r="B266" s="4">
-        <v>18</v>
-      </c>
-      <c r="C266" s="8">
-        <v>86.95</v>
+        <v>207</v>
+      </c>
+      <c r="B266" s="3">
+        <v>0</v>
+      </c>
+      <c r="C266" s="3">
+        <v>42.49</v>
       </c>
       <c r="D266" s="4" t="s">
-        <v>364</v>
+        <v>419</v>
       </c>
     </row>
     <row r="267" spans="1:4">
       <c r="A267" t="s">
-        <v>209</v>
-      </c>
-      <c r="B267" s="3">
-        <v>2</v>
+        <v>208</v>
+      </c>
+      <c r="B267" s="4">
+        <v>18</v>
       </c>
       <c r="C267" s="8">
-        <v>312.57</v>
+        <v>86.95</v>
       </c>
       <c r="D267" s="4" t="s">
         <v>364</v>
@@ -5613,13 +5613,13 @@
     </row>
     <row r="268" spans="1:4">
       <c r="A268" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B268" s="3">
-        <v>14</v>
-      </c>
-      <c r="C268" s="3">
-        <v>71.709999999999994</v>
+        <v>2</v>
+      </c>
+      <c r="C268" s="8">
+        <v>312.57</v>
       </c>
       <c r="D268" s="4" t="s">
         <v>364</v>
@@ -5627,41 +5627,41 @@
     </row>
     <row r="269" spans="1:4">
       <c r="A269" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B269" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C269" s="3">
-        <v>77.760000000000005</v>
+        <v>71.709999999999994</v>
       </c>
       <c r="D269" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="270" spans="1:4">
       <c r="A270" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B270" s="3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C270" s="3">
-        <v>54.7</v>
+        <v>77.760000000000005</v>
       </c>
       <c r="D270" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="271" spans="1:4">
       <c r="A271" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B271" s="3">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C271" s="3">
-        <v>67.28</v>
+        <v>54.7</v>
       </c>
       <c r="D271" s="4" t="s">
         <v>364</v>
@@ -5669,13 +5669,13 @@
     </row>
     <row r="272" spans="1:4">
       <c r="A272" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B272" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C272" s="3">
-        <v>334.36</v>
+        <v>67.28</v>
       </c>
       <c r="D272" s="4" t="s">
         <v>364</v>
@@ -5683,13 +5683,13 @@
     </row>
     <row r="273" spans="1:4">
       <c r="A273" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B273" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C273" s="3">
-        <v>78.87</v>
+        <v>334.36</v>
       </c>
       <c r="D273" s="4" t="s">
         <v>364</v>
@@ -5697,13 +5697,13 @@
     </row>
     <row r="274" spans="1:4">
       <c r="A274" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B274" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C274" s="3">
-        <v>83.84</v>
+        <v>78.87</v>
       </c>
       <c r="D274" s="4" t="s">
         <v>364</v>
@@ -5711,13 +5711,13 @@
     </row>
     <row r="275" spans="1:4">
       <c r="A275" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B275" s="3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C275" s="3">
-        <v>331.2</v>
+        <v>83.84</v>
       </c>
       <c r="D275" s="4" t="s">
         <v>364</v>
@@ -5725,13 +5725,13 @@
     </row>
     <row r="276" spans="1:4">
       <c r="A276" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B276" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C276" s="3">
-        <v>79.75</v>
+        <v>331.2</v>
       </c>
       <c r="D276" s="4" t="s">
         <v>364</v>
@@ -5739,13 +5739,13 @@
     </row>
     <row r="277" spans="1:4">
       <c r="A277" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B277" s="3">
         <v>7</v>
       </c>
       <c r="C277" s="3">
-        <v>83.84</v>
+        <v>79.75</v>
       </c>
       <c r="D277" s="4" t="s">
         <v>364</v>
@@ -5753,13 +5753,13 @@
     </row>
     <row r="278" spans="1:4">
       <c r="A278" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B278" s="3">
-        <v>2</v>
-      </c>
-      <c r="C278" s="8">
-        <v>347.3</v>
+        <v>7</v>
+      </c>
+      <c r="C278" s="3">
+        <v>83.84</v>
       </c>
       <c r="D278" s="4" t="s">
         <v>364</v>
@@ -5770,10 +5770,10 @@
         <v>220</v>
       </c>
       <c r="B279" s="3">
-        <v>4</v>
-      </c>
-      <c r="C279" s="3">
-        <v>284</v>
+        <v>2</v>
+      </c>
+      <c r="C279" s="8">
+        <v>347.3</v>
       </c>
       <c r="D279" s="4" t="s">
         <v>364</v>
@@ -5781,27 +5781,27 @@
     </row>
     <row r="280" spans="1:4">
       <c r="A280" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B280" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C280" s="3">
-        <v>28.15</v>
+        <v>284</v>
       </c>
       <c r="D280" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="281" spans="1:4">
       <c r="A281" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B281" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C281" s="3">
-        <v>45.08</v>
+        <v>28.15</v>
       </c>
       <c r="D281" s="4" t="s">
         <v>366</v>
@@ -5809,13 +5809,13 @@
     </row>
     <row r="282" spans="1:4">
       <c r="A282" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B282" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C282" s="3">
-        <v>51.52</v>
+        <v>45.08</v>
       </c>
       <c r="D282" s="4" t="s">
         <v>366</v>
@@ -5823,27 +5823,27 @@
     </row>
     <row r="283" spans="1:4">
       <c r="A283" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B283" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C283" s="3">
-        <v>40.57</v>
+        <v>51.52</v>
       </c>
       <c r="D283" s="4" t="s">
-        <v>419</v>
+        <v>366</v>
       </c>
     </row>
     <row r="284" spans="1:4">
       <c r="A284" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B284" s="3">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C284" s="3">
-        <v>36.229999999999997</v>
+        <v>40.57</v>
       </c>
       <c r="D284" s="4" t="s">
         <v>419</v>
@@ -5851,41 +5851,41 @@
     </row>
     <row r="285" spans="1:4">
       <c r="A285" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B285" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C285" s="3">
-        <v>54.12</v>
+        <v>36.229999999999997</v>
       </c>
       <c r="D285" s="4" t="s">
-        <v>366</v>
+        <v>419</v>
       </c>
     </row>
     <row r="286" spans="1:4">
       <c r="A286" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B286" s="3">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C286" s="3">
-        <v>69.55</v>
+        <v>54.12</v>
       </c>
       <c r="D286" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="287" spans="1:4">
       <c r="A287" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B287" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C287" s="3">
-        <v>295.14999999999998</v>
+        <v>69.55</v>
       </c>
       <c r="D287" s="4" t="s">
         <v>364</v>
@@ -5893,41 +5893,41 @@
     </row>
     <row r="288" spans="1:4">
       <c r="A288" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B288" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C288" s="3">
-        <v>38.56</v>
+        <v>295.14999999999998</v>
       </c>
       <c r="D288" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="289" spans="1:4">
       <c r="A289" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B289" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C289" s="3">
-        <v>60.95</v>
+        <v>38.56</v>
       </c>
       <c r="D289" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="290" spans="1:4">
       <c r="A290" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B290" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C290" s="3">
-        <v>78.209999999999994</v>
+        <v>60.95</v>
       </c>
       <c r="D290" s="4" t="s">
         <v>367</v>
@@ -5935,27 +5935,27 @@
     </row>
     <row r="291" spans="1:4">
       <c r="A291" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B291" s="3">
-        <v>228</v>
+        <v>10</v>
       </c>
       <c r="C291" s="3">
-        <v>51.15</v>
+        <v>78.209999999999994</v>
       </c>
       <c r="D291" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="292" spans="1:4">
       <c r="A292" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B292" s="3">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="C292" s="3">
-        <v>6591.8</v>
+        <v>51.15</v>
       </c>
       <c r="D292" s="4" t="s">
         <v>364</v>
@@ -5963,13 +5963,13 @@
     </row>
     <row r="293" spans="1:4">
       <c r="A293" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B293" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C293" s="3">
-        <v>182.42</v>
+        <v>6591.8</v>
       </c>
       <c r="D293" s="4" t="s">
         <v>364</v>
@@ -5977,13 +5977,13 @@
     </row>
     <row r="294" spans="1:4">
       <c r="A294" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B294" s="3">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="C294" s="3">
-        <v>222.62</v>
+        <v>182.42</v>
       </c>
       <c r="D294" s="4" t="s">
         <v>364</v>
@@ -5991,13 +5991,13 @@
     </row>
     <row r="295" spans="1:4">
       <c r="A295" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B295" s="3">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="C295" s="3">
-        <v>2314.8000000000002</v>
+        <v>222.62</v>
       </c>
       <c r="D295" s="4" t="s">
         <v>364</v>
@@ -6005,13 +6005,13 @@
     </row>
     <row r="296" spans="1:4">
       <c r="A296" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B296" s="3">
         <v>0</v>
       </c>
       <c r="C296" s="3">
-        <v>894.8</v>
+        <v>2314.8000000000002</v>
       </c>
       <c r="D296" s="4" t="s">
         <v>364</v>
@@ -6019,27 +6019,27 @@
     </row>
     <row r="297" spans="1:4">
       <c r="A297" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B297" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C297" s="3">
-        <v>31.6</v>
+        <v>894.8</v>
       </c>
       <c r="D297" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="298" spans="1:4">
       <c r="A298" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B298" s="3">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C298" s="3">
-        <v>77.28</v>
+        <v>31.6</v>
       </c>
       <c r="D298" s="4" t="s">
         <v>366</v>
@@ -6047,13 +6047,13 @@
     </row>
     <row r="299" spans="1:4">
       <c r="A299" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B299" s="3">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="C299" s="3">
-        <v>43.8</v>
+        <v>77.28</v>
       </c>
       <c r="D299" s="4" t="s">
         <v>366</v>
@@ -6061,13 +6061,13 @@
     </row>
     <row r="300" spans="1:4">
       <c r="A300" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B300" s="3">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C300" s="3">
-        <v>21.9</v>
+        <v>43.8</v>
       </c>
       <c r="D300" s="4" t="s">
         <v>366</v>
@@ -6075,13 +6075,13 @@
     </row>
     <row r="301" spans="1:4">
       <c r="A301" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B301" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C301" s="3">
-        <v>798.6</v>
+        <v>21.9</v>
       </c>
       <c r="D301" s="4" t="s">
         <v>366</v>
@@ -6089,13 +6089,13 @@
     </row>
     <row r="302" spans="1:4">
       <c r="A302" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B302" s="3">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="C302" s="3">
-        <v>23.19</v>
+        <v>798.6</v>
       </c>
       <c r="D302" s="4" t="s">
         <v>366</v>
@@ -6103,13 +6103,13 @@
     </row>
     <row r="303" spans="1:4">
       <c r="A303" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B303" s="3">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="C303" s="3">
-        <v>8.24</v>
+        <v>23.19</v>
       </c>
       <c r="D303" s="4" t="s">
         <v>366</v>
@@ -6117,13 +6117,13 @@
     </row>
     <row r="304" spans="1:4">
       <c r="A304" t="s">
-        <v>456</v>
+        <v>244</v>
       </c>
       <c r="B304" s="3">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="C304" s="3">
-        <v>13.72</v>
+        <v>8.24</v>
       </c>
       <c r="D304" s="4" t="s">
         <v>366</v>
@@ -6131,10 +6131,10 @@
     </row>
     <row r="305" spans="1:4">
       <c r="A305" t="s">
-        <v>245</v>
+        <v>456</v>
       </c>
       <c r="B305" s="3">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C305" s="3">
         <v>13.72</v>
@@ -6145,13 +6145,13 @@
     </row>
     <row r="306" spans="1:4">
       <c r="A306" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B306" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C306" s="3">
-        <v>31.95</v>
+        <v>13.72</v>
       </c>
       <c r="D306" s="4" t="s">
         <v>366</v>
@@ -6159,13 +6159,13 @@
     </row>
     <row r="307" spans="1:4">
       <c r="A307" t="s">
-        <v>370</v>
+        <v>246</v>
       </c>
       <c r="B307" s="3">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="C307" s="3">
-        <v>16.2</v>
+        <v>31.95</v>
       </c>
       <c r="D307" s="4" t="s">
         <v>366</v>
@@ -6173,13 +6173,13 @@
     </row>
     <row r="308" spans="1:4">
       <c r="A308" t="s">
-        <v>247</v>
+        <v>370</v>
       </c>
       <c r="B308" s="3">
-        <v>6</v>
+        <v>105</v>
       </c>
       <c r="C308" s="3">
-        <v>36.869999999999997</v>
+        <v>16.2</v>
       </c>
       <c r="D308" s="4" t="s">
         <v>366</v>
@@ -6187,13 +6187,13 @@
     </row>
     <row r="309" spans="1:4">
       <c r="A309" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B309" s="3">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C309" s="3">
-        <v>31.48</v>
+        <v>36.869999999999997</v>
       </c>
       <c r="D309" s="4" t="s">
         <v>366</v>
@@ -6201,13 +6201,13 @@
     </row>
     <row r="310" spans="1:4">
       <c r="A310" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B310" s="3">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C310" s="3">
-        <v>21.9</v>
+        <v>31.48</v>
       </c>
       <c r="D310" s="4" t="s">
         <v>366</v>
@@ -6215,13 +6215,13 @@
     </row>
     <row r="311" spans="1:4">
       <c r="A311" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B311" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C311" s="3">
-        <v>23.19</v>
+        <v>21.9</v>
       </c>
       <c r="D311" s="4" t="s">
         <v>366</v>
@@ -6229,13 +6229,13 @@
     </row>
     <row r="312" spans="1:4">
       <c r="A312" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B312" s="3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C312" s="3">
-        <v>19.55</v>
+        <v>23.19</v>
       </c>
       <c r="D312" s="4" t="s">
         <v>366</v>
@@ -6243,13 +6243,13 @@
     </row>
     <row r="313" spans="1:4">
       <c r="A313" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B313" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C313" s="3">
-        <v>19.07</v>
+        <v>19.55</v>
       </c>
       <c r="D313" s="4" t="s">
         <v>366</v>
@@ -6257,13 +6257,13 @@
     </row>
     <row r="314" spans="1:4">
       <c r="A314" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B314" s="3">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C314" s="3">
-        <v>21.9</v>
+        <v>19.07</v>
       </c>
       <c r="D314" s="4" t="s">
         <v>366</v>
@@ -6271,27 +6271,27 @@
     </row>
     <row r="315" spans="1:4">
       <c r="A315" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B315" s="3">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C315" s="3">
-        <v>79.349999999999994</v>
+        <v>21.9</v>
       </c>
       <c r="D315" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="316" spans="1:4">
       <c r="A316" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B316" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C316" s="3">
-        <v>862.7</v>
+        <v>79.349999999999994</v>
       </c>
       <c r="D316" s="4" t="s">
         <v>367</v>
@@ -6299,13 +6299,13 @@
     </row>
     <row r="317" spans="1:4">
       <c r="A317" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B317" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C317" s="3">
-        <v>56.93</v>
+        <v>862.7</v>
       </c>
       <c r="D317" s="4" t="s">
         <v>367</v>
@@ -6313,13 +6313,13 @@
     </row>
     <row r="318" spans="1:4">
       <c r="A318" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B318" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C318" s="3">
-        <v>1265</v>
+        <v>56.93</v>
       </c>
       <c r="D318" s="4" t="s">
         <v>367</v>
@@ -6327,27 +6327,27 @@
     </row>
     <row r="319" spans="1:4">
       <c r="A319" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B319" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C319" s="3">
-        <v>76</v>
+        <v>1265</v>
       </c>
       <c r="D319" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="320" spans="1:4">
       <c r="A320" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B320" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="C320" s="3">
-        <v>267.85000000000002</v>
+        <v>76</v>
       </c>
       <c r="D320" s="4" t="s">
         <v>364</v>
@@ -6355,13 +6355,13 @@
     </row>
     <row r="321" spans="1:4">
       <c r="A321" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B321" s="3">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C321" s="3">
-        <v>74.7</v>
+        <v>267.85000000000002</v>
       </c>
       <c r="D321" s="4" t="s">
         <v>364</v>
@@ -6369,13 +6369,13 @@
     </row>
     <row r="322" spans="1:4">
       <c r="A322" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B322" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C322" s="3">
-        <v>327.3</v>
+        <v>74.7</v>
       </c>
       <c r="D322" s="4" t="s">
         <v>364</v>
@@ -6383,13 +6383,13 @@
     </row>
     <row r="323" spans="1:4">
       <c r="A323" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B323" s="3">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C323" s="3">
-        <v>72.13</v>
+        <v>327.3</v>
       </c>
       <c r="D323" s="4" t="s">
         <v>364</v>
@@ -6397,13 +6397,13 @@
     </row>
     <row r="324" spans="1:4">
       <c r="A324" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B324" s="3">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="C324" s="3">
-        <v>302.39999999999998</v>
+        <v>72.13</v>
       </c>
       <c r="D324" s="4" t="s">
         <v>364</v>
@@ -6411,41 +6411,41 @@
     </row>
     <row r="325" spans="1:4">
       <c r="A325" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B325" s="3">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C325" s="3">
-        <v>36.799999999999997</v>
+        <v>302.39999999999998</v>
       </c>
       <c r="D325" s="4" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="326" spans="1:4">
       <c r="A326" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B326" s="3">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C326" s="3">
-        <v>428.5</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D326" s="4" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="327" spans="1:4">
       <c r="A327" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B327" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C327" s="3">
-        <v>450.22</v>
+        <v>428.5</v>
       </c>
       <c r="D327" s="4" t="s">
         <v>364</v>
@@ -6453,13 +6453,13 @@
     </row>
     <row r="328" spans="1:4">
       <c r="A328" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B328" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C328" s="3">
-        <v>465.7</v>
+        <v>450.22</v>
       </c>
       <c r="D328" s="4" t="s">
         <v>364</v>
@@ -6467,13 +6467,13 @@
     </row>
     <row r="329" spans="1:4">
       <c r="A329" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B329" s="3">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C329" s="3">
-        <v>38.25</v>
+        <v>465.7</v>
       </c>
       <c r="D329" s="4" t="s">
         <v>364</v>
@@ -6481,13 +6481,13 @@
     </row>
     <row r="330" spans="1:4">
       <c r="A330" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B330" s="3">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C330" s="3">
-        <v>87.49</v>
+        <v>38.25</v>
       </c>
       <c r="D330" s="4" t="s">
         <v>364</v>
@@ -6495,13 +6495,13 @@
     </row>
     <row r="331" spans="1:4">
       <c r="A331" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B331" s="3">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C331" s="3">
-        <v>63.13</v>
+        <v>87.49</v>
       </c>
       <c r="D331" s="4" t="s">
         <v>364</v>
@@ -6509,27 +6509,27 @@
     </row>
     <row r="332" spans="1:4">
       <c r="A332" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B332" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C332" s="3">
-        <v>377.78</v>
+        <v>63.13</v>
       </c>
       <c r="D332" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="333" spans="1:4">
       <c r="A333" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B333" s="3">
         <v>2</v>
       </c>
       <c r="C333" s="3">
-        <v>3333.85</v>
+        <v>377.78</v>
       </c>
       <c r="D333" s="4" t="s">
         <v>368</v>
@@ -6537,13 +6537,13 @@
     </row>
     <row r="334" spans="1:4">
       <c r="A334" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B334" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C334" s="3">
-        <v>374.67</v>
+        <v>3333.85</v>
       </c>
       <c r="D334" s="4" t="s">
         <v>368</v>
@@ -6551,13 +6551,13 @@
     </row>
     <row r="335" spans="1:4">
       <c r="A335" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B335" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C335" s="3">
-        <v>120.06</v>
+        <v>374.67</v>
       </c>
       <c r="D335" s="4" t="s">
         <v>368</v>
@@ -6565,41 +6565,41 @@
     </row>
     <row r="336" spans="1:4">
       <c r="A336" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B336" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C336" s="3">
-        <v>54.2</v>
+        <v>120.06</v>
       </c>
       <c r="D336" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="337" spans="1:4">
       <c r="A337" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B337" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C337" s="3">
-        <v>31.5</v>
+        <v>54.2</v>
       </c>
       <c r="D337" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="338" spans="1:4">
       <c r="A338" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B338" s="3">
         <v>0</v>
       </c>
       <c r="C338" s="3">
-        <v>114.09</v>
+        <v>31.5</v>
       </c>
       <c r="D338" s="4" t="s">
         <v>364</v>
@@ -6607,13 +6607,13 @@
     </row>
     <row r="339" spans="1:4">
       <c r="A339" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B339" s="3">
         <v>0</v>
       </c>
       <c r="C339" s="3">
-        <v>139.9</v>
+        <v>114.09</v>
       </c>
       <c r="D339" s="4" t="s">
         <v>364</v>
@@ -6621,13 +6621,13 @@
     </row>
     <row r="340" spans="1:4">
       <c r="A340" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B340" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C340" s="3">
-        <v>50.13</v>
+        <v>139.9</v>
       </c>
       <c r="D340" s="4" t="s">
         <v>364</v>
@@ -6635,13 +6635,13 @@
     </row>
     <row r="341" spans="1:4">
       <c r="A341" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B341" s="3">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C341" s="3">
-        <v>140.26</v>
+        <v>50.13</v>
       </c>
       <c r="D341" s="4" t="s">
         <v>364</v>
@@ -6649,55 +6649,55 @@
     </row>
     <row r="342" spans="1:4">
       <c r="A342" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B342" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C342" s="3">
-        <v>370.53</v>
+        <v>140.26</v>
       </c>
       <c r="D342" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="343" spans="1:4">
       <c r="A343" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B343" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C343" s="3">
-        <v>30.9</v>
+        <v>370.53</v>
       </c>
       <c r="D343" s="4" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
     </row>
     <row r="344" spans="1:4">
       <c r="A344" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B344" s="3">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C344" s="3">
-        <v>5746.5</v>
+        <v>30.9</v>
       </c>
       <c r="D344" s="4" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="345" spans="1:4">
       <c r="A345" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B345" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C345" s="3">
-        <v>516.46</v>
+        <v>5746.5</v>
       </c>
       <c r="D345" s="4" t="s">
         <v>364</v>
@@ -6705,13 +6705,13 @@
     </row>
     <row r="346" spans="1:4">
       <c r="A346" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B346" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C346" s="3">
-        <v>185.15</v>
+        <v>516.46</v>
       </c>
       <c r="D346" s="4" t="s">
         <v>364</v>
@@ -6719,58 +6719,58 @@
     </row>
     <row r="347" spans="1:4">
       <c r="A347" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B347" s="3">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="C347" s="3">
-        <v>11.5</v>
+        <v>185.15</v>
       </c>
       <c r="D347" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="348" spans="1:4">
       <c r="A348" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B348" s="3">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C348" s="3">
-        <v>724.5</v>
+        <v>11.5</v>
       </c>
       <c r="D348" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="349" spans="1:4">
       <c r="A349" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B349" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C349" s="3">
-        <v>450.22</v>
+        <v>724.5</v>
       </c>
       <c r="D349" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="350" spans="1:4">
       <c r="A350" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B350" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C350" s="3">
-        <v>461.23</v>
+        <v>450.22</v>
       </c>
       <c r="D350" s="4" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -6781,7 +6781,7 @@
         <v>1</v>
       </c>
       <c r="C351" s="3">
-        <v>518.41999999999996</v>
+        <v>461.23</v>
       </c>
       <c r="D351" s="4" t="s">
         <v>357</v>
@@ -6789,13 +6789,13 @@
     </row>
     <row r="352" spans="1:4">
       <c r="A352" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B352" s="3">
         <v>1</v>
       </c>
       <c r="C352" s="3">
-        <v>348.08</v>
+        <v>518.41999999999996</v>
       </c>
       <c r="D352" s="4" t="s">
         <v>357</v>
@@ -6803,13 +6803,13 @@
     </row>
     <row r="353" spans="1:4">
       <c r="A353" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B353" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C353" s="3">
-        <v>33.479999999999997</v>
+        <v>348.08</v>
       </c>
       <c r="D353" s="4" t="s">
         <v>357</v>
@@ -6817,13 +6817,13 @@
     </row>
     <row r="354" spans="1:4">
       <c r="A354" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B354" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C354" s="3">
-        <v>35.79</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D354" s="4" t="s">
         <v>357</v>
@@ -6831,13 +6831,13 @@
     </row>
     <row r="355" spans="1:4">
       <c r="A355" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B355" s="3">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C355" s="3">
-        <v>377.7</v>
+        <v>35.79</v>
       </c>
       <c r="D355" s="4" t="s">
         <v>357</v>
@@ -6845,13 +6845,13 @@
     </row>
     <row r="356" spans="1:4">
       <c r="A356" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B356" s="3">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C356" s="3">
-        <v>33.21</v>
+        <v>377.7</v>
       </c>
       <c r="D356" s="4" t="s">
         <v>357</v>
@@ -6859,13 +6859,13 @@
     </row>
     <row r="357" spans="1:4">
       <c r="A357" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B357" s="3">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C357" s="3">
-        <v>27.16</v>
+        <v>33.21</v>
       </c>
       <c r="D357" s="4" t="s">
         <v>357</v>
@@ -6873,13 +6873,13 @@
     </row>
     <row r="358" spans="1:4">
       <c r="A358" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B358" s="3">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C358" s="3">
-        <v>361.41</v>
+        <v>27.16</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>357</v>
@@ -6887,13 +6887,13 @@
     </row>
     <row r="359" spans="1:4">
       <c r="A359" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B359" s="3">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="C359" s="3">
-        <v>29.25</v>
+        <v>361.41</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>357</v>
@@ -6901,13 +6901,13 @@
     </row>
     <row r="360" spans="1:4">
       <c r="A360" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B360" s="3">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="C360" s="3">
-        <v>304.54000000000002</v>
+        <v>29.25</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>357</v>
@@ -6915,13 +6915,13 @@
     </row>
     <row r="361" spans="1:4">
       <c r="A361" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B361" s="3">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C361" s="3">
-        <v>34.049999999999997</v>
+        <v>304.54000000000002</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>357</v>
@@ -6929,55 +6929,55 @@
     </row>
     <row r="362" spans="1:4">
       <c r="A362" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B362" s="3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C362" s="3">
-        <v>57.7</v>
+        <v>34.049999999999997</v>
       </c>
       <c r="D362" s="4" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
     </row>
     <row r="363" spans="1:4">
       <c r="A363" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B363" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C363" s="3">
-        <v>90.9</v>
+        <v>57.7</v>
       </c>
       <c r="D363" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="364" spans="1:4">
       <c r="A364" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B364" s="3">
-        <v>218</v>
+        <v>10</v>
       </c>
       <c r="C364" s="3">
-        <v>47.62</v>
+        <v>90.9</v>
       </c>
       <c r="D364" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="365" spans="1:4">
       <c r="A365" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B365" s="3">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="C365" s="3">
-        <v>7173.59</v>
+        <v>47.62</v>
       </c>
       <c r="D365" s="4" t="s">
         <v>364</v>
@@ -6985,13 +6985,13 @@
     </row>
     <row r="366" spans="1:4">
       <c r="A366" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B366" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C366" s="3">
-        <v>677.79</v>
+        <v>7173.59</v>
       </c>
       <c r="D366" s="4" t="s">
         <v>364</v>
@@ -6999,13 +6999,13 @@
     </row>
     <row r="367" spans="1:4">
       <c r="A367" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B367" s="3">
-        <v>13</v>
-      </c>
-      <c r="C367" s="8">
-        <v>171.47</v>
+        <v>1</v>
+      </c>
+      <c r="C367" s="3">
+        <v>677.79</v>
       </c>
       <c r="D367" s="4" t="s">
         <v>364</v>
@@ -7013,13 +7013,13 @@
     </row>
     <row r="368" spans="1:4">
       <c r="A368" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B368" s="3">
-        <v>65</v>
-      </c>
-      <c r="C368" s="3">
-        <v>212.75</v>
+        <v>13</v>
+      </c>
+      <c r="C368" s="8">
+        <v>171.47</v>
       </c>
       <c r="D368" s="4" t="s">
         <v>364</v>
@@ -7027,13 +7027,13 @@
     </row>
     <row r="369" spans="1:4">
       <c r="A369" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B369" s="3">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="C369" s="3">
-        <v>2335.67</v>
+        <v>212.75</v>
       </c>
       <c r="D369" s="4" t="s">
         <v>364</v>
@@ -7041,13 +7041,13 @@
     </row>
     <row r="370" spans="1:4">
       <c r="A370" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B370" s="3">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C370" s="3">
-        <v>66.180000000000007</v>
+        <v>2335.67</v>
       </c>
       <c r="D370" s="4" t="s">
         <v>364</v>
@@ -7055,13 +7055,13 @@
     </row>
     <row r="371" spans="1:4">
       <c r="A371" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B371" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C371" s="3">
-        <v>8139.6</v>
+        <v>66.180000000000007</v>
       </c>
       <c r="D371" s="4" t="s">
         <v>364</v>
@@ -7069,13 +7069,13 @@
     </row>
     <row r="372" spans="1:4">
       <c r="A372" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B372" s="3">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C372" s="3">
-        <v>259.81</v>
+        <v>8139.6</v>
       </c>
       <c r="D372" s="4" t="s">
         <v>364</v>
@@ -7083,13 +7083,13 @@
     </row>
     <row r="373" spans="1:4">
       <c r="A373" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B373" s="3">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C373" s="3">
-        <v>259.8</v>
+        <v>259.81</v>
       </c>
       <c r="D373" s="4" t="s">
         <v>364</v>
@@ -7097,13 +7097,13 @@
     </row>
     <row r="374" spans="1:4">
       <c r="A374" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B374" s="3">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C374" s="3">
-        <v>310.2</v>
+        <v>259.8</v>
       </c>
       <c r="D374" s="4" t="s">
         <v>364</v>
@@ -7111,13 +7111,13 @@
     </row>
     <row r="375" spans="1:4">
       <c r="A375" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B375" s="3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C375" s="3">
-        <v>36.43</v>
+        <v>310.2</v>
       </c>
       <c r="D375" s="4" t="s">
         <v>364</v>
@@ -7125,13 +7125,13 @@
     </row>
     <row r="376" spans="1:4">
       <c r="A376" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B376" s="3">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C376" s="3">
-        <v>87.22</v>
+        <v>36.43</v>
       </c>
       <c r="D376" s="4" t="s">
         <v>364</v>
@@ -7139,13 +7139,13 @@
     </row>
     <row r="377" spans="1:4">
       <c r="A377" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B377" s="3">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C377" s="3">
-        <v>319.60000000000002</v>
+        <v>87.22</v>
       </c>
       <c r="D377" s="4" t="s">
         <v>364</v>
@@ -7153,13 +7153,13 @@
     </row>
     <row r="378" spans="1:4">
       <c r="A378" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B378" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C378" s="3">
-        <v>62.6</v>
+        <v>319.60000000000002</v>
       </c>
       <c r="D378" s="4" t="s">
         <v>364</v>
@@ -7167,13 +7167,13 @@
     </row>
     <row r="379" spans="1:4">
       <c r="A379" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B379" s="3">
-        <v>8</v>
-      </c>
-      <c r="C379" s="8">
-        <v>385.25</v>
+        <v>14</v>
+      </c>
+      <c r="C379" s="3">
+        <v>62.6</v>
       </c>
       <c r="D379" s="4" t="s">
         <v>364</v>
@@ -7181,27 +7181,27 @@
     </row>
     <row r="380" spans="1:4">
       <c r="A380" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B380" s="3">
-        <v>28</v>
-      </c>
-      <c r="C380" s="3">
-        <v>67.28</v>
+        <v>8</v>
+      </c>
+      <c r="C380" s="8">
+        <v>385.25</v>
       </c>
       <c r="D380" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="381" spans="1:4">
       <c r="A381" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B381" s="3">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="C381" s="3">
-        <v>1138.5</v>
+        <v>67.28</v>
       </c>
       <c r="D381" s="4" t="s">
         <v>367</v>
@@ -7209,27 +7209,27 @@
     </row>
     <row r="382" spans="1:4">
       <c r="A382" t="s">
-        <v>350</v>
+        <v>319</v>
       </c>
       <c r="B382" s="3">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C382" s="3">
-        <v>58.69</v>
+        <v>1138.5</v>
       </c>
       <c r="D382" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="383" spans="1:4">
       <c r="A383" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B383" s="3">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C383" s="3">
-        <v>289.33999999999997</v>
+        <v>58.69</v>
       </c>
       <c r="D383" s="4" t="s">
         <v>364</v>
@@ -7237,13 +7237,13 @@
     </row>
     <row r="384" spans="1:4">
       <c r="A384" t="s">
-        <v>320</v>
+        <v>351</v>
       </c>
       <c r="B384" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C384" s="3">
-        <v>48.76</v>
+        <v>289.33999999999997</v>
       </c>
       <c r="D384" s="4" t="s">
         <v>364</v>
@@ -7251,13 +7251,13 @@
     </row>
     <row r="385" spans="1:4">
       <c r="A385" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B385" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C385" s="3">
-        <v>242.34</v>
+        <v>48.76</v>
       </c>
       <c r="D385" s="4" t="s">
         <v>364</v>
@@ -7265,13 +7265,13 @@
     </row>
     <row r="386" spans="1:4">
       <c r="A386" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B386" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C386" s="3">
-        <v>65.599999999999994</v>
+        <v>242.34</v>
       </c>
       <c r="D386" s="4" t="s">
         <v>364</v>
@@ -7279,13 +7279,13 @@
     </row>
     <row r="387" spans="1:4">
       <c r="A387" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B387" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C387" s="3">
-        <v>255.03</v>
+        <v>65.599999999999994</v>
       </c>
       <c r="D387" s="4" t="s">
         <v>364</v>
@@ -7293,13 +7293,13 @@
     </row>
     <row r="388" spans="1:4">
       <c r="A388" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B388" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C388" s="3">
-        <v>220.8</v>
+        <v>255.03</v>
       </c>
       <c r="D388" s="4" t="s">
         <v>364</v>
@@ -7307,13 +7307,13 @@
     </row>
     <row r="389" spans="1:4">
       <c r="A389" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B389" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C389" s="3">
-        <v>255.02</v>
+        <v>220.8</v>
       </c>
       <c r="D389" s="4" t="s">
         <v>364</v>
@@ -7321,13 +7321,13 @@
     </row>
     <row r="390" spans="1:4">
       <c r="A390" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B390" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C390" s="3">
-        <v>68.86</v>
+        <v>255.02</v>
       </c>
       <c r="D390" s="4" t="s">
         <v>364</v>
@@ -7335,13 +7335,13 @@
     </row>
     <row r="391" spans="1:4">
       <c r="A391" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B391" s="3">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C391" s="3">
-        <v>344.28</v>
+        <v>68.86</v>
       </c>
       <c r="D391" s="4" t="s">
         <v>364</v>
@@ -7349,13 +7349,13 @@
     </row>
     <row r="392" spans="1:4">
       <c r="A392" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B392" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C392" s="3">
-        <v>60.29</v>
+        <v>344.28</v>
       </c>
       <c r="D392" s="4" t="s">
         <v>364</v>
@@ -7363,13 +7363,13 @@
     </row>
     <row r="393" spans="1:4">
       <c r="A393" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B393" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C393" s="3">
-        <v>261.8</v>
+        <v>60.29</v>
       </c>
       <c r="D393" s="4" t="s">
         <v>364</v>
@@ -7377,55 +7377,55 @@
     </row>
     <row r="394" spans="1:4">
       <c r="A394" t="s">
-        <v>382</v>
+        <v>329</v>
       </c>
       <c r="B394" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C394" s="3">
-        <v>30.58</v>
+        <v>261.8</v>
       </c>
       <c r="D394" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="395" spans="1:4">
       <c r="A395" t="s">
-        <v>330</v>
+        <v>382</v>
       </c>
       <c r="B395" s="3">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="C395" s="3">
-        <v>16.95</v>
+        <v>30.58</v>
       </c>
       <c r="D395" s="4" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
     </row>
     <row r="396" spans="1:4">
       <c r="A396" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B396" s="3">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C396" s="3">
-        <v>24.95</v>
+        <v>16.95</v>
       </c>
       <c r="D396" s="4" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
     </row>
     <row r="397" spans="1:4">
       <c r="A397" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B397" s="3">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="C397" s="3">
-        <v>641.49</v>
+        <v>24.95</v>
       </c>
       <c r="D397" s="4" t="s">
         <v>367</v>
@@ -7433,13 +7433,13 @@
     </row>
     <row r="398" spans="1:4">
       <c r="A398" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B398" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C398" s="3">
-        <v>39.57</v>
+        <v>641.49</v>
       </c>
       <c r="D398" s="4" t="s">
         <v>367</v>
@@ -7447,13 +7447,13 @@
     </row>
     <row r="399" spans="1:4">
       <c r="A399" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B399" s="3">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C399" s="3">
-        <v>51.83</v>
+        <v>39.57</v>
       </c>
       <c r="D399" s="4" t="s">
         <v>367</v>
@@ -7461,27 +7461,27 @@
     </row>
     <row r="400" spans="1:4">
       <c r="A400" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B400" s="3">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C400" s="3">
-        <v>33.840000000000003</v>
+        <v>51.83</v>
       </c>
       <c r="D400" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="401" spans="1:4">
       <c r="A401" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B401" s="3">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="C401" s="3">
-        <v>150.15</v>
+        <v>33.840000000000003</v>
       </c>
       <c r="D401" s="4" t="s">
         <v>364</v>
@@ -7489,13 +7489,13 @@
     </row>
     <row r="402" spans="1:4">
       <c r="A402" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B402" s="3">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C402" s="3">
-        <v>144.5</v>
+        <v>150.15</v>
       </c>
       <c r="D402" s="4" t="s">
         <v>364</v>
@@ -7503,13 +7503,13 @@
     </row>
     <row r="403" spans="1:4">
       <c r="A403" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B403" s="3">
         <v>25</v>
       </c>
       <c r="C403" s="3">
-        <v>100.93</v>
+        <v>144.5</v>
       </c>
       <c r="D403" s="4" t="s">
         <v>364</v>
@@ -7517,13 +7517,13 @@
     </row>
     <row r="404" spans="1:4">
       <c r="A404" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B404" s="3">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C404" s="3">
-        <v>124.5</v>
+        <v>100.93</v>
       </c>
       <c r="D404" s="4" t="s">
         <v>364</v>
@@ -7531,13 +7531,13 @@
     </row>
     <row r="405" spans="1:4">
       <c r="A405" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B405" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C405" s="3">
-        <v>27.21</v>
+        <v>124.5</v>
       </c>
       <c r="D405" s="4" t="s">
         <v>364</v>
@@ -7545,41 +7545,41 @@
     </row>
     <row r="406" spans="1:4">
       <c r="A406" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B406" s="3">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="C406" s="3">
-        <v>24.79</v>
+        <v>27.21</v>
       </c>
       <c r="D406" s="4" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
     </row>
     <row r="407" spans="1:4">
       <c r="A407" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B407" s="3">
-        <v>6</v>
+        <v>94</v>
       </c>
       <c r="C407" s="3">
-        <v>37.1</v>
+        <v>24.79</v>
       </c>
       <c r="D407" s="4" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
     </row>
     <row r="408" spans="1:4">
       <c r="A408" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B408" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C408" s="3">
-        <v>178.04</v>
+        <v>37.1</v>
       </c>
       <c r="D408" s="4" t="s">
         <v>364</v>
@@ -7587,41 +7587,41 @@
     </row>
     <row r="409" spans="1:4">
       <c r="A409" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B409" s="3">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="C409" s="3">
-        <v>23.88</v>
+        <v>178.04</v>
       </c>
       <c r="D409" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="410" spans="1:4">
       <c r="A410" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B410" s="3">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="C410" s="3">
-        <v>20.68</v>
+        <v>23.88</v>
       </c>
       <c r="D410" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="411" spans="1:4">
       <c r="A411" t="s">
-        <v>372</v>
+        <v>345</v>
       </c>
       <c r="B411" s="3">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="C411" s="3">
-        <v>97.54</v>
+        <v>20.68</v>
       </c>
       <c r="D411" s="4" t="s">
         <v>364</v>
@@ -7629,13 +7629,13 @@
     </row>
     <row r="412" spans="1:4">
       <c r="A412" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B412" s="3">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C412" s="3">
-        <v>304.02999999999997</v>
+        <v>97.54</v>
       </c>
       <c r="D412" s="4" t="s">
         <v>364</v>
@@ -7643,27 +7643,27 @@
     </row>
     <row r="413" spans="1:4">
       <c r="A413" t="s">
-        <v>346</v>
+        <v>373</v>
       </c>
       <c r="B413" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C413" s="3">
-        <v>1934.56</v>
+        <v>304.02999999999997</v>
       </c>
       <c r="D413" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="414" spans="1:4">
       <c r="A414" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B414" s="3">
         <v>0</v>
       </c>
       <c r="C414" s="3">
-        <v>230.99</v>
+        <v>1934.56</v>
       </c>
       <c r="D414" s="4" t="s">
         <v>368</v>
@@ -7671,55 +7671,55 @@
     </row>
     <row r="415" spans="1:4">
       <c r="A415" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B415" s="3">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="C415" s="3">
-        <v>33.39</v>
+        <v>230.99</v>
       </c>
       <c r="D415" s="4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="416" spans="1:4">
       <c r="A416" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B416" s="3">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="C416" s="3">
-        <v>20.66</v>
+        <v>33.39</v>
       </c>
       <c r="D416" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="417" spans="1:4">
       <c r="A417" t="s">
-        <v>375</v>
+        <v>349</v>
       </c>
       <c r="B417" s="3">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="C417" s="3">
-        <v>97.5</v>
+        <v>20.66</v>
       </c>
       <c r="D417" s="4" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
     </row>
     <row r="418" spans="1:4">
       <c r="A418" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B418" s="3">
-        <v>401</v>
+        <v>68</v>
       </c>
       <c r="C418" s="3">
-        <v>24.7</v>
+        <v>97.5</v>
       </c>
       <c r="D418" s="4" t="s">
         <v>374</v>
@@ -7727,13 +7727,13 @@
     </row>
     <row r="419" spans="1:4">
       <c r="A419" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B419" s="3">
-        <v>439</v>
+        <v>401</v>
       </c>
       <c r="C419" s="3">
-        <v>35.75</v>
+        <v>24.7</v>
       </c>
       <c r="D419" s="4" t="s">
         <v>374</v>
@@ -7741,13 +7741,13 @@
     </row>
     <row r="420" spans="1:4">
       <c r="A420" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B420" s="3">
-        <v>150</v>
+        <v>439</v>
       </c>
       <c r="C420" s="3">
-        <v>9.1</v>
+        <v>35.75</v>
       </c>
       <c r="D420" s="4" t="s">
         <v>374</v>
@@ -7755,13 +7755,13 @@
     </row>
     <row r="421" spans="1:4">
       <c r="A421" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B421" s="3">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C421" s="3">
-        <v>5.43</v>
+        <v>9.1</v>
       </c>
       <c r="D421" s="4" t="s">
         <v>374</v>
@@ -7769,13 +7769,13 @@
     </row>
     <row r="422" spans="1:4">
       <c r="A422" t="s">
-        <v>432</v>
+        <v>379</v>
       </c>
       <c r="B422" s="3">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="C422" s="3">
-        <v>11.99</v>
+        <v>5.43</v>
       </c>
       <c r="D422" s="4" t="s">
         <v>374</v>
@@ -7783,27 +7783,27 @@
     </row>
     <row r="423" spans="1:4">
       <c r="A423" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
       <c r="B423" s="3">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="C423" s="3">
-        <v>9.75</v>
+        <v>11.99</v>
       </c>
       <c r="D423" s="4" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="424" spans="1:4">
       <c r="A424" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B424" s="3">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="C424" s="3">
-        <v>6.37</v>
+        <v>9.75</v>
       </c>
       <c r="D424" s="4" t="s">
         <v>380</v>
@@ -7811,13 +7811,13 @@
     </row>
     <row r="425" spans="1:4">
       <c r="A425" t="s">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="B425" s="3">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C425" s="3">
-        <v>10.53</v>
+        <v>6.37</v>
       </c>
       <c r="D425" s="4" t="s">
         <v>380</v>
@@ -7825,27 +7825,27 @@
     </row>
     <row r="426" spans="1:4">
       <c r="A426" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="B426" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C426" s="3">
-        <v>11.59</v>
+        <v>10.53</v>
       </c>
       <c r="D426" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="427" spans="1:4">
       <c r="A427" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="B427" s="3">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C427" s="3">
-        <v>12.09</v>
+        <v>11.59</v>
       </c>
       <c r="D427" s="4" t="s">
         <v>381</v>
@@ -7853,10 +7853,10 @@
     </row>
     <row r="428" spans="1:4">
       <c r="A428" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B428" s="3">
-        <v>195</v>
+        <v>36</v>
       </c>
       <c r="C428" s="3">
         <v>12.09</v>
@@ -7867,13 +7867,13 @@
     </row>
     <row r="429" spans="1:4">
       <c r="A429" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B429" s="3">
         <v>195</v>
       </c>
       <c r="C429" s="3">
-        <v>6.5</v>
+        <v>12.09</v>
       </c>
       <c r="D429" s="4" t="s">
         <v>381</v>
@@ -7881,10 +7881,10 @@
     </row>
     <row r="430" spans="1:4">
       <c r="A430" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B430" s="3">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="C430" s="3">
         <v>6.5</v>
@@ -7895,27 +7895,27 @@
     </row>
     <row r="431" spans="1:4">
       <c r="A431" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="B431" s="3">
-        <v>2</v>
+        <v>182</v>
       </c>
       <c r="C431" s="3">
-        <v>5017</v>
+        <v>6.5</v>
       </c>
       <c r="D431" s="4" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
     </row>
     <row r="432" spans="1:4">
       <c r="A432" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B432" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C432" s="3">
-        <v>4437.1499999999996</v>
+        <v>5017</v>
       </c>
       <c r="D432" s="4" t="s">
         <v>364</v>
@@ -7923,13 +7923,13 @@
     </row>
     <row r="433" spans="1:4">
       <c r="A433" t="s">
-        <v>429</v>
+        <v>453</v>
       </c>
       <c r="B433" s="3">
         <v>7</v>
       </c>
       <c r="C433" s="3">
-        <v>6239.83</v>
+        <v>4437.1499999999996</v>
       </c>
       <c r="D433" s="4" t="s">
         <v>364</v>
@@ -7937,13 +7937,13 @@
     </row>
     <row r="434" spans="1:4">
       <c r="A434" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="B434" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C434" s="3">
-        <v>5980</v>
+        <v>6239.83</v>
       </c>
       <c r="D434" s="4" t="s">
         <v>364</v>
@@ -7951,13 +7951,13 @@
     </row>
     <row r="435" spans="1:4">
       <c r="A435" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="B435" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C435" s="3">
-        <v>3556.4</v>
+        <v>5980</v>
       </c>
       <c r="D435" s="4" t="s">
         <v>364</v>
@@ -7965,13 +7965,13 @@
     </row>
     <row r="436" spans="1:4">
       <c r="A436" t="s">
-        <v>450</v>
+        <v>428</v>
       </c>
       <c r="B436" s="3">
         <v>2</v>
       </c>
       <c r="C436" s="3">
-        <v>6463</v>
+        <v>3556.4</v>
       </c>
       <c r="D436" s="4" t="s">
         <v>364</v>
@@ -7979,13 +7979,13 @@
     </row>
     <row r="437" spans="1:4">
       <c r="A437" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B437" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C437" s="3">
-        <v>5199</v>
+        <v>6463</v>
       </c>
       <c r="D437" s="4" t="s">
         <v>364</v>
@@ -7993,55 +7993,55 @@
     </row>
     <row r="438" spans="1:4">
       <c r="A438" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B438" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C438" s="3">
-        <v>70.25</v>
+        <v>5199</v>
       </c>
       <c r="D438" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="439" spans="1:4">
       <c r="A439" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="B439" s="3">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="C439" s="3">
-        <v>45</v>
+        <v>70.25</v>
       </c>
       <c r="D439" s="4" t="s">
-        <v>454</v>
+        <v>367</v>
       </c>
     </row>
     <row r="440" spans="1:4">
       <c r="A440" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B440" s="3">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C440" s="3">
-        <v>70.25</v>
+        <v>45</v>
       </c>
       <c r="D440" s="4" t="s">
-        <v>367</v>
+        <v>454</v>
       </c>
     </row>
     <row r="441" spans="1:4">
       <c r="A441" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B441" s="3">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C441" s="3">
-        <v>58.9</v>
+        <v>70.25</v>
       </c>
       <c r="D441" s="4" t="s">
         <v>367</v>
@@ -8049,13 +8049,13 @@
     </row>
     <row r="442" spans="1:4">
       <c r="A442" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B442" s="3">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="C442" s="3">
-        <v>89.21</v>
+        <v>58.9</v>
       </c>
       <c r="D442" s="4" t="s">
         <v>367</v>
@@ -8063,13 +8063,13 @@
     </row>
     <row r="443" spans="1:4">
       <c r="A443" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B443" s="3">
         <v>60</v>
       </c>
       <c r="C443" s="3">
-        <v>59.18</v>
+        <v>89.21</v>
       </c>
       <c r="D443" s="4" t="s">
         <v>367</v>
@@ -8077,13 +8077,13 @@
     </row>
     <row r="444" spans="1:4">
       <c r="A444" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B444" s="3">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C444" s="3">
-        <v>60.62</v>
+        <v>59.18</v>
       </c>
       <c r="D444" s="4" t="s">
         <v>367</v>
@@ -8091,13 +8091,13 @@
     </row>
     <row r="445" spans="1:4">
       <c r="A445" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B445" s="3">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="C445" s="3">
-        <v>3431.7</v>
+        <v>60.62</v>
       </c>
       <c r="D445" s="4" t="s">
         <v>367</v>
@@ -8105,13 +8105,13 @@
     </row>
     <row r="446" spans="1:4">
       <c r="A446" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B446" s="3">
         <v>3</v>
       </c>
       <c r="C446" s="3">
-        <v>1260.2</v>
+        <v>3431.7</v>
       </c>
       <c r="D446" s="4" t="s">
         <v>367</v>
@@ -8119,13 +8119,13 @@
     </row>
     <row r="447" spans="1:4">
       <c r="A447" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B447" s="3">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C447" s="3">
-        <v>47.2</v>
+        <v>1260.2</v>
       </c>
       <c r="D447" s="4" t="s">
         <v>367</v>
@@ -8133,15 +8133,29 @@
     </row>
     <row r="448" spans="1:4">
       <c r="A448" t="s">
+        <v>464</v>
+      </c>
+      <c r="B448" s="3">
+        <v>56</v>
+      </c>
+      <c r="C448" s="3">
+        <v>47.2</v>
+      </c>
+      <c r="D448" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4">
+      <c r="A449" t="s">
         <v>468</v>
       </c>
-      <c r="B448" s="3">
+      <c r="B449" s="3">
         <v>60</v>
       </c>
-      <c r="C448" s="3">
+      <c r="C449" s="3">
         <v>71.760000000000005</v>
       </c>
-      <c r="D448" s="4" t="s">
+      <c r="D449" s="4" t="s">
         <v>367</v>
       </c>
     </row>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="470">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -1421,6 +1421,9 @@
   </si>
   <si>
     <t>FUCHS TITAN FFL-52529 1L ulei DCT-LV</t>
+  </si>
+  <si>
+    <t>CYC PREMUS LI-CA NLGI2 410ml vaselina</t>
   </si>
 </sst>
 </file>
@@ -1865,7 +1868,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D449"/>
+  <dimension ref="A1:D450"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="49.85546875" customWidth="1"/>
@@ -1892,7 +1895,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="3">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="C2" s="3">
         <v>12.4</v>
@@ -2144,7 +2147,7 @@
         <v>396</v>
       </c>
       <c r="B20" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C20" s="3">
         <v>534.95000000000005</v>
@@ -2242,7 +2245,7 @@
         <v>403</v>
       </c>
       <c r="B27" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C27" s="3">
         <v>442.81</v>
@@ -2284,7 +2287,7 @@
         <v>422</v>
       </c>
       <c r="B30" s="3">
-        <v>401</v>
+        <v>377</v>
       </c>
       <c r="C30" s="3">
         <v>45.19</v>
@@ -2326,7 +2329,7 @@
         <v>423</v>
       </c>
       <c r="B33" s="3">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C33" s="3">
         <v>207.95</v>
@@ -2508,7 +2511,7 @@
         <v>13</v>
       </c>
       <c r="B46" s="3">
-        <v>1729</v>
+        <v>1693</v>
       </c>
       <c r="C46" s="3">
         <v>13</v>
@@ -2648,10 +2651,10 @@
         <v>22</v>
       </c>
       <c r="B56" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C56" s="3">
-        <v>1982.77</v>
+        <v>2731.15</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>368</v>
@@ -2690,7 +2693,7 @@
         <v>23</v>
       </c>
       <c r="B59" s="3">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C59" s="3">
         <v>255</v>
@@ -2984,7 +2987,7 @@
         <v>443</v>
       </c>
       <c r="B80" s="3">
-        <v>670</v>
+        <v>646</v>
       </c>
       <c r="C80" s="3">
         <v>19.48</v>
@@ -3023,41 +3026,41 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>446</v>
+        <v>469</v>
       </c>
       <c r="B83" s="3">
-        <v>41</v>
+        <v>240</v>
       </c>
       <c r="C83" s="3">
-        <v>22.21</v>
+        <v>14.42</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>447</v>
+        <v>357</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>40</v>
+        <v>446</v>
       </c>
       <c r="B84" s="3">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="C84" s="3">
-        <v>25.4</v>
+        <v>22.21</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>366</v>
+        <v>447</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B85" s="3">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C85" s="3">
-        <v>40.92</v>
+        <v>25.4</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>366</v>
@@ -3065,13 +3068,13 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B86" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C86" s="3">
-        <v>25.4</v>
+        <v>40.92</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>366</v>
@@ -3079,13 +3082,13 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B87" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C87" s="3">
-        <v>28.07</v>
+        <v>25.4</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>366</v>
@@ -3093,13 +3096,13 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>384</v>
+        <v>43</v>
       </c>
       <c r="B88" s="3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C88" s="3">
-        <v>23.33</v>
+        <v>28.07</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>366</v>
@@ -3107,41 +3110,41 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>44</v>
+        <v>384</v>
       </c>
       <c r="B89" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C89" s="3">
-        <v>34.630000000000003</v>
+        <v>23.33</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B90" s="3">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="C90" s="3">
-        <v>18.37</v>
+        <v>34.630000000000003</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B91" s="3">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="C91" s="3">
-        <v>82.88</v>
+        <v>18.37</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>369</v>
@@ -3149,13 +3152,13 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B92" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C92" s="3">
-        <v>161.01</v>
+        <v>82.88</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>369</v>
@@ -3163,13 +3166,13 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B93" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C93" s="3">
-        <v>50.23</v>
+        <v>161.01</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>369</v>
@@ -3177,55 +3180,55 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B94" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C94" s="3">
-        <v>65.83</v>
+        <v>50.23</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B95" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C95" s="3">
-        <v>46.76</v>
+        <v>65.83</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B96" s="3">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C96" s="3">
-        <v>62.11</v>
+        <v>46.76</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B97" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C97" s="3">
-        <v>47.61</v>
+        <v>62.11</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>367</v>
@@ -3233,13 +3236,13 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B98" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C98" s="3">
-        <v>63.76</v>
+        <v>47.61</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>367</v>
@@ -3247,13 +3250,13 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B99" s="3">
         <v>1</v>
       </c>
       <c r="C99" s="3">
-        <v>1159.2</v>
+        <v>63.76</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>367</v>
@@ -3261,13 +3264,13 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B100" s="3">
         <v>1</v>
       </c>
       <c r="C100" s="3">
-        <v>255</v>
+        <v>1159.2</v>
       </c>
       <c r="D100" s="4" t="s">
         <v>367</v>
@@ -3275,13 +3278,13 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B101" s="3">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C101" s="3">
-        <v>69.55</v>
+        <v>255</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>367</v>
@@ -3289,13 +3292,13 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C102" s="3">
-        <v>1391.04</v>
+        <v>69.55</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>367</v>
@@ -3303,13 +3306,13 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B103" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C103" s="3">
-        <v>87.1</v>
+        <v>1391.04</v>
       </c>
       <c r="D103" s="4" t="s">
         <v>367</v>
@@ -3317,13 +3320,13 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B104" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C104" s="3">
-        <v>40.54</v>
+        <v>87.1</v>
       </c>
       <c r="D104" s="4" t="s">
         <v>367</v>
@@ -3331,13 +3334,13 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B105" s="3">
         <v>1</v>
       </c>
       <c r="C105" s="3">
-        <v>460.01</v>
+        <v>40.54</v>
       </c>
       <c r="D105" s="4" t="s">
         <v>367</v>
@@ -3351,7 +3354,7 @@
         <v>1</v>
       </c>
       <c r="C106" s="3">
-        <v>639.4</v>
+        <v>460.01</v>
       </c>
       <c r="D106" s="4" t="s">
         <v>367</v>
@@ -3359,13 +3362,13 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B107" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C107" s="3">
-        <v>103.89</v>
+        <v>639.4</v>
       </c>
       <c r="D107" s="4" t="s">
         <v>367</v>
@@ -3373,13 +3376,13 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B108" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C108" s="3">
-        <v>58.48</v>
+        <v>103.89</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>367</v>
@@ -3387,13 +3390,13 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B109" s="3">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="C109" s="3">
-        <v>56.93</v>
+        <v>58.48</v>
       </c>
       <c r="D109" s="4" t="s">
         <v>367</v>
@@ -3404,10 +3407,10 @@
         <v>63</v>
       </c>
       <c r="B110" s="3">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C110" s="3">
-        <v>63.76</v>
+        <v>56.93</v>
       </c>
       <c r="D110" s="4" t="s">
         <v>367</v>
@@ -3415,13 +3418,13 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B111" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C111" s="3">
-        <v>61.92</v>
+        <v>63.76</v>
       </c>
       <c r="D111" s="4" t="s">
         <v>367</v>
@@ -3429,13 +3432,13 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B112" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C112" s="3">
-        <v>63.76</v>
+        <v>61.92</v>
       </c>
       <c r="D112" s="4" t="s">
         <v>367</v>
@@ -3443,13 +3446,13 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B113" s="3">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C113" s="3">
-        <v>69.56</v>
+        <v>63.76</v>
       </c>
       <c r="D113" s="4" t="s">
         <v>367</v>
@@ -3457,13 +3460,13 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B114" s="3">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C114" s="3">
-        <v>59.68</v>
+        <v>69.56</v>
       </c>
       <c r="D114" s="4" t="s">
         <v>367</v>
@@ -3471,13 +3474,13 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B115" s="3">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C115" s="3">
-        <v>56.93</v>
+        <v>59.68</v>
       </c>
       <c r="D115" s="4" t="s">
         <v>367</v>
@@ -3485,13 +3488,13 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B116" s="3">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="C116" s="3">
-        <v>80.73</v>
+        <v>56.93</v>
       </c>
       <c r="D116" s="4" t="s">
         <v>367</v>
@@ -3499,13 +3502,13 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B117" s="3">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C117" s="3">
-        <v>98.95</v>
+        <v>80.73</v>
       </c>
       <c r="D117" s="4" t="s">
         <v>367</v>
@@ -3513,13 +3516,13 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B118" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C118" s="3">
-        <v>93.25</v>
+        <v>98.95</v>
       </c>
       <c r="D118" s="4" t="s">
         <v>367</v>
@@ -3527,13 +3530,13 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B119" s="3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C119" s="3">
-        <v>63.76</v>
+        <v>93.25</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>367</v>
@@ -3541,10 +3544,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B120" s="3">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C120" s="3">
         <v>63.76</v>
@@ -3555,13 +3558,13 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B121" s="3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C121" s="3">
-        <v>81.150000000000006</v>
+        <v>63.76</v>
       </c>
       <c r="D121" s="4" t="s">
         <v>367</v>
@@ -3569,13 +3572,13 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B122" s="3">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C122" s="3">
-        <v>63.76</v>
+        <v>81.150000000000006</v>
       </c>
       <c r="D122" s="4" t="s">
         <v>367</v>
@@ -3583,13 +3586,13 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B123" s="3">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C123" s="3">
-        <v>69.87</v>
+        <v>63.76</v>
       </c>
       <c r="D123" s="4" t="s">
         <v>367</v>
@@ -3597,13 +3600,13 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B124" s="3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C124" s="3">
-        <v>63.76</v>
+        <v>69.87</v>
       </c>
       <c r="D124" s="4" t="s">
         <v>367</v>
@@ -3611,13 +3614,13 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B125" s="3">
-        <v>6</v>
-      </c>
-      <c r="C125" s="8">
-        <v>79.91</v>
+        <v>14</v>
+      </c>
+      <c r="C125" s="3">
+        <v>63.76</v>
       </c>
       <c r="D125" s="4" t="s">
         <v>367</v>
@@ -3625,13 +3628,13 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B126" s="3">
         <v>6</v>
       </c>
-      <c r="C126" s="3">
-        <v>69.56</v>
+      <c r="C126" s="8">
+        <v>79.91</v>
       </c>
       <c r="D126" s="4" t="s">
         <v>367</v>
@@ -3639,13 +3642,13 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B127" s="3">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="C127" s="3">
-        <v>52.17</v>
+        <v>69.56</v>
       </c>
       <c r="D127" s="4" t="s">
         <v>367</v>
@@ -3653,13 +3656,13 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B128" s="3">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="C128" s="3">
-        <v>208.66</v>
+        <v>52.17</v>
       </c>
       <c r="D128" s="4" t="s">
         <v>367</v>
@@ -3667,13 +3670,13 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B129" s="3">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C129" s="3">
-        <v>88.87</v>
+        <v>208.66</v>
       </c>
       <c r="D129" s="4" t="s">
         <v>367</v>
@@ -3681,13 +3684,13 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B130" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C130" s="3">
-        <v>67.27</v>
+        <v>88.87</v>
       </c>
       <c r="D130" s="4" t="s">
         <v>367</v>
@@ -3695,13 +3698,13 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B131" s="3">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C131" s="3">
-        <v>69.55</v>
+        <v>67.27</v>
       </c>
       <c r="D131" s="4" t="s">
         <v>367</v>
@@ -3709,13 +3712,13 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B132" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C132" s="3">
-        <v>63.89</v>
+        <v>69.55</v>
       </c>
       <c r="D132" s="4" t="s">
         <v>367</v>
@@ -3723,13 +3726,13 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B133" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C133" s="3">
-        <v>149.91</v>
+        <v>63.89</v>
       </c>
       <c r="D133" s="4" t="s">
         <v>367</v>
@@ -3737,13 +3740,13 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B134" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C134" s="3">
-        <v>38.57</v>
+        <v>149.91</v>
       </c>
       <c r="D134" s="4" t="s">
         <v>367</v>
@@ -3751,13 +3754,13 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B135" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C135" s="3">
-        <v>207.31</v>
+        <v>38.57</v>
       </c>
       <c r="D135" s="4" t="s">
         <v>367</v>
@@ -3765,16 +3768,16 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B136" s="3">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C136" s="3">
-        <v>58.24</v>
+        <v>207.31</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3782,10 +3785,10 @@
         <v>89</v>
       </c>
       <c r="B137" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C137" s="3">
-        <v>65.23</v>
+        <v>58.24</v>
       </c>
       <c r="D137" s="4" t="s">
         <v>364</v>
@@ -3793,13 +3796,13 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B138" s="3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C138" s="3">
-        <v>290.95</v>
+        <v>65.23</v>
       </c>
       <c r="D138" s="4" t="s">
         <v>364</v>
@@ -3810,10 +3813,10 @@
         <v>90</v>
       </c>
       <c r="B139" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C139" s="3">
-        <v>325.87</v>
+        <v>290.95</v>
       </c>
       <c r="D139" s="4" t="s">
         <v>364</v>
@@ -3821,27 +3824,27 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B140" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C140" s="3">
-        <v>5165.8</v>
+        <v>325.87</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B141" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C141" s="3">
-        <v>511.75</v>
+        <v>5165.8</v>
       </c>
       <c r="D141" s="4" t="s">
         <v>367</v>
@@ -3849,13 +3852,13 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B142" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C142" s="3">
-        <v>572.70000000000005</v>
+        <v>511.75</v>
       </c>
       <c r="D142" s="4" t="s">
         <v>367</v>
@@ -3863,55 +3866,55 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B143" s="3">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="C143" s="3">
-        <v>66.98</v>
+        <v>572.70000000000005</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B144" s="3">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="C144" s="3">
-        <v>367.42</v>
+        <v>66.98</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B145" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C145" s="3">
-        <v>51.52</v>
+        <v>367.42</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B146" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C146" s="3">
-        <v>23.19</v>
+        <v>51.52</v>
       </c>
       <c r="D146" s="4" t="s">
         <v>366</v>
@@ -3919,10 +3922,10 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B147" s="3">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C147" s="3">
         <v>23.19</v>
@@ -3933,27 +3936,27 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B148" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C148" s="3">
-        <v>69.55</v>
+        <v>23.19</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B149" s="3">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C149" s="3">
-        <v>3169.7</v>
+        <v>69.55</v>
       </c>
       <c r="D149" s="4" t="s">
         <v>367</v>
@@ -3961,13 +3964,13 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B150" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C150" s="3">
-        <v>81.14</v>
+        <v>3169.7</v>
       </c>
       <c r="D150" s="4" t="s">
         <v>367</v>
@@ -3975,10 +3978,10 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B151" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C151" s="3">
         <v>81.14</v>
@@ -3989,41 +3992,41 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B152" s="3">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C152" s="3">
-        <v>66.98</v>
+        <v>81.14</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B153" s="3">
-        <v>30</v>
-      </c>
-      <c r="C153" s="8">
-        <v>77.63</v>
+        <v>58</v>
+      </c>
+      <c r="C153" s="3">
+        <v>66.98</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
     </row>
     <row r="154" spans="1:4">
       <c r="A154" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B154" s="3">
-        <v>26</v>
-      </c>
-      <c r="C154" s="3">
-        <v>93.35</v>
+        <v>30</v>
+      </c>
+      <c r="C154" s="8">
+        <v>77.63</v>
       </c>
       <c r="D154" s="4" t="s">
         <v>367</v>
@@ -4031,13 +4034,13 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B155" s="3">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C155" s="3">
-        <v>1217.1600000000001</v>
+        <v>93.35</v>
       </c>
       <c r="D155" s="4" t="s">
         <v>367</v>
@@ -4045,13 +4048,13 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B156" s="3">
         <v>0</v>
       </c>
       <c r="C156" s="3">
-        <v>3079</v>
+        <v>1217.1600000000001</v>
       </c>
       <c r="D156" s="4" t="s">
         <v>367</v>
@@ -4059,16 +4062,16 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B157" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C157" s="3">
-        <v>43.7</v>
+        <v>3079</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4076,10 +4079,10 @@
         <v>108</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C158" s="3">
-        <v>48.95</v>
+        <v>43.7</v>
       </c>
       <c r="D158" s="4" t="s">
         <v>366</v>
@@ -4087,27 +4090,27 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B159" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C159" s="3">
-        <v>72.33</v>
+        <v>48.95</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B160" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C160" s="3">
-        <v>284.19</v>
+        <v>72.33</v>
       </c>
       <c r="D160" s="4" t="s">
         <v>364</v>
@@ -4115,38 +4118,38 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B161" s="3">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C161" s="3">
-        <v>101.5</v>
+        <v>284.19</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="162" spans="1:4">
       <c r="A162" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B162" s="3">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="C162" s="3">
-        <v>32.200000000000003</v>
+        <v>101.5</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B163" s="3">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="C163" s="3">
         <v>32.200000000000003</v>
@@ -4157,13 +4160,13 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B164" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C164" s="3">
-        <v>37.43</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D164" s="4" t="s">
         <v>354</v>
@@ -4171,13 +4174,13 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B165" s="3">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="C165" s="3">
-        <v>32.200000000000003</v>
+        <v>37.43</v>
       </c>
       <c r="D165" s="4" t="s">
         <v>354</v>
@@ -4185,41 +4188,41 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B166" s="3">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="C166" s="3">
-        <v>115.01</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B167" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C167" s="3">
-        <v>38.39</v>
+        <v>115.01</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B168" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C168" s="3">
-        <v>151.47999999999999</v>
+        <v>38.39</v>
       </c>
       <c r="D168" s="4" t="s">
         <v>364</v>
@@ -4227,13 +4230,13 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B169" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C169" s="3">
-        <v>181.68</v>
+        <v>151.47999999999999</v>
       </c>
       <c r="D169" s="4" t="s">
         <v>364</v>
@@ -4241,27 +4244,27 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B170" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C170" s="3">
-        <v>20.059999999999999</v>
+        <v>181.68</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
     </row>
     <row r="171" spans="1:4">
       <c r="A171" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B171" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C171" s="3">
-        <v>12.88</v>
+        <v>20.059999999999999</v>
       </c>
       <c r="D171" s="4" t="s">
         <v>355</v>
@@ -4269,13 +4272,13 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B172" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C172" s="3">
-        <v>26.73</v>
+        <v>12.88</v>
       </c>
       <c r="D172" s="4" t="s">
         <v>355</v>
@@ -4283,13 +4286,13 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B173" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C173" s="3">
-        <v>29.95</v>
+        <v>26.73</v>
       </c>
       <c r="D173" s="4" t="s">
         <v>355</v>
@@ -4297,13 +4300,13 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B174" s="3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C174" s="3">
-        <v>58.68</v>
+        <v>29.95</v>
       </c>
       <c r="D174" s="4" t="s">
         <v>355</v>
@@ -4311,13 +4314,13 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B175" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C175" s="3">
-        <v>79.98</v>
+        <v>58.68</v>
       </c>
       <c r="D175" s="4" t="s">
         <v>355</v>
@@ -4325,55 +4328,55 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B176" s="3">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C176" s="3">
-        <v>38.770000000000003</v>
+        <v>79.98</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="177" spans="1:4">
       <c r="A177" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B177" s="3">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C177" s="3">
-        <v>107.35</v>
+        <v>38.770000000000003</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
     </row>
     <row r="178" spans="1:4">
       <c r="A178" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B178" s="3">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C178" s="3">
-        <v>61.83</v>
+        <v>107.35</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="179" spans="1:4">
       <c r="A179" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B179" s="3">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C179" s="3">
-        <v>243.16</v>
+        <v>61.83</v>
       </c>
       <c r="D179" s="4" t="s">
         <v>364</v>
@@ -4381,41 +4384,41 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B180" s="3">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C180" s="3">
-        <v>63.78</v>
+        <v>243.16</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="181" spans="1:4">
       <c r="A181" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B181" s="3">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C181" s="3">
-        <v>75.989999999999995</v>
+        <v>63.78</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="182" spans="1:4">
       <c r="A182" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B182" s="3">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C182" s="3">
-        <v>297.64999999999998</v>
+        <v>75.989999999999995</v>
       </c>
       <c r="D182" s="4" t="s">
         <v>364</v>
@@ -4423,13 +4426,13 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B183" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C183" s="3">
-        <v>77.28</v>
+        <v>297.64999999999998</v>
       </c>
       <c r="D183" s="4" t="s">
         <v>364</v>
@@ -4437,13 +4440,13 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B184" s="3">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C184" s="3">
-        <v>75.989999999999995</v>
+        <v>77.28</v>
       </c>
       <c r="D184" s="4" t="s">
         <v>364</v>
@@ -4451,13 +4454,13 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B185" s="3">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C185" s="3">
-        <v>342.24</v>
+        <v>75.989999999999995</v>
       </c>
       <c r="D185" s="4" t="s">
         <v>364</v>
@@ -4465,27 +4468,27 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B186" s="3">
         <v>2</v>
       </c>
       <c r="C186" s="3">
-        <v>633.75</v>
+        <v>342.24</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="187" spans="1:4">
       <c r="A187" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B187" s="3">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="C187" s="3">
-        <v>50.51</v>
+        <v>633.75</v>
       </c>
       <c r="D187" s="4" t="s">
         <v>367</v>
@@ -4493,13 +4496,13 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" t="s">
-        <v>430</v>
+        <v>137</v>
       </c>
       <c r="B188" s="3">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="C188" s="3">
-        <v>581.9</v>
+        <v>50.51</v>
       </c>
       <c r="D188" s="4" t="s">
         <v>367</v>
@@ -4507,13 +4510,13 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" t="s">
-        <v>138</v>
+        <v>430</v>
       </c>
       <c r="B189" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C189" s="3">
-        <v>579.13</v>
+        <v>581.9</v>
       </c>
       <c r="D189" s="4" t="s">
         <v>367</v>
@@ -4521,55 +4524,55 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B190" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C190" s="3">
-        <v>122.36</v>
+        <v>579.13</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="191" spans="1:4">
       <c r="A191" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B191" s="3">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C191" s="3">
-        <v>35.81</v>
+        <v>122.36</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
     </row>
     <row r="192" spans="1:4">
       <c r="A192" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B192" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C192" s="3">
-        <v>59.25</v>
+        <v>35.81</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="193" spans="1:4">
       <c r="A193" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B193" s="3">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C193" s="3">
-        <v>260</v>
+        <v>59.25</v>
       </c>
       <c r="D193" s="4" t="s">
         <v>364</v>
@@ -4577,13 +4580,13 @@
     </row>
     <row r="194" spans="1:4">
       <c r="A194" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B194" s="3">
-        <v>22</v>
-      </c>
-      <c r="C194" s="7">
-        <v>59.62</v>
+        <v>2</v>
+      </c>
+      <c r="C194" s="3">
+        <v>260</v>
       </c>
       <c r="D194" s="4" t="s">
         <v>364</v>
@@ -4591,13 +4594,13 @@
     </row>
     <row r="195" spans="1:4">
       <c r="A195" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B195" s="3">
-        <v>4</v>
-      </c>
-      <c r="C195" s="3">
-        <v>248.77</v>
+        <v>22</v>
+      </c>
+      <c r="C195" s="7">
+        <v>59.62</v>
       </c>
       <c r="D195" s="4" t="s">
         <v>364</v>
@@ -4605,13 +4608,13 @@
     </row>
     <row r="196" spans="1:4">
       <c r="A196" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B196" s="3">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C196" s="3">
-        <v>74.7</v>
+        <v>248.77</v>
       </c>
       <c r="D196" s="4" t="s">
         <v>364</v>
@@ -4619,13 +4622,13 @@
     </row>
     <row r="197" spans="1:4">
       <c r="A197" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B197" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C197" s="3">
-        <v>296.3</v>
+        <v>74.7</v>
       </c>
       <c r="D197" s="4" t="s">
         <v>364</v>
@@ -4633,13 +4636,13 @@
     </row>
     <row r="198" spans="1:4">
       <c r="A198" t="s">
-        <v>385</v>
+        <v>146</v>
       </c>
       <c r="B198" s="3">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C198" s="3">
-        <v>168.7</v>
+        <v>296.3</v>
       </c>
       <c r="D198" s="4" t="s">
         <v>364</v>
@@ -4647,13 +4650,13 @@
     </row>
     <row r="199" spans="1:4">
       <c r="A199" t="s">
-        <v>147</v>
+        <v>385</v>
       </c>
       <c r="B199" s="3">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="C199" s="3">
-        <v>44.5</v>
+        <v>168.7</v>
       </c>
       <c r="D199" s="4" t="s">
         <v>364</v>
@@ -4661,13 +4664,13 @@
     </row>
     <row r="200" spans="1:4">
       <c r="A200" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B200" s="3">
-        <v>10</v>
-      </c>
-      <c r="C200" s="10">
-        <v>210.88</v>
+        <v>26</v>
+      </c>
+      <c r="C200" s="3">
+        <v>44.5</v>
       </c>
       <c r="D200" s="4" t="s">
         <v>364</v>
@@ -4675,13 +4678,13 @@
     </row>
     <row r="201" spans="1:4">
       <c r="A201" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B201" s="3">
-        <v>2</v>
-      </c>
-      <c r="C201" s="3">
-        <v>2189.02</v>
+        <v>9</v>
+      </c>
+      <c r="C201" s="10">
+        <v>210.88</v>
       </c>
       <c r="D201" s="4" t="s">
         <v>364</v>
@@ -4689,13 +4692,13 @@
     </row>
     <row r="202" spans="1:4">
       <c r="A202" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B202" s="3">
         <v>2</v>
       </c>
       <c r="C202" s="3">
-        <v>453.22</v>
+        <v>2189.02</v>
       </c>
       <c r="D202" s="4" t="s">
         <v>364</v>
@@ -4703,13 +4706,13 @@
     </row>
     <row r="203" spans="1:4">
       <c r="A203" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B203" s="3">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C203" s="3">
-        <v>48.64</v>
+        <v>453.22</v>
       </c>
       <c r="D203" s="4" t="s">
         <v>364</v>
@@ -4717,13 +4720,13 @@
     </row>
     <row r="204" spans="1:4">
       <c r="A204" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B204" s="3">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C204" s="3">
-        <v>126.63</v>
+        <v>48.64</v>
       </c>
       <c r="D204" s="4" t="s">
         <v>364</v>
@@ -4731,41 +4734,41 @@
     </row>
     <row r="205" spans="1:4">
       <c r="A205" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B205" s="3">
         <v>5</v>
       </c>
       <c r="C205" s="3">
-        <v>69.56</v>
+        <v>126.63</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="206" spans="1:4">
       <c r="A206" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B206" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C206" s="3">
-        <v>44.51</v>
+        <v>69.56</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="207" spans="1:4">
       <c r="A207" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B207" s="3">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C207" s="3">
-        <v>145.94</v>
+        <v>44.51</v>
       </c>
       <c r="D207" s="4" t="s">
         <v>364</v>
@@ -4773,13 +4776,13 @@
     </row>
     <row r="208" spans="1:4">
       <c r="A208" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B208" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C208" s="3">
-        <v>199.77</v>
+        <v>145.94</v>
       </c>
       <c r="D208" s="4" t="s">
         <v>364</v>
@@ -4787,13 +4790,13 @@
     </row>
     <row r="209" spans="1:4">
       <c r="A209" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B209" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C209" s="3">
-        <v>2060</v>
+        <v>199.77</v>
       </c>
       <c r="D209" s="4" t="s">
         <v>364</v>
@@ -4801,13 +4804,13 @@
     </row>
     <row r="210" spans="1:4">
       <c r="A210" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B210" s="3">
-        <v>34</v>
-      </c>
-      <c r="C210" s="8">
-        <v>58.32</v>
+        <v>0</v>
+      </c>
+      <c r="C210" s="3">
+        <v>2060</v>
       </c>
       <c r="D210" s="4" t="s">
         <v>364</v>
@@ -4815,13 +4818,13 @@
     </row>
     <row r="211" spans="1:4">
       <c r="A211" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B211" s="3">
-        <v>2</v>
-      </c>
-      <c r="C211" s="3">
-        <v>183.41</v>
+        <v>34</v>
+      </c>
+      <c r="C211" s="8">
+        <v>58.32</v>
       </c>
       <c r="D211" s="4" t="s">
         <v>364</v>
@@ -4829,13 +4832,13 @@
     </row>
     <row r="212" spans="1:4">
       <c r="A212" t="s">
-        <v>352</v>
+        <v>159</v>
       </c>
       <c r="B212" s="3">
-        <v>8</v>
-      </c>
-      <c r="C212" s="8">
-        <v>257.70999999999998</v>
+        <v>2</v>
+      </c>
+      <c r="C212" s="3">
+        <v>183.41</v>
       </c>
       <c r="D212" s="4" t="s">
         <v>364</v>
@@ -4843,41 +4846,41 @@
     </row>
     <row r="213" spans="1:4">
       <c r="A213" t="s">
-        <v>160</v>
+        <v>352</v>
       </c>
       <c r="B213" s="3">
-        <v>34</v>
-      </c>
-      <c r="C213" s="3">
-        <v>33.479999999999997</v>
+        <v>8</v>
+      </c>
+      <c r="C213" s="8">
+        <v>257.70999999999998</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="214" spans="1:4">
       <c r="A214" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B214" s="3">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="C214" s="3">
-        <v>48.13</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D214" s="4" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="215" spans="1:4">
       <c r="A215" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B215" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C215" s="3">
-        <v>5400</v>
+        <v>48.13</v>
       </c>
       <c r="D215" s="4" t="s">
         <v>364</v>
@@ -4885,13 +4888,13 @@
     </row>
     <row r="216" spans="1:4">
       <c r="A216" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B216" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C216" s="3">
-        <v>170.78</v>
+        <v>5400</v>
       </c>
       <c r="D216" s="4" t="s">
         <v>364</v>
@@ -4899,13 +4902,13 @@
     </row>
     <row r="217" spans="1:4">
       <c r="A217" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B217" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C217" s="3">
-        <v>216.3</v>
+        <v>170.78</v>
       </c>
       <c r="D217" s="4" t="s">
         <v>364</v>
@@ -4913,13 +4916,13 @@
     </row>
     <row r="218" spans="1:4">
       <c r="A218" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B218" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="C218" s="3">
-        <v>59.7</v>
+        <v>216.3</v>
       </c>
       <c r="D218" s="4" t="s">
         <v>364</v>
@@ -4927,13 +4930,13 @@
     </row>
     <row r="219" spans="1:4">
       <c r="A219" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B219" s="3">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C219" s="3">
-        <v>265.05</v>
+        <v>59.7</v>
       </c>
       <c r="D219" s="4" t="s">
         <v>364</v>
@@ -4941,97 +4944,97 @@
     </row>
     <row r="220" spans="1:4">
       <c r="A220" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B220" s="3">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C220" s="3">
-        <v>36.799999999999997</v>
+        <v>265.05</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="221" spans="1:4">
       <c r="A221" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B221" s="3">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C221" s="3">
-        <v>103.04</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
     </row>
     <row r="222" spans="1:4">
       <c r="A222" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B222" s="3">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="C222" s="3">
-        <v>36.75</v>
+        <v>103.04</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
     </row>
     <row r="223" spans="1:4">
       <c r="A223" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B223" s="3">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="C223" s="3">
-        <v>47.16</v>
+        <v>36.75</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
     </row>
     <row r="224" spans="1:4">
       <c r="A224" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B224" s="3">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C224" s="3">
-        <v>16.809999999999999</v>
+        <v>47.16</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="225" spans="1:4">
       <c r="A225" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B225" s="3">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C225" s="3">
-        <v>37.299999999999997</v>
+        <v>16.809999999999999</v>
       </c>
       <c r="D225" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="226" spans="1:4">
       <c r="A226" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B226" s="3">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="C226" s="3">
-        <v>126.24</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="D226" s="4" t="s">
         <v>364</v>
@@ -5039,13 +5042,13 @@
     </row>
     <row r="227" spans="1:4">
       <c r="A227" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B227" s="3">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C227" s="3">
-        <v>154.62</v>
+        <v>126.24</v>
       </c>
       <c r="D227" s="4" t="s">
         <v>364</v>
@@ -5053,13 +5056,13 @@
     </row>
     <row r="228" spans="1:4">
       <c r="A228" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B228" s="3">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C228" s="3">
-        <v>508.2</v>
+        <v>154.62</v>
       </c>
       <c r="D228" s="4" t="s">
         <v>364</v>
@@ -5067,13 +5070,13 @@
     </row>
     <row r="229" spans="1:4">
       <c r="A229" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B229" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C229" s="3">
-        <v>5069</v>
+        <v>508.2</v>
       </c>
       <c r="D229" s="4" t="s">
         <v>364</v>
@@ -5081,13 +5084,13 @@
     </row>
     <row r="230" spans="1:4">
       <c r="A230" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B230" s="3">
         <v>0</v>
       </c>
       <c r="C230" s="3">
-        <v>466.78</v>
+        <v>5069</v>
       </c>
       <c r="D230" s="4" t="s">
         <v>364</v>
@@ -5095,27 +5098,27 @@
     </row>
     <row r="231" spans="1:4">
       <c r="A231" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B231" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C231" s="3">
-        <v>57.5</v>
+        <v>466.78</v>
       </c>
       <c r="D231" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="232" spans="1:4">
       <c r="A232" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B232" s="3">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C232" s="3">
-        <v>63.13</v>
+        <v>57.5</v>
       </c>
       <c r="D232" s="4" t="s">
         <v>367</v>
@@ -5123,13 +5126,13 @@
     </row>
     <row r="233" spans="1:4">
       <c r="A233" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B233" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C233" s="3">
-        <v>20789.41</v>
+        <v>63.13</v>
       </c>
       <c r="D233" s="4" t="s">
         <v>367</v>
@@ -5143,7 +5146,7 @@
         <v>1</v>
       </c>
       <c r="C234" s="3">
-        <v>33057.85</v>
+        <v>20789.41</v>
       </c>
       <c r="D234" s="4" t="s">
         <v>367</v>
@@ -5151,13 +5154,13 @@
     </row>
     <row r="235" spans="1:4">
       <c r="A235" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B235" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C235" s="3">
-        <v>83.5</v>
+        <v>33057.85</v>
       </c>
       <c r="D235" s="4" t="s">
         <v>367</v>
@@ -5165,16 +5168,16 @@
     </row>
     <row r="236" spans="1:4">
       <c r="A236" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B236" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C236" s="3">
-        <v>45.72</v>
+        <v>83.5</v>
       </c>
       <c r="D236" s="4" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5182,10 +5185,10 @@
         <v>182</v>
       </c>
       <c r="B237" s="3">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C237" s="3">
-        <v>81.650000000000006</v>
+        <v>45.72</v>
       </c>
       <c r="D237" s="4" t="s">
         <v>419</v>
@@ -5193,13 +5196,13 @@
     </row>
     <row r="238" spans="1:4">
       <c r="A238" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B238" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C238" s="3">
-        <v>50.71</v>
+        <v>81.650000000000006</v>
       </c>
       <c r="D238" s="4" t="s">
         <v>419</v>
@@ -5207,13 +5210,13 @@
     </row>
     <row r="239" spans="1:4">
       <c r="A239" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B239" s="3">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C239" s="3">
-        <v>51.75</v>
+        <v>50.71</v>
       </c>
       <c r="D239" s="4" t="s">
         <v>419</v>
@@ -5221,13 +5224,13 @@
     </row>
     <row r="240" spans="1:4">
       <c r="A240" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B240" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C240" s="3">
-        <v>36.94</v>
+        <v>51.75</v>
       </c>
       <c r="D240" s="4" t="s">
         <v>419</v>
@@ -5235,13 +5238,13 @@
     </row>
     <row r="241" spans="1:4">
       <c r="A241" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B241" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C241" s="3">
-        <v>36.799999999999997</v>
+        <v>36.94</v>
       </c>
       <c r="D241" s="4" t="s">
         <v>419</v>
@@ -5255,7 +5258,7 @@
         <v>12</v>
       </c>
       <c r="C242" s="3">
-        <v>79.58</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D242" s="4" t="s">
         <v>419</v>
@@ -5263,27 +5266,27 @@
     </row>
     <row r="243" spans="1:4">
       <c r="A243" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B243" s="3">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C243" s="3">
-        <v>67.28</v>
+        <v>79.58</v>
       </c>
       <c r="D243" s="4" t="s">
-        <v>367</v>
+        <v>419</v>
       </c>
     </row>
     <row r="244" spans="1:4">
       <c r="A244" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B244" s="3">
-        <v>27</v>
-      </c>
-      <c r="C244" s="8">
-        <v>79.599999999999994</v>
+        <v>30</v>
+      </c>
+      <c r="C244" s="3">
+        <v>67.28</v>
       </c>
       <c r="D244" s="4" t="s">
         <v>367</v>
@@ -5291,13 +5294,13 @@
     </row>
     <row r="245" spans="1:4">
       <c r="A245" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B245" s="3">
         <v>27</v>
       </c>
       <c r="C245" s="8">
-        <v>75.88</v>
+        <v>79.599999999999994</v>
       </c>
       <c r="D245" s="4" t="s">
         <v>367</v>
@@ -5305,13 +5308,13 @@
     </row>
     <row r="246" spans="1:4">
       <c r="A246" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B246" s="3">
-        <v>21</v>
-      </c>
-      <c r="C246" s="3">
-        <v>109.08</v>
+        <v>27</v>
+      </c>
+      <c r="C246" s="8">
+        <v>75.88</v>
       </c>
       <c r="D246" s="4" t="s">
         <v>367</v>
@@ -5319,27 +5322,27 @@
     </row>
     <row r="247" spans="1:4">
       <c r="A247" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B247" s="3">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="C247" s="3">
-        <v>33.479999999999997</v>
+        <v>109.08</v>
       </c>
       <c r="D247" s="4" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
     </row>
     <row r="248" spans="1:4">
       <c r="A248" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B248" s="3">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="C248" s="3">
-        <v>422.09</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D248" s="4" t="s">
         <v>356</v>
@@ -5347,13 +5350,13 @@
     </row>
     <row r="249" spans="1:4">
       <c r="A249" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B249" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C249" s="3">
-        <v>1277.7</v>
+        <v>422.09</v>
       </c>
       <c r="D249" s="4" t="s">
         <v>356</v>
@@ -5361,27 +5364,27 @@
     </row>
     <row r="250" spans="1:4">
       <c r="A250" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B250" s="3">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C250" s="3">
-        <v>6.44</v>
+        <v>1277.7</v>
       </c>
       <c r="D250" s="4" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
     </row>
     <row r="251" spans="1:4">
       <c r="A251" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B251" s="3">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C251" s="3">
-        <v>108.2</v>
+        <v>6.44</v>
       </c>
       <c r="D251" s="4" t="s">
         <v>366</v>
@@ -5389,16 +5392,16 @@
     </row>
     <row r="252" spans="1:4">
       <c r="A252" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B252" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C252" s="3">
-        <v>4456.4799999999996</v>
+        <v>108.2</v>
       </c>
       <c r="D252" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5406,10 +5409,10 @@
         <v>196</v>
       </c>
       <c r="B253" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C253" s="3">
-        <v>7429</v>
+        <v>4456.4799999999996</v>
       </c>
       <c r="D253" s="4" t="s">
         <v>364</v>
@@ -5417,13 +5420,13 @@
     </row>
     <row r="254" spans="1:4">
       <c r="A254" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B254" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C254" s="3">
-        <v>609.5</v>
+        <v>7429</v>
       </c>
       <c r="D254" s="4" t="s">
         <v>364</v>
@@ -5431,24 +5434,24 @@
     </row>
     <row r="255" spans="1:4">
       <c r="A255" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B255" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C255" s="3">
-        <v>32.200000000000003</v>
+        <v>609.5</v>
       </c>
       <c r="D255" s="4" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
     </row>
     <row r="256" spans="1:4">
       <c r="A256" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B256" s="3">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C256" s="3">
         <v>32.200000000000003</v>
@@ -5459,10 +5462,10 @@
     </row>
     <row r="257" spans="1:4">
       <c r="A257" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B257" s="3">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C257" s="3">
         <v>32.200000000000003</v>
@@ -5473,10 +5476,10 @@
     </row>
     <row r="258" spans="1:4">
       <c r="A258" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B258" s="3">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="C258" s="3">
         <v>32.200000000000003</v>
@@ -5487,13 +5490,13 @@
     </row>
     <row r="259" spans="1:4">
       <c r="A259" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B259" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C259" s="3">
-        <v>40.4</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D259" s="4" t="s">
         <v>354</v>
@@ -5501,13 +5504,13 @@
     </row>
     <row r="260" spans="1:4">
       <c r="A260" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B260" s="3">
-        <v>175</v>
+        <v>3</v>
       </c>
       <c r="C260" s="3">
-        <v>36.06</v>
+        <v>40.4</v>
       </c>
       <c r="D260" s="4" t="s">
         <v>354</v>
@@ -5515,27 +5518,27 @@
     </row>
     <row r="261" spans="1:4">
       <c r="A261" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B261" s="3">
-        <v>10</v>
+        <v>175</v>
       </c>
       <c r="C261" s="3">
-        <v>56</v>
+        <v>36.06</v>
       </c>
       <c r="D261" s="4" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
     </row>
     <row r="262" spans="1:4">
       <c r="A262" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B262" s="3">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C262" s="3">
-        <v>57.63</v>
+        <v>56</v>
       </c>
       <c r="D262" s="4" t="s">
         <v>367</v>
@@ -5543,13 +5546,13 @@
     </row>
     <row r="263" spans="1:4">
       <c r="A263" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B263" s="3">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C263" s="3">
-        <v>60.78</v>
+        <v>57.63</v>
       </c>
       <c r="D263" s="4" t="s">
         <v>367</v>
@@ -5557,69 +5560,69 @@
     </row>
     <row r="264" spans="1:4">
       <c r="A264" t="s">
-        <v>420</v>
+        <v>206</v>
       </c>
       <c r="B264" s="3">
         <v>4</v>
       </c>
       <c r="C264" s="3">
-        <v>65</v>
+        <v>60.78</v>
       </c>
       <c r="D264" s="4" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
     </row>
     <row r="265" spans="1:4">
       <c r="A265" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B265" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C265" s="3">
-        <v>29.63</v>
+        <v>65</v>
       </c>
       <c r="D265" s="4" t="s">
-        <v>354</v>
+        <v>419</v>
       </c>
     </row>
     <row r="266" spans="1:4">
       <c r="A266" t="s">
-        <v>207</v>
+        <v>421</v>
       </c>
       <c r="B266" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C266" s="3">
-        <v>42.49</v>
+        <v>29.63</v>
       </c>
       <c r="D266" s="4" t="s">
-        <v>419</v>
+        <v>354</v>
       </c>
     </row>
     <row r="267" spans="1:4">
       <c r="A267" t="s">
-        <v>208</v>
-      </c>
-      <c r="B267" s="4">
-        <v>18</v>
-      </c>
-      <c r="C267" s="8">
-        <v>86.95</v>
+        <v>207</v>
+      </c>
+      <c r="B267" s="3">
+        <v>0</v>
+      </c>
+      <c r="C267" s="3">
+        <v>42.49</v>
       </c>
       <c r="D267" s="4" t="s">
-        <v>364</v>
+        <v>419</v>
       </c>
     </row>
     <row r="268" spans="1:4">
       <c r="A268" t="s">
-        <v>209</v>
-      </c>
-      <c r="B268" s="3">
-        <v>2</v>
+        <v>208</v>
+      </c>
+      <c r="B268" s="4">
+        <v>18</v>
       </c>
       <c r="C268" s="8">
-        <v>312.57</v>
+        <v>86.95</v>
       </c>
       <c r="D268" s="4" t="s">
         <v>364</v>
@@ -5627,13 +5630,13 @@
     </row>
     <row r="269" spans="1:4">
       <c r="A269" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B269" s="3">
-        <v>14</v>
-      </c>
-      <c r="C269" s="3">
-        <v>71.709999999999994</v>
+        <v>2</v>
+      </c>
+      <c r="C269" s="8">
+        <v>312.57</v>
       </c>
       <c r="D269" s="4" t="s">
         <v>364</v>
@@ -5641,41 +5644,41 @@
     </row>
     <row r="270" spans="1:4">
       <c r="A270" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B270" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C270" s="3">
-        <v>77.760000000000005</v>
+        <v>71.709999999999994</v>
       </c>
       <c r="D270" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="271" spans="1:4">
       <c r="A271" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B271" s="3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C271" s="3">
-        <v>54.7</v>
+        <v>77.760000000000005</v>
       </c>
       <c r="D271" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="272" spans="1:4">
       <c r="A272" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B272" s="3">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C272" s="3">
-        <v>67.28</v>
+        <v>54.7</v>
       </c>
       <c r="D272" s="4" t="s">
         <v>364</v>
@@ -5683,13 +5686,13 @@
     </row>
     <row r="273" spans="1:4">
       <c r="A273" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B273" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C273" s="3">
-        <v>334.36</v>
+        <v>67.28</v>
       </c>
       <c r="D273" s="4" t="s">
         <v>364</v>
@@ -5697,13 +5700,13 @@
     </row>
     <row r="274" spans="1:4">
       <c r="A274" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B274" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C274" s="3">
-        <v>78.87</v>
+        <v>334.36</v>
       </c>
       <c r="D274" s="4" t="s">
         <v>364</v>
@@ -5711,13 +5714,13 @@
     </row>
     <row r="275" spans="1:4">
       <c r="A275" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B275" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C275" s="3">
-        <v>83.84</v>
+        <v>78.87</v>
       </c>
       <c r="D275" s="4" t="s">
         <v>364</v>
@@ -5725,13 +5728,13 @@
     </row>
     <row r="276" spans="1:4">
       <c r="A276" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B276" s="3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C276" s="3">
-        <v>331.2</v>
+        <v>83.84</v>
       </c>
       <c r="D276" s="4" t="s">
         <v>364</v>
@@ -5739,13 +5742,13 @@
     </row>
     <row r="277" spans="1:4">
       <c r="A277" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B277" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C277" s="3">
-        <v>79.75</v>
+        <v>331.2</v>
       </c>
       <c r="D277" s="4" t="s">
         <v>364</v>
@@ -5753,13 +5756,13 @@
     </row>
     <row r="278" spans="1:4">
       <c r="A278" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B278" s="3">
         <v>7</v>
       </c>
       <c r="C278" s="3">
-        <v>83.84</v>
+        <v>79.75</v>
       </c>
       <c r="D278" s="4" t="s">
         <v>364</v>
@@ -5767,13 +5770,13 @@
     </row>
     <row r="279" spans="1:4">
       <c r="A279" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B279" s="3">
-        <v>2</v>
-      </c>
-      <c r="C279" s="8">
-        <v>347.3</v>
+        <v>7</v>
+      </c>
+      <c r="C279" s="3">
+        <v>83.84</v>
       </c>
       <c r="D279" s="4" t="s">
         <v>364</v>
@@ -5784,10 +5787,10 @@
         <v>220</v>
       </c>
       <c r="B280" s="3">
-        <v>4</v>
-      </c>
-      <c r="C280" s="3">
-        <v>284</v>
+        <v>2</v>
+      </c>
+      <c r="C280" s="8">
+        <v>347.3</v>
       </c>
       <c r="D280" s="4" t="s">
         <v>364</v>
@@ -5795,27 +5798,27 @@
     </row>
     <row r="281" spans="1:4">
       <c r="A281" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B281" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C281" s="3">
-        <v>28.15</v>
+        <v>284</v>
       </c>
       <c r="D281" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="282" spans="1:4">
       <c r="A282" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B282" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C282" s="3">
-        <v>45.08</v>
+        <v>28.15</v>
       </c>
       <c r="D282" s="4" t="s">
         <v>366</v>
@@ -5823,13 +5826,13 @@
     </row>
     <row r="283" spans="1:4">
       <c r="A283" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B283" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C283" s="3">
-        <v>51.52</v>
+        <v>45.08</v>
       </c>
       <c r="D283" s="4" t="s">
         <v>366</v>
@@ -5837,27 +5840,27 @@
     </row>
     <row r="284" spans="1:4">
       <c r="A284" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B284" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C284" s="3">
-        <v>40.57</v>
+        <v>51.52</v>
       </c>
       <c r="D284" s="4" t="s">
-        <v>419</v>
+        <v>366</v>
       </c>
     </row>
     <row r="285" spans="1:4">
       <c r="A285" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B285" s="3">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C285" s="3">
-        <v>36.229999999999997</v>
+        <v>40.57</v>
       </c>
       <c r="D285" s="4" t="s">
         <v>419</v>
@@ -5865,41 +5868,41 @@
     </row>
     <row r="286" spans="1:4">
       <c r="A286" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B286" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C286" s="3">
-        <v>54.12</v>
+        <v>36.229999999999997</v>
       </c>
       <c r="D286" s="4" t="s">
-        <v>366</v>
+        <v>419</v>
       </c>
     </row>
     <row r="287" spans="1:4">
       <c r="A287" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B287" s="3">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C287" s="3">
-        <v>69.55</v>
+        <v>54.12</v>
       </c>
       <c r="D287" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="288" spans="1:4">
       <c r="A288" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B288" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C288" s="3">
-        <v>295.14999999999998</v>
+        <v>69.55</v>
       </c>
       <c r="D288" s="4" t="s">
         <v>364</v>
@@ -5907,41 +5910,41 @@
     </row>
     <row r="289" spans="1:4">
       <c r="A289" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B289" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C289" s="3">
-        <v>38.56</v>
+        <v>295.14999999999998</v>
       </c>
       <c r="D289" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="290" spans="1:4">
       <c r="A290" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B290" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C290" s="3">
-        <v>60.95</v>
+        <v>38.56</v>
       </c>
       <c r="D290" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="291" spans="1:4">
       <c r="A291" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B291" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C291" s="3">
-        <v>78.209999999999994</v>
+        <v>60.95</v>
       </c>
       <c r="D291" s="4" t="s">
         <v>367</v>
@@ -5949,27 +5952,27 @@
     </row>
     <row r="292" spans="1:4">
       <c r="A292" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B292" s="3">
-        <v>228</v>
+        <v>10</v>
       </c>
       <c r="C292" s="3">
-        <v>51.15</v>
+        <v>78.209999999999994</v>
       </c>
       <c r="D292" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="293" spans="1:4">
       <c r="A293" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B293" s="3">
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="C293" s="3">
-        <v>6591.8</v>
+        <v>51.15</v>
       </c>
       <c r="D293" s="4" t="s">
         <v>364</v>
@@ -5977,13 +5980,13 @@
     </row>
     <row r="294" spans="1:4">
       <c r="A294" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B294" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C294" s="3">
-        <v>182.42</v>
+        <v>6591.8</v>
       </c>
       <c r="D294" s="4" t="s">
         <v>364</v>
@@ -5991,13 +5994,13 @@
     </row>
     <row r="295" spans="1:4">
       <c r="A295" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B295" s="3">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="C295" s="3">
-        <v>222.62</v>
+        <v>182.42</v>
       </c>
       <c r="D295" s="4" t="s">
         <v>364</v>
@@ -6005,13 +6008,13 @@
     </row>
     <row r="296" spans="1:4">
       <c r="A296" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B296" s="3">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C296" s="3">
-        <v>2314.8000000000002</v>
+        <v>222.62</v>
       </c>
       <c r="D296" s="4" t="s">
         <v>364</v>
@@ -6019,13 +6022,13 @@
     </row>
     <row r="297" spans="1:4">
       <c r="A297" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B297" s="3">
         <v>0</v>
       </c>
       <c r="C297" s="3">
-        <v>894.8</v>
+        <v>2314.8000000000002</v>
       </c>
       <c r="D297" s="4" t="s">
         <v>364</v>
@@ -6033,27 +6036,27 @@
     </row>
     <row r="298" spans="1:4">
       <c r="A298" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B298" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C298" s="3">
-        <v>31.6</v>
+        <v>894.8</v>
       </c>
       <c r="D298" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="299" spans="1:4">
       <c r="A299" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B299" s="3">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C299" s="3">
-        <v>77.28</v>
+        <v>31.6</v>
       </c>
       <c r="D299" s="4" t="s">
         <v>366</v>
@@ -6061,13 +6064,13 @@
     </row>
     <row r="300" spans="1:4">
       <c r="A300" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B300" s="3">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="C300" s="3">
-        <v>43.8</v>
+        <v>77.28</v>
       </c>
       <c r="D300" s="4" t="s">
         <v>366</v>
@@ -6075,13 +6078,13 @@
     </row>
     <row r="301" spans="1:4">
       <c r="A301" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B301" s="3">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C301" s="3">
-        <v>21.9</v>
+        <v>43.8</v>
       </c>
       <c r="D301" s="4" t="s">
         <v>366</v>
@@ -6089,13 +6092,13 @@
     </row>
     <row r="302" spans="1:4">
       <c r="A302" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B302" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C302" s="3">
-        <v>798.6</v>
+        <v>21.9</v>
       </c>
       <c r="D302" s="4" t="s">
         <v>366</v>
@@ -6103,13 +6106,13 @@
     </row>
     <row r="303" spans="1:4">
       <c r="A303" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B303" s="3">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="C303" s="3">
-        <v>23.19</v>
+        <v>798.6</v>
       </c>
       <c r="D303" s="4" t="s">
         <v>366</v>
@@ -6117,13 +6120,13 @@
     </row>
     <row r="304" spans="1:4">
       <c r="A304" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B304" s="3">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="C304" s="3">
-        <v>8.24</v>
+        <v>23.19</v>
       </c>
       <c r="D304" s="4" t="s">
         <v>366</v>
@@ -6131,13 +6134,13 @@
     </row>
     <row r="305" spans="1:4">
       <c r="A305" t="s">
-        <v>456</v>
+        <v>244</v>
       </c>
       <c r="B305" s="3">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="C305" s="3">
-        <v>13.72</v>
+        <v>8.24</v>
       </c>
       <c r="D305" s="4" t="s">
         <v>366</v>
@@ -6145,10 +6148,10 @@
     </row>
     <row r="306" spans="1:4">
       <c r="A306" t="s">
-        <v>245</v>
+        <v>456</v>
       </c>
       <c r="B306" s="3">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C306" s="3">
         <v>13.72</v>
@@ -6159,13 +6162,13 @@
     </row>
     <row r="307" spans="1:4">
       <c r="A307" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B307" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C307" s="3">
-        <v>31.95</v>
+        <v>13.72</v>
       </c>
       <c r="D307" s="4" t="s">
         <v>366</v>
@@ -6173,13 +6176,13 @@
     </row>
     <row r="308" spans="1:4">
       <c r="A308" t="s">
-        <v>370</v>
+        <v>246</v>
       </c>
       <c r="B308" s="3">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="C308" s="3">
-        <v>16.2</v>
+        <v>31.95</v>
       </c>
       <c r="D308" s="4" t="s">
         <v>366</v>
@@ -6187,13 +6190,13 @@
     </row>
     <row r="309" spans="1:4">
       <c r="A309" t="s">
-        <v>247</v>
+        <v>370</v>
       </c>
       <c r="B309" s="3">
-        <v>6</v>
+        <v>105</v>
       </c>
       <c r="C309" s="3">
-        <v>36.869999999999997</v>
+        <v>16.2</v>
       </c>
       <c r="D309" s="4" t="s">
         <v>366</v>
@@ -6201,13 +6204,13 @@
     </row>
     <row r="310" spans="1:4">
       <c r="A310" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B310" s="3">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C310" s="3">
-        <v>31.48</v>
+        <v>36.869999999999997</v>
       </c>
       <c r="D310" s="4" t="s">
         <v>366</v>
@@ -6215,13 +6218,13 @@
     </row>
     <row r="311" spans="1:4">
       <c r="A311" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B311" s="3">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C311" s="3">
-        <v>21.9</v>
+        <v>31.48</v>
       </c>
       <c r="D311" s="4" t="s">
         <v>366</v>
@@ -6229,13 +6232,13 @@
     </row>
     <row r="312" spans="1:4">
       <c r="A312" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B312" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C312" s="3">
-        <v>23.19</v>
+        <v>21.9</v>
       </c>
       <c r="D312" s="4" t="s">
         <v>366</v>
@@ -6243,13 +6246,13 @@
     </row>
     <row r="313" spans="1:4">
       <c r="A313" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B313" s="3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C313" s="3">
-        <v>19.55</v>
+        <v>23.19</v>
       </c>
       <c r="D313" s="4" t="s">
         <v>366</v>
@@ -6257,13 +6260,13 @@
     </row>
     <row r="314" spans="1:4">
       <c r="A314" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B314" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C314" s="3">
-        <v>19.07</v>
+        <v>19.55</v>
       </c>
       <c r="D314" s="4" t="s">
         <v>366</v>
@@ -6271,13 +6274,13 @@
     </row>
     <row r="315" spans="1:4">
       <c r="A315" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B315" s="3">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C315" s="3">
-        <v>21.9</v>
+        <v>19.07</v>
       </c>
       <c r="D315" s="4" t="s">
         <v>366</v>
@@ -6285,27 +6288,27 @@
     </row>
     <row r="316" spans="1:4">
       <c r="A316" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B316" s="3">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C316" s="3">
-        <v>79.349999999999994</v>
+        <v>21.9</v>
       </c>
       <c r="D316" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="317" spans="1:4">
       <c r="A317" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B317" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C317" s="3">
-        <v>862.7</v>
+        <v>79.349999999999994</v>
       </c>
       <c r="D317" s="4" t="s">
         <v>367</v>
@@ -6313,13 +6316,13 @@
     </row>
     <row r="318" spans="1:4">
       <c r="A318" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B318" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C318" s="3">
-        <v>56.93</v>
+        <v>862.7</v>
       </c>
       <c r="D318" s="4" t="s">
         <v>367</v>
@@ -6327,13 +6330,13 @@
     </row>
     <row r="319" spans="1:4">
       <c r="A319" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B319" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C319" s="3">
-        <v>1265</v>
+        <v>56.93</v>
       </c>
       <c r="D319" s="4" t="s">
         <v>367</v>
@@ -6341,27 +6344,27 @@
     </row>
     <row r="320" spans="1:4">
       <c r="A320" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B320" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C320" s="3">
-        <v>76</v>
+        <v>1265</v>
       </c>
       <c r="D320" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="321" spans="1:4">
       <c r="A321" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B321" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="C321" s="3">
-        <v>267.85000000000002</v>
+        <v>76</v>
       </c>
       <c r="D321" s="4" t="s">
         <v>364</v>
@@ -6369,13 +6372,13 @@
     </row>
     <row r="322" spans="1:4">
       <c r="A322" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B322" s="3">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C322" s="3">
-        <v>74.7</v>
+        <v>267.85000000000002</v>
       </c>
       <c r="D322" s="4" t="s">
         <v>364</v>
@@ -6383,13 +6386,13 @@
     </row>
     <row r="323" spans="1:4">
       <c r="A323" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B323" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C323" s="3">
-        <v>327.3</v>
+        <v>74.7</v>
       </c>
       <c r="D323" s="4" t="s">
         <v>364</v>
@@ -6397,13 +6400,13 @@
     </row>
     <row r="324" spans="1:4">
       <c r="A324" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B324" s="3">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C324" s="3">
-        <v>72.13</v>
+        <v>327.3</v>
       </c>
       <c r="D324" s="4" t="s">
         <v>364</v>
@@ -6411,13 +6414,13 @@
     </row>
     <row r="325" spans="1:4">
       <c r="A325" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B325" s="3">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="C325" s="3">
-        <v>302.39999999999998</v>
+        <v>72.13</v>
       </c>
       <c r="D325" s="4" t="s">
         <v>364</v>
@@ -6425,41 +6428,41 @@
     </row>
     <row r="326" spans="1:4">
       <c r="A326" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B326" s="3">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C326" s="3">
-        <v>36.799999999999997</v>
+        <v>302.39999999999998</v>
       </c>
       <c r="D326" s="4" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="327" spans="1:4">
       <c r="A327" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B327" s="3">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C327" s="3">
-        <v>428.5</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D327" s="4" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="328" spans="1:4">
       <c r="A328" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B328" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C328" s="3">
-        <v>450.22</v>
+        <v>428.5</v>
       </c>
       <c r="D328" s="4" t="s">
         <v>364</v>
@@ -6467,13 +6470,13 @@
     </row>
     <row r="329" spans="1:4">
       <c r="A329" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B329" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C329" s="3">
-        <v>465.7</v>
+        <v>450.22</v>
       </c>
       <c r="D329" s="4" t="s">
         <v>364</v>
@@ -6481,13 +6484,13 @@
     </row>
     <row r="330" spans="1:4">
       <c r="A330" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B330" s="3">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C330" s="3">
-        <v>38.25</v>
+        <v>465.7</v>
       </c>
       <c r="D330" s="4" t="s">
         <v>364</v>
@@ -6495,13 +6498,13 @@
     </row>
     <row r="331" spans="1:4">
       <c r="A331" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B331" s="3">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C331" s="3">
-        <v>87.49</v>
+        <v>38.25</v>
       </c>
       <c r="D331" s="4" t="s">
         <v>364</v>
@@ -6509,13 +6512,13 @@
     </row>
     <row r="332" spans="1:4">
       <c r="A332" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B332" s="3">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C332" s="3">
-        <v>63.13</v>
+        <v>87.49</v>
       </c>
       <c r="D332" s="4" t="s">
         <v>364</v>
@@ -6523,27 +6526,27 @@
     </row>
     <row r="333" spans="1:4">
       <c r="A333" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B333" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C333" s="3">
-        <v>377.78</v>
+        <v>63.13</v>
       </c>
       <c r="D333" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="334" spans="1:4">
       <c r="A334" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B334" s="3">
         <v>2</v>
       </c>
       <c r="C334" s="3">
-        <v>3333.85</v>
+        <v>377.78</v>
       </c>
       <c r="D334" s="4" t="s">
         <v>368</v>
@@ -6551,13 +6554,13 @@
     </row>
     <row r="335" spans="1:4">
       <c r="A335" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B335" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C335" s="3">
-        <v>374.67</v>
+        <v>3333.85</v>
       </c>
       <c r="D335" s="4" t="s">
         <v>368</v>
@@ -6565,13 +6568,13 @@
     </row>
     <row r="336" spans="1:4">
       <c r="A336" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B336" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C336" s="3">
-        <v>120.06</v>
+        <v>374.67</v>
       </c>
       <c r="D336" s="4" t="s">
         <v>368</v>
@@ -6579,41 +6582,41 @@
     </row>
     <row r="337" spans="1:4">
       <c r="A337" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B337" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C337" s="3">
-        <v>54.2</v>
+        <v>120.06</v>
       </c>
       <c r="D337" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="338" spans="1:4">
       <c r="A338" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B338" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C338" s="3">
-        <v>31.5</v>
+        <v>54.2</v>
       </c>
       <c r="D338" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="339" spans="1:4">
       <c r="A339" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B339" s="3">
         <v>0</v>
       </c>
       <c r="C339" s="3">
-        <v>114.09</v>
+        <v>31.5</v>
       </c>
       <c r="D339" s="4" t="s">
         <v>364</v>
@@ -6621,13 +6624,13 @@
     </row>
     <row r="340" spans="1:4">
       <c r="A340" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B340" s="3">
         <v>0</v>
       </c>
       <c r="C340" s="3">
-        <v>139.9</v>
+        <v>114.09</v>
       </c>
       <c r="D340" s="4" t="s">
         <v>364</v>
@@ -6635,13 +6638,13 @@
     </row>
     <row r="341" spans="1:4">
       <c r="A341" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B341" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C341" s="3">
-        <v>50.13</v>
+        <v>139.9</v>
       </c>
       <c r="D341" s="4" t="s">
         <v>364</v>
@@ -6649,13 +6652,13 @@
     </row>
     <row r="342" spans="1:4">
       <c r="A342" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B342" s="3">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C342" s="3">
-        <v>140.26</v>
+        <v>50.13</v>
       </c>
       <c r="D342" s="4" t="s">
         <v>364</v>
@@ -6663,55 +6666,55 @@
     </row>
     <row r="343" spans="1:4">
       <c r="A343" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B343" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C343" s="3">
-        <v>370.53</v>
+        <v>140.26</v>
       </c>
       <c r="D343" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="344" spans="1:4">
       <c r="A344" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B344" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C344" s="3">
-        <v>30.9</v>
+        <v>370.53</v>
       </c>
       <c r="D344" s="4" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
     </row>
     <row r="345" spans="1:4">
       <c r="A345" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B345" s="3">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C345" s="3">
-        <v>5746.5</v>
+        <v>30.9</v>
       </c>
       <c r="D345" s="4" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="346" spans="1:4">
       <c r="A346" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B346" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C346" s="3">
-        <v>516.46</v>
+        <v>5746.5</v>
       </c>
       <c r="D346" s="4" t="s">
         <v>364</v>
@@ -6719,13 +6722,13 @@
     </row>
     <row r="347" spans="1:4">
       <c r="A347" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B347" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C347" s="3">
-        <v>185.15</v>
+        <v>516.46</v>
       </c>
       <c r="D347" s="4" t="s">
         <v>364</v>
@@ -6733,58 +6736,58 @@
     </row>
     <row r="348" spans="1:4">
       <c r="A348" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B348" s="3">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="C348" s="3">
-        <v>11.5</v>
+        <v>185.15</v>
       </c>
       <c r="D348" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="349" spans="1:4">
       <c r="A349" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B349" s="3">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C349" s="3">
-        <v>724.5</v>
+        <v>11.5</v>
       </c>
       <c r="D349" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="350" spans="1:4">
       <c r="A350" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B350" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C350" s="3">
-        <v>450.22</v>
+        <v>724.5</v>
       </c>
       <c r="D350" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="351" spans="1:4">
       <c r="A351" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B351" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C351" s="3">
-        <v>461.23</v>
+        <v>450.22</v>
       </c>
       <c r="D351" s="4" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -6795,7 +6798,7 @@
         <v>1</v>
       </c>
       <c r="C352" s="3">
-        <v>518.41999999999996</v>
+        <v>461.23</v>
       </c>
       <c r="D352" s="4" t="s">
         <v>357</v>
@@ -6803,13 +6806,13 @@
     </row>
     <row r="353" spans="1:4">
       <c r="A353" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B353" s="3">
         <v>1</v>
       </c>
       <c r="C353" s="3">
-        <v>348.08</v>
+        <v>518.41999999999996</v>
       </c>
       <c r="D353" s="4" t="s">
         <v>357</v>
@@ -6817,13 +6820,13 @@
     </row>
     <row r="354" spans="1:4">
       <c r="A354" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B354" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C354" s="3">
-        <v>33.479999999999997</v>
+        <v>348.08</v>
       </c>
       <c r="D354" s="4" t="s">
         <v>357</v>
@@ -6831,13 +6834,13 @@
     </row>
     <row r="355" spans="1:4">
       <c r="A355" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B355" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C355" s="3">
-        <v>35.79</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D355" s="4" t="s">
         <v>357</v>
@@ -6845,13 +6848,13 @@
     </row>
     <row r="356" spans="1:4">
       <c r="A356" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B356" s="3">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C356" s="3">
-        <v>377.7</v>
+        <v>35.79</v>
       </c>
       <c r="D356" s="4" t="s">
         <v>357</v>
@@ -6859,13 +6862,13 @@
     </row>
     <row r="357" spans="1:4">
       <c r="A357" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B357" s="3">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C357" s="3">
-        <v>33.21</v>
+        <v>377.7</v>
       </c>
       <c r="D357" s="4" t="s">
         <v>357</v>
@@ -6873,13 +6876,13 @@
     </row>
     <row r="358" spans="1:4">
       <c r="A358" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B358" s="3">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C358" s="3">
-        <v>27.16</v>
+        <v>33.21</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>357</v>
@@ -6887,13 +6890,13 @@
     </row>
     <row r="359" spans="1:4">
       <c r="A359" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B359" s="3">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C359" s="3">
-        <v>361.41</v>
+        <v>27.16</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>357</v>
@@ -6901,13 +6904,13 @@
     </row>
     <row r="360" spans="1:4">
       <c r="A360" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B360" s="3">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="C360" s="3">
-        <v>29.25</v>
+        <v>361.41</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>357</v>
@@ -6915,13 +6918,13 @@
     </row>
     <row r="361" spans="1:4">
       <c r="A361" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B361" s="3">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="C361" s="3">
-        <v>304.54000000000002</v>
+        <v>29.25</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>357</v>
@@ -6929,13 +6932,13 @@
     </row>
     <row r="362" spans="1:4">
       <c r="A362" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B362" s="3">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C362" s="3">
-        <v>34.049999999999997</v>
+        <v>304.54000000000002</v>
       </c>
       <c r="D362" s="4" t="s">
         <v>357</v>
@@ -6943,55 +6946,55 @@
     </row>
     <row r="363" spans="1:4">
       <c r="A363" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B363" s="3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C363" s="3">
-        <v>57.7</v>
+        <v>34.049999999999997</v>
       </c>
       <c r="D363" s="4" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
     </row>
     <row r="364" spans="1:4">
       <c r="A364" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B364" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C364" s="3">
-        <v>90.9</v>
+        <v>57.7</v>
       </c>
       <c r="D364" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="365" spans="1:4">
       <c r="A365" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B365" s="3">
-        <v>218</v>
+        <v>10</v>
       </c>
       <c r="C365" s="3">
-        <v>47.62</v>
+        <v>90.9</v>
       </c>
       <c r="D365" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="366" spans="1:4">
       <c r="A366" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B366" s="3">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="C366" s="3">
-        <v>7173.59</v>
+        <v>47.62</v>
       </c>
       <c r="D366" s="4" t="s">
         <v>364</v>
@@ -6999,13 +7002,13 @@
     </row>
     <row r="367" spans="1:4">
       <c r="A367" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B367" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C367" s="3">
-        <v>677.79</v>
+        <v>7173.59</v>
       </c>
       <c r="D367" s="4" t="s">
         <v>364</v>
@@ -7013,13 +7016,13 @@
     </row>
     <row r="368" spans="1:4">
       <c r="A368" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B368" s="3">
-        <v>13</v>
-      </c>
-      <c r="C368" s="8">
-        <v>171.47</v>
+        <v>1</v>
+      </c>
+      <c r="C368" s="3">
+        <v>677.79</v>
       </c>
       <c r="D368" s="4" t="s">
         <v>364</v>
@@ -7027,13 +7030,13 @@
     </row>
     <row r="369" spans="1:4">
       <c r="A369" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B369" s="3">
-        <v>65</v>
-      </c>
-      <c r="C369" s="3">
-        <v>212.75</v>
+        <v>13</v>
+      </c>
+      <c r="C369" s="8">
+        <v>171.47</v>
       </c>
       <c r="D369" s="4" t="s">
         <v>364</v>
@@ -7041,13 +7044,13 @@
     </row>
     <row r="370" spans="1:4">
       <c r="A370" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B370" s="3">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="C370" s="3">
-        <v>2335.67</v>
+        <v>212.75</v>
       </c>
       <c r="D370" s="4" t="s">
         <v>364</v>
@@ -7055,13 +7058,13 @@
     </row>
     <row r="371" spans="1:4">
       <c r="A371" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B371" s="3">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C371" s="3">
-        <v>66.180000000000007</v>
+        <v>2335.67</v>
       </c>
       <c r="D371" s="4" t="s">
         <v>364</v>
@@ -7069,13 +7072,13 @@
     </row>
     <row r="372" spans="1:4">
       <c r="A372" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B372" s="3">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C372" s="3">
-        <v>8139.6</v>
+        <v>66.180000000000007</v>
       </c>
       <c r="D372" s="4" t="s">
         <v>364</v>
@@ -7083,13 +7086,13 @@
     </row>
     <row r="373" spans="1:4">
       <c r="A373" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B373" s="3">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C373" s="3">
-        <v>259.81</v>
+        <v>8139.6</v>
       </c>
       <c r="D373" s="4" t="s">
         <v>364</v>
@@ -7097,13 +7100,13 @@
     </row>
     <row r="374" spans="1:4">
       <c r="A374" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B374" s="3">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C374" s="3">
-        <v>259.8</v>
+        <v>259.81</v>
       </c>
       <c r="D374" s="4" t="s">
         <v>364</v>
@@ -7111,13 +7114,13 @@
     </row>
     <row r="375" spans="1:4">
       <c r="A375" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B375" s="3">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C375" s="3">
-        <v>310.2</v>
+        <v>259.8</v>
       </c>
       <c r="D375" s="4" t="s">
         <v>364</v>
@@ -7125,13 +7128,13 @@
     </row>
     <row r="376" spans="1:4">
       <c r="A376" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B376" s="3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C376" s="3">
-        <v>36.43</v>
+        <v>310.2</v>
       </c>
       <c r="D376" s="4" t="s">
         <v>364</v>
@@ -7139,13 +7142,13 @@
     </row>
     <row r="377" spans="1:4">
       <c r="A377" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B377" s="3">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C377" s="3">
-        <v>87.22</v>
+        <v>36.43</v>
       </c>
       <c r="D377" s="4" t="s">
         <v>364</v>
@@ -7153,13 +7156,13 @@
     </row>
     <row r="378" spans="1:4">
       <c r="A378" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B378" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C378" s="3">
-        <v>319.60000000000002</v>
+        <v>87.22</v>
       </c>
       <c r="D378" s="4" t="s">
         <v>364</v>
@@ -7167,13 +7170,13 @@
     </row>
     <row r="379" spans="1:4">
       <c r="A379" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B379" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C379" s="3">
-        <v>62.6</v>
+        <v>319.60000000000002</v>
       </c>
       <c r="D379" s="4" t="s">
         <v>364</v>
@@ -7181,13 +7184,13 @@
     </row>
     <row r="380" spans="1:4">
       <c r="A380" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B380" s="3">
-        <v>8</v>
-      </c>
-      <c r="C380" s="8">
-        <v>385.25</v>
+        <v>14</v>
+      </c>
+      <c r="C380" s="3">
+        <v>62.6</v>
       </c>
       <c r="D380" s="4" t="s">
         <v>364</v>
@@ -7195,27 +7198,27 @@
     </row>
     <row r="381" spans="1:4">
       <c r="A381" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B381" s="3">
-        <v>28</v>
-      </c>
-      <c r="C381" s="3">
-        <v>67.28</v>
+        <v>8</v>
+      </c>
+      <c r="C381" s="8">
+        <v>385.25</v>
       </c>
       <c r="D381" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="382" spans="1:4">
       <c r="A382" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B382" s="3">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C382" s="3">
-        <v>1138.5</v>
+        <v>67.28</v>
       </c>
       <c r="D382" s="4" t="s">
         <v>367</v>
@@ -7223,27 +7226,27 @@
     </row>
     <row r="383" spans="1:4">
       <c r="A383" t="s">
-        <v>350</v>
+        <v>319</v>
       </c>
       <c r="B383" s="3">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C383" s="3">
-        <v>58.69</v>
+        <v>1138.5</v>
       </c>
       <c r="D383" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="384" spans="1:4">
       <c r="A384" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B384" s="3">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C384" s="3">
-        <v>289.33999999999997</v>
+        <v>58.69</v>
       </c>
       <c r="D384" s="4" t="s">
         <v>364</v>
@@ -7251,13 +7254,13 @@
     </row>
     <row r="385" spans="1:4">
       <c r="A385" t="s">
-        <v>320</v>
+        <v>351</v>
       </c>
       <c r="B385" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C385" s="3">
-        <v>48.76</v>
+        <v>289.33999999999997</v>
       </c>
       <c r="D385" s="4" t="s">
         <v>364</v>
@@ -7265,13 +7268,13 @@
     </row>
     <row r="386" spans="1:4">
       <c r="A386" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B386" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C386" s="3">
-        <v>242.34</v>
+        <v>48.76</v>
       </c>
       <c r="D386" s="4" t="s">
         <v>364</v>
@@ -7279,13 +7282,13 @@
     </row>
     <row r="387" spans="1:4">
       <c r="A387" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B387" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C387" s="3">
-        <v>65.599999999999994</v>
+        <v>242.34</v>
       </c>
       <c r="D387" s="4" t="s">
         <v>364</v>
@@ -7293,13 +7296,13 @@
     </row>
     <row r="388" spans="1:4">
       <c r="A388" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B388" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C388" s="3">
-        <v>255.03</v>
+        <v>65.599999999999994</v>
       </c>
       <c r="D388" s="4" t="s">
         <v>364</v>
@@ -7307,13 +7310,13 @@
     </row>
     <row r="389" spans="1:4">
       <c r="A389" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B389" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C389" s="3">
-        <v>220.8</v>
+        <v>255.03</v>
       </c>
       <c r="D389" s="4" t="s">
         <v>364</v>
@@ -7321,13 +7324,13 @@
     </row>
     <row r="390" spans="1:4">
       <c r="A390" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B390" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C390" s="3">
-        <v>255.02</v>
+        <v>220.8</v>
       </c>
       <c r="D390" s="4" t="s">
         <v>364</v>
@@ -7335,13 +7338,13 @@
     </row>
     <row r="391" spans="1:4">
       <c r="A391" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B391" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C391" s="3">
-        <v>68.86</v>
+        <v>255.02</v>
       </c>
       <c r="D391" s="4" t="s">
         <v>364</v>
@@ -7349,13 +7352,13 @@
     </row>
     <row r="392" spans="1:4">
       <c r="A392" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B392" s="3">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C392" s="3">
-        <v>344.28</v>
+        <v>68.86</v>
       </c>
       <c r="D392" s="4" t="s">
         <v>364</v>
@@ -7363,13 +7366,13 @@
     </row>
     <row r="393" spans="1:4">
       <c r="A393" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B393" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C393" s="3">
-        <v>60.29</v>
+        <v>344.28</v>
       </c>
       <c r="D393" s="4" t="s">
         <v>364</v>
@@ -7377,13 +7380,13 @@
     </row>
     <row r="394" spans="1:4">
       <c r="A394" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B394" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C394" s="3">
-        <v>261.8</v>
+        <v>60.29</v>
       </c>
       <c r="D394" s="4" t="s">
         <v>364</v>
@@ -7391,55 +7394,55 @@
     </row>
     <row r="395" spans="1:4">
       <c r="A395" t="s">
-        <v>382</v>
+        <v>329</v>
       </c>
       <c r="B395" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C395" s="3">
-        <v>30.58</v>
+        <v>261.8</v>
       </c>
       <c r="D395" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="396" spans="1:4">
       <c r="A396" t="s">
-        <v>330</v>
+        <v>382</v>
       </c>
       <c r="B396" s="3">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="C396" s="3">
-        <v>16.95</v>
+        <v>30.58</v>
       </c>
       <c r="D396" s="4" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
     </row>
     <row r="397" spans="1:4">
       <c r="A397" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B397" s="3">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C397" s="3">
-        <v>24.95</v>
+        <v>16.95</v>
       </c>
       <c r="D397" s="4" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
     </row>
     <row r="398" spans="1:4">
       <c r="A398" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B398" s="3">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="C398" s="3">
-        <v>641.49</v>
+        <v>24.95</v>
       </c>
       <c r="D398" s="4" t="s">
         <v>367</v>
@@ -7447,13 +7450,13 @@
     </row>
     <row r="399" spans="1:4">
       <c r="A399" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B399" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C399" s="3">
-        <v>39.57</v>
+        <v>641.49</v>
       </c>
       <c r="D399" s="4" t="s">
         <v>367</v>
@@ -7461,13 +7464,13 @@
     </row>
     <row r="400" spans="1:4">
       <c r="A400" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B400" s="3">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C400" s="3">
-        <v>51.83</v>
+        <v>39.57</v>
       </c>
       <c r="D400" s="4" t="s">
         <v>367</v>
@@ -7475,27 +7478,27 @@
     </row>
     <row r="401" spans="1:4">
       <c r="A401" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B401" s="3">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C401" s="3">
-        <v>33.840000000000003</v>
+        <v>51.83</v>
       </c>
       <c r="D401" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="402" spans="1:4">
       <c r="A402" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B402" s="3">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="C402" s="3">
-        <v>150.15</v>
+        <v>33.840000000000003</v>
       </c>
       <c r="D402" s="4" t="s">
         <v>364</v>
@@ -7503,13 +7506,13 @@
     </row>
     <row r="403" spans="1:4">
       <c r="A403" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B403" s="3">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C403" s="3">
-        <v>144.5</v>
+        <v>150.15</v>
       </c>
       <c r="D403" s="4" t="s">
         <v>364</v>
@@ -7517,13 +7520,13 @@
     </row>
     <row r="404" spans="1:4">
       <c r="A404" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B404" s="3">
         <v>25</v>
       </c>
       <c r="C404" s="3">
-        <v>100.93</v>
+        <v>144.5</v>
       </c>
       <c r="D404" s="4" t="s">
         <v>364</v>
@@ -7531,13 +7534,13 @@
     </row>
     <row r="405" spans="1:4">
       <c r="A405" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B405" s="3">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C405" s="3">
-        <v>124.5</v>
+        <v>100.93</v>
       </c>
       <c r="D405" s="4" t="s">
         <v>364</v>
@@ -7545,13 +7548,13 @@
     </row>
     <row r="406" spans="1:4">
       <c r="A406" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B406" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C406" s="3">
-        <v>27.21</v>
+        <v>124.5</v>
       </c>
       <c r="D406" s="4" t="s">
         <v>364</v>
@@ -7559,41 +7562,41 @@
     </row>
     <row r="407" spans="1:4">
       <c r="A407" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B407" s="3">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="C407" s="3">
-        <v>24.79</v>
+        <v>27.21</v>
       </c>
       <c r="D407" s="4" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
     </row>
     <row r="408" spans="1:4">
       <c r="A408" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B408" s="3">
-        <v>6</v>
+        <v>94</v>
       </c>
       <c r="C408" s="3">
-        <v>37.1</v>
+        <v>24.79</v>
       </c>
       <c r="D408" s="4" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
     </row>
     <row r="409" spans="1:4">
       <c r="A409" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B409" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C409" s="3">
-        <v>178.04</v>
+        <v>37.1</v>
       </c>
       <c r="D409" s="4" t="s">
         <v>364</v>
@@ -7601,41 +7604,41 @@
     </row>
     <row r="410" spans="1:4">
       <c r="A410" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B410" s="3">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="C410" s="3">
-        <v>23.88</v>
+        <v>178.04</v>
       </c>
       <c r="D410" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="411" spans="1:4">
       <c r="A411" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B411" s="3">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="C411" s="3">
-        <v>20.68</v>
+        <v>23.88</v>
       </c>
       <c r="D411" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="412" spans="1:4">
       <c r="A412" t="s">
-        <v>372</v>
+        <v>345</v>
       </c>
       <c r="B412" s="3">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="C412" s="3">
-        <v>97.54</v>
+        <v>20.68</v>
       </c>
       <c r="D412" s="4" t="s">
         <v>364</v>
@@ -7643,13 +7646,13 @@
     </row>
     <row r="413" spans="1:4">
       <c r="A413" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B413" s="3">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C413" s="3">
-        <v>304.02999999999997</v>
+        <v>97.54</v>
       </c>
       <c r="D413" s="4" t="s">
         <v>364</v>
@@ -7657,27 +7660,27 @@
     </row>
     <row r="414" spans="1:4">
       <c r="A414" t="s">
-        <v>346</v>
+        <v>373</v>
       </c>
       <c r="B414" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C414" s="3">
-        <v>1934.56</v>
+        <v>304.02999999999997</v>
       </c>
       <c r="D414" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="415" spans="1:4">
       <c r="A415" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B415" s="3">
         <v>0</v>
       </c>
       <c r="C415" s="3">
-        <v>230.99</v>
+        <v>1934.56</v>
       </c>
       <c r="D415" s="4" t="s">
         <v>368</v>
@@ -7685,55 +7688,55 @@
     </row>
     <row r="416" spans="1:4">
       <c r="A416" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B416" s="3">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="C416" s="3">
-        <v>33.39</v>
+        <v>230.99</v>
       </c>
       <c r="D416" s="4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="417" spans="1:4">
       <c r="A417" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B417" s="3">
         <v>0</v>
       </c>
       <c r="C417" s="3">
-        <v>20.66</v>
+        <v>33.39</v>
       </c>
       <c r="D417" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="418" spans="1:4">
       <c r="A418" t="s">
-        <v>375</v>
+        <v>349</v>
       </c>
       <c r="B418" s="3">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="C418" s="3">
-        <v>97.5</v>
+        <v>20.66</v>
       </c>
       <c r="D418" s="4" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
     </row>
     <row r="419" spans="1:4">
       <c r="A419" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B419" s="3">
-        <v>401</v>
+        <v>68</v>
       </c>
       <c r="C419" s="3">
-        <v>24.7</v>
+        <v>97.5</v>
       </c>
       <c r="D419" s="4" t="s">
         <v>374</v>
@@ -7741,13 +7744,13 @@
     </row>
     <row r="420" spans="1:4">
       <c r="A420" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B420" s="3">
-        <v>439</v>
+        <v>401</v>
       </c>
       <c r="C420" s="3">
-        <v>35.75</v>
+        <v>24.7</v>
       </c>
       <c r="D420" s="4" t="s">
         <v>374</v>
@@ -7755,13 +7758,13 @@
     </row>
     <row r="421" spans="1:4">
       <c r="A421" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B421" s="3">
-        <v>150</v>
+        <v>439</v>
       </c>
       <c r="C421" s="3">
-        <v>9.1</v>
+        <v>35.75</v>
       </c>
       <c r="D421" s="4" t="s">
         <v>374</v>
@@ -7769,13 +7772,13 @@
     </row>
     <row r="422" spans="1:4">
       <c r="A422" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B422" s="3">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C422" s="3">
-        <v>5.43</v>
+        <v>9.1</v>
       </c>
       <c r="D422" s="4" t="s">
         <v>374</v>
@@ -7783,13 +7786,13 @@
     </row>
     <row r="423" spans="1:4">
       <c r="A423" t="s">
-        <v>432</v>
+        <v>379</v>
       </c>
       <c r="B423" s="3">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="C423" s="3">
-        <v>11.99</v>
+        <v>5.43</v>
       </c>
       <c r="D423" s="4" t="s">
         <v>374</v>
@@ -7797,27 +7800,27 @@
     </row>
     <row r="424" spans="1:4">
       <c r="A424" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
       <c r="B424" s="3">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="C424" s="3">
-        <v>9.75</v>
+        <v>11.99</v>
       </c>
       <c r="D424" s="4" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="425" spans="1:4">
       <c r="A425" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B425" s="3">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="C425" s="3">
-        <v>6.37</v>
+        <v>9.75</v>
       </c>
       <c r="D425" s="4" t="s">
         <v>380</v>
@@ -7825,13 +7828,13 @@
     </row>
     <row r="426" spans="1:4">
       <c r="A426" t="s">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="B426" s="3">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C426" s="3">
-        <v>10.53</v>
+        <v>6.37</v>
       </c>
       <c r="D426" s="4" t="s">
         <v>380</v>
@@ -7839,27 +7842,27 @@
     </row>
     <row r="427" spans="1:4">
       <c r="A427" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="B427" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C427" s="3">
-        <v>11.59</v>
+        <v>10.53</v>
       </c>
       <c r="D427" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="428" spans="1:4">
       <c r="A428" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="B428" s="3">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C428" s="3">
-        <v>12.09</v>
+        <v>11.59</v>
       </c>
       <c r="D428" s="4" t="s">
         <v>381</v>
@@ -7867,10 +7870,10 @@
     </row>
     <row r="429" spans="1:4">
       <c r="A429" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B429" s="3">
-        <v>195</v>
+        <v>36</v>
       </c>
       <c r="C429" s="3">
         <v>12.09</v>
@@ -7881,13 +7884,13 @@
     </row>
     <row r="430" spans="1:4">
       <c r="A430" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B430" s="3">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C430" s="3">
-        <v>6.5</v>
+        <v>12.09</v>
       </c>
       <c r="D430" s="4" t="s">
         <v>381</v>
@@ -7895,10 +7898,10 @@
     </row>
     <row r="431" spans="1:4">
       <c r="A431" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B431" s="3">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="C431" s="3">
         <v>6.5</v>
@@ -7909,27 +7912,27 @@
     </row>
     <row r="432" spans="1:4">
       <c r="A432" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="B432" s="3">
-        <v>2</v>
+        <v>182</v>
       </c>
       <c r="C432" s="3">
-        <v>5017</v>
+        <v>6.5</v>
       </c>
       <c r="D432" s="4" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
     </row>
     <row r="433" spans="1:4">
       <c r="A433" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B433" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C433" s="3">
-        <v>4437.1499999999996</v>
+        <v>5017</v>
       </c>
       <c r="D433" s="4" t="s">
         <v>364</v>
@@ -7937,13 +7940,13 @@
     </row>
     <row r="434" spans="1:4">
       <c r="A434" t="s">
-        <v>429</v>
+        <v>453</v>
       </c>
       <c r="B434" s="3">
         <v>7</v>
       </c>
       <c r="C434" s="3">
-        <v>6239.83</v>
+        <v>4437.1499999999996</v>
       </c>
       <c r="D434" s="4" t="s">
         <v>364</v>
@@ -7951,13 +7954,13 @@
     </row>
     <row r="435" spans="1:4">
       <c r="A435" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="B435" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C435" s="3">
-        <v>5980</v>
+        <v>6239.83</v>
       </c>
       <c r="D435" s="4" t="s">
         <v>364</v>
@@ -7965,13 +7968,13 @@
     </row>
     <row r="436" spans="1:4">
       <c r="A436" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="B436" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C436" s="3">
-        <v>3556.4</v>
+        <v>5980</v>
       </c>
       <c r="D436" s="4" t="s">
         <v>364</v>
@@ -7979,13 +7982,13 @@
     </row>
     <row r="437" spans="1:4">
       <c r="A437" t="s">
-        <v>450</v>
+        <v>428</v>
       </c>
       <c r="B437" s="3">
         <v>2</v>
       </c>
       <c r="C437" s="3">
-        <v>6463</v>
+        <v>3556.4</v>
       </c>
       <c r="D437" s="4" t="s">
         <v>364</v>
@@ -7993,13 +7996,13 @@
     </row>
     <row r="438" spans="1:4">
       <c r="A438" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B438" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C438" s="3">
-        <v>5199</v>
+        <v>6463</v>
       </c>
       <c r="D438" s="4" t="s">
         <v>364</v>
@@ -8007,55 +8010,55 @@
     </row>
     <row r="439" spans="1:4">
       <c r="A439" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B439" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C439" s="3">
-        <v>70.25</v>
+        <v>5199</v>
       </c>
       <c r="D439" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="440" spans="1:4">
       <c r="A440" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="B440" s="3">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="C440" s="3">
-        <v>45</v>
+        <v>70.25</v>
       </c>
       <c r="D440" s="4" t="s">
-        <v>454</v>
+        <v>367</v>
       </c>
     </row>
     <row r="441" spans="1:4">
       <c r="A441" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B441" s="3">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="C441" s="3">
-        <v>70.25</v>
+        <v>45</v>
       </c>
       <c r="D441" s="4" t="s">
-        <v>367</v>
+        <v>454</v>
       </c>
     </row>
     <row r="442" spans="1:4">
       <c r="A442" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B442" s="3">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C442" s="3">
-        <v>58.9</v>
+        <v>70.25</v>
       </c>
       <c r="D442" s="4" t="s">
         <v>367</v>
@@ -8063,13 +8066,13 @@
     </row>
     <row r="443" spans="1:4">
       <c r="A443" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B443" s="3">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="C443" s="3">
-        <v>89.21</v>
+        <v>58.9</v>
       </c>
       <c r="D443" s="4" t="s">
         <v>367</v>
@@ -8077,13 +8080,13 @@
     </row>
     <row r="444" spans="1:4">
       <c r="A444" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B444" s="3">
         <v>60</v>
       </c>
       <c r="C444" s="3">
-        <v>59.18</v>
+        <v>89.21</v>
       </c>
       <c r="D444" s="4" t="s">
         <v>367</v>
@@ -8091,13 +8094,13 @@
     </row>
     <row r="445" spans="1:4">
       <c r="A445" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B445" s="3">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C445" s="3">
-        <v>60.62</v>
+        <v>59.18</v>
       </c>
       <c r="D445" s="4" t="s">
         <v>367</v>
@@ -8105,13 +8108,13 @@
     </row>
     <row r="446" spans="1:4">
       <c r="A446" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B446" s="3">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="C446" s="3">
-        <v>3431.7</v>
+        <v>60.62</v>
       </c>
       <c r="D446" s="4" t="s">
         <v>367</v>
@@ -8119,13 +8122,13 @@
     </row>
     <row r="447" spans="1:4">
       <c r="A447" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B447" s="3">
         <v>3</v>
       </c>
       <c r="C447" s="3">
-        <v>1260.2</v>
+        <v>3431.7</v>
       </c>
       <c r="D447" s="4" t="s">
         <v>367</v>
@@ -8133,13 +8136,13 @@
     </row>
     <row r="448" spans="1:4">
       <c r="A448" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B448" s="3">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C448" s="3">
-        <v>47.2</v>
+        <v>1260.2</v>
       </c>
       <c r="D448" s="4" t="s">
         <v>367</v>
@@ -8147,15 +8150,29 @@
     </row>
     <row r="449" spans="1:4">
       <c r="A449" t="s">
+        <v>464</v>
+      </c>
+      <c r="B449" s="3">
+        <v>56</v>
+      </c>
+      <c r="C449" s="3">
+        <v>47.2</v>
+      </c>
+      <c r="D449" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4">
+      <c r="A450" t="s">
         <v>468</v>
       </c>
-      <c r="B449" s="3">
+      <c r="B450" s="3">
         <v>60</v>
       </c>
-      <c r="C449" s="3">
+      <c r="C450" s="3">
         <v>71.760000000000005</v>
       </c>
-      <c r="D449" s="4" t="s">
+      <c r="D450" s="4" t="s">
         <v>367</v>
       </c>
     </row>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="471">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -1424,6 +1424,9 @@
   </si>
   <si>
     <t>CYC PREMUS LI-CA NLGI2 410ml vaselina</t>
+  </si>
+  <si>
+    <t>SWAG 99906161 ULEI SERVODIRECTIE</t>
   </si>
 </sst>
 </file>
@@ -1868,7 +1871,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D450"/>
+  <dimension ref="A1:D451"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="49.85546875" customWidth="1"/>
@@ -8176,6 +8179,20 @@
         <v>367</v>
       </c>
     </row>
+    <row r="451" spans="1:4">
+      <c r="A451" t="s">
+        <v>470</v>
+      </c>
+      <c r="B451" s="3">
+        <v>12</v>
+      </c>
+      <c r="C451" s="3">
+        <v>45</v>
+      </c>
+      <c r="D451" s="4" t="s">
+        <v>454</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -2010,7 +2010,7 @@
         <v>395</v>
       </c>
       <c r="B10" s="3">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C10" s="3">
         <v>343.45</v>
@@ -2318,7 +2318,7 @@
         <v>9</v>
       </c>
       <c r="B32" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C32" s="3">
         <v>5899.25</v>
@@ -2332,7 +2332,7 @@
         <v>423</v>
       </c>
       <c r="B33" s="3">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="C33" s="3">
         <v>207.95</v>
@@ -2402,7 +2402,7 @@
         <v>11</v>
       </c>
       <c r="B38" s="3">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="C38" s="3">
         <v>189</v>
@@ -2458,7 +2458,7 @@
         <v>465</v>
       </c>
       <c r="B42" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C42" s="3">
         <v>907.2</v>
@@ -2514,7 +2514,7 @@
         <v>13</v>
       </c>
       <c r="B46" s="3">
-        <v>1693</v>
+        <v>1633</v>
       </c>
       <c r="C46" s="3">
         <v>13</v>
@@ -2850,7 +2850,7 @@
         <v>32</v>
       </c>
       <c r="B70" s="3">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C70" s="3">
         <v>87.12</v>
@@ -2878,7 +2878,7 @@
         <v>33</v>
       </c>
       <c r="B72" s="3">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C72" s="3">
         <v>18.96</v>
@@ -2990,7 +2990,7 @@
         <v>443</v>
       </c>
       <c r="B80" s="3">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="C80" s="3">
         <v>19.48</v>
@@ -3004,7 +3004,7 @@
         <v>444</v>
       </c>
       <c r="B81" s="3">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C81" s="3">
         <v>70.72</v>
@@ -3046,7 +3046,7 @@
         <v>446</v>
       </c>
       <c r="B84" s="3">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C84" s="3">
         <v>22.21</v>
@@ -3886,7 +3886,7 @@
         <v>94</v>
       </c>
       <c r="B144" s="3">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C144" s="3">
         <v>66.98</v>
@@ -4656,7 +4656,7 @@
         <v>385</v>
       </c>
       <c r="B199" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C199" s="3">
         <v>168.7</v>
@@ -4726,7 +4726,7 @@
         <v>151</v>
       </c>
       <c r="B204" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C204" s="3">
         <v>48.64</v>
@@ -4740,7 +4740,7 @@
         <v>152</v>
       </c>
       <c r="B205" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C205" s="3">
         <v>126.63</v>
@@ -4908,7 +4908,7 @@
         <v>163</v>
       </c>
       <c r="B217" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C217" s="3">
         <v>170.78</v>
@@ -5286,7 +5286,7 @@
         <v>187</v>
       </c>
       <c r="B244" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C244" s="3">
         <v>67.28</v>
@@ -5972,7 +5972,7 @@
         <v>232</v>
       </c>
       <c r="B293" s="3">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C293" s="3">
         <v>51.15</v>
@@ -6000,7 +6000,7 @@
         <v>234</v>
       </c>
       <c r="B295" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C295" s="3">
         <v>182.42</v>
@@ -6014,7 +6014,7 @@
         <v>235</v>
       </c>
       <c r="B296" s="3">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C296" s="3">
         <v>222.62</v>
@@ -6854,7 +6854,7 @@
         <v>292</v>
       </c>
       <c r="B356" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C356" s="3">
         <v>35.79</v>
@@ -6994,7 +6994,7 @@
         <v>302</v>
       </c>
       <c r="B366" s="3">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C366" s="3">
         <v>47.62</v>
@@ -7050,7 +7050,7 @@
         <v>306</v>
       </c>
       <c r="B370" s="3">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C370" s="3">
         <v>212.75</v>
@@ -7106,7 +7106,7 @@
         <v>310</v>
       </c>
       <c r="B374" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C374" s="3">
         <v>259.81</v>
@@ -7302,7 +7302,7 @@
         <v>322</v>
       </c>
       <c r="B388" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C388" s="3">
         <v>65.599999999999994</v>
@@ -7316,7 +7316,7 @@
         <v>323</v>
       </c>
       <c r="B389" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C389" s="3">
         <v>255.03</v>
@@ -7372,7 +7372,7 @@
         <v>327</v>
       </c>
       <c r="B393" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C393" s="3">
         <v>344.28</v>
@@ -7638,7 +7638,7 @@
         <v>345</v>
       </c>
       <c r="B412" s="3">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C412" s="3">
         <v>20.68</v>
@@ -7652,7 +7652,7 @@
         <v>372</v>
       </c>
       <c r="B413" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C413" s="3">
         <v>97.54</v>
@@ -8184,7 +8184,7 @@
         <v>470</v>
       </c>
       <c r="B451" s="3">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C451" s="3">
         <v>45</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="470">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -1358,9 +1358,6 @@
   </si>
   <si>
     <t>MAX X-100</t>
-  </si>
-  <si>
-    <t>FUCHS TITAN ATF 4134 (M9-G) 1L</t>
   </si>
   <si>
     <t>CASTROL GTX A3/B3 15W40 1L</t>
@@ -1871,7 +1868,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D451"/>
+  <dimension ref="A1:D450"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="49.85546875" customWidth="1"/>
@@ -1982,7 +1979,7 @@
         <v>406</v>
       </c>
       <c r="B8" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C8" s="3">
         <v>635.11</v>
@@ -2010,7 +2007,7 @@
         <v>395</v>
       </c>
       <c r="B10" s="3">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" s="3">
         <v>343.45</v>
@@ -2290,7 +2287,7 @@
         <v>422</v>
       </c>
       <c r="B30" s="3">
-        <v>377</v>
+        <v>305</v>
       </c>
       <c r="C30" s="3">
         <v>45.19</v>
@@ -2360,7 +2357,7 @@
         <v>425</v>
       </c>
       <c r="B35" s="3">
-        <v>292</v>
+        <v>256</v>
       </c>
       <c r="C35" s="3">
         <v>42.7</v>
@@ -2413,10 +2410,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B39" s="3">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="C39" s="3">
         <v>26.6</v>
@@ -2430,7 +2427,7 @@
         <v>426</v>
       </c>
       <c r="B40" s="3">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="C40" s="3">
         <v>26.29</v>
@@ -2455,7 +2452,7 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B42" s="3">
         <v>4</v>
@@ -2469,7 +2466,7 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B43" s="3">
         <v>6</v>
@@ -2483,7 +2480,7 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B44" s="3">
         <v>6</v>
@@ -2514,7 +2511,7 @@
         <v>13</v>
       </c>
       <c r="B46" s="3">
-        <v>1633</v>
+        <v>1609</v>
       </c>
       <c r="C46" s="3">
         <v>13</v>
@@ -2668,7 +2665,7 @@
         <v>417</v>
       </c>
       <c r="B57" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C57" s="3">
         <v>144.84</v>
@@ -2696,7 +2693,7 @@
         <v>23</v>
       </c>
       <c r="B59" s="3">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C59" s="3">
         <v>255</v>
@@ -2906,7 +2903,7 @@
         <v>35</v>
       </c>
       <c r="B74" s="3">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C74" s="3">
         <v>89.38</v>
@@ -2990,7 +2987,7 @@
         <v>443</v>
       </c>
       <c r="B80" s="3">
-        <v>634</v>
+        <v>622</v>
       </c>
       <c r="C80" s="3">
         <v>19.48</v>
@@ -3004,7 +3001,7 @@
         <v>444</v>
       </c>
       <c r="B81" s="3">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C81" s="3">
         <v>70.72</v>
@@ -3029,7 +3026,7 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B83" s="3">
         <v>240</v>
@@ -3704,7 +3701,7 @@
         <v>83</v>
       </c>
       <c r="B131" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C131" s="3">
         <v>67.27</v>
@@ -4852,7 +4849,7 @@
         <v>352</v>
       </c>
       <c r="B213" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C213" s="8">
         <v>257.70999999999998</v>
@@ -5034,7 +5031,7 @@
         <v>172</v>
       </c>
       <c r="B226" s="3">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C226" s="3">
         <v>37.299999999999997</v>
@@ -5972,7 +5969,7 @@
         <v>232</v>
       </c>
       <c r="B293" s="3">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C293" s="3">
         <v>51.15</v>
@@ -6014,7 +6011,7 @@
         <v>235</v>
       </c>
       <c r="B296" s="3">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C296" s="3">
         <v>222.62</v>
@@ -6151,7 +6148,7 @@
     </row>
     <row r="306" spans="1:4">
       <c r="A306" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B306" s="3">
         <v>21</v>
@@ -6700,7 +6697,7 @@
         <v>282</v>
       </c>
       <c r="B345" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C345" s="3">
         <v>30.9</v>
@@ -7246,7 +7243,7 @@
         <v>350</v>
       </c>
       <c r="B384" s="3">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C384" s="3">
         <v>58.69</v>
@@ -7330,7 +7327,7 @@
         <v>324</v>
       </c>
       <c r="B390" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C390" s="3">
         <v>220.8</v>
@@ -7736,7 +7733,7 @@
         <v>375</v>
       </c>
       <c r="B419" s="3">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C419" s="3">
         <v>97.5</v>
@@ -7764,7 +7761,7 @@
         <v>377</v>
       </c>
       <c r="B421" s="3">
-        <v>439</v>
+        <v>409</v>
       </c>
       <c r="C421" s="3">
         <v>35.75</v>
@@ -7778,7 +7775,7 @@
         <v>378</v>
       </c>
       <c r="B422" s="3">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="C422" s="3">
         <v>9.1</v>
@@ -7806,7 +7803,7 @@
         <v>432</v>
       </c>
       <c r="B424" s="3">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C424" s="3">
         <v>11.99</v>
@@ -7834,7 +7831,7 @@
         <v>415</v>
       </c>
       <c r="B426" s="3">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C426" s="3">
         <v>6.37</v>
@@ -7890,7 +7887,7 @@
         <v>435</v>
       </c>
       <c r="B430" s="3">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C430" s="3">
         <v>12.09</v>
@@ -7904,7 +7901,7 @@
         <v>436</v>
       </c>
       <c r="B431" s="3">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C431" s="3">
         <v>6.5</v>
@@ -7918,7 +7915,7 @@
         <v>437</v>
       </c>
       <c r="B432" s="3">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C432" s="3">
         <v>6.5</v>
@@ -7929,7 +7926,7 @@
     </row>
     <row r="433" spans="1:4">
       <c r="A433" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B433" s="3">
         <v>2</v>
@@ -7943,7 +7940,7 @@
     </row>
     <row r="434" spans="1:4">
       <c r="A434" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B434" s="3">
         <v>7</v>
@@ -7999,7 +7996,7 @@
     </row>
     <row r="438" spans="1:4">
       <c r="A438" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B438" s="3">
         <v>2</v>
@@ -8013,7 +8010,7 @@
     </row>
     <row r="439" spans="1:4">
       <c r="A439" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B439" s="3">
         <v>1</v>
@@ -8027,30 +8024,30 @@
     </row>
     <row r="440" spans="1:4">
       <c r="A440" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="B440" s="3">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="C440" s="3">
-        <v>70.25</v>
+        <v>45</v>
       </c>
       <c r="D440" s="4" t="s">
-        <v>367</v>
+        <v>453</v>
       </c>
     </row>
     <row r="441" spans="1:4">
       <c r="A441" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B441" s="3">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C441" s="3">
-        <v>45</v>
+        <v>70.25</v>
       </c>
       <c r="D441" s="4" t="s">
-        <v>454</v>
+        <v>367</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -8058,10 +8055,10 @@
         <v>457</v>
       </c>
       <c r="B442" s="3">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C442" s="3">
-        <v>70.25</v>
+        <v>58.9</v>
       </c>
       <c r="D442" s="4" t="s">
         <v>367</v>
@@ -8072,10 +8069,10 @@
         <v>458</v>
       </c>
       <c r="B443" s="3">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="C443" s="3">
-        <v>58.9</v>
+        <v>89.21</v>
       </c>
       <c r="D443" s="4" t="s">
         <v>367</v>
@@ -8089,7 +8086,7 @@
         <v>60</v>
       </c>
       <c r="C444" s="3">
-        <v>89.21</v>
+        <v>59.18</v>
       </c>
       <c r="D444" s="4" t="s">
         <v>367</v>
@@ -8100,10 +8097,10 @@
         <v>460</v>
       </c>
       <c r="B445" s="3">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C445" s="3">
-        <v>59.18</v>
+        <v>60.62</v>
       </c>
       <c r="D445" s="4" t="s">
         <v>367</v>
@@ -8114,10 +8111,10 @@
         <v>461</v>
       </c>
       <c r="B446" s="3">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="C446" s="3">
-        <v>60.62</v>
+        <v>3431.7</v>
       </c>
       <c r="D446" s="4" t="s">
         <v>367</v>
@@ -8131,7 +8128,7 @@
         <v>3</v>
       </c>
       <c r="C447" s="3">
-        <v>3431.7</v>
+        <v>1260.2</v>
       </c>
       <c r="D447" s="4" t="s">
         <v>367</v>
@@ -8142,10 +8139,10 @@
         <v>463</v>
       </c>
       <c r="B448" s="3">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C448" s="3">
-        <v>1260.2</v>
+        <v>47.2</v>
       </c>
       <c r="D448" s="4" t="s">
         <v>367</v>
@@ -8153,13 +8150,13 @@
     </row>
     <row r="449" spans="1:4">
       <c r="A449" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B449" s="3">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C449" s="3">
-        <v>47.2</v>
+        <v>71.760000000000005</v>
       </c>
       <c r="D449" s="4" t="s">
         <v>367</v>
@@ -8167,30 +8164,16 @@
     </row>
     <row r="450" spans="1:4">
       <c r="A450" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B450" s="3">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C450" s="3">
-        <v>71.760000000000005</v>
+        <v>45</v>
       </c>
       <c r="D450" s="4" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="451" spans="1:4">
-      <c r="A451" t="s">
-        <v>470</v>
-      </c>
-      <c r="B451" s="3">
-        <v>36</v>
-      </c>
-      <c r="C451" s="3">
-        <v>45</v>
-      </c>
-      <c r="D451" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
   </sheetData>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -2007,7 +2007,7 @@
         <v>395</v>
       </c>
       <c r="B10" s="3">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" s="3">
         <v>343.45</v>
@@ -2105,7 +2105,7 @@
         <v>7</v>
       </c>
       <c r="B17" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C17" s="3">
         <v>909.67</v>
@@ -2147,7 +2147,7 @@
         <v>396</v>
       </c>
       <c r="B20" s="3">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C20" s="3">
         <v>534.95000000000005</v>
@@ -2721,7 +2721,7 @@
         <v>440</v>
       </c>
       <c r="B61" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C61" s="3">
         <v>135.29</v>
@@ -2749,7 +2749,7 @@
         <v>26</v>
       </c>
       <c r="B63" s="3">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C63" s="3">
         <v>101.08</v>
@@ -2987,7 +2987,7 @@
         <v>443</v>
       </c>
       <c r="B80" s="3">
-        <v>622</v>
+        <v>607</v>
       </c>
       <c r="C80" s="3">
         <v>19.48</v>
@@ -3043,7 +3043,7 @@
         <v>446</v>
       </c>
       <c r="B84" s="3">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C84" s="3">
         <v>22.21</v>
@@ -3141,7 +3141,7 @@
         <v>45</v>
       </c>
       <c r="B91" s="3">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C91" s="3">
         <v>18.37</v>
@@ -3155,7 +3155,7 @@
         <v>46</v>
       </c>
       <c r="B92" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C92" s="3">
         <v>82.88</v>
@@ -3183,7 +3183,7 @@
         <v>48</v>
       </c>
       <c r="B94" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C94" s="3">
         <v>50.23</v>
@@ -4135,7 +4135,7 @@
         <v>111</v>
       </c>
       <c r="B162" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C162" s="3">
         <v>101.5</v>
@@ -4569,7 +4569,7 @@
         <v>141</v>
       </c>
       <c r="B193" s="3">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C193" s="3">
         <v>59.25</v>
@@ -4583,7 +4583,7 @@
         <v>142</v>
       </c>
       <c r="B194" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C194" s="3">
         <v>260</v>
@@ -5031,7 +5031,7 @@
         <v>172</v>
       </c>
       <c r="B226" s="3">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C226" s="3">
         <v>37.299999999999997</v>
@@ -5059,7 +5059,7 @@
         <v>174</v>
       </c>
       <c r="B228" s="3">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C228" s="3">
         <v>154.62</v>
@@ -5675,7 +5675,7 @@
         <v>212</v>
       </c>
       <c r="B272" s="3">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C272" s="3">
         <v>54.7</v>
@@ -5969,7 +5969,7 @@
         <v>232</v>
       </c>
       <c r="B293" s="3">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C293" s="3">
         <v>51.15</v>
@@ -6011,7 +6011,7 @@
         <v>235</v>
       </c>
       <c r="B296" s="3">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C296" s="3">
         <v>222.62</v>
@@ -6193,7 +6193,7 @@
         <v>370</v>
       </c>
       <c r="B309" s="3">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C309" s="3">
         <v>16.2</v>
@@ -6249,7 +6249,7 @@
         <v>250</v>
       </c>
       <c r="B313" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C313" s="3">
         <v>23.19</v>
@@ -6991,7 +6991,7 @@
         <v>302</v>
       </c>
       <c r="B366" s="3">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C366" s="3">
         <v>47.62</v>
@@ -7047,7 +7047,7 @@
         <v>306</v>
       </c>
       <c r="B370" s="3">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C370" s="3">
         <v>212.75</v>
@@ -7075,7 +7075,7 @@
         <v>308</v>
       </c>
       <c r="B372" s="3">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C372" s="3">
         <v>66.180000000000007</v>
@@ -7117,7 +7117,7 @@
         <v>311</v>
       </c>
       <c r="B375" s="3">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C375" s="3">
         <v>259.8</v>
@@ -7131,7 +7131,7 @@
         <v>312</v>
       </c>
       <c r="B376" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C376" s="3">
         <v>310.2</v>
@@ -7663,7 +7663,7 @@
         <v>373</v>
       </c>
       <c r="B414" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C414" s="3">
         <v>304.02999999999997</v>
@@ -7747,7 +7747,7 @@
         <v>376</v>
       </c>
       <c r="B420" s="3">
-        <v>401</v>
+        <v>386</v>
       </c>
       <c r="C420" s="3">
         <v>24.7</v>
@@ -7761,7 +7761,7 @@
         <v>377</v>
       </c>
       <c r="B421" s="3">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="C421" s="3">
         <v>35.75</v>
@@ -7859,7 +7859,7 @@
         <v>416</v>
       </c>
       <c r="B428" s="3">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C428" s="3">
         <v>11.59</v>
@@ -7887,7 +7887,7 @@
         <v>435</v>
       </c>
       <c r="B430" s="3">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C430" s="3">
         <v>12.09</v>
@@ -7901,7 +7901,7 @@
         <v>436</v>
       </c>
       <c r="B431" s="3">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C431" s="3">
         <v>6.5</v>
@@ -8027,7 +8027,7 @@
         <v>454</v>
       </c>
       <c r="B440" s="3">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C440" s="3">
         <v>45</v>
@@ -8139,7 +8139,7 @@
         <v>463</v>
       </c>
       <c r="B448" s="3">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C448" s="3">
         <v>47.2</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -1993,10 +1993,10 @@
         <v>394</v>
       </c>
       <c r="B9" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C9" s="3">
-        <v>309.52</v>
+        <v>320</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>359</v>
@@ -2021,10 +2021,10 @@
         <v>412</v>
       </c>
       <c r="B11" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C11" s="3">
-        <v>467.19</v>
+        <v>476.85</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>360</v>
@@ -2035,10 +2035,10 @@
         <v>413</v>
       </c>
       <c r="B12" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C12" s="3">
-        <v>535.12</v>
+        <v>545.9</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>360</v>
@@ -2105,10 +2105,10 @@
         <v>7</v>
       </c>
       <c r="B17" s="3">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C17" s="3">
-        <v>909.67</v>
+        <v>920.45</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>362</v>
@@ -2217,10 +2217,10 @@
         <v>401</v>
       </c>
       <c r="B25" s="3">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C25" s="3">
-        <v>376.62</v>
+        <v>381.54</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>363</v>
@@ -2231,10 +2231,10 @@
         <v>402</v>
       </c>
       <c r="B26" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C26" s="3">
-        <v>409.88</v>
+        <v>417.6</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>363</v>
@@ -2259,10 +2259,10 @@
         <v>404</v>
       </c>
       <c r="B28" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C28" s="3">
-        <v>491.37</v>
+        <v>489.63</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>363</v>
@@ -2273,10 +2273,10 @@
         <v>405</v>
       </c>
       <c r="B29" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C29" s="3">
-        <v>478.19</v>
+        <v>508.27</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>363</v>
@@ -2315,7 +2315,7 @@
         <v>9</v>
       </c>
       <c r="B32" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" s="3">
         <v>5899.25</v>
@@ -2427,7 +2427,7 @@
         <v>426</v>
       </c>
       <c r="B40" s="3">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C40" s="3">
         <v>26.29</v>
@@ -2441,7 +2441,7 @@
         <v>427</v>
       </c>
       <c r="B41" s="3">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C41" s="3">
         <v>120.32</v>
@@ -2665,7 +2665,7 @@
         <v>417</v>
       </c>
       <c r="B57" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C57" s="3">
         <v>144.84</v>
@@ -2847,7 +2847,7 @@
         <v>32</v>
       </c>
       <c r="B70" s="3">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C70" s="3">
         <v>87.12</v>
@@ -3967,7 +3967,7 @@
         <v>100</v>
       </c>
       <c r="B150" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C150" s="3">
         <v>3169.7</v>
@@ -4247,7 +4247,7 @@
         <v>119</v>
       </c>
       <c r="B170" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C170" s="3">
         <v>181.68</v>
@@ -4373,7 +4373,7 @@
         <v>128</v>
       </c>
       <c r="B179" s="3">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C179" s="3">
         <v>61.83</v>
@@ -4863,7 +4863,7 @@
         <v>160</v>
       </c>
       <c r="B214" s="3">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C214" s="3">
         <v>33.479999999999997</v>
@@ -5045,7 +5045,7 @@
         <v>173</v>
       </c>
       <c r="B227" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C227" s="3">
         <v>126.24</v>
@@ -5311,7 +5311,7 @@
         <v>189</v>
       </c>
       <c r="B246" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C246" s="8">
         <v>75.88</v>
@@ -5703,7 +5703,7 @@
         <v>214</v>
       </c>
       <c r="B274" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C274" s="3">
         <v>334.36</v>
@@ -5969,7 +5969,7 @@
         <v>232</v>
       </c>
       <c r="B293" s="3">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C293" s="3">
         <v>51.15</v>
@@ -6011,7 +6011,7 @@
         <v>235</v>
       </c>
       <c r="B296" s="3">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C296" s="3">
         <v>222.62</v>
@@ -6991,7 +6991,7 @@
         <v>302</v>
       </c>
       <c r="B366" s="3">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C366" s="3">
         <v>47.62</v>
@@ -7047,7 +7047,7 @@
         <v>306</v>
       </c>
       <c r="B370" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C370" s="3">
         <v>212.75</v>
@@ -7131,7 +7131,7 @@
         <v>312</v>
       </c>
       <c r="B376" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C376" s="3">
         <v>310.2</v>
@@ -7215,7 +7215,7 @@
         <v>318</v>
       </c>
       <c r="B382" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C382" s="3">
         <v>67.28</v>
@@ -7663,7 +7663,7 @@
         <v>373</v>
       </c>
       <c r="B414" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C414" s="3">
         <v>304.02999999999997</v>
@@ -7747,7 +7747,7 @@
         <v>376</v>
       </c>
       <c r="B420" s="3">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="C420" s="3">
         <v>24.7</v>
@@ -7761,7 +7761,7 @@
         <v>377</v>
       </c>
       <c r="B421" s="3">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C421" s="3">
         <v>35.75</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -3533,10 +3533,10 @@
         <v>71</v>
       </c>
       <c r="B119" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C119" s="3">
-        <v>93.25</v>
+        <v>119.03</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>367</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -2329,7 +2329,7 @@
         <v>423</v>
       </c>
       <c r="B33" s="3">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C33" s="3">
         <v>207.95</v>
@@ -2399,7 +2399,7 @@
         <v>11</v>
       </c>
       <c r="B38" s="3">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C38" s="3">
         <v>189</v>
@@ -2511,7 +2511,7 @@
         <v>13</v>
       </c>
       <c r="B46" s="3">
-        <v>1609</v>
+        <v>1585</v>
       </c>
       <c r="C46" s="3">
         <v>13</v>
@@ -2693,7 +2693,7 @@
         <v>23</v>
       </c>
       <c r="B59" s="3">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C59" s="3">
         <v>255</v>
@@ -2987,7 +2987,7 @@
         <v>443</v>
       </c>
       <c r="B80" s="3">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="C80" s="3">
         <v>19.48</v>
@@ -3043,7 +3043,7 @@
         <v>446</v>
       </c>
       <c r="B84" s="3">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C84" s="3">
         <v>22.21</v>
@@ -3183,7 +3183,7 @@
         <v>48</v>
       </c>
       <c r="B94" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C94" s="3">
         <v>50.23</v>
@@ -3813,7 +3813,7 @@
         <v>90</v>
       </c>
       <c r="B139" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C139" s="3">
         <v>290.95</v>
@@ -4471,7 +4471,7 @@
         <v>135</v>
       </c>
       <c r="B186" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C186" s="3">
         <v>342.24</v>
@@ -4863,7 +4863,7 @@
         <v>160</v>
       </c>
       <c r="B214" s="3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C214" s="3">
         <v>33.479999999999997</v>
@@ -4961,7 +4961,7 @@
         <v>167</v>
       </c>
       <c r="B221" s="3">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C221" s="3">
         <v>36.799999999999997</v>
@@ -5059,7 +5059,7 @@
         <v>174</v>
       </c>
       <c r="B228" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C228" s="3">
         <v>154.62</v>
@@ -5185,7 +5185,7 @@
         <v>182</v>
       </c>
       <c r="B237" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C237" s="3">
         <v>45.72</v>
@@ -5311,7 +5311,7 @@
         <v>189</v>
       </c>
       <c r="B246" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C246" s="8">
         <v>75.88</v>
@@ -5535,7 +5535,7 @@
         <v>204</v>
       </c>
       <c r="B262" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C262" s="3">
         <v>56</v>
@@ -5969,7 +5969,7 @@
         <v>232</v>
       </c>
       <c r="B293" s="3">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C293" s="3">
         <v>51.15</v>
@@ -6011,7 +6011,7 @@
         <v>235</v>
       </c>
       <c r="B296" s="3">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C296" s="3">
         <v>222.62</v>
@@ -6991,7 +6991,7 @@
         <v>302</v>
       </c>
       <c r="B366" s="3">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="C366" s="3">
         <v>47.62</v>
@@ -7215,7 +7215,7 @@
         <v>318</v>
       </c>
       <c r="B382" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C382" s="3">
         <v>67.28</v>
@@ -7243,7 +7243,7 @@
         <v>350</v>
       </c>
       <c r="B384" s="3">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C384" s="3">
         <v>58.69</v>
@@ -7663,7 +7663,7 @@
         <v>373</v>
       </c>
       <c r="B414" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C414" s="3">
         <v>304.02999999999997</v>
@@ -7761,7 +7761,7 @@
         <v>377</v>
       </c>
       <c r="B421" s="3">
-        <v>401</v>
+        <v>376</v>
       </c>
       <c r="C421" s="3">
         <v>35.75</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -1979,7 +1979,7 @@
         <v>406</v>
       </c>
       <c r="B8" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" s="3">
         <v>635.11</v>
@@ -2147,7 +2147,7 @@
         <v>396</v>
       </c>
       <c r="B20" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C20" s="3">
         <v>534.95000000000005</v>
@@ -2329,7 +2329,7 @@
         <v>423</v>
       </c>
       <c r="B33" s="3">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C33" s="3">
         <v>207.95</v>
@@ -2357,7 +2357,7 @@
         <v>425</v>
       </c>
       <c r="B35" s="3">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="C35" s="3">
         <v>42.7</v>
@@ -2385,7 +2385,7 @@
         <v>10</v>
       </c>
       <c r="B37" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C37" s="3">
         <v>122.46</v>
@@ -2399,7 +2399,7 @@
         <v>11</v>
       </c>
       <c r="B38" s="3">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C38" s="3">
         <v>189</v>
@@ -2847,7 +2847,7 @@
         <v>32</v>
       </c>
       <c r="B70" s="3">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C70" s="3">
         <v>87.12</v>
@@ -2987,7 +2987,7 @@
         <v>443</v>
       </c>
       <c r="B80" s="3">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C80" s="3">
         <v>19.48</v>
@@ -3001,7 +3001,7 @@
         <v>444</v>
       </c>
       <c r="B81" s="3">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C81" s="3">
         <v>70.72</v>
@@ -3043,7 +3043,7 @@
         <v>446</v>
       </c>
       <c r="B84" s="3">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C84" s="3">
         <v>22.21</v>
@@ -3141,7 +3141,7 @@
         <v>45</v>
       </c>
       <c r="B91" s="3">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C91" s="3">
         <v>18.37</v>
@@ -4163,7 +4163,7 @@
         <v>113</v>
       </c>
       <c r="B164" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C164" s="3">
         <v>32.200000000000003</v>
@@ -4345,7 +4345,7 @@
         <v>126</v>
       </c>
       <c r="B177" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C177" s="3">
         <v>38.770000000000003</v>
@@ -4555,7 +4555,7 @@
         <v>140</v>
       </c>
       <c r="B192" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C192" s="3">
         <v>35.81</v>
@@ -4583,7 +4583,7 @@
         <v>142</v>
       </c>
       <c r="B194" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C194" s="3">
         <v>260</v>
@@ -4597,7 +4597,7 @@
         <v>143</v>
       </c>
       <c r="B195" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C195" s="7">
         <v>59.62</v>
@@ -4737,7 +4737,7 @@
         <v>152</v>
       </c>
       <c r="B205" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C205" s="3">
         <v>126.63</v>
@@ -5927,7 +5927,7 @@
         <v>229</v>
       </c>
       <c r="B290" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C290" s="3">
         <v>38.56</v>
@@ -5969,7 +5969,7 @@
         <v>232</v>
       </c>
       <c r="B293" s="3">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C293" s="3">
         <v>51.15</v>
@@ -5997,7 +5997,7 @@
         <v>234</v>
       </c>
       <c r="B295" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C295" s="3">
         <v>182.42</v>
@@ -6011,7 +6011,7 @@
         <v>235</v>
       </c>
       <c r="B296" s="3">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C296" s="3">
         <v>222.62</v>
@@ -6557,7 +6557,7 @@
         <v>272</v>
       </c>
       <c r="B335" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C335" s="3">
         <v>3333.85</v>
@@ -6991,7 +6991,7 @@
         <v>302</v>
       </c>
       <c r="B366" s="3">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C366" s="3">
         <v>47.62</v>
@@ -7047,7 +7047,7 @@
         <v>306</v>
       </c>
       <c r="B370" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C370" s="3">
         <v>212.75</v>
@@ -7117,7 +7117,7 @@
         <v>311</v>
       </c>
       <c r="B375" s="3">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C375" s="3">
         <v>259.8</v>
@@ -7131,7 +7131,7 @@
         <v>312</v>
       </c>
       <c r="B376" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C376" s="3">
         <v>310.2</v>
@@ -7215,7 +7215,7 @@
         <v>318</v>
       </c>
       <c r="B382" s="3">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C382" s="3">
         <v>67.28</v>
@@ -7439,7 +7439,7 @@
         <v>331</v>
       </c>
       <c r="B398" s="3">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C398" s="3">
         <v>24.95</v>
@@ -7523,7 +7523,7 @@
         <v>337</v>
       </c>
       <c r="B404" s="3">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C404" s="3">
         <v>144.5</v>
@@ -7593,7 +7593,7 @@
         <v>342</v>
       </c>
       <c r="B409" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C409" s="3">
         <v>37.1</v>
@@ -7607,7 +7607,7 @@
         <v>343</v>
       </c>
       <c r="B410" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C410" s="3">
         <v>178.04</v>
@@ -7635,7 +7635,7 @@
         <v>345</v>
       </c>
       <c r="B412" s="3">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="C412" s="3">
         <v>20.68</v>
@@ -7649,7 +7649,7 @@
         <v>372</v>
       </c>
       <c r="B413" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C413" s="3">
         <v>97.54</v>
@@ -7733,7 +7733,7 @@
         <v>375</v>
       </c>
       <c r="B419" s="3">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C419" s="3">
         <v>97.5</v>
@@ -7747,7 +7747,7 @@
         <v>376</v>
       </c>
       <c r="B420" s="3">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="C420" s="3">
         <v>24.7</v>
@@ -7887,7 +7887,7 @@
         <v>435</v>
       </c>
       <c r="B430" s="3">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C430" s="3">
         <v>12.09</v>
@@ -8027,7 +8027,7 @@
         <v>454</v>
       </c>
       <c r="B440" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C440" s="3">
         <v>45</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="471">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -1424,6 +1424,9 @@
   </si>
   <si>
     <t>SWAG 99906161 ULEI SERVODIRECTIE</t>
+  </si>
+  <si>
+    <t>CYC PREMUS LI-CA NLGI2 180kg vaselina</t>
   </si>
 </sst>
 </file>
@@ -1868,7 +1871,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D450"/>
+  <dimension ref="A1:D451"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="49.85546875" customWidth="1"/>
@@ -2203,7 +2206,7 @@
         <v>400</v>
       </c>
       <c r="B24" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C24" s="3">
         <v>358.39</v>
@@ -2217,7 +2220,7 @@
         <v>401</v>
       </c>
       <c r="B25" s="3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C25" s="3">
         <v>381.54</v>
@@ -2287,7 +2290,7 @@
         <v>422</v>
       </c>
       <c r="B30" s="3">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="C30" s="3">
         <v>45.19</v>
@@ -2329,7 +2332,7 @@
         <v>423</v>
       </c>
       <c r="B33" s="3">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="C33" s="3">
         <v>207.95</v>
@@ -2427,7 +2430,7 @@
         <v>426</v>
       </c>
       <c r="B40" s="3">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C40" s="3">
         <v>26.29</v>
@@ -2441,7 +2444,7 @@
         <v>427</v>
       </c>
       <c r="B41" s="3">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C41" s="3">
         <v>120.32</v>
@@ -2945,7 +2948,7 @@
         <v>38</v>
       </c>
       <c r="B77" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C77" s="3">
         <v>103.51</v>
@@ -3026,13 +3029,13 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B83" s="3">
-        <v>240</v>
+        <v>1</v>
       </c>
       <c r="C83" s="3">
-        <v>14.42</v>
+        <v>4256.54</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>357</v>
@@ -3040,41 +3043,41 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>446</v>
+        <v>468</v>
       </c>
       <c r="B84" s="3">
-        <v>21</v>
+        <v>228</v>
       </c>
       <c r="C84" s="3">
-        <v>22.21</v>
+        <v>14.42</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>447</v>
+        <v>357</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>40</v>
+        <v>446</v>
       </c>
       <c r="B85" s="3">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C85" s="3">
-        <v>25.4</v>
+        <v>22.21</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>366</v>
+        <v>447</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B86" s="3">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C86" s="3">
-        <v>40.92</v>
+        <v>25.4</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>366</v>
@@ -3082,13 +3085,13 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B87" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C87" s="3">
-        <v>25.4</v>
+        <v>40.92</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>366</v>
@@ -3096,13 +3099,13 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B88" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C88" s="3">
-        <v>28.07</v>
+        <v>25.4</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>366</v>
@@ -3110,13 +3113,13 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>384</v>
+        <v>43</v>
       </c>
       <c r="B89" s="3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C89" s="3">
-        <v>23.33</v>
+        <v>28.07</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>366</v>
@@ -3124,41 +3127,41 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>44</v>
+        <v>384</v>
       </c>
       <c r="B90" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C90" s="3">
-        <v>34.630000000000003</v>
+        <v>23.33</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B91" s="3">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="C91" s="3">
-        <v>18.37</v>
+        <v>34.630000000000003</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B92" s="3">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="C92" s="3">
-        <v>82.88</v>
+        <v>18.37</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>369</v>
@@ -3166,13 +3169,13 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B93" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C93" s="3">
-        <v>161.01</v>
+        <v>82.88</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>369</v>
@@ -3180,13 +3183,13 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B94" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C94" s="3">
-        <v>50.23</v>
+        <v>161.01</v>
       </c>
       <c r="D94" s="4" t="s">
         <v>369</v>
@@ -3194,55 +3197,55 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B95" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C95" s="3">
-        <v>65.83</v>
+        <v>50.23</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B96" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C96" s="3">
-        <v>46.76</v>
+        <v>65.83</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B97" s="3">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C97" s="3">
-        <v>62.11</v>
+        <v>46.76</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B98" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C98" s="3">
-        <v>47.61</v>
+        <v>62.11</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>367</v>
@@ -3250,13 +3253,13 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B99" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C99" s="3">
-        <v>63.76</v>
+        <v>47.61</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>367</v>
@@ -3264,13 +3267,13 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B100" s="3">
         <v>1</v>
       </c>
       <c r="C100" s="3">
-        <v>1159.2</v>
+        <v>63.76</v>
       </c>
       <c r="D100" s="4" t="s">
         <v>367</v>
@@ -3278,13 +3281,13 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B101" s="3">
         <v>1</v>
       </c>
       <c r="C101" s="3">
-        <v>255</v>
+        <v>1159.2</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>367</v>
@@ -3292,13 +3295,13 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B102" s="3">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C102" s="3">
-        <v>69.55</v>
+        <v>255</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>367</v>
@@ -3306,13 +3309,13 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B103" s="3">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C103" s="3">
-        <v>1391.04</v>
+        <v>69.55</v>
       </c>
       <c r="D103" s="4" t="s">
         <v>367</v>
@@ -3320,13 +3323,13 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B104" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C104" s="3">
-        <v>87.1</v>
+        <v>1391.04</v>
       </c>
       <c r="D104" s="4" t="s">
         <v>367</v>
@@ -3334,13 +3337,13 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B105" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C105" s="3">
-        <v>40.54</v>
+        <v>87.1</v>
       </c>
       <c r="D105" s="4" t="s">
         <v>367</v>
@@ -3348,13 +3351,13 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B106" s="3">
         <v>1</v>
       </c>
       <c r="C106" s="3">
-        <v>460.01</v>
+        <v>40.54</v>
       </c>
       <c r="D106" s="4" t="s">
         <v>367</v>
@@ -3368,7 +3371,7 @@
         <v>1</v>
       </c>
       <c r="C107" s="3">
-        <v>639.4</v>
+        <v>460.01</v>
       </c>
       <c r="D107" s="4" t="s">
         <v>367</v>
@@ -3376,13 +3379,13 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B108" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C108" s="3">
-        <v>103.89</v>
+        <v>639.4</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>367</v>
@@ -3390,13 +3393,13 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B109" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C109" s="3">
-        <v>58.48</v>
+        <v>103.89</v>
       </c>
       <c r="D109" s="4" t="s">
         <v>367</v>
@@ -3404,13 +3407,13 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B110" s="3">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="C110" s="3">
-        <v>56.93</v>
+        <v>58.48</v>
       </c>
       <c r="D110" s="4" t="s">
         <v>367</v>
@@ -3421,10 +3424,10 @@
         <v>63</v>
       </c>
       <c r="B111" s="3">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C111" s="3">
-        <v>63.76</v>
+        <v>56.93</v>
       </c>
       <c r="D111" s="4" t="s">
         <v>367</v>
@@ -3432,13 +3435,13 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B112" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C112" s="3">
-        <v>61.92</v>
+        <v>63.76</v>
       </c>
       <c r="D112" s="4" t="s">
         <v>367</v>
@@ -3446,13 +3449,13 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B113" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C113" s="3">
-        <v>63.76</v>
+        <v>61.92</v>
       </c>
       <c r="D113" s="4" t="s">
         <v>367</v>
@@ -3460,13 +3463,13 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B114" s="3">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C114" s="3">
-        <v>69.56</v>
+        <v>63.76</v>
       </c>
       <c r="D114" s="4" t="s">
         <v>367</v>
@@ -3474,13 +3477,13 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B115" s="3">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C115" s="3">
-        <v>59.68</v>
+        <v>69.56</v>
       </c>
       <c r="D115" s="4" t="s">
         <v>367</v>
@@ -3488,13 +3491,13 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B116" s="3">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C116" s="3">
-        <v>56.93</v>
+        <v>59.68</v>
       </c>
       <c r="D116" s="4" t="s">
         <v>367</v>
@@ -3502,13 +3505,13 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B117" s="3">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="C117" s="3">
-        <v>80.73</v>
+        <v>56.93</v>
       </c>
       <c r="D117" s="4" t="s">
         <v>367</v>
@@ -3516,13 +3519,13 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B118" s="3">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C118" s="3">
-        <v>98.95</v>
+        <v>80.73</v>
       </c>
       <c r="D118" s="4" t="s">
         <v>367</v>
@@ -3530,13 +3533,13 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B119" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C119" s="3">
-        <v>119.03</v>
+        <v>98.95</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>367</v>
@@ -3544,13 +3547,13 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B120" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C120" s="3">
-        <v>63.76</v>
+        <v>119.03</v>
       </c>
       <c r="D120" s="4" t="s">
         <v>367</v>
@@ -3558,10 +3561,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B121" s="3">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C121" s="3">
         <v>63.76</v>
@@ -3572,13 +3575,13 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B122" s="3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C122" s="3">
-        <v>81.150000000000006</v>
+        <v>63.76</v>
       </c>
       <c r="D122" s="4" t="s">
         <v>367</v>
@@ -3586,13 +3589,13 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B123" s="3">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C123" s="3">
-        <v>63.76</v>
+        <v>81.150000000000006</v>
       </c>
       <c r="D123" s="4" t="s">
         <v>367</v>
@@ -3600,13 +3603,13 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B124" s="3">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C124" s="3">
-        <v>69.87</v>
+        <v>63.76</v>
       </c>
       <c r="D124" s="4" t="s">
         <v>367</v>
@@ -3614,13 +3617,13 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B125" s="3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C125" s="3">
-        <v>63.76</v>
+        <v>69.87</v>
       </c>
       <c r="D125" s="4" t="s">
         <v>367</v>
@@ -3628,13 +3631,13 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B126" s="3">
-        <v>6</v>
-      </c>
-      <c r="C126" s="8">
-        <v>79.91</v>
+        <v>14</v>
+      </c>
+      <c r="C126" s="3">
+        <v>63.76</v>
       </c>
       <c r="D126" s="4" t="s">
         <v>367</v>
@@ -3642,13 +3645,13 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B127" s="3">
         <v>6</v>
       </c>
-      <c r="C127" s="3">
-        <v>69.56</v>
+      <c r="C127" s="8">
+        <v>79.91</v>
       </c>
       <c r="D127" s="4" t="s">
         <v>367</v>
@@ -3656,13 +3659,13 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B128" s="3">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="C128" s="3">
-        <v>52.17</v>
+        <v>69.56</v>
       </c>
       <c r="D128" s="4" t="s">
         <v>367</v>
@@ -3670,13 +3673,13 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B129" s="3">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="C129" s="3">
-        <v>208.66</v>
+        <v>52.17</v>
       </c>
       <c r="D129" s="4" t="s">
         <v>367</v>
@@ -3684,13 +3687,13 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B130" s="3">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C130" s="3">
-        <v>88.87</v>
+        <v>208.66</v>
       </c>
       <c r="D130" s="4" t="s">
         <v>367</v>
@@ -3698,13 +3701,13 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B131" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C131" s="3">
-        <v>67.27</v>
+        <v>88.87</v>
       </c>
       <c r="D131" s="4" t="s">
         <v>367</v>
@@ -3712,13 +3715,13 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B132" s="3">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C132" s="3">
-        <v>69.55</v>
+        <v>67.27</v>
       </c>
       <c r="D132" s="4" t="s">
         <v>367</v>
@@ -3726,13 +3729,13 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B133" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C133" s="3">
-        <v>63.89</v>
+        <v>69.55</v>
       </c>
       <c r="D133" s="4" t="s">
         <v>367</v>
@@ -3740,13 +3743,13 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B134" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C134" s="3">
-        <v>149.91</v>
+        <v>63.89</v>
       </c>
       <c r="D134" s="4" t="s">
         <v>367</v>
@@ -3754,13 +3757,13 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B135" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C135" s="3">
-        <v>38.57</v>
+        <v>149.91</v>
       </c>
       <c r="D135" s="4" t="s">
         <v>367</v>
@@ -3768,13 +3771,13 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B136" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C136" s="3">
-        <v>207.31</v>
+        <v>38.57</v>
       </c>
       <c r="D136" s="4" t="s">
         <v>367</v>
@@ -3782,16 +3785,16 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B137" s="3">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C137" s="3">
-        <v>58.24</v>
+        <v>207.31</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3799,10 +3802,10 @@
         <v>89</v>
       </c>
       <c r="B138" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C138" s="3">
-        <v>65.23</v>
+        <v>58.24</v>
       </c>
       <c r="D138" s="4" t="s">
         <v>364</v>
@@ -3810,13 +3813,13 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B139" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C139" s="3">
-        <v>290.95</v>
+        <v>65.23</v>
       </c>
       <c r="D139" s="4" t="s">
         <v>364</v>
@@ -3827,10 +3830,10 @@
         <v>90</v>
       </c>
       <c r="B140" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C140" s="3">
-        <v>325.87</v>
+        <v>290.95</v>
       </c>
       <c r="D140" s="4" t="s">
         <v>364</v>
@@ -3838,27 +3841,27 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B141" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C141" s="3">
-        <v>5165.8</v>
+        <v>325.87</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B142" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C142" s="3">
-        <v>511.75</v>
+        <v>5165.8</v>
       </c>
       <c r="D142" s="4" t="s">
         <v>367</v>
@@ -3866,13 +3869,13 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B143" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C143" s="3">
-        <v>572.70000000000005</v>
+        <v>511.75</v>
       </c>
       <c r="D143" s="4" t="s">
         <v>367</v>
@@ -3880,55 +3883,55 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B144" s="3">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="C144" s="3">
-        <v>66.98</v>
+        <v>572.70000000000005</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B145" s="3">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="C145" s="3">
-        <v>367.42</v>
+        <v>66.98</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B146" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C146" s="3">
-        <v>51.52</v>
+        <v>367.42</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B147" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C147" s="3">
-        <v>23.19</v>
+        <v>51.52</v>
       </c>
       <c r="D147" s="4" t="s">
         <v>366</v>
@@ -3936,10 +3939,10 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B148" s="3">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C148" s="3">
         <v>23.19</v>
@@ -3950,27 +3953,27 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B149" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C149" s="3">
-        <v>69.55</v>
+        <v>23.19</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B150" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C150" s="3">
-        <v>3169.7</v>
+        <v>69.55</v>
       </c>
       <c r="D150" s="4" t="s">
         <v>367</v>
@@ -3978,13 +3981,13 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B151" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C151" s="3">
-        <v>81.14</v>
+        <v>3169.7</v>
       </c>
       <c r="D151" s="4" t="s">
         <v>367</v>
@@ -3992,10 +3995,10 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B152" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C152" s="3">
         <v>81.14</v>
@@ -4006,41 +4009,41 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B153" s="3">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C153" s="3">
-        <v>66.98</v>
+        <v>81.14</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
     </row>
     <row r="154" spans="1:4">
       <c r="A154" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B154" s="3">
-        <v>30</v>
-      </c>
-      <c r="C154" s="8">
-        <v>77.63</v>
+        <v>58</v>
+      </c>
+      <c r="C154" s="3">
+        <v>66.98</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B155" s="3">
-        <v>26</v>
-      </c>
-      <c r="C155" s="3">
-        <v>93.35</v>
+        <v>30</v>
+      </c>
+      <c r="C155" s="8">
+        <v>77.63</v>
       </c>
       <c r="D155" s="4" t="s">
         <v>367</v>
@@ -4048,13 +4051,13 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B156" s="3">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C156" s="3">
-        <v>1217.1600000000001</v>
+        <v>93.35</v>
       </c>
       <c r="D156" s="4" t="s">
         <v>367</v>
@@ -4062,13 +4065,13 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B157" s="3">
         <v>0</v>
       </c>
       <c r="C157" s="3">
-        <v>3079</v>
+        <v>1217.1600000000001</v>
       </c>
       <c r="D157" s="4" t="s">
         <v>367</v>
@@ -4076,16 +4079,16 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B158" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C158" s="3">
-        <v>43.7</v>
+        <v>3079</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4093,10 +4096,10 @@
         <v>108</v>
       </c>
       <c r="B159" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C159" s="3">
-        <v>48.95</v>
+        <v>43.7</v>
       </c>
       <c r="D159" s="4" t="s">
         <v>366</v>
@@ -4104,27 +4107,27 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B160" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C160" s="3">
-        <v>72.33</v>
+        <v>48.95</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="161" spans="1:4">
       <c r="A161" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B161" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C161" s="3">
-        <v>284.19</v>
+        <v>72.33</v>
       </c>
       <c r="D161" s="4" t="s">
         <v>364</v>
@@ -4132,38 +4135,38 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B162" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C162" s="3">
-        <v>101.5</v>
+        <v>284.19</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B163" s="3">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C163" s="3">
-        <v>32.200000000000003</v>
+        <v>101.5</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B164" s="3">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="C164" s="3">
         <v>32.200000000000003</v>
@@ -4174,13 +4177,13 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C165" s="3">
-        <v>37.43</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D165" s="4" t="s">
         <v>354</v>
@@ -4188,13 +4191,13 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B166" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C166" s="3">
-        <v>32.200000000000003</v>
+        <v>37.43</v>
       </c>
       <c r="D166" s="4" t="s">
         <v>354</v>
@@ -4202,41 +4205,41 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B167" s="3">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="C167" s="3">
-        <v>115.01</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B168" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C168" s="3">
-        <v>38.39</v>
+        <v>115.01</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="169" spans="1:4">
       <c r="A169" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B169" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C169" s="3">
-        <v>151.47999999999999</v>
+        <v>38.39</v>
       </c>
       <c r="D169" s="4" t="s">
         <v>364</v>
@@ -4244,13 +4247,13 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B170" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C170" s="3">
-        <v>181.68</v>
+        <v>151.47999999999999</v>
       </c>
       <c r="D170" s="4" t="s">
         <v>364</v>
@@ -4258,27 +4261,27 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B171" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C171" s="3">
-        <v>20.059999999999999</v>
+        <v>181.68</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
     </row>
     <row r="172" spans="1:4">
       <c r="A172" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B172" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C172" s="3">
-        <v>12.88</v>
+        <v>20.059999999999999</v>
       </c>
       <c r="D172" s="4" t="s">
         <v>355</v>
@@ -4286,13 +4289,13 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B173" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C173" s="3">
-        <v>26.73</v>
+        <v>12.88</v>
       </c>
       <c r="D173" s="4" t="s">
         <v>355</v>
@@ -4300,13 +4303,13 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B174" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C174" s="3">
-        <v>29.95</v>
+        <v>26.73</v>
       </c>
       <c r="D174" s="4" t="s">
         <v>355</v>
@@ -4314,13 +4317,13 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B175" s="3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C175" s="3">
-        <v>58.68</v>
+        <v>29.95</v>
       </c>
       <c r="D175" s="4" t="s">
         <v>355</v>
@@ -4328,13 +4331,13 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B176" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C176" s="3">
-        <v>79.98</v>
+        <v>58.68</v>
       </c>
       <c r="D176" s="4" t="s">
         <v>355</v>
@@ -4342,55 +4345,55 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B177" s="3">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C177" s="3">
-        <v>38.770000000000003</v>
+        <v>79.98</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="178" spans="1:4">
       <c r="A178" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B178" s="3">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C178" s="3">
-        <v>107.35</v>
+        <v>38.770000000000003</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
     </row>
     <row r="179" spans="1:4">
       <c r="A179" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B179" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C179" s="3">
-        <v>61.83</v>
+        <v>107.35</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="180" spans="1:4">
       <c r="A180" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B180" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C180" s="3">
-        <v>243.16</v>
+        <v>61.83</v>
       </c>
       <c r="D180" s="4" t="s">
         <v>364</v>
@@ -4398,41 +4401,41 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B181" s="3">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C181" s="3">
-        <v>63.78</v>
+        <v>243.16</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="182" spans="1:4">
       <c r="A182" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B182" s="3">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C182" s="3">
-        <v>75.989999999999995</v>
+        <v>63.78</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="183" spans="1:4">
       <c r="A183" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B183" s="3">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C183" s="3">
-        <v>297.64999999999998</v>
+        <v>75.989999999999995</v>
       </c>
       <c r="D183" s="4" t="s">
         <v>364</v>
@@ -4440,13 +4443,13 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B184" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C184" s="3">
-        <v>77.28</v>
+        <v>297.64999999999998</v>
       </c>
       <c r="D184" s="4" t="s">
         <v>364</v>
@@ -4454,13 +4457,13 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B185" s="3">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C185" s="3">
-        <v>75.989999999999995</v>
+        <v>77.28</v>
       </c>
       <c r="D185" s="4" t="s">
         <v>364</v>
@@ -4468,13 +4471,13 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B186" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C186" s="3">
-        <v>342.24</v>
+        <v>75.989999999999995</v>
       </c>
       <c r="D186" s="4" t="s">
         <v>364</v>
@@ -4482,27 +4485,27 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B187" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C187" s="3">
-        <v>633.75</v>
+        <v>342.24</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="188" spans="1:4">
       <c r="A188" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B188" s="3">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="C188" s="3">
-        <v>50.51</v>
+        <v>633.75</v>
       </c>
       <c r="D188" s="4" t="s">
         <v>367</v>
@@ -4510,13 +4513,13 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" t="s">
-        <v>430</v>
+        <v>137</v>
       </c>
       <c r="B189" s="3">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="C189" s="3">
-        <v>581.9</v>
+        <v>50.51</v>
       </c>
       <c r="D189" s="4" t="s">
         <v>367</v>
@@ -4524,13 +4527,13 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" t="s">
-        <v>138</v>
+        <v>430</v>
       </c>
       <c r="B190" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C190" s="3">
-        <v>579.13</v>
+        <v>581.9</v>
       </c>
       <c r="D190" s="4" t="s">
         <v>367</v>
@@ -4538,55 +4541,55 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B191" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C191" s="3">
-        <v>122.36</v>
+        <v>579.13</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="192" spans="1:4">
       <c r="A192" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B192" s="3">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C192" s="3">
-        <v>35.81</v>
+        <v>122.36</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
     </row>
     <row r="193" spans="1:4">
       <c r="A193" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B193" s="3">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C193" s="3">
-        <v>59.25</v>
+        <v>35.81</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="194" spans="1:4">
       <c r="A194" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B194" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C194" s="3">
-        <v>260</v>
+        <v>59.25</v>
       </c>
       <c r="D194" s="4" t="s">
         <v>364</v>
@@ -4594,13 +4597,13 @@
     </row>
     <row r="195" spans="1:4">
       <c r="A195" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B195" s="3">
-        <v>21</v>
-      </c>
-      <c r="C195" s="7">
-        <v>59.62</v>
+        <v>0</v>
+      </c>
+      <c r="C195" s="3">
+        <v>260</v>
       </c>
       <c r="D195" s="4" t="s">
         <v>364</v>
@@ -4608,13 +4611,13 @@
     </row>
     <row r="196" spans="1:4">
       <c r="A196" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B196" s="3">
-        <v>4</v>
-      </c>
-      <c r="C196" s="3">
-        <v>248.77</v>
+        <v>21</v>
+      </c>
+      <c r="C196" s="7">
+        <v>59.62</v>
       </c>
       <c r="D196" s="4" t="s">
         <v>364</v>
@@ -4622,13 +4625,13 @@
     </row>
     <row r="197" spans="1:4">
       <c r="A197" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B197" s="3">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C197" s="3">
-        <v>74.7</v>
+        <v>248.77</v>
       </c>
       <c r="D197" s="4" t="s">
         <v>364</v>
@@ -4636,13 +4639,13 @@
     </row>
     <row r="198" spans="1:4">
       <c r="A198" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B198" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C198" s="3">
-        <v>296.3</v>
+        <v>74.7</v>
       </c>
       <c r="D198" s="4" t="s">
         <v>364</v>
@@ -4650,13 +4653,13 @@
     </row>
     <row r="199" spans="1:4">
       <c r="A199" t="s">
-        <v>385</v>
+        <v>146</v>
       </c>
       <c r="B199" s="3">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C199" s="3">
-        <v>168.7</v>
+        <v>296.3</v>
       </c>
       <c r="D199" s="4" t="s">
         <v>364</v>
@@ -4664,13 +4667,13 @@
     </row>
     <row r="200" spans="1:4">
       <c r="A200" t="s">
-        <v>147</v>
+        <v>385</v>
       </c>
       <c r="B200" s="3">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="C200" s="3">
-        <v>44.5</v>
+        <v>168.7</v>
       </c>
       <c r="D200" s="4" t="s">
         <v>364</v>
@@ -4678,13 +4681,13 @@
     </row>
     <row r="201" spans="1:4">
       <c r="A201" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B201" s="3">
-        <v>9</v>
-      </c>
-      <c r="C201" s="10">
-        <v>210.88</v>
+        <v>26</v>
+      </c>
+      <c r="C201" s="3">
+        <v>44.5</v>
       </c>
       <c r="D201" s="4" t="s">
         <v>364</v>
@@ -4692,13 +4695,13 @@
     </row>
     <row r="202" spans="1:4">
       <c r="A202" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B202" s="3">
-        <v>2</v>
-      </c>
-      <c r="C202" s="3">
-        <v>2189.02</v>
+        <v>9</v>
+      </c>
+      <c r="C202" s="10">
+        <v>210.88</v>
       </c>
       <c r="D202" s="4" t="s">
         <v>364</v>
@@ -4706,13 +4709,13 @@
     </row>
     <row r="203" spans="1:4">
       <c r="A203" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B203" s="3">
         <v>2</v>
       </c>
       <c r="C203" s="3">
-        <v>453.22</v>
+        <v>2189.02</v>
       </c>
       <c r="D203" s="4" t="s">
         <v>364</v>
@@ -4720,13 +4723,13 @@
     </row>
     <row r="204" spans="1:4">
       <c r="A204" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B204" s="3">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C204" s="3">
-        <v>48.64</v>
+        <v>453.22</v>
       </c>
       <c r="D204" s="4" t="s">
         <v>364</v>
@@ -4734,13 +4737,13 @@
     </row>
     <row r="205" spans="1:4">
       <c r="A205" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B205" s="3">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C205" s="3">
-        <v>126.63</v>
+        <v>48.64</v>
       </c>
       <c r="D205" s="4" t="s">
         <v>364</v>
@@ -4748,41 +4751,41 @@
     </row>
     <row r="206" spans="1:4">
       <c r="A206" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B206" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C206" s="3">
-        <v>69.56</v>
+        <v>126.63</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="207" spans="1:4">
       <c r="A207" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B207" s="3">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C207" s="3">
-        <v>44.51</v>
+        <v>69.56</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="208" spans="1:4">
       <c r="A208" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B208" s="3">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C208" s="3">
-        <v>145.94</v>
+        <v>44.51</v>
       </c>
       <c r="D208" s="4" t="s">
         <v>364</v>
@@ -4790,13 +4793,13 @@
     </row>
     <row r="209" spans="1:4">
       <c r="A209" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B209" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C209" s="3">
-        <v>199.77</v>
+        <v>145.94</v>
       </c>
       <c r="D209" s="4" t="s">
         <v>364</v>
@@ -4804,13 +4807,13 @@
     </row>
     <row r="210" spans="1:4">
       <c r="A210" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B210" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C210" s="3">
-        <v>2060</v>
+        <v>199.77</v>
       </c>
       <c r="D210" s="4" t="s">
         <v>364</v>
@@ -4818,13 +4821,13 @@
     </row>
     <row r="211" spans="1:4">
       <c r="A211" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B211" s="3">
-        <v>34</v>
-      </c>
-      <c r="C211" s="8">
-        <v>58.32</v>
+        <v>0</v>
+      </c>
+      <c r="C211" s="3">
+        <v>2060</v>
       </c>
       <c r="D211" s="4" t="s">
         <v>364</v>
@@ -4832,13 +4835,13 @@
     </row>
     <row r="212" spans="1:4">
       <c r="A212" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B212" s="3">
-        <v>2</v>
-      </c>
-      <c r="C212" s="3">
-        <v>183.41</v>
+        <v>34</v>
+      </c>
+      <c r="C212" s="8">
+        <v>58.32</v>
       </c>
       <c r="D212" s="4" t="s">
         <v>364</v>
@@ -4846,13 +4849,13 @@
     </row>
     <row r="213" spans="1:4">
       <c r="A213" t="s">
-        <v>352</v>
+        <v>159</v>
       </c>
       <c r="B213" s="3">
-        <v>7</v>
-      </c>
-      <c r="C213" s="8">
-        <v>257.70999999999998</v>
+        <v>2</v>
+      </c>
+      <c r="C213" s="3">
+        <v>183.41</v>
       </c>
       <c r="D213" s="4" t="s">
         <v>364</v>
@@ -4860,41 +4863,41 @@
     </row>
     <row r="214" spans="1:4">
       <c r="A214" t="s">
-        <v>160</v>
+        <v>352</v>
       </c>
       <c r="B214" s="3">
-        <v>30</v>
-      </c>
-      <c r="C214" s="3">
-        <v>33.479999999999997</v>
+        <v>7</v>
+      </c>
+      <c r="C214" s="8">
+        <v>257.70999999999998</v>
       </c>
       <c r="D214" s="4" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="215" spans="1:4">
       <c r="A215" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B215" s="3">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C215" s="3">
-        <v>48.13</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="216" spans="1:4">
       <c r="A216" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B216" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C216" s="3">
-        <v>5400</v>
+        <v>48.13</v>
       </c>
       <c r="D216" s="4" t="s">
         <v>364</v>
@@ -4902,13 +4905,13 @@
     </row>
     <row r="217" spans="1:4">
       <c r="A217" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B217" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C217" s="3">
-        <v>170.78</v>
+        <v>5400</v>
       </c>
       <c r="D217" s="4" t="s">
         <v>364</v>
@@ -4916,13 +4919,13 @@
     </row>
     <row r="218" spans="1:4">
       <c r="A218" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B218" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C218" s="3">
-        <v>216.3</v>
+        <v>170.78</v>
       </c>
       <c r="D218" s="4" t="s">
         <v>364</v>
@@ -4930,13 +4933,13 @@
     </row>
     <row r="219" spans="1:4">
       <c r="A219" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B219" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="C219" s="3">
-        <v>59.7</v>
+        <v>216.3</v>
       </c>
       <c r="D219" s="4" t="s">
         <v>364</v>
@@ -4944,13 +4947,13 @@
     </row>
     <row r="220" spans="1:4">
       <c r="A220" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B220" s="3">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C220" s="3">
-        <v>265.05</v>
+        <v>59.7</v>
       </c>
       <c r="D220" s="4" t="s">
         <v>364</v>
@@ -4958,97 +4961,97 @@
     </row>
     <row r="221" spans="1:4">
       <c r="A221" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B221" s="3">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="C221" s="3">
-        <v>36.799999999999997</v>
+        <v>265.05</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="222" spans="1:4">
       <c r="A222" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B222" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C222" s="3">
-        <v>103.04</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
     </row>
     <row r="223" spans="1:4">
       <c r="A223" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B223" s="3">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="C223" s="3">
-        <v>36.75</v>
+        <v>103.04</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
     </row>
     <row r="224" spans="1:4">
       <c r="A224" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B224" s="3">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="C224" s="3">
-        <v>47.16</v>
+        <v>36.75</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
     </row>
     <row r="225" spans="1:4">
       <c r="A225" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B225" s="3">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C225" s="3">
-        <v>16.809999999999999</v>
+        <v>47.16</v>
       </c>
       <c r="D225" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="226" spans="1:4">
       <c r="A226" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B226" s="3">
         <v>27</v>
       </c>
       <c r="C226" s="3">
-        <v>37.299999999999997</v>
+        <v>16.809999999999999</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="227" spans="1:4">
       <c r="A227" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B227" s="3">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C227" s="3">
-        <v>126.24</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="D227" s="4" t="s">
         <v>364</v>
@@ -5056,13 +5059,13 @@
     </row>
     <row r="228" spans="1:4">
       <c r="A228" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B228" s="3">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C228" s="3">
-        <v>154.62</v>
+        <v>126.24</v>
       </c>
       <c r="D228" s="4" t="s">
         <v>364</v>
@@ -5070,13 +5073,13 @@
     </row>
     <row r="229" spans="1:4">
       <c r="A229" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B229" s="3">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C229" s="3">
-        <v>508.2</v>
+        <v>154.62</v>
       </c>
       <c r="D229" s="4" t="s">
         <v>364</v>
@@ -5084,13 +5087,13 @@
     </row>
     <row r="230" spans="1:4">
       <c r="A230" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B230" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C230" s="3">
-        <v>5069</v>
+        <v>508.2</v>
       </c>
       <c r="D230" s="4" t="s">
         <v>364</v>
@@ -5098,13 +5101,13 @@
     </row>
     <row r="231" spans="1:4">
       <c r="A231" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B231" s="3">
         <v>0</v>
       </c>
       <c r="C231" s="3">
-        <v>466.78</v>
+        <v>5069</v>
       </c>
       <c r="D231" s="4" t="s">
         <v>364</v>
@@ -5112,27 +5115,27 @@
     </row>
     <row r="232" spans="1:4">
       <c r="A232" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B232" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C232" s="3">
-        <v>57.5</v>
+        <v>466.78</v>
       </c>
       <c r="D232" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="233" spans="1:4">
       <c r="A233" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B233" s="3">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C233" s="3">
-        <v>63.13</v>
+        <v>57.5</v>
       </c>
       <c r="D233" s="4" t="s">
         <v>367</v>
@@ -5140,13 +5143,13 @@
     </row>
     <row r="234" spans="1:4">
       <c r="A234" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B234" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C234" s="3">
-        <v>20789.41</v>
+        <v>63.13</v>
       </c>
       <c r="D234" s="4" t="s">
         <v>367</v>
@@ -5160,7 +5163,7 @@
         <v>1</v>
       </c>
       <c r="C235" s="3">
-        <v>33057.85</v>
+        <v>20789.41</v>
       </c>
       <c r="D235" s="4" t="s">
         <v>367</v>
@@ -5168,13 +5171,13 @@
     </row>
     <row r="236" spans="1:4">
       <c r="A236" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B236" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C236" s="3">
-        <v>83.5</v>
+        <v>33057.85</v>
       </c>
       <c r="D236" s="4" t="s">
         <v>367</v>
@@ -5182,16 +5185,16 @@
     </row>
     <row r="237" spans="1:4">
       <c r="A237" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B237" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C237" s="3">
-        <v>45.72</v>
+        <v>83.5</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5199,10 +5202,10 @@
         <v>182</v>
       </c>
       <c r="B238" s="3">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C238" s="3">
-        <v>81.650000000000006</v>
+        <v>45.72</v>
       </c>
       <c r="D238" s="4" t="s">
         <v>419</v>
@@ -5210,13 +5213,13 @@
     </row>
     <row r="239" spans="1:4">
       <c r="A239" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B239" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C239" s="3">
-        <v>50.71</v>
+        <v>81.650000000000006</v>
       </c>
       <c r="D239" s="4" t="s">
         <v>419</v>
@@ -5224,13 +5227,13 @@
     </row>
     <row r="240" spans="1:4">
       <c r="A240" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B240" s="3">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C240" s="3">
-        <v>51.75</v>
+        <v>50.71</v>
       </c>
       <c r="D240" s="4" t="s">
         <v>419</v>
@@ -5238,13 +5241,13 @@
     </row>
     <row r="241" spans="1:4">
       <c r="A241" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B241" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C241" s="3">
-        <v>36.94</v>
+        <v>51.75</v>
       </c>
       <c r="D241" s="4" t="s">
         <v>419</v>
@@ -5252,13 +5255,13 @@
     </row>
     <row r="242" spans="1:4">
       <c r="A242" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B242" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C242" s="3">
-        <v>36.799999999999997</v>
+        <v>36.94</v>
       </c>
       <c r="D242" s="4" t="s">
         <v>419</v>
@@ -5272,7 +5275,7 @@
         <v>12</v>
       </c>
       <c r="C243" s="3">
-        <v>79.58</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D243" s="4" t="s">
         <v>419</v>
@@ -5280,27 +5283,27 @@
     </row>
     <row r="244" spans="1:4">
       <c r="A244" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B244" s="3">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C244" s="3">
-        <v>67.28</v>
+        <v>79.58</v>
       </c>
       <c r="D244" s="4" t="s">
-        <v>367</v>
+        <v>419</v>
       </c>
     </row>
     <row r="245" spans="1:4">
       <c r="A245" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B245" s="3">
-        <v>27</v>
-      </c>
-      <c r="C245" s="8">
-        <v>79.599999999999994</v>
+        <v>28</v>
+      </c>
+      <c r="C245" s="3">
+        <v>67.28</v>
       </c>
       <c r="D245" s="4" t="s">
         <v>367</v>
@@ -5308,13 +5311,13 @@
     </row>
     <row r="246" spans="1:4">
       <c r="A246" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B246" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C246" s="8">
-        <v>75.88</v>
+        <v>79.599999999999994</v>
       </c>
       <c r="D246" s="4" t="s">
         <v>367</v>
@@ -5322,13 +5325,13 @@
     </row>
     <row r="247" spans="1:4">
       <c r="A247" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B247" s="3">
-        <v>21</v>
-      </c>
-      <c r="C247" s="3">
-        <v>109.08</v>
+        <v>23</v>
+      </c>
+      <c r="C247" s="8">
+        <v>75.88</v>
       </c>
       <c r="D247" s="4" t="s">
         <v>367</v>
@@ -5336,27 +5339,27 @@
     </row>
     <row r="248" spans="1:4">
       <c r="A248" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B248" s="3">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="C248" s="3">
-        <v>33.479999999999997</v>
+        <v>109.08</v>
       </c>
       <c r="D248" s="4" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
     </row>
     <row r="249" spans="1:4">
       <c r="A249" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B249" s="3">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="C249" s="3">
-        <v>422.09</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D249" s="4" t="s">
         <v>356</v>
@@ -5364,13 +5367,13 @@
     </row>
     <row r="250" spans="1:4">
       <c r="A250" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B250" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C250" s="3">
-        <v>1277.7</v>
+        <v>422.09</v>
       </c>
       <c r="D250" s="4" t="s">
         <v>356</v>
@@ -5378,27 +5381,27 @@
     </row>
     <row r="251" spans="1:4">
       <c r="A251" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B251" s="3">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C251" s="3">
-        <v>6.44</v>
+        <v>1277.7</v>
       </c>
       <c r="D251" s="4" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
     </row>
     <row r="252" spans="1:4">
       <c r="A252" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B252" s="3">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C252" s="3">
-        <v>108.2</v>
+        <v>6.44</v>
       </c>
       <c r="D252" s="4" t="s">
         <v>366</v>
@@ -5406,16 +5409,16 @@
     </row>
     <row r="253" spans="1:4">
       <c r="A253" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B253" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C253" s="3">
-        <v>4456.4799999999996</v>
+        <v>108.2</v>
       </c>
       <c r="D253" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5423,10 +5426,10 @@
         <v>196</v>
       </c>
       <c r="B254" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C254" s="3">
-        <v>7429</v>
+        <v>4456.4799999999996</v>
       </c>
       <c r="D254" s="4" t="s">
         <v>364</v>
@@ -5434,13 +5437,13 @@
     </row>
     <row r="255" spans="1:4">
       <c r="A255" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B255" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C255" s="3">
-        <v>609.5</v>
+        <v>7429</v>
       </c>
       <c r="D255" s="4" t="s">
         <v>364</v>
@@ -5448,24 +5451,24 @@
     </row>
     <row r="256" spans="1:4">
       <c r="A256" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B256" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C256" s="3">
-        <v>32.200000000000003</v>
+        <v>609.5</v>
       </c>
       <c r="D256" s="4" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
     </row>
     <row r="257" spans="1:4">
       <c r="A257" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B257" s="3">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C257" s="3">
         <v>32.200000000000003</v>
@@ -5476,10 +5479,10 @@
     </row>
     <row r="258" spans="1:4">
       <c r="A258" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B258" s="3">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C258" s="3">
         <v>32.200000000000003</v>
@@ -5490,10 +5493,10 @@
     </row>
     <row r="259" spans="1:4">
       <c r="A259" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B259" s="3">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="C259" s="3">
         <v>32.200000000000003</v>
@@ -5504,13 +5507,13 @@
     </row>
     <row r="260" spans="1:4">
       <c r="A260" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B260" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C260" s="3">
-        <v>40.4</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D260" s="4" t="s">
         <v>354</v>
@@ -5518,13 +5521,13 @@
     </row>
     <row r="261" spans="1:4">
       <c r="A261" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B261" s="3">
-        <v>175</v>
+        <v>3</v>
       </c>
       <c r="C261" s="3">
-        <v>36.06</v>
+        <v>40.4</v>
       </c>
       <c r="D261" s="4" t="s">
         <v>354</v>
@@ -5532,27 +5535,27 @@
     </row>
     <row r="262" spans="1:4">
       <c r="A262" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B262" s="3">
-        <v>1</v>
+        <v>175</v>
       </c>
       <c r="C262" s="3">
-        <v>56</v>
+        <v>36.06</v>
       </c>
       <c r="D262" s="4" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
     </row>
     <row r="263" spans="1:4">
       <c r="A263" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B263" s="3">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C263" s="3">
-        <v>57.63</v>
+        <v>56</v>
       </c>
       <c r="D263" s="4" t="s">
         <v>367</v>
@@ -5560,13 +5563,13 @@
     </row>
     <row r="264" spans="1:4">
       <c r="A264" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B264" s="3">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C264" s="3">
-        <v>60.78</v>
+        <v>57.63</v>
       </c>
       <c r="D264" s="4" t="s">
         <v>367</v>
@@ -5574,69 +5577,69 @@
     </row>
     <row r="265" spans="1:4">
       <c r="A265" t="s">
-        <v>420</v>
+        <v>206</v>
       </c>
       <c r="B265" s="3">
         <v>4</v>
       </c>
       <c r="C265" s="3">
-        <v>65</v>
+        <v>60.78</v>
       </c>
       <c r="D265" s="4" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
     </row>
     <row r="266" spans="1:4">
       <c r="A266" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B266" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C266" s="3">
-        <v>29.63</v>
+        <v>65</v>
       </c>
       <c r="D266" s="4" t="s">
-        <v>354</v>
+        <v>419</v>
       </c>
     </row>
     <row r="267" spans="1:4">
       <c r="A267" t="s">
-        <v>207</v>
+        <v>421</v>
       </c>
       <c r="B267" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C267" s="3">
-        <v>42.49</v>
+        <v>29.63</v>
       </c>
       <c r="D267" s="4" t="s">
-        <v>419</v>
+        <v>354</v>
       </c>
     </row>
     <row r="268" spans="1:4">
       <c r="A268" t="s">
-        <v>208</v>
-      </c>
-      <c r="B268" s="4">
-        <v>18</v>
-      </c>
-      <c r="C268" s="8">
-        <v>86.95</v>
+        <v>207</v>
+      </c>
+      <c r="B268" s="3">
+        <v>0</v>
+      </c>
+      <c r="C268" s="3">
+        <v>42.49</v>
       </c>
       <c r="D268" s="4" t="s">
-        <v>364</v>
+        <v>419</v>
       </c>
     </row>
     <row r="269" spans="1:4">
       <c r="A269" t="s">
-        <v>209</v>
-      </c>
-      <c r="B269" s="3">
-        <v>2</v>
+        <v>208</v>
+      </c>
+      <c r="B269" s="4">
+        <v>18</v>
       </c>
       <c r="C269" s="8">
-        <v>312.57</v>
+        <v>86.95</v>
       </c>
       <c r="D269" s="4" t="s">
         <v>364</v>
@@ -5644,13 +5647,13 @@
     </row>
     <row r="270" spans="1:4">
       <c r="A270" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B270" s="3">
-        <v>14</v>
-      </c>
-      <c r="C270" s="3">
-        <v>71.709999999999994</v>
+        <v>2</v>
+      </c>
+      <c r="C270" s="8">
+        <v>312.57</v>
       </c>
       <c r="D270" s="4" t="s">
         <v>364</v>
@@ -5658,41 +5661,41 @@
     </row>
     <row r="271" spans="1:4">
       <c r="A271" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B271" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C271" s="3">
-        <v>77.760000000000005</v>
+        <v>71.709999999999994</v>
       </c>
       <c r="D271" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="272" spans="1:4">
       <c r="A272" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B272" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C272" s="3">
-        <v>54.7</v>
+        <v>77.760000000000005</v>
       </c>
       <c r="D272" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="273" spans="1:4">
       <c r="A273" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B273" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C273" s="3">
-        <v>67.28</v>
+        <v>54.7</v>
       </c>
       <c r="D273" s="4" t="s">
         <v>364</v>
@@ -5700,13 +5703,13 @@
     </row>
     <row r="274" spans="1:4">
       <c r="A274" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B274" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C274" s="3">
-        <v>334.36</v>
+        <v>67.28</v>
       </c>
       <c r="D274" s="4" t="s">
         <v>364</v>
@@ -5714,13 +5717,13 @@
     </row>
     <row r="275" spans="1:4">
       <c r="A275" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B275" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C275" s="3">
-        <v>78.87</v>
+        <v>334.36</v>
       </c>
       <c r="D275" s="4" t="s">
         <v>364</v>
@@ -5728,13 +5731,13 @@
     </row>
     <row r="276" spans="1:4">
       <c r="A276" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B276" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C276" s="3">
-        <v>83.84</v>
+        <v>78.87</v>
       </c>
       <c r="D276" s="4" t="s">
         <v>364</v>
@@ -5742,13 +5745,13 @@
     </row>
     <row r="277" spans="1:4">
       <c r="A277" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B277" s="3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C277" s="3">
-        <v>331.2</v>
+        <v>83.84</v>
       </c>
       <c r="D277" s="4" t="s">
         <v>364</v>
@@ -5756,13 +5759,13 @@
     </row>
     <row r="278" spans="1:4">
       <c r="A278" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B278" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C278" s="3">
-        <v>79.75</v>
+        <v>331.2</v>
       </c>
       <c r="D278" s="4" t="s">
         <v>364</v>
@@ -5770,13 +5773,13 @@
     </row>
     <row r="279" spans="1:4">
       <c r="A279" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B279" s="3">
         <v>7</v>
       </c>
       <c r="C279" s="3">
-        <v>83.84</v>
+        <v>79.75</v>
       </c>
       <c r="D279" s="4" t="s">
         <v>364</v>
@@ -5784,13 +5787,13 @@
     </row>
     <row r="280" spans="1:4">
       <c r="A280" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B280" s="3">
-        <v>2</v>
-      </c>
-      <c r="C280" s="8">
-        <v>347.3</v>
+        <v>7</v>
+      </c>
+      <c r="C280" s="3">
+        <v>83.84</v>
       </c>
       <c r="D280" s="4" t="s">
         <v>364</v>
@@ -5801,10 +5804,10 @@
         <v>220</v>
       </c>
       <c r="B281" s="3">
-        <v>4</v>
-      </c>
-      <c r="C281" s="3">
-        <v>284</v>
+        <v>2</v>
+      </c>
+      <c r="C281" s="8">
+        <v>347.3</v>
       </c>
       <c r="D281" s="4" t="s">
         <v>364</v>
@@ -5812,27 +5815,27 @@
     </row>
     <row r="282" spans="1:4">
       <c r="A282" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B282" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C282" s="3">
-        <v>28.15</v>
+        <v>284</v>
       </c>
       <c r="D282" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="283" spans="1:4">
       <c r="A283" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B283" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C283" s="3">
-        <v>45.08</v>
+        <v>28.15</v>
       </c>
       <c r="D283" s="4" t="s">
         <v>366</v>
@@ -5840,13 +5843,13 @@
     </row>
     <row r="284" spans="1:4">
       <c r="A284" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B284" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C284" s="3">
-        <v>51.52</v>
+        <v>45.08</v>
       </c>
       <c r="D284" s="4" t="s">
         <v>366</v>
@@ -5854,27 +5857,27 @@
     </row>
     <row r="285" spans="1:4">
       <c r="A285" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B285" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C285" s="3">
-        <v>40.57</v>
+        <v>51.52</v>
       </c>
       <c r="D285" s="4" t="s">
-        <v>419</v>
+        <v>366</v>
       </c>
     </row>
     <row r="286" spans="1:4">
       <c r="A286" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B286" s="3">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C286" s="3">
-        <v>36.229999999999997</v>
+        <v>40.57</v>
       </c>
       <c r="D286" s="4" t="s">
         <v>419</v>
@@ -5882,41 +5885,41 @@
     </row>
     <row r="287" spans="1:4">
       <c r="A287" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B287" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C287" s="3">
-        <v>54.12</v>
+        <v>36.229999999999997</v>
       </c>
       <c r="D287" s="4" t="s">
-        <v>366</v>
+        <v>419</v>
       </c>
     </row>
     <row r="288" spans="1:4">
       <c r="A288" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B288" s="3">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C288" s="3">
-        <v>69.55</v>
+        <v>54.12</v>
       </c>
       <c r="D288" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="289" spans="1:4">
       <c r="A289" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B289" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C289" s="3">
-        <v>295.14999999999998</v>
+        <v>69.55</v>
       </c>
       <c r="D289" s="4" t="s">
         <v>364</v>
@@ -5924,41 +5927,41 @@
     </row>
     <row r="290" spans="1:4">
       <c r="A290" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B290" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C290" s="3">
-        <v>38.56</v>
+        <v>295.14999999999998</v>
       </c>
       <c r="D290" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="291" spans="1:4">
       <c r="A291" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B291" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C291" s="3">
-        <v>60.95</v>
+        <v>38.56</v>
       </c>
       <c r="D291" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="292" spans="1:4">
       <c r="A292" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B292" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C292" s="3">
-        <v>78.209999999999994</v>
+        <v>60.95</v>
       </c>
       <c r="D292" s="4" t="s">
         <v>367</v>
@@ -5966,27 +5969,27 @@
     </row>
     <row r="293" spans="1:4">
       <c r="A293" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B293" s="3">
-        <v>206</v>
+        <v>10</v>
       </c>
       <c r="C293" s="3">
-        <v>51.15</v>
+        <v>78.209999999999994</v>
       </c>
       <c r="D293" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="294" spans="1:4">
       <c r="A294" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B294" s="3">
-        <v>0</v>
+        <v>203</v>
       </c>
       <c r="C294" s="3">
-        <v>6591.8</v>
+        <v>51.15</v>
       </c>
       <c r="D294" s="4" t="s">
         <v>364</v>
@@ -5994,13 +5997,13 @@
     </row>
     <row r="295" spans="1:4">
       <c r="A295" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B295" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C295" s="3">
-        <v>182.42</v>
+        <v>6591.8</v>
       </c>
       <c r="D295" s="4" t="s">
         <v>364</v>
@@ -6008,13 +6011,13 @@
     </row>
     <row r="296" spans="1:4">
       <c r="A296" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B296" s="3">
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="C296" s="3">
-        <v>222.62</v>
+        <v>182.42</v>
       </c>
       <c r="D296" s="4" t="s">
         <v>364</v>
@@ -6022,13 +6025,13 @@
     </row>
     <row r="297" spans="1:4">
       <c r="A297" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B297" s="3">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="C297" s="3">
-        <v>2314.8000000000002</v>
+        <v>222.62</v>
       </c>
       <c r="D297" s="4" t="s">
         <v>364</v>
@@ -6036,13 +6039,13 @@
     </row>
     <row r="298" spans="1:4">
       <c r="A298" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B298" s="3">
         <v>0</v>
       </c>
       <c r="C298" s="3">
-        <v>894.8</v>
+        <v>2314.8000000000002</v>
       </c>
       <c r="D298" s="4" t="s">
         <v>364</v>
@@ -6050,27 +6053,27 @@
     </row>
     <row r="299" spans="1:4">
       <c r="A299" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B299" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C299" s="3">
-        <v>31.6</v>
+        <v>894.8</v>
       </c>
       <c r="D299" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="300" spans="1:4">
       <c r="A300" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B300" s="3">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C300" s="3">
-        <v>77.28</v>
+        <v>31.6</v>
       </c>
       <c r="D300" s="4" t="s">
         <v>366</v>
@@ -6078,13 +6081,13 @@
     </row>
     <row r="301" spans="1:4">
       <c r="A301" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B301" s="3">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="C301" s="3">
-        <v>43.8</v>
+        <v>77.28</v>
       </c>
       <c r="D301" s="4" t="s">
         <v>366</v>
@@ -6092,13 +6095,13 @@
     </row>
     <row r="302" spans="1:4">
       <c r="A302" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B302" s="3">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C302" s="3">
-        <v>21.9</v>
+        <v>43.8</v>
       </c>
       <c r="D302" s="4" t="s">
         <v>366</v>
@@ -6106,13 +6109,13 @@
     </row>
     <row r="303" spans="1:4">
       <c r="A303" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B303" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C303" s="3">
-        <v>798.6</v>
+        <v>21.9</v>
       </c>
       <c r="D303" s="4" t="s">
         <v>366</v>
@@ -6120,13 +6123,13 @@
     </row>
     <row r="304" spans="1:4">
       <c r="A304" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B304" s="3">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="C304" s="3">
-        <v>23.19</v>
+        <v>798.6</v>
       </c>
       <c r="D304" s="4" t="s">
         <v>366</v>
@@ -6134,13 +6137,13 @@
     </row>
     <row r="305" spans="1:4">
       <c r="A305" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B305" s="3">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="C305" s="3">
-        <v>8.24</v>
+        <v>23.19</v>
       </c>
       <c r="D305" s="4" t="s">
         <v>366</v>
@@ -6148,13 +6151,13 @@
     </row>
     <row r="306" spans="1:4">
       <c r="A306" t="s">
-        <v>455</v>
+        <v>244</v>
       </c>
       <c r="B306" s="3">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="C306" s="3">
-        <v>13.72</v>
+        <v>8.24</v>
       </c>
       <c r="D306" s="4" t="s">
         <v>366</v>
@@ -6162,10 +6165,10 @@
     </row>
     <row r="307" spans="1:4">
       <c r="A307" t="s">
-        <v>245</v>
+        <v>455</v>
       </c>
       <c r="B307" s="3">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C307" s="3">
         <v>13.72</v>
@@ -6176,13 +6179,13 @@
     </row>
     <row r="308" spans="1:4">
       <c r="A308" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B308" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C308" s="3">
-        <v>31.95</v>
+        <v>13.72</v>
       </c>
       <c r="D308" s="4" t="s">
         <v>366</v>
@@ -6190,13 +6193,13 @@
     </row>
     <row r="309" spans="1:4">
       <c r="A309" t="s">
-        <v>370</v>
+        <v>246</v>
       </c>
       <c r="B309" s="3">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="C309" s="3">
-        <v>16.2</v>
+        <v>31.95</v>
       </c>
       <c r="D309" s="4" t="s">
         <v>366</v>
@@ -6204,13 +6207,13 @@
     </row>
     <row r="310" spans="1:4">
       <c r="A310" t="s">
-        <v>247</v>
+        <v>370</v>
       </c>
       <c r="B310" s="3">
-        <v>6</v>
+        <v>103</v>
       </c>
       <c r="C310" s="3">
-        <v>36.869999999999997</v>
+        <v>16.2</v>
       </c>
       <c r="D310" s="4" t="s">
         <v>366</v>
@@ -6218,13 +6221,13 @@
     </row>
     <row r="311" spans="1:4">
       <c r="A311" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B311" s="3">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C311" s="3">
-        <v>31.48</v>
+        <v>36.869999999999997</v>
       </c>
       <c r="D311" s="4" t="s">
         <v>366</v>
@@ -6232,13 +6235,13 @@
     </row>
     <row r="312" spans="1:4">
       <c r="A312" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B312" s="3">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C312" s="3">
-        <v>21.9</v>
+        <v>31.48</v>
       </c>
       <c r="D312" s="4" t="s">
         <v>366</v>
@@ -6246,13 +6249,13 @@
     </row>
     <row r="313" spans="1:4">
       <c r="A313" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B313" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C313" s="3">
-        <v>23.19</v>
+        <v>21.9</v>
       </c>
       <c r="D313" s="4" t="s">
         <v>366</v>
@@ -6260,13 +6263,13 @@
     </row>
     <row r="314" spans="1:4">
       <c r="A314" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B314" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C314" s="3">
-        <v>19.55</v>
+        <v>23.19</v>
       </c>
       <c r="D314" s="4" t="s">
         <v>366</v>
@@ -6274,13 +6277,13 @@
     </row>
     <row r="315" spans="1:4">
       <c r="A315" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B315" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C315" s="3">
-        <v>19.07</v>
+        <v>19.55</v>
       </c>
       <c r="D315" s="4" t="s">
         <v>366</v>
@@ -6288,13 +6291,13 @@
     </row>
     <row r="316" spans="1:4">
       <c r="A316" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B316" s="3">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C316" s="3">
-        <v>21.9</v>
+        <v>19.07</v>
       </c>
       <c r="D316" s="4" t="s">
         <v>366</v>
@@ -6302,27 +6305,27 @@
     </row>
     <row r="317" spans="1:4">
       <c r="A317" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B317" s="3">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C317" s="3">
-        <v>79.349999999999994</v>
+        <v>21.9</v>
       </c>
       <c r="D317" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="318" spans="1:4">
       <c r="A318" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B318" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C318" s="3">
-        <v>862.7</v>
+        <v>79.349999999999994</v>
       </c>
       <c r="D318" s="4" t="s">
         <v>367</v>
@@ -6330,13 +6333,13 @@
     </row>
     <row r="319" spans="1:4">
       <c r="A319" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B319" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C319" s="3">
-        <v>56.93</v>
+        <v>862.7</v>
       </c>
       <c r="D319" s="4" t="s">
         <v>367</v>
@@ -6344,13 +6347,13 @@
     </row>
     <row r="320" spans="1:4">
       <c r="A320" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B320" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C320" s="3">
-        <v>1265</v>
+        <v>56.93</v>
       </c>
       <c r="D320" s="4" t="s">
         <v>367</v>
@@ -6358,27 +6361,27 @@
     </row>
     <row r="321" spans="1:4">
       <c r="A321" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B321" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C321" s="3">
-        <v>76</v>
+        <v>1265</v>
       </c>
       <c r="D321" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="322" spans="1:4">
       <c r="A322" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B322" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="C322" s="3">
-        <v>267.85000000000002</v>
+        <v>76</v>
       </c>
       <c r="D322" s="4" t="s">
         <v>364</v>
@@ -6386,13 +6389,13 @@
     </row>
     <row r="323" spans="1:4">
       <c r="A323" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B323" s="3">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C323" s="3">
-        <v>74.7</v>
+        <v>267.85000000000002</v>
       </c>
       <c r="D323" s="4" t="s">
         <v>364</v>
@@ -6400,13 +6403,13 @@
     </row>
     <row r="324" spans="1:4">
       <c r="A324" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B324" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C324" s="3">
-        <v>327.3</v>
+        <v>74.7</v>
       </c>
       <c r="D324" s="4" t="s">
         <v>364</v>
@@ -6414,13 +6417,13 @@
     </row>
     <row r="325" spans="1:4">
       <c r="A325" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B325" s="3">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C325" s="3">
-        <v>72.13</v>
+        <v>327.3</v>
       </c>
       <c r="D325" s="4" t="s">
         <v>364</v>
@@ -6428,13 +6431,13 @@
     </row>
     <row r="326" spans="1:4">
       <c r="A326" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B326" s="3">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="C326" s="3">
-        <v>302.39999999999998</v>
+        <v>72.13</v>
       </c>
       <c r="D326" s="4" t="s">
         <v>364</v>
@@ -6442,41 +6445,41 @@
     </row>
     <row r="327" spans="1:4">
       <c r="A327" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B327" s="3">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C327" s="3">
-        <v>36.799999999999997</v>
+        <v>302.39999999999998</v>
       </c>
       <c r="D327" s="4" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="328" spans="1:4">
       <c r="A328" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B328" s="3">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C328" s="3">
-        <v>428.5</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D328" s="4" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="329" spans="1:4">
       <c r="A329" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B329" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C329" s="3">
-        <v>450.22</v>
+        <v>428.5</v>
       </c>
       <c r="D329" s="4" t="s">
         <v>364</v>
@@ -6484,13 +6487,13 @@
     </row>
     <row r="330" spans="1:4">
       <c r="A330" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B330" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C330" s="3">
-        <v>465.7</v>
+        <v>450.22</v>
       </c>
       <c r="D330" s="4" t="s">
         <v>364</v>
@@ -6498,13 +6501,13 @@
     </row>
     <row r="331" spans="1:4">
       <c r="A331" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B331" s="3">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C331" s="3">
-        <v>38.25</v>
+        <v>465.7</v>
       </c>
       <c r="D331" s="4" t="s">
         <v>364</v>
@@ -6512,13 +6515,13 @@
     </row>
     <row r="332" spans="1:4">
       <c r="A332" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B332" s="3">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C332" s="3">
-        <v>87.49</v>
+        <v>38.25</v>
       </c>
       <c r="D332" s="4" t="s">
         <v>364</v>
@@ -6526,13 +6529,13 @@
     </row>
     <row r="333" spans="1:4">
       <c r="A333" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B333" s="3">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C333" s="3">
-        <v>63.13</v>
+        <v>87.49</v>
       </c>
       <c r="D333" s="4" t="s">
         <v>364</v>
@@ -6540,27 +6543,27 @@
     </row>
     <row r="334" spans="1:4">
       <c r="A334" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B334" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C334" s="3">
-        <v>377.78</v>
+        <v>63.13</v>
       </c>
       <c r="D334" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="335" spans="1:4">
       <c r="A335" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B335" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C335" s="3">
-        <v>3333.85</v>
+        <v>377.78</v>
       </c>
       <c r="D335" s="4" t="s">
         <v>368</v>
@@ -6568,13 +6571,13 @@
     </row>
     <row r="336" spans="1:4">
       <c r="A336" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B336" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C336" s="3">
-        <v>374.67</v>
+        <v>3333.85</v>
       </c>
       <c r="D336" s="4" t="s">
         <v>368</v>
@@ -6582,13 +6585,13 @@
     </row>
     <row r="337" spans="1:4">
       <c r="A337" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B337" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C337" s="3">
-        <v>120.06</v>
+        <v>374.67</v>
       </c>
       <c r="D337" s="4" t="s">
         <v>368</v>
@@ -6596,41 +6599,41 @@
     </row>
     <row r="338" spans="1:4">
       <c r="A338" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B338" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C338" s="3">
-        <v>54.2</v>
+        <v>120.06</v>
       </c>
       <c r="D338" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="339" spans="1:4">
       <c r="A339" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B339" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C339" s="3">
-        <v>31.5</v>
+        <v>54.2</v>
       </c>
       <c r="D339" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="340" spans="1:4">
       <c r="A340" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B340" s="3">
         <v>0</v>
       </c>
       <c r="C340" s="3">
-        <v>114.09</v>
+        <v>31.5</v>
       </c>
       <c r="D340" s="4" t="s">
         <v>364</v>
@@ -6638,13 +6641,13 @@
     </row>
     <row r="341" spans="1:4">
       <c r="A341" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B341" s="3">
         <v>0</v>
       </c>
       <c r="C341" s="3">
-        <v>139.9</v>
+        <v>114.09</v>
       </c>
       <c r="D341" s="4" t="s">
         <v>364</v>
@@ -6652,13 +6655,13 @@
     </row>
     <row r="342" spans="1:4">
       <c r="A342" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B342" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C342" s="3">
-        <v>50.13</v>
+        <v>139.9</v>
       </c>
       <c r="D342" s="4" t="s">
         <v>364</v>
@@ -6666,13 +6669,13 @@
     </row>
     <row r="343" spans="1:4">
       <c r="A343" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B343" s="3">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C343" s="3">
-        <v>140.26</v>
+        <v>50.13</v>
       </c>
       <c r="D343" s="4" t="s">
         <v>364</v>
@@ -6680,55 +6683,55 @@
     </row>
     <row r="344" spans="1:4">
       <c r="A344" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B344" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C344" s="3">
-        <v>370.53</v>
+        <v>140.26</v>
       </c>
       <c r="D344" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="345" spans="1:4">
       <c r="A345" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B345" s="3">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C345" s="3">
-        <v>30.9</v>
+        <v>370.53</v>
       </c>
       <c r="D345" s="4" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
     </row>
     <row r="346" spans="1:4">
       <c r="A346" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B346" s="3">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C346" s="3">
-        <v>5746.5</v>
+        <v>30.9</v>
       </c>
       <c r="D346" s="4" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="347" spans="1:4">
       <c r="A347" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B347" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C347" s="3">
-        <v>516.46</v>
+        <v>5746.5</v>
       </c>
       <c r="D347" s="4" t="s">
         <v>364</v>
@@ -6736,13 +6739,13 @@
     </row>
     <row r="348" spans="1:4">
       <c r="A348" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B348" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C348" s="3">
-        <v>185.15</v>
+        <v>516.46</v>
       </c>
       <c r="D348" s="4" t="s">
         <v>364</v>
@@ -6750,58 +6753,58 @@
     </row>
     <row r="349" spans="1:4">
       <c r="A349" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B349" s="3">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="C349" s="3">
-        <v>11.5</v>
+        <v>185.15</v>
       </c>
       <c r="D349" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="350" spans="1:4">
       <c r="A350" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B350" s="3">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C350" s="3">
-        <v>724.5</v>
+        <v>11.5</v>
       </c>
       <c r="D350" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="351" spans="1:4">
       <c r="A351" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B351" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C351" s="3">
-        <v>450.22</v>
+        <v>724.5</v>
       </c>
       <c r="D351" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="352" spans="1:4">
       <c r="A352" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B352" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C352" s="3">
-        <v>461.23</v>
+        <v>450.22</v>
       </c>
       <c r="D352" s="4" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -6812,7 +6815,7 @@
         <v>1</v>
       </c>
       <c r="C353" s="3">
-        <v>518.41999999999996</v>
+        <v>461.23</v>
       </c>
       <c r="D353" s="4" t="s">
         <v>357</v>
@@ -6820,13 +6823,13 @@
     </row>
     <row r="354" spans="1:4">
       <c r="A354" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B354" s="3">
         <v>1</v>
       </c>
       <c r="C354" s="3">
-        <v>348.08</v>
+        <v>518.41999999999996</v>
       </c>
       <c r="D354" s="4" t="s">
         <v>357</v>
@@ -6834,13 +6837,13 @@
     </row>
     <row r="355" spans="1:4">
       <c r="A355" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B355" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C355" s="3">
-        <v>33.479999999999997</v>
+        <v>348.08</v>
       </c>
       <c r="D355" s="4" t="s">
         <v>357</v>
@@ -6848,13 +6851,13 @@
     </row>
     <row r="356" spans="1:4">
       <c r="A356" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B356" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C356" s="3">
-        <v>35.79</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D356" s="4" t="s">
         <v>357</v>
@@ -6862,13 +6865,13 @@
     </row>
     <row r="357" spans="1:4">
       <c r="A357" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B357" s="3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C357" s="3">
-        <v>377.7</v>
+        <v>35.79</v>
       </c>
       <c r="D357" s="4" t="s">
         <v>357</v>
@@ -6876,13 +6879,13 @@
     </row>
     <row r="358" spans="1:4">
       <c r="A358" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B358" s="3">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C358" s="3">
-        <v>33.21</v>
+        <v>377.7</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>357</v>
@@ -6890,13 +6893,13 @@
     </row>
     <row r="359" spans="1:4">
       <c r="A359" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B359" s="3">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C359" s="3">
-        <v>27.16</v>
+        <v>33.21</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>357</v>
@@ -6904,13 +6907,13 @@
     </row>
     <row r="360" spans="1:4">
       <c r="A360" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B360" s="3">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C360" s="3">
-        <v>361.41</v>
+        <v>27.16</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>357</v>
@@ -6918,13 +6921,13 @@
     </row>
     <row r="361" spans="1:4">
       <c r="A361" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B361" s="3">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="C361" s="3">
-        <v>29.25</v>
+        <v>361.41</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>357</v>
@@ -6932,13 +6935,13 @@
     </row>
     <row r="362" spans="1:4">
       <c r="A362" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B362" s="3">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="C362" s="3">
-        <v>304.54000000000002</v>
+        <v>29.25</v>
       </c>
       <c r="D362" s="4" t="s">
         <v>357</v>
@@ -6946,13 +6949,13 @@
     </row>
     <row r="363" spans="1:4">
       <c r="A363" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B363" s="3">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C363" s="3">
-        <v>34.049999999999997</v>
+        <v>304.54000000000002</v>
       </c>
       <c r="D363" s="4" t="s">
         <v>357</v>
@@ -6960,55 +6963,55 @@
     </row>
     <row r="364" spans="1:4">
       <c r="A364" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B364" s="3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C364" s="3">
-        <v>57.7</v>
+        <v>34.049999999999997</v>
       </c>
       <c r="D364" s="4" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
     </row>
     <row r="365" spans="1:4">
       <c r="A365" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B365" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C365" s="3">
-        <v>90.9</v>
+        <v>57.7</v>
       </c>
       <c r="D365" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="366" spans="1:4">
       <c r="A366" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B366" s="3">
-        <v>199</v>
+        <v>10</v>
       </c>
       <c r="C366" s="3">
-        <v>47.62</v>
+        <v>90.9</v>
       </c>
       <c r="D366" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="367" spans="1:4">
       <c r="A367" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B367" s="3">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="C367" s="3">
-        <v>7173.59</v>
+        <v>47.62</v>
       </c>
       <c r="D367" s="4" t="s">
         <v>364</v>
@@ -7016,13 +7019,13 @@
     </row>
     <row r="368" spans="1:4">
       <c r="A368" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B368" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C368" s="3">
-        <v>677.79</v>
+        <v>7173.59</v>
       </c>
       <c r="D368" s="4" t="s">
         <v>364</v>
@@ -7030,13 +7033,13 @@
     </row>
     <row r="369" spans="1:4">
       <c r="A369" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B369" s="3">
-        <v>13</v>
-      </c>
-      <c r="C369" s="8">
-        <v>171.47</v>
+        <v>1</v>
+      </c>
+      <c r="C369" s="3">
+        <v>677.79</v>
       </c>
       <c r="D369" s="4" t="s">
         <v>364</v>
@@ -7044,13 +7047,13 @@
     </row>
     <row r="370" spans="1:4">
       <c r="A370" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B370" s="3">
-        <v>46</v>
-      </c>
-      <c r="C370" s="3">
-        <v>212.75</v>
+        <v>12</v>
+      </c>
+      <c r="C370" s="8">
+        <v>171.47</v>
       </c>
       <c r="D370" s="4" t="s">
         <v>364</v>
@@ -7058,13 +7061,13 @@
     </row>
     <row r="371" spans="1:4">
       <c r="A371" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B371" s="3">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="C371" s="3">
-        <v>2335.67</v>
+        <v>212.75</v>
       </c>
       <c r="D371" s="4" t="s">
         <v>364</v>
@@ -7072,13 +7075,13 @@
     </row>
     <row r="372" spans="1:4">
       <c r="A372" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B372" s="3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C372" s="3">
-        <v>66.180000000000007</v>
+        <v>2335.67</v>
       </c>
       <c r="D372" s="4" t="s">
         <v>364</v>
@@ -7086,13 +7089,13 @@
     </row>
     <row r="373" spans="1:4">
       <c r="A373" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B373" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C373" s="3">
-        <v>8139.6</v>
+        <v>66.180000000000007</v>
       </c>
       <c r="D373" s="4" t="s">
         <v>364</v>
@@ -7100,13 +7103,13 @@
     </row>
     <row r="374" spans="1:4">
       <c r="A374" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B374" s="3">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C374" s="3">
-        <v>259.81</v>
+        <v>8139.6</v>
       </c>
       <c r="D374" s="4" t="s">
         <v>364</v>
@@ -7114,13 +7117,13 @@
     </row>
     <row r="375" spans="1:4">
       <c r="A375" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B375" s="3">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="C375" s="3">
-        <v>259.8</v>
+        <v>259.81</v>
       </c>
       <c r="D375" s="4" t="s">
         <v>364</v>
@@ -7128,13 +7131,13 @@
     </row>
     <row r="376" spans="1:4">
       <c r="A376" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B376" s="3">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C376" s="3">
-        <v>310.2</v>
+        <v>259.8</v>
       </c>
       <c r="D376" s="4" t="s">
         <v>364</v>
@@ -7142,13 +7145,13 @@
     </row>
     <row r="377" spans="1:4">
       <c r="A377" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B377" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C377" s="3">
-        <v>36.43</v>
+        <v>310.2</v>
       </c>
       <c r="D377" s="4" t="s">
         <v>364</v>
@@ -7156,13 +7159,13 @@
     </row>
     <row r="378" spans="1:4">
       <c r="A378" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B378" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C378" s="3">
-        <v>87.22</v>
+        <v>36.43</v>
       </c>
       <c r="D378" s="4" t="s">
         <v>364</v>
@@ -7170,13 +7173,13 @@
     </row>
     <row r="379" spans="1:4">
       <c r="A379" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B379" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C379" s="3">
-        <v>319.60000000000002</v>
+        <v>87.22</v>
       </c>
       <c r="D379" s="4" t="s">
         <v>364</v>
@@ -7184,13 +7187,13 @@
     </row>
     <row r="380" spans="1:4">
       <c r="A380" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B380" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C380" s="3">
-        <v>62.6</v>
+        <v>319.60000000000002</v>
       </c>
       <c r="D380" s="4" t="s">
         <v>364</v>
@@ -7198,13 +7201,13 @@
     </row>
     <row r="381" spans="1:4">
       <c r="A381" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B381" s="3">
-        <v>8</v>
-      </c>
-      <c r="C381" s="8">
-        <v>385.25</v>
+        <v>14</v>
+      </c>
+      <c r="C381" s="3">
+        <v>62.6</v>
       </c>
       <c r="D381" s="4" t="s">
         <v>364</v>
@@ -7212,27 +7215,27 @@
     </row>
     <row r="382" spans="1:4">
       <c r="A382" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B382" s="3">
-        <v>11</v>
-      </c>
-      <c r="C382" s="3">
-        <v>67.28</v>
+        <v>8</v>
+      </c>
+      <c r="C382" s="8">
+        <v>385.25</v>
       </c>
       <c r="D382" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="383" spans="1:4">
       <c r="A383" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B383" s="3">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C383" s="3">
-        <v>1138.5</v>
+        <v>67.28</v>
       </c>
       <c r="D383" s="4" t="s">
         <v>367</v>
@@ -7240,27 +7243,27 @@
     </row>
     <row r="384" spans="1:4">
       <c r="A384" t="s">
-        <v>350</v>
+        <v>319</v>
       </c>
       <c r="B384" s="3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C384" s="3">
-        <v>58.69</v>
+        <v>1138.5</v>
       </c>
       <c r="D384" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="385" spans="1:4">
       <c r="A385" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B385" s="3">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C385" s="3">
-        <v>289.33999999999997</v>
+        <v>58.69</v>
       </c>
       <c r="D385" s="4" t="s">
         <v>364</v>
@@ -7268,13 +7271,13 @@
     </row>
     <row r="386" spans="1:4">
       <c r="A386" t="s">
-        <v>320</v>
+        <v>351</v>
       </c>
       <c r="B386" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C386" s="3">
-        <v>48.76</v>
+        <v>289.33999999999997</v>
       </c>
       <c r="D386" s="4" t="s">
         <v>364</v>
@@ -7282,13 +7285,13 @@
     </row>
     <row r="387" spans="1:4">
       <c r="A387" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B387" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C387" s="3">
-        <v>242.34</v>
+        <v>48.76</v>
       </c>
       <c r="D387" s="4" t="s">
         <v>364</v>
@@ -7296,13 +7299,13 @@
     </row>
     <row r="388" spans="1:4">
       <c r="A388" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B388" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C388" s="3">
-        <v>65.599999999999994</v>
+        <v>242.34</v>
       </c>
       <c r="D388" s="4" t="s">
         <v>364</v>
@@ -7310,13 +7313,13 @@
     </row>
     <row r="389" spans="1:4">
       <c r="A389" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B389" s="3">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C389" s="3">
-        <v>255.03</v>
+        <v>65.599999999999994</v>
       </c>
       <c r="D389" s="4" t="s">
         <v>364</v>
@@ -7324,13 +7327,13 @@
     </row>
     <row r="390" spans="1:4">
       <c r="A390" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B390" s="3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C390" s="3">
-        <v>220.8</v>
+        <v>255.03</v>
       </c>
       <c r="D390" s="4" t="s">
         <v>364</v>
@@ -7338,13 +7341,13 @@
     </row>
     <row r="391" spans="1:4">
       <c r="A391" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B391" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C391" s="3">
-        <v>255.02</v>
+        <v>220.8</v>
       </c>
       <c r="D391" s="4" t="s">
         <v>364</v>
@@ -7352,13 +7355,13 @@
     </row>
     <row r="392" spans="1:4">
       <c r="A392" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B392" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C392" s="3">
-        <v>68.86</v>
+        <v>255.02</v>
       </c>
       <c r="D392" s="4" t="s">
         <v>364</v>
@@ -7366,13 +7369,13 @@
     </row>
     <row r="393" spans="1:4">
       <c r="A393" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B393" s="3">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C393" s="3">
-        <v>344.28</v>
+        <v>68.86</v>
       </c>
       <c r="D393" s="4" t="s">
         <v>364</v>
@@ -7380,13 +7383,13 @@
     </row>
     <row r="394" spans="1:4">
       <c r="A394" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B394" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C394" s="3">
-        <v>60.29</v>
+        <v>344.28</v>
       </c>
       <c r="D394" s="4" t="s">
         <v>364</v>
@@ -7394,13 +7397,13 @@
     </row>
     <row r="395" spans="1:4">
       <c r="A395" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B395" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C395" s="3">
-        <v>261.8</v>
+        <v>60.29</v>
       </c>
       <c r="D395" s="4" t="s">
         <v>364</v>
@@ -7408,55 +7411,55 @@
     </row>
     <row r="396" spans="1:4">
       <c r="A396" t="s">
-        <v>382</v>
+        <v>329</v>
       </c>
       <c r="B396" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C396" s="3">
-        <v>30.58</v>
+        <v>261.8</v>
       </c>
       <c r="D396" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="397" spans="1:4">
       <c r="A397" t="s">
-        <v>330</v>
+        <v>382</v>
       </c>
       <c r="B397" s="3">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="C397" s="3">
-        <v>16.95</v>
+        <v>30.58</v>
       </c>
       <c r="D397" s="4" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
     </row>
     <row r="398" spans="1:4">
       <c r="A398" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B398" s="3">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="C398" s="3">
-        <v>24.95</v>
+        <v>16.95</v>
       </c>
       <c r="D398" s="4" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
     </row>
     <row r="399" spans="1:4">
       <c r="A399" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B399" s="3">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C399" s="3">
-        <v>641.49</v>
+        <v>24.95</v>
       </c>
       <c r="D399" s="4" t="s">
         <v>367</v>
@@ -7464,13 +7467,13 @@
     </row>
     <row r="400" spans="1:4">
       <c r="A400" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B400" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C400" s="3">
-        <v>39.57</v>
+        <v>641.49</v>
       </c>
       <c r="D400" s="4" t="s">
         <v>367</v>
@@ -7478,13 +7481,13 @@
     </row>
     <row r="401" spans="1:4">
       <c r="A401" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B401" s="3">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C401" s="3">
-        <v>51.83</v>
+        <v>39.57</v>
       </c>
       <c r="D401" s="4" t="s">
         <v>367</v>
@@ -7492,27 +7495,27 @@
     </row>
     <row r="402" spans="1:4">
       <c r="A402" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B402" s="3">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C402" s="3">
-        <v>33.840000000000003</v>
+        <v>51.83</v>
       </c>
       <c r="D402" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="403" spans="1:4">
       <c r="A403" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B403" s="3">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="C403" s="3">
-        <v>150.15</v>
+        <v>33.840000000000003</v>
       </c>
       <c r="D403" s="4" t="s">
         <v>364</v>
@@ -7520,13 +7523,13 @@
     </row>
     <row r="404" spans="1:4">
       <c r="A404" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B404" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C404" s="3">
-        <v>144.5</v>
+        <v>150.15</v>
       </c>
       <c r="D404" s="4" t="s">
         <v>364</v>
@@ -7534,13 +7537,13 @@
     </row>
     <row r="405" spans="1:4">
       <c r="A405" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B405" s="3">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C405" s="3">
-        <v>100.93</v>
+        <v>144.5</v>
       </c>
       <c r="D405" s="4" t="s">
         <v>364</v>
@@ -7548,13 +7551,13 @@
     </row>
     <row r="406" spans="1:4">
       <c r="A406" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B406" s="3">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C406" s="3">
-        <v>124.5</v>
+        <v>100.93</v>
       </c>
       <c r="D406" s="4" t="s">
         <v>364</v>
@@ -7562,13 +7565,13 @@
     </row>
     <row r="407" spans="1:4">
       <c r="A407" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B407" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C407" s="3">
-        <v>27.21</v>
+        <v>124.5</v>
       </c>
       <c r="D407" s="4" t="s">
         <v>364</v>
@@ -7576,41 +7579,41 @@
     </row>
     <row r="408" spans="1:4">
       <c r="A408" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B408" s="3">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="C408" s="3">
-        <v>24.79</v>
+        <v>27.21</v>
       </c>
       <c r="D408" s="4" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
     </row>
     <row r="409" spans="1:4">
       <c r="A409" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B409" s="3">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="C409" s="3">
-        <v>37.1</v>
+        <v>24.79</v>
       </c>
       <c r="D409" s="4" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
     </row>
     <row r="410" spans="1:4">
       <c r="A410" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B410" s="3">
         <v>0</v>
       </c>
       <c r="C410" s="3">
-        <v>178.04</v>
+        <v>37.1</v>
       </c>
       <c r="D410" s="4" t="s">
         <v>364</v>
@@ -7618,41 +7621,41 @@
     </row>
     <row r="411" spans="1:4">
       <c r="A411" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B411" s="3">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="C411" s="3">
-        <v>23.88</v>
+        <v>178.04</v>
       </c>
       <c r="D411" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="412" spans="1:4">
       <c r="A412" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B412" s="3">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C412" s="3">
-        <v>20.68</v>
+        <v>23.88</v>
       </c>
       <c r="D412" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="413" spans="1:4">
       <c r="A413" t="s">
-        <v>372</v>
+        <v>345</v>
       </c>
       <c r="B413" s="3">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="C413" s="3">
-        <v>97.54</v>
+        <v>20.68</v>
       </c>
       <c r="D413" s="4" t="s">
         <v>364</v>
@@ -7660,13 +7663,13 @@
     </row>
     <row r="414" spans="1:4">
       <c r="A414" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B414" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C414" s="3">
-        <v>304.02999999999997</v>
+        <v>97.54</v>
       </c>
       <c r="D414" s="4" t="s">
         <v>364</v>
@@ -7674,27 +7677,27 @@
     </row>
     <row r="415" spans="1:4">
       <c r="A415" t="s">
-        <v>346</v>
+        <v>373</v>
       </c>
       <c r="B415" s="3">
         <v>0</v>
       </c>
       <c r="C415" s="3">
-        <v>1934.56</v>
+        <v>304.02999999999997</v>
       </c>
       <c r="D415" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="416" spans="1:4">
       <c r="A416" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B416" s="3">
         <v>0</v>
       </c>
       <c r="C416" s="3">
-        <v>230.99</v>
+        <v>1934.56</v>
       </c>
       <c r="D416" s="4" t="s">
         <v>368</v>
@@ -7702,55 +7705,55 @@
     </row>
     <row r="417" spans="1:4">
       <c r="A417" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B417" s="3">
         <v>0</v>
       </c>
       <c r="C417" s="3">
-        <v>33.39</v>
+        <v>230.99</v>
       </c>
       <c r="D417" s="4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="418" spans="1:4">
       <c r="A418" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B418" s="3">
         <v>0</v>
       </c>
       <c r="C418" s="3">
-        <v>20.66</v>
+        <v>33.39</v>
       </c>
       <c r="D418" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="419" spans="1:4">
       <c r="A419" t="s">
-        <v>375</v>
+        <v>349</v>
       </c>
       <c r="B419" s="3">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="C419" s="3">
-        <v>97.5</v>
+        <v>20.66</v>
       </c>
       <c r="D419" s="4" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
     </row>
     <row r="420" spans="1:4">
       <c r="A420" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B420" s="3">
-        <v>369</v>
+        <v>58</v>
       </c>
       <c r="C420" s="3">
-        <v>24.7</v>
+        <v>97.5</v>
       </c>
       <c r="D420" s="4" t="s">
         <v>374</v>
@@ -7758,13 +7761,13 @@
     </row>
     <row r="421" spans="1:4">
       <c r="A421" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B421" s="3">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="C421" s="3">
-        <v>35.75</v>
+        <v>24.7</v>
       </c>
       <c r="D421" s="4" t="s">
         <v>374</v>
@@ -7772,13 +7775,13 @@
     </row>
     <row r="422" spans="1:4">
       <c r="A422" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B422" s="3">
-        <v>130</v>
+        <v>376</v>
       </c>
       <c r="C422" s="3">
-        <v>9.1</v>
+        <v>35.75</v>
       </c>
       <c r="D422" s="4" t="s">
         <v>374</v>
@@ -7786,13 +7789,13 @@
     </row>
     <row r="423" spans="1:4">
       <c r="A423" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B423" s="3">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="C423" s="3">
-        <v>5.43</v>
+        <v>9.1</v>
       </c>
       <c r="D423" s="4" t="s">
         <v>374</v>
@@ -7800,13 +7803,13 @@
     </row>
     <row r="424" spans="1:4">
       <c r="A424" t="s">
-        <v>432</v>
+        <v>379</v>
       </c>
       <c r="B424" s="3">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="C424" s="3">
-        <v>11.99</v>
+        <v>5.43</v>
       </c>
       <c r="D424" s="4" t="s">
         <v>374</v>
@@ -7814,27 +7817,27 @@
     </row>
     <row r="425" spans="1:4">
       <c r="A425" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
       <c r="B425" s="3">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="C425" s="3">
-        <v>9.75</v>
+        <v>11.99</v>
       </c>
       <c r="D425" s="4" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="426" spans="1:4">
       <c r="A426" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B426" s="3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C426" s="3">
-        <v>6.37</v>
+        <v>9.75</v>
       </c>
       <c r="D426" s="4" t="s">
         <v>380</v>
@@ -7842,13 +7845,13 @@
     </row>
     <row r="427" spans="1:4">
       <c r="A427" t="s">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="B427" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C427" s="3">
-        <v>10.53</v>
+        <v>6.37</v>
       </c>
       <c r="D427" s="4" t="s">
         <v>380</v>
@@ -7856,27 +7859,27 @@
     </row>
     <row r="428" spans="1:4">
       <c r="A428" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="B428" s="3">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C428" s="3">
-        <v>11.59</v>
+        <v>10.53</v>
       </c>
       <c r="D428" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="429" spans="1:4">
       <c r="A429" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="B429" s="3">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="C429" s="3">
-        <v>12.09</v>
+        <v>11.59</v>
       </c>
       <c r="D429" s="4" t="s">
         <v>381</v>
@@ -7884,10 +7887,10 @@
     </row>
     <row r="430" spans="1:4">
       <c r="A430" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B430" s="3">
-        <v>187</v>
+        <v>36</v>
       </c>
       <c r="C430" s="3">
         <v>12.09</v>
@@ -7898,13 +7901,13 @@
     </row>
     <row r="431" spans="1:4">
       <c r="A431" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B431" s="3">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C431" s="3">
-        <v>6.5</v>
+        <v>12.09</v>
       </c>
       <c r="D431" s="4" t="s">
         <v>381</v>
@@ -7912,10 +7915,10 @@
     </row>
     <row r="432" spans="1:4">
       <c r="A432" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B432" s="3">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C432" s="3">
         <v>6.5</v>
@@ -7926,27 +7929,27 @@
     </row>
     <row r="433" spans="1:4">
       <c r="A433" t="s">
-        <v>451</v>
+        <v>437</v>
       </c>
       <c r="B433" s="3">
-        <v>2</v>
+        <v>176</v>
       </c>
       <c r="C433" s="3">
-        <v>5017</v>
+        <v>6.5</v>
       </c>
       <c r="D433" s="4" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
     </row>
     <row r="434" spans="1:4">
       <c r="A434" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B434" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C434" s="3">
-        <v>4437.1499999999996</v>
+        <v>5017</v>
       </c>
       <c r="D434" s="4" t="s">
         <v>364</v>
@@ -7954,13 +7957,13 @@
     </row>
     <row r="435" spans="1:4">
       <c r="A435" t="s">
-        <v>429</v>
+        <v>452</v>
       </c>
       <c r="B435" s="3">
         <v>7</v>
       </c>
       <c r="C435" s="3">
-        <v>6239.83</v>
+        <v>4437.1499999999996</v>
       </c>
       <c r="D435" s="4" t="s">
         <v>364</v>
@@ -7968,13 +7971,13 @@
     </row>
     <row r="436" spans="1:4">
       <c r="A436" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="B436" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C436" s="3">
-        <v>5980</v>
+        <v>6239.83</v>
       </c>
       <c r="D436" s="4" t="s">
         <v>364</v>
@@ -7982,13 +7985,13 @@
     </row>
     <row r="437" spans="1:4">
       <c r="A437" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="B437" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C437" s="3">
-        <v>3556.4</v>
+        <v>5980</v>
       </c>
       <c r="D437" s="4" t="s">
         <v>364</v>
@@ -7996,13 +7999,13 @@
     </row>
     <row r="438" spans="1:4">
       <c r="A438" t="s">
-        <v>449</v>
+        <v>428</v>
       </c>
       <c r="B438" s="3">
         <v>2</v>
       </c>
       <c r="C438" s="3">
-        <v>6463</v>
+        <v>3556.4</v>
       </c>
       <c r="D438" s="4" t="s">
         <v>364</v>
@@ -8010,13 +8013,13 @@
     </row>
     <row r="439" spans="1:4">
       <c r="A439" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B439" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C439" s="3">
-        <v>5199</v>
+        <v>6463</v>
       </c>
       <c r="D439" s="4" t="s">
         <v>364</v>
@@ -8024,41 +8027,41 @@
     </row>
     <row r="440" spans="1:4">
       <c r="A440" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="B440" s="3">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C440" s="3">
-        <v>45</v>
+        <v>5199</v>
       </c>
       <c r="D440" s="4" t="s">
-        <v>453</v>
+        <v>364</v>
       </c>
     </row>
     <row r="441" spans="1:4">
       <c r="A441" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B441" s="3">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C441" s="3">
-        <v>70.25</v>
+        <v>45</v>
       </c>
       <c r="D441" s="4" t="s">
-        <v>367</v>
+        <v>453</v>
       </c>
     </row>
     <row r="442" spans="1:4">
       <c r="A442" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B442" s="3">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C442" s="3">
-        <v>58.9</v>
+        <v>70.25</v>
       </c>
       <c r="D442" s="4" t="s">
         <v>367</v>
@@ -8066,13 +8069,13 @@
     </row>
     <row r="443" spans="1:4">
       <c r="A443" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B443" s="3">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="C443" s="3">
-        <v>89.21</v>
+        <v>58.9</v>
       </c>
       <c r="D443" s="4" t="s">
         <v>367</v>
@@ -8080,13 +8083,13 @@
     </row>
     <row r="444" spans="1:4">
       <c r="A444" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B444" s="3">
         <v>60</v>
       </c>
       <c r="C444" s="3">
-        <v>59.18</v>
+        <v>89.21</v>
       </c>
       <c r="D444" s="4" t="s">
         <v>367</v>
@@ -8094,13 +8097,13 @@
     </row>
     <row r="445" spans="1:4">
       <c r="A445" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B445" s="3">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C445" s="3">
-        <v>60.62</v>
+        <v>59.18</v>
       </c>
       <c r="D445" s="4" t="s">
         <v>367</v>
@@ -8108,13 +8111,13 @@
     </row>
     <row r="446" spans="1:4">
       <c r="A446" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B446" s="3">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="C446" s="3">
-        <v>3431.7</v>
+        <v>60.62</v>
       </c>
       <c r="D446" s="4" t="s">
         <v>367</v>
@@ -8122,13 +8125,13 @@
     </row>
     <row r="447" spans="1:4">
       <c r="A447" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B447" s="3">
         <v>3</v>
       </c>
       <c r="C447" s="3">
-        <v>1260.2</v>
+        <v>3431.7</v>
       </c>
       <c r="D447" s="4" t="s">
         <v>367</v>
@@ -8136,13 +8139,13 @@
     </row>
     <row r="448" spans="1:4">
       <c r="A448" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B448" s="3">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="C448" s="3">
-        <v>47.2</v>
+        <v>1260.2</v>
       </c>
       <c r="D448" s="4" t="s">
         <v>367</v>
@@ -8150,13 +8153,13 @@
     </row>
     <row r="449" spans="1:4">
       <c r="A449" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="B449" s="3">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="C449" s="3">
-        <v>71.760000000000005</v>
+        <v>47.2</v>
       </c>
       <c r="D449" s="4" t="s">
         <v>367</v>
@@ -8164,15 +8167,29 @@
     </row>
     <row r="450" spans="1:4">
       <c r="A450" t="s">
+        <v>467</v>
+      </c>
+      <c r="B450" s="3">
+        <v>60</v>
+      </c>
+      <c r="C450" s="3">
+        <v>71.760000000000005</v>
+      </c>
+      <c r="D450" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4">
+      <c r="A451" t="s">
         <v>469</v>
       </c>
-      <c r="B450" s="3">
+      <c r="B451" s="3">
         <v>36</v>
       </c>
-      <c r="C450" s="3">
+      <c r="C451" s="3">
         <v>45</v>
       </c>
-      <c r="D450" s="4" t="s">
+      <c r="D451" s="4" t="s">
         <v>453</v>
       </c>
     </row>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -2024,7 +2024,7 @@
         <v>412</v>
       </c>
       <c r="B11" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C11" s="3">
         <v>476.85</v>
@@ -2290,7 +2290,7 @@
         <v>422</v>
       </c>
       <c r="B30" s="3">
-        <v>293</v>
+        <v>269</v>
       </c>
       <c r="C30" s="3">
         <v>45.19</v>
@@ -2332,7 +2332,7 @@
         <v>423</v>
       </c>
       <c r="B33" s="3">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="C33" s="3">
         <v>207.95</v>
@@ -2430,7 +2430,7 @@
         <v>426</v>
       </c>
       <c r="B40" s="3">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="C40" s="3">
         <v>26.29</v>
@@ -2850,7 +2850,7 @@
         <v>32</v>
       </c>
       <c r="B70" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C70" s="3">
         <v>87.12</v>
@@ -2878,7 +2878,7 @@
         <v>33</v>
       </c>
       <c r="B72" s="3">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C72" s="3">
         <v>18.96</v>
@@ -2892,7 +2892,7 @@
         <v>34</v>
       </c>
       <c r="B73" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C73" s="3">
         <v>73.13</v>
@@ -2906,7 +2906,7 @@
         <v>35</v>
       </c>
       <c r="B74" s="3">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C74" s="3">
         <v>89.38</v>
@@ -2934,7 +2934,7 @@
         <v>37</v>
       </c>
       <c r="B76" s="3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C76" s="3">
         <v>73.13</v>
@@ -2948,7 +2948,7 @@
         <v>38</v>
       </c>
       <c r="B77" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C77" s="3">
         <v>103.51</v>
@@ -2990,7 +2990,7 @@
         <v>443</v>
       </c>
       <c r="B80" s="3">
-        <v>600</v>
+        <v>578</v>
       </c>
       <c r="C80" s="3">
         <v>19.48</v>
@@ -3032,7 +3032,7 @@
         <v>470</v>
       </c>
       <c r="B83" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C83" s="3">
         <v>4256.54</v>
@@ -3046,7 +3046,7 @@
         <v>468</v>
       </c>
       <c r="B84" s="3">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="C84" s="3">
         <v>14.42</v>
@@ -3060,7 +3060,7 @@
         <v>446</v>
       </c>
       <c r="B85" s="3">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C85" s="3">
         <v>22.21</v>
@@ -3172,7 +3172,7 @@
         <v>46</v>
       </c>
       <c r="B93" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C93" s="3">
         <v>82.88</v>
@@ -4236,7 +4236,7 @@
         <v>117</v>
       </c>
       <c r="B169" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C169" s="3">
         <v>38.39</v>
@@ -4698,7 +4698,7 @@
         <v>148</v>
       </c>
       <c r="B202" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C202" s="10">
         <v>210.88</v>
@@ -4782,7 +4782,7 @@
         <v>154</v>
       </c>
       <c r="B208" s="3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C208" s="3">
         <v>44.51</v>
@@ -5076,7 +5076,7 @@
         <v>174</v>
       </c>
       <c r="B229" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C229" s="3">
         <v>154.62</v>
@@ -5300,7 +5300,7 @@
         <v>187</v>
       </c>
       <c r="B245" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C245" s="3">
         <v>67.28</v>
@@ -5986,7 +5986,7 @@
         <v>232</v>
       </c>
       <c r="B294" s="3">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C294" s="3">
         <v>51.15</v>
@@ -6014,7 +6014,7 @@
         <v>234</v>
       </c>
       <c r="B296" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C296" s="3">
         <v>182.42</v>
@@ -7008,7 +7008,7 @@
         <v>302</v>
       </c>
       <c r="B367" s="3">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C367" s="3">
         <v>47.62</v>
@@ -7050,7 +7050,7 @@
         <v>305</v>
       </c>
       <c r="B370" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C370" s="8">
         <v>171.47</v>
@@ -7064,7 +7064,7 @@
         <v>306</v>
       </c>
       <c r="B371" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C371" s="3">
         <v>212.75</v>
@@ -7092,7 +7092,7 @@
         <v>308</v>
       </c>
       <c r="B373" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C373" s="3">
         <v>66.180000000000007</v>
@@ -7456,7 +7456,7 @@
         <v>331</v>
       </c>
       <c r="B399" s="3">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C399" s="3">
         <v>24.95</v>
@@ -7652,7 +7652,7 @@
         <v>345</v>
       </c>
       <c r="B413" s="3">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C413" s="3">
         <v>20.68</v>
@@ -7666,7 +7666,7 @@
         <v>372</v>
       </c>
       <c r="B414" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C414" s="3">
         <v>97.54</v>
@@ -7764,7 +7764,7 @@
         <v>376</v>
       </c>
       <c r="B421" s="3">
-        <v>369</v>
+        <v>349</v>
       </c>
       <c r="C421" s="3">
         <v>24.7</v>
@@ -7778,7 +7778,7 @@
         <v>377</v>
       </c>
       <c r="B422" s="3">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="C422" s="3">
         <v>35.75</v>
@@ -7792,7 +7792,7 @@
         <v>378</v>
       </c>
       <c r="B423" s="3">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C423" s="3">
         <v>9.1</v>
@@ -7932,7 +7932,7 @@
         <v>437</v>
       </c>
       <c r="B433" s="3">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C433" s="3">
         <v>6.5</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -3172,7 +3172,7 @@
         <v>46</v>
       </c>
       <c r="B93" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C93" s="3">
         <v>82.88</v>
@@ -6056,7 +6056,7 @@
         <v>237</v>
       </c>
       <c r="B299" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C299" s="3">
         <v>894.8</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -1940,7 +1940,7 @@
         <v>391</v>
       </c>
       <c r="B5" s="3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C5" s="9">
         <v>245.7</v>
@@ -2024,7 +2024,7 @@
         <v>412</v>
       </c>
       <c r="B11" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" s="3">
         <v>476.85</v>
@@ -2220,7 +2220,7 @@
         <v>401</v>
       </c>
       <c r="B25" s="3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C25" s="3">
         <v>381.54</v>
@@ -2332,7 +2332,7 @@
         <v>423</v>
       </c>
       <c r="B33" s="3">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="C33" s="3">
         <v>207.95</v>
@@ -2402,7 +2402,7 @@
         <v>11</v>
       </c>
       <c r="B38" s="3">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C38" s="3">
         <v>189</v>
@@ -2514,7 +2514,7 @@
         <v>13</v>
       </c>
       <c r="B46" s="3">
-        <v>1585</v>
+        <v>1561</v>
       </c>
       <c r="C46" s="3">
         <v>13</v>
@@ -2850,7 +2850,7 @@
         <v>32</v>
       </c>
       <c r="B70" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C70" s="3">
         <v>87.12</v>
@@ -2906,7 +2906,7 @@
         <v>35</v>
       </c>
       <c r="B74" s="3">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C74" s="3">
         <v>89.38</v>
@@ -2990,7 +2990,7 @@
         <v>443</v>
       </c>
       <c r="B80" s="3">
-        <v>578</v>
+        <v>542</v>
       </c>
       <c r="C80" s="3">
         <v>19.48</v>
@@ -3158,7 +3158,7 @@
         <v>45</v>
       </c>
       <c r="B92" s="3">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C92" s="3">
         <v>18.37</v>
@@ -3536,10 +3536,10 @@
         <v>70</v>
       </c>
       <c r="B119" s="3">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C119" s="3">
-        <v>98.95</v>
+        <v>103.09</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>367</v>
@@ -3746,10 +3746,10 @@
         <v>85</v>
       </c>
       <c r="B134" s="3">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="C134" s="3">
-        <v>63.89</v>
+        <v>78.84</v>
       </c>
       <c r="D134" s="4" t="s">
         <v>367</v>
@@ -4068,7 +4068,7 @@
         <v>106</v>
       </c>
       <c r="B157" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C157" s="3">
         <v>1217.1600000000001</v>
@@ -4586,7 +4586,7 @@
         <v>141</v>
       </c>
       <c r="B194" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C194" s="3">
         <v>59.25</v>
@@ -4600,10 +4600,10 @@
         <v>142</v>
       </c>
       <c r="B195" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C195" s="3">
-        <v>260</v>
+        <v>260.33</v>
       </c>
       <c r="D195" s="4" t="s">
         <v>364</v>
@@ -4782,7 +4782,7 @@
         <v>154</v>
       </c>
       <c r="B208" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C208" s="3">
         <v>44.51</v>
@@ -4894,7 +4894,7 @@
         <v>161</v>
       </c>
       <c r="B216" s="3">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C216" s="3">
         <v>48.13</v>
@@ -4908,7 +4908,7 @@
         <v>162</v>
       </c>
       <c r="B217" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C217" s="3">
         <v>5400</v>
@@ -4936,7 +4936,7 @@
         <v>164</v>
       </c>
       <c r="B219" s="3">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C219" s="3">
         <v>216.3</v>
@@ -5048,7 +5048,7 @@
         <v>172</v>
       </c>
       <c r="B227" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C227" s="3">
         <v>37.299999999999997</v>
@@ -5328,7 +5328,7 @@
         <v>189</v>
       </c>
       <c r="B247" s="3">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C247" s="8">
         <v>75.88</v>
@@ -5790,7 +5790,7 @@
         <v>219</v>
       </c>
       <c r="B280" s="3">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C280" s="3">
         <v>83.84</v>
@@ -5986,7 +5986,7 @@
         <v>232</v>
       </c>
       <c r="B294" s="3">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C294" s="3">
         <v>51.15</v>
@@ -6014,7 +6014,7 @@
         <v>234</v>
       </c>
       <c r="B296" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C296" s="3">
         <v>182.42</v>
@@ -6028,7 +6028,7 @@
         <v>235</v>
       </c>
       <c r="B297" s="3">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C297" s="3">
         <v>222.62</v>
@@ -6238,7 +6238,7 @@
         <v>248</v>
       </c>
       <c r="B312" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C312" s="3">
         <v>31.48</v>
@@ -6714,7 +6714,7 @@
         <v>282</v>
       </c>
       <c r="B346" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C346" s="3">
         <v>30.9</v>
@@ -7008,7 +7008,7 @@
         <v>302</v>
       </c>
       <c r="B367" s="3">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="C367" s="3">
         <v>47.62</v>
@@ -7050,7 +7050,7 @@
         <v>305</v>
       </c>
       <c r="B370" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C370" s="8">
         <v>171.47</v>
@@ -7064,7 +7064,7 @@
         <v>306</v>
       </c>
       <c r="B371" s="3">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C371" s="3">
         <v>212.75</v>
@@ -7092,7 +7092,7 @@
         <v>308</v>
       </c>
       <c r="B373" s="3">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C373" s="3">
         <v>66.180000000000007</v>
@@ -7176,7 +7176,7 @@
         <v>314</v>
       </c>
       <c r="B379" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C379" s="3">
         <v>87.22</v>
@@ -7260,7 +7260,7 @@
         <v>350</v>
       </c>
       <c r="B385" s="3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C385" s="3">
         <v>58.69</v>
@@ -7750,7 +7750,7 @@
         <v>375</v>
       </c>
       <c r="B420" s="3">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C420" s="3">
         <v>97.5</v>
@@ -7764,7 +7764,7 @@
         <v>376</v>
       </c>
       <c r="B421" s="3">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C421" s="3">
         <v>24.7</v>
@@ -7778,7 +7778,7 @@
         <v>377</v>
       </c>
       <c r="B422" s="3">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="C422" s="3">
         <v>35.75</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -4810,7 +4810,7 @@
         <v>156</v>
       </c>
       <c r="B210" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C210" s="3">
         <v>199.77</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -5720,7 +5720,7 @@
         <v>214</v>
       </c>
       <c r="B275" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C275" s="3">
         <v>334.36</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -1898,7 +1898,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="3">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="C2" s="3">
         <v>12.4</v>
@@ -2514,7 +2514,7 @@
         <v>13</v>
       </c>
       <c r="B46" s="3">
-        <v>1561</v>
+        <v>1519</v>
       </c>
       <c r="C46" s="3">
         <v>13</v>
@@ -2850,7 +2850,7 @@
         <v>32</v>
       </c>
       <c r="B70" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C70" s="3">
         <v>87.12</v>
@@ -2878,7 +2878,7 @@
         <v>33</v>
       </c>
       <c r="B72" s="3">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C72" s="3">
         <v>18.96</v>
@@ -2892,7 +2892,7 @@
         <v>34</v>
       </c>
       <c r="B73" s="3">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C73" s="3">
         <v>73.13</v>
@@ -3046,7 +3046,7 @@
         <v>468</v>
       </c>
       <c r="B84" s="3">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C84" s="3">
         <v>14.42</v>
@@ -3060,7 +3060,7 @@
         <v>446</v>
       </c>
       <c r="B85" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C85" s="3">
         <v>22.21</v>
@@ -3900,7 +3900,7 @@
         <v>94</v>
       </c>
       <c r="B145" s="3">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C145" s="3">
         <v>66.98</v>
@@ -4474,7 +4474,7 @@
         <v>134</v>
       </c>
       <c r="B186" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C186" s="3">
         <v>75.989999999999995</v>
@@ -4488,7 +4488,7 @@
         <v>135</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C187" s="3">
         <v>342.24</v>
@@ -4586,7 +4586,7 @@
         <v>141</v>
       </c>
       <c r="B194" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C194" s="3">
         <v>59.25</v>
@@ -4600,7 +4600,7 @@
         <v>142</v>
       </c>
       <c r="B195" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C195" s="3">
         <v>260.33</v>
@@ -4782,7 +4782,7 @@
         <v>154</v>
       </c>
       <c r="B208" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C208" s="3">
         <v>44.51</v>
@@ -4880,7 +4880,7 @@
         <v>160</v>
       </c>
       <c r="B215" s="3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C215" s="3">
         <v>33.479999999999997</v>
@@ -4978,7 +4978,7 @@
         <v>167</v>
       </c>
       <c r="B222" s="3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C222" s="3">
         <v>36.799999999999997</v>
@@ -5076,7 +5076,7 @@
         <v>174</v>
       </c>
       <c r="B229" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C229" s="3">
         <v>154.62</v>
@@ -5314,7 +5314,7 @@
         <v>188</v>
       </c>
       <c r="B246" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C246" s="8">
         <v>79.599999999999994</v>
@@ -5356,7 +5356,7 @@
         <v>191</v>
       </c>
       <c r="B249" s="3">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C249" s="3">
         <v>33.479999999999997</v>
@@ -5538,7 +5538,7 @@
         <v>203</v>
       </c>
       <c r="B262" s="3">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C262" s="3">
         <v>36.06</v>
@@ -5986,7 +5986,7 @@
         <v>232</v>
       </c>
       <c r="B294" s="3">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C294" s="3">
         <v>51.15</v>
@@ -6028,7 +6028,7 @@
         <v>235</v>
       </c>
       <c r="B297" s="3">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C297" s="3">
         <v>222.62</v>
@@ -6378,7 +6378,7 @@
         <v>258</v>
       </c>
       <c r="B322" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C322" s="3">
         <v>76</v>
@@ -6714,7 +6714,7 @@
         <v>282</v>
       </c>
       <c r="B346" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C346" s="3">
         <v>30.9</v>
@@ -6910,7 +6910,7 @@
         <v>295</v>
       </c>
       <c r="B360" s="3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C360" s="3">
         <v>27.16</v>
@@ -7008,7 +7008,7 @@
         <v>302</v>
       </c>
       <c r="B367" s="3">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C367" s="3">
         <v>47.62</v>
@@ -7064,7 +7064,7 @@
         <v>306</v>
       </c>
       <c r="B371" s="3">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C371" s="3">
         <v>212.75</v>
@@ -7092,7 +7092,7 @@
         <v>308</v>
       </c>
       <c r="B373" s="3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C373" s="3">
         <v>66.180000000000007</v>
@@ -7134,7 +7134,7 @@
         <v>311</v>
       </c>
       <c r="B376" s="3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C376" s="3">
         <v>259.8</v>
@@ -7232,7 +7232,7 @@
         <v>318</v>
       </c>
       <c r="B383" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C383" s="3">
         <v>67.28</v>
@@ -7316,7 +7316,7 @@
         <v>322</v>
       </c>
       <c r="B389" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C389" s="3">
         <v>65.599999999999994</v>
@@ -7330,7 +7330,7 @@
         <v>323</v>
       </c>
       <c r="B390" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C390" s="3">
         <v>255.03</v>
@@ -7652,7 +7652,7 @@
         <v>345</v>
       </c>
       <c r="B413" s="3">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="C413" s="3">
         <v>20.68</v>
@@ -7666,7 +7666,7 @@
         <v>372</v>
       </c>
       <c r="B414" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C414" s="3">
         <v>97.54</v>
@@ -7750,7 +7750,7 @@
         <v>375</v>
       </c>
       <c r="B420" s="3">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C420" s="3">
         <v>97.5</v>
@@ -7764,7 +7764,7 @@
         <v>376</v>
       </c>
       <c r="B421" s="3">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="C421" s="3">
         <v>24.7</v>
@@ -7778,7 +7778,7 @@
         <v>377</v>
       </c>
       <c r="B422" s="3">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C422" s="3">
         <v>35.75</v>
@@ -7792,7 +7792,7 @@
         <v>378</v>
       </c>
       <c r="B423" s="3">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="C423" s="3">
         <v>9.1</v>
@@ -7820,7 +7820,7 @@
         <v>432</v>
       </c>
       <c r="B425" s="3">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C425" s="3">
         <v>11.99</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -2290,7 +2290,7 @@
         <v>422</v>
       </c>
       <c r="B30" s="3">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C30" s="3">
         <v>45.19</v>
@@ -2332,7 +2332,7 @@
         <v>423</v>
       </c>
       <c r="B33" s="3">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C33" s="3">
         <v>207.95</v>
@@ -2514,7 +2514,7 @@
         <v>13</v>
       </c>
       <c r="B46" s="3">
-        <v>1519</v>
+        <v>1502</v>
       </c>
       <c r="C46" s="3">
         <v>13</v>
@@ -2878,7 +2878,7 @@
         <v>33</v>
       </c>
       <c r="B72" s="3">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C72" s="3">
         <v>18.96</v>
@@ -2906,7 +2906,7 @@
         <v>35</v>
       </c>
       <c r="B74" s="3">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C74" s="3">
         <v>89.38</v>
@@ -2934,7 +2934,7 @@
         <v>37</v>
       </c>
       <c r="B76" s="3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C76" s="3">
         <v>73.13</v>
@@ -2990,7 +2990,7 @@
         <v>443</v>
       </c>
       <c r="B80" s="3">
-        <v>542</v>
+        <v>515</v>
       </c>
       <c r="C80" s="3">
         <v>19.48</v>
@@ -3004,7 +3004,7 @@
         <v>444</v>
       </c>
       <c r="B81" s="3">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C81" s="3">
         <v>70.72</v>
@@ -3046,7 +3046,7 @@
         <v>468</v>
       </c>
       <c r="B84" s="3">
-        <v>212</v>
+        <v>176</v>
       </c>
       <c r="C84" s="3">
         <v>14.42</v>
@@ -3158,7 +3158,7 @@
         <v>45</v>
       </c>
       <c r="B92" s="3">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C92" s="3">
         <v>18.37</v>
@@ -3900,7 +3900,7 @@
         <v>94</v>
       </c>
       <c r="B145" s="3">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C145" s="3">
         <v>66.98</v>
@@ -4180,7 +4180,7 @@
         <v>113</v>
       </c>
       <c r="B165" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C165" s="3">
         <v>32.200000000000003</v>
@@ -4362,7 +4362,7 @@
         <v>126</v>
       </c>
       <c r="B178" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C178" s="3">
         <v>38.770000000000003</v>
@@ -4614,7 +4614,7 @@
         <v>143</v>
       </c>
       <c r="B196" s="3">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C196" s="7">
         <v>59.62</v>
@@ -4670,7 +4670,7 @@
         <v>385</v>
       </c>
       <c r="B200" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C200" s="3">
         <v>168.7</v>
@@ -5048,7 +5048,7 @@
         <v>172</v>
       </c>
       <c r="B227" s="3">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C227" s="3">
         <v>37.299999999999997</v>
@@ -5062,7 +5062,7 @@
         <v>173</v>
       </c>
       <c r="B228" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C228" s="3">
         <v>126.24</v>
@@ -5076,7 +5076,7 @@
         <v>174</v>
       </c>
       <c r="B229" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C229" s="3">
         <v>154.62</v>
@@ -5342,7 +5342,7 @@
         <v>190</v>
       </c>
       <c r="B248" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C248" s="3">
         <v>109.08</v>
@@ -5986,7 +5986,7 @@
         <v>232</v>
       </c>
       <c r="B294" s="3">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C294" s="3">
         <v>51.15</v>
@@ -6028,7 +6028,7 @@
         <v>235</v>
       </c>
       <c r="B297" s="3">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C297" s="3">
         <v>222.62</v>
@@ -6056,7 +6056,7 @@
         <v>237</v>
       </c>
       <c r="B299" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C299" s="3">
         <v>894.8</v>
@@ -7008,7 +7008,7 @@
         <v>302</v>
       </c>
       <c r="B367" s="3">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C367" s="3">
         <v>47.62</v>
@@ -7064,7 +7064,7 @@
         <v>306</v>
       </c>
       <c r="B371" s="3">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C371" s="3">
         <v>212.75</v>
@@ -7750,7 +7750,7 @@
         <v>375</v>
       </c>
       <c r="B420" s="3">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C420" s="3">
         <v>97.5</v>
@@ -7764,7 +7764,7 @@
         <v>376</v>
       </c>
       <c r="B421" s="3">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="C421" s="3">
         <v>24.7</v>
@@ -7778,7 +7778,7 @@
         <v>377</v>
       </c>
       <c r="B422" s="3">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="C422" s="3">
         <v>35.75</v>
@@ -7792,7 +7792,7 @@
         <v>378</v>
       </c>
       <c r="B423" s="3">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C423" s="3">
         <v>9.1</v>
@@ -7848,7 +7848,7 @@
         <v>415</v>
       </c>
       <c r="B427" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C427" s="3">
         <v>6.37</v>
@@ -7904,7 +7904,7 @@
         <v>435</v>
       </c>
       <c r="B431" s="3">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C431" s="3">
         <v>12.09</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -1940,7 +1940,7 @@
         <v>391</v>
       </c>
       <c r="B5" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="9">
         <v>245.7</v>
@@ -1954,7 +1954,7 @@
         <v>392</v>
       </c>
       <c r="B6" s="3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6" s="9">
         <v>269.10000000000002</v>
@@ -1996,7 +1996,7 @@
         <v>394</v>
       </c>
       <c r="B9" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" s="3">
         <v>320</v>
@@ -2220,7 +2220,7 @@
         <v>401</v>
       </c>
       <c r="B25" s="3">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C25" s="3">
         <v>381.54</v>
@@ -2234,7 +2234,7 @@
         <v>402</v>
       </c>
       <c r="B26" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C26" s="3">
         <v>417.6</v>
@@ -2262,7 +2262,7 @@
         <v>404</v>
       </c>
       <c r="B28" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C28" s="3">
         <v>489.63</v>
@@ -2332,7 +2332,7 @@
         <v>423</v>
       </c>
       <c r="B33" s="3">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="C33" s="3">
         <v>207.95</v>
@@ -2444,7 +2444,7 @@
         <v>427</v>
       </c>
       <c r="B41" s="3">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C41" s="3">
         <v>120.32</v>
@@ -2514,7 +2514,7 @@
         <v>13</v>
       </c>
       <c r="B46" s="3">
-        <v>1502</v>
+        <v>1478</v>
       </c>
       <c r="C46" s="3">
         <v>13</v>
@@ -2528,7 +2528,7 @@
         <v>14</v>
       </c>
       <c r="B47" s="3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C47" s="3">
         <v>23.37</v>
@@ -2850,7 +2850,7 @@
         <v>32</v>
       </c>
       <c r="B70" s="3">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C70" s="3">
         <v>87.12</v>
@@ -2906,7 +2906,7 @@
         <v>35</v>
       </c>
       <c r="B74" s="3">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C74" s="3">
         <v>89.38</v>
@@ -2990,7 +2990,7 @@
         <v>443</v>
       </c>
       <c r="B80" s="3">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="C80" s="3">
         <v>19.48</v>
@@ -3004,7 +3004,7 @@
         <v>444</v>
       </c>
       <c r="B81" s="3">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C81" s="3">
         <v>70.72</v>
@@ -3060,7 +3060,7 @@
         <v>446</v>
       </c>
       <c r="B85" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C85" s="3">
         <v>22.21</v>
@@ -3158,7 +3158,7 @@
         <v>45</v>
       </c>
       <c r="B92" s="3">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C92" s="3">
         <v>18.37</v>
@@ -3536,7 +3536,7 @@
         <v>70</v>
       </c>
       <c r="B119" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C119" s="3">
         <v>103.09</v>
@@ -4670,7 +4670,7 @@
         <v>385</v>
       </c>
       <c r="B200" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C200" s="3">
         <v>168.7</v>
@@ -4698,7 +4698,7 @@
         <v>148</v>
       </c>
       <c r="B202" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C202" s="10">
         <v>210.88</v>
@@ -4880,7 +4880,7 @@
         <v>160</v>
       </c>
       <c r="B215" s="3">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C215" s="3">
         <v>33.479999999999997</v>
@@ -5048,7 +5048,7 @@
         <v>172</v>
       </c>
       <c r="B227" s="3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C227" s="3">
         <v>37.299999999999997</v>
@@ -5314,7 +5314,7 @@
         <v>188</v>
       </c>
       <c r="B246" s="3">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C246" s="8">
         <v>79.599999999999994</v>
@@ -6028,7 +6028,7 @@
         <v>235</v>
       </c>
       <c r="B297" s="3">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C297" s="3">
         <v>222.62</v>
@@ -6336,7 +6336,7 @@
         <v>255</v>
       </c>
       <c r="B319" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C319" s="3">
         <v>862.7</v>
@@ -6756,7 +6756,7 @@
         <v>285</v>
       </c>
       <c r="B349" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C349" s="3">
         <v>185.15</v>
@@ -7064,7 +7064,7 @@
         <v>306</v>
       </c>
       <c r="B371" s="3">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C371" s="3">
         <v>212.75</v>
@@ -7120,7 +7120,7 @@
         <v>310</v>
       </c>
       <c r="B375" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C375" s="3">
         <v>259.81</v>
@@ -7470,7 +7470,7 @@
         <v>332</v>
       </c>
       <c r="B400" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C400" s="3">
         <v>641.49</v>
@@ -7778,7 +7778,7 @@
         <v>377</v>
       </c>
       <c r="B422" s="3">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="C422" s="3">
         <v>35.75</v>
@@ -8044,7 +8044,7 @@
         <v>454</v>
       </c>
       <c r="B441" s="3">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C441" s="3">
         <v>45</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -3788,7 +3788,7 @@
         <v>88</v>
       </c>
       <c r="B137" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C137" s="3">
         <v>207.31</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -2906,7 +2906,7 @@
         <v>35</v>
       </c>
       <c r="B74" s="3">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C74" s="3">
         <v>89.38</v>
@@ -2990,7 +2990,7 @@
         <v>443</v>
       </c>
       <c r="B80" s="3">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="C80" s="3">
         <v>19.48</v>
@@ -3242,7 +3242,7 @@
         <v>51</v>
       </c>
       <c r="B98" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C98" s="3">
         <v>62.11</v>
@@ -3788,10 +3788,10 @@
         <v>88</v>
       </c>
       <c r="B137" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C137" s="3">
-        <v>207.31</v>
+        <v>299</v>
       </c>
       <c r="D137" s="4" t="s">
         <v>367</v>
@@ -4936,7 +4936,7 @@
         <v>164</v>
       </c>
       <c r="B219" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C219" s="3">
         <v>216.3</v>
@@ -5048,7 +5048,7 @@
         <v>172</v>
       </c>
       <c r="B227" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C227" s="3">
         <v>37.299999999999997</v>
@@ -5328,7 +5328,7 @@
         <v>189</v>
       </c>
       <c r="B247" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C247" s="8">
         <v>75.88</v>
@@ -5874,7 +5874,7 @@
         <v>224</v>
       </c>
       <c r="B286" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C286" s="3">
         <v>40.57</v>
@@ -5986,7 +5986,7 @@
         <v>232</v>
       </c>
       <c r="B294" s="3">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C294" s="3">
         <v>51.15</v>
@@ -6028,7 +6028,7 @@
         <v>235</v>
       </c>
       <c r="B297" s="3">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C297" s="3">
         <v>222.62</v>
@@ -6168,7 +6168,7 @@
         <v>455</v>
       </c>
       <c r="B307" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C307" s="3">
         <v>13.72</v>
@@ -6182,7 +6182,7 @@
         <v>245</v>
       </c>
       <c r="B308" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C308" s="3">
         <v>13.72</v>
@@ -6434,7 +6434,7 @@
         <v>262</v>
       </c>
       <c r="B326" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C326" s="3">
         <v>72.13</v>
@@ -6448,7 +6448,7 @@
         <v>263</v>
       </c>
       <c r="B327" s="3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C327" s="3">
         <v>302.39999999999998</v>
@@ -6462,7 +6462,7 @@
         <v>264</v>
       </c>
       <c r="B328" s="3">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C328" s="3">
         <v>36.799999999999997</v>
@@ -7008,7 +7008,7 @@
         <v>302</v>
       </c>
       <c r="B367" s="3">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C367" s="3">
         <v>47.62</v>
@@ -7050,7 +7050,7 @@
         <v>305</v>
       </c>
       <c r="B370" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C370" s="8">
         <v>171.47</v>
@@ -7064,7 +7064,7 @@
         <v>306</v>
       </c>
       <c r="B371" s="3">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C371" s="3">
         <v>212.75</v>
@@ -7092,7 +7092,7 @@
         <v>308</v>
       </c>
       <c r="B373" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C373" s="3">
         <v>66.180000000000007</v>
@@ -7134,7 +7134,7 @@
         <v>311</v>
       </c>
       <c r="B376" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C376" s="3">
         <v>259.8</v>
@@ -7148,7 +7148,7 @@
         <v>312</v>
       </c>
       <c r="B377" s="3">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C377" s="3">
         <v>310.2</v>
@@ -7330,7 +7330,7 @@
         <v>323</v>
       </c>
       <c r="B390" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C390" s="3">
         <v>255.03</v>
@@ -7344,7 +7344,7 @@
         <v>324</v>
       </c>
       <c r="B391" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C391" s="3">
         <v>220.8</v>
@@ -7652,7 +7652,7 @@
         <v>345</v>
       </c>
       <c r="B413" s="3">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C413" s="3">
         <v>20.68</v>
@@ -7750,7 +7750,7 @@
         <v>375</v>
       </c>
       <c r="B420" s="3">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C420" s="3">
         <v>97.5</v>
@@ -7764,7 +7764,7 @@
         <v>376</v>
       </c>
       <c r="B421" s="3">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="C421" s="3">
         <v>24.7</v>
@@ -7778,7 +7778,7 @@
         <v>377</v>
       </c>
       <c r="B422" s="3">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="C422" s="3">
         <v>35.75</v>
@@ -7792,7 +7792,7 @@
         <v>378</v>
       </c>
       <c r="B423" s="3">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C423" s="3">
         <v>9.1</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -3354,7 +3354,7 @@
         <v>59</v>
       </c>
       <c r="B106" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C106" s="3">
         <v>40.54</v>
@@ -4810,7 +4810,7 @@
         <v>156</v>
       </c>
       <c r="B210" s="3">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C210" s="3">
         <v>199.77</v>
@@ -5048,7 +5048,7 @@
         <v>172</v>
       </c>
       <c r="B227" s="3">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="C227" s="3">
         <v>37.299999999999997</v>
@@ -5328,7 +5328,7 @@
         <v>189</v>
       </c>
       <c r="B247" s="3">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C247" s="8">
         <v>75.88</v>
@@ -6014,7 +6014,7 @@
         <v>234</v>
       </c>
       <c r="B296" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C296" s="3">
         <v>182.42</v>
@@ -6056,7 +6056,7 @@
         <v>237</v>
       </c>
       <c r="B299" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C299" s="3">
         <v>894.8</v>
@@ -7050,7 +7050,7 @@
         <v>305</v>
       </c>
       <c r="B370" s="3">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C370" s="8">
         <v>171.47</v>
@@ -7148,7 +7148,7 @@
         <v>312</v>
       </c>
       <c r="B377" s="3">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="C377" s="3">
         <v>310.2</v>
@@ -7232,10 +7232,10 @@
         <v>318</v>
       </c>
       <c r="B383" s="3">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C383" s="3">
-        <v>67.28</v>
+        <v>81.760000000000005</v>
       </c>
       <c r="D383" s="4" t="s">
         <v>367</v>
@@ -7316,7 +7316,7 @@
         <v>322</v>
       </c>
       <c r="B389" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C389" s="3">
         <v>65.599999999999994</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -1954,7 +1954,7 @@
         <v>392</v>
       </c>
       <c r="B6" s="3">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C6" s="9">
         <v>269.10000000000002</v>
@@ -2024,7 +2024,7 @@
         <v>412</v>
       </c>
       <c r="B11" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C11" s="3">
         <v>476.85</v>
@@ -2234,7 +2234,7 @@
         <v>402</v>
       </c>
       <c r="B26" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C26" s="3">
         <v>417.6</v>
@@ -2262,7 +2262,7 @@
         <v>404</v>
       </c>
       <c r="B28" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C28" s="3">
         <v>489.63</v>
@@ -2276,7 +2276,7 @@
         <v>405</v>
       </c>
       <c r="B29" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C29" s="3">
         <v>508.27</v>
@@ -2304,10 +2304,10 @@
         <v>8</v>
       </c>
       <c r="B31" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31" s="3">
-        <v>5899.25</v>
+        <v>6200</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>364</v>
@@ -2514,7 +2514,7 @@
         <v>13</v>
       </c>
       <c r="B46" s="3">
-        <v>1478</v>
+        <v>1463</v>
       </c>
       <c r="C46" s="3">
         <v>13</v>
@@ -2850,7 +2850,7 @@
         <v>32</v>
       </c>
       <c r="B70" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C70" s="3">
         <v>87.12</v>
@@ -2906,7 +2906,7 @@
         <v>35</v>
       </c>
       <c r="B74" s="3">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C74" s="3">
         <v>89.38</v>
@@ -2948,7 +2948,7 @@
         <v>38</v>
       </c>
       <c r="B77" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C77" s="3">
         <v>103.51</v>
@@ -2990,7 +2990,7 @@
         <v>443</v>
       </c>
       <c r="B80" s="3">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C80" s="3">
         <v>19.48</v>
@@ -3004,7 +3004,7 @@
         <v>444</v>
       </c>
       <c r="B81" s="3">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C81" s="3">
         <v>70.72</v>
@@ -3060,7 +3060,7 @@
         <v>446</v>
       </c>
       <c r="B85" s="3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C85" s="3">
         <v>22.21</v>
@@ -3158,7 +3158,7 @@
         <v>45</v>
       </c>
       <c r="B92" s="3">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C92" s="3">
         <v>18.37</v>
@@ -4208,7 +4208,7 @@
         <v>115</v>
       </c>
       <c r="B167" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C167" s="3">
         <v>32.200000000000003</v>
@@ -4978,7 +4978,7 @@
         <v>167</v>
       </c>
       <c r="B222" s="3">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C222" s="3">
         <v>36.799999999999997</v>
@@ -5076,7 +5076,7 @@
         <v>174</v>
       </c>
       <c r="B229" s="3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C229" s="3">
         <v>154.62</v>
@@ -5300,7 +5300,7 @@
         <v>187</v>
       </c>
       <c r="B245" s="3">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C245" s="3">
         <v>67.28</v>
@@ -5356,7 +5356,7 @@
         <v>191</v>
       </c>
       <c r="B249" s="3">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C249" s="3">
         <v>33.479999999999997</v>
@@ -5538,7 +5538,7 @@
         <v>203</v>
       </c>
       <c r="B262" s="3">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C262" s="3">
         <v>36.06</v>
@@ -5818,7 +5818,7 @@
         <v>220</v>
       </c>
       <c r="B282" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C282" s="3">
         <v>284</v>
@@ -6014,7 +6014,7 @@
         <v>234</v>
       </c>
       <c r="B296" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C296" s="3">
         <v>182.42</v>
@@ -6224,7 +6224,7 @@
         <v>247</v>
       </c>
       <c r="B311" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C311" s="3">
         <v>36.869999999999997</v>
@@ -7008,7 +7008,7 @@
         <v>302</v>
       </c>
       <c r="B367" s="3">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C367" s="3">
         <v>47.62</v>
@@ -7064,7 +7064,7 @@
         <v>306</v>
       </c>
       <c r="B371" s="3">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C371" s="3">
         <v>212.75</v>
@@ -7148,7 +7148,7 @@
         <v>312</v>
       </c>
       <c r="B377" s="3">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C377" s="3">
         <v>310.2</v>
@@ -7456,7 +7456,7 @@
         <v>331</v>
       </c>
       <c r="B399" s="3">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C399" s="3">
         <v>24.95</v>
@@ -7764,7 +7764,7 @@
         <v>376</v>
       </c>
       <c r="B421" s="3">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="C421" s="3">
         <v>24.7</v>
@@ -8044,7 +8044,7 @@
         <v>454</v>
       </c>
       <c r="B441" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C441" s="3">
         <v>45</v>
@@ -8156,7 +8156,7 @@
         <v>463</v>
       </c>
       <c r="B449" s="3">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C449" s="3">
         <v>47.2</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -4810,7 +4810,7 @@
         <v>156</v>
       </c>
       <c r="B210" s="3">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C210" s="3">
         <v>199.77</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -2290,7 +2290,7 @@
         <v>422</v>
       </c>
       <c r="B30" s="3">
-        <v>267</v>
+        <v>243</v>
       </c>
       <c r="C30" s="3">
         <v>45.19</v>
@@ -2332,7 +2332,7 @@
         <v>423</v>
       </c>
       <c r="B33" s="3">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C33" s="3">
         <v>207.95</v>
@@ -2444,7 +2444,7 @@
         <v>427</v>
       </c>
       <c r="B41" s="3">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C41" s="3">
         <v>120.32</v>
@@ -2724,7 +2724,7 @@
         <v>440</v>
       </c>
       <c r="B61" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C61" s="3">
         <v>135.29</v>
@@ -2738,7 +2738,7 @@
         <v>25</v>
       </c>
       <c r="B62" s="3">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C62" s="3">
         <v>26.21</v>
@@ -2752,7 +2752,7 @@
         <v>26</v>
       </c>
       <c r="B63" s="3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C63" s="3">
         <v>101.08</v>
@@ -2780,7 +2780,7 @@
         <v>27</v>
       </c>
       <c r="B65" s="3">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C65" s="3">
         <v>29.13</v>
@@ -2794,7 +2794,7 @@
         <v>28</v>
       </c>
       <c r="B66" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C66" s="3">
         <v>102.31</v>
@@ -2906,7 +2906,7 @@
         <v>35</v>
       </c>
       <c r="B74" s="3">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C74" s="3">
         <v>89.38</v>
@@ -2934,7 +2934,7 @@
         <v>37</v>
       </c>
       <c r="B76" s="3">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C76" s="3">
         <v>73.13</v>
@@ -2948,7 +2948,7 @@
         <v>38</v>
       </c>
       <c r="B77" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C77" s="3">
         <v>103.51</v>
@@ -2990,7 +2990,7 @@
         <v>443</v>
       </c>
       <c r="B80" s="3">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="C80" s="3">
         <v>19.48</v>
@@ -3046,7 +3046,7 @@
         <v>468</v>
       </c>
       <c r="B84" s="3">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C84" s="3">
         <v>14.42</v>
@@ -3060,7 +3060,7 @@
         <v>446</v>
       </c>
       <c r="B85" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C85" s="3">
         <v>22.21</v>
@@ -3172,7 +3172,7 @@
         <v>46</v>
       </c>
       <c r="B93" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C93" s="3">
         <v>82.88</v>
@@ -4782,7 +4782,7 @@
         <v>154</v>
       </c>
       <c r="B208" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C208" s="3">
         <v>44.51</v>
@@ -5048,7 +5048,7 @@
         <v>172</v>
       </c>
       <c r="B227" s="3">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C227" s="3">
         <v>37.299999999999997</v>
@@ -5076,7 +5076,7 @@
         <v>174</v>
       </c>
       <c r="B229" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C229" s="3">
         <v>154.62</v>
@@ -5370,7 +5370,7 @@
         <v>192</v>
       </c>
       <c r="B250" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C250" s="3">
         <v>422.09</v>
@@ -5986,7 +5986,7 @@
         <v>232</v>
       </c>
       <c r="B294" s="3">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C294" s="3">
         <v>51.15</v>
@@ -6014,7 +6014,7 @@
         <v>234</v>
       </c>
       <c r="B296" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C296" s="3">
         <v>182.42</v>
@@ -6028,7 +6028,7 @@
         <v>235</v>
       </c>
       <c r="B297" s="3">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C297" s="3">
         <v>222.62</v>
@@ -6714,7 +6714,7 @@
         <v>282</v>
       </c>
       <c r="B346" s="3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C346" s="3">
         <v>30.9</v>
@@ -7008,7 +7008,7 @@
         <v>302</v>
       </c>
       <c r="B367" s="3">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C367" s="3">
         <v>47.62</v>
@@ -7064,7 +7064,7 @@
         <v>306</v>
       </c>
       <c r="B371" s="3">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C371" s="3">
         <v>212.75</v>
@@ -7092,7 +7092,7 @@
         <v>308</v>
       </c>
       <c r="B373" s="3">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C373" s="3">
         <v>66.180000000000007</v>
@@ -7148,7 +7148,7 @@
         <v>312</v>
       </c>
       <c r="B377" s="3">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C377" s="3">
         <v>310.2</v>
@@ -7750,7 +7750,7 @@
         <v>375</v>
       </c>
       <c r="B420" s="3">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C420" s="3">
         <v>97.5</v>
@@ -7778,7 +7778,7 @@
         <v>377</v>
       </c>
       <c r="B422" s="3">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C422" s="3">
         <v>35.75</v>
@@ -8184,7 +8184,7 @@
         <v>469</v>
       </c>
       <c r="B451" s="3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C451" s="3">
         <v>45</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="473">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -1427,6 +1427,12 @@
   </si>
   <si>
     <t>CYC PREMUS LI-CA NLGI2 180kg vaselina</t>
+  </si>
+  <si>
+    <t>CYC MAX X-100 5W40 CART 5L</t>
+  </si>
+  <si>
+    <t>RAV Spuma activa de curatare 0.5L PROMO</t>
   </si>
 </sst>
 </file>
@@ -1871,7 +1877,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D451"/>
+  <dimension ref="A1:D453"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="49.85546875" customWidth="1"/>
@@ -2024,7 +2030,7 @@
         <v>412</v>
       </c>
       <c r="B11" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11" s="3">
         <v>476.85</v>
@@ -2332,7 +2338,7 @@
         <v>423</v>
       </c>
       <c r="B33" s="3">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C33" s="3">
         <v>207.95</v>
@@ -2514,7 +2520,7 @@
         <v>13</v>
       </c>
       <c r="B46" s="3">
-        <v>1463</v>
+        <v>1449</v>
       </c>
       <c r="C46" s="3">
         <v>13</v>
@@ -2850,10 +2856,10 @@
         <v>32</v>
       </c>
       <c r="B70" s="3">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="C70" s="3">
-        <v>87.12</v>
+        <v>88.33</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>386</v>
@@ -2906,7 +2912,7 @@
         <v>35</v>
       </c>
       <c r="B74" s="3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C74" s="3">
         <v>89.38</v>
@@ -2990,7 +2996,7 @@
         <v>443</v>
       </c>
       <c r="B80" s="3">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="C80" s="3">
         <v>19.48</v>
@@ -3057,13 +3063,13 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="B85" s="3">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="C85" s="3">
-        <v>22.21</v>
+        <v>104.95</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>447</v>
@@ -3071,27 +3077,27 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>40</v>
+        <v>446</v>
       </c>
       <c r="B86" s="3">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C86" s="3">
-        <v>25.4</v>
+        <v>22.21</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>366</v>
+        <v>447</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B87" s="3">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C87" s="3">
-        <v>40.92</v>
+        <v>25.4</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>366</v>
@@ -3099,13 +3105,13 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B88" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C88" s="3">
-        <v>25.4</v>
+        <v>40.92</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>366</v>
@@ -3113,13 +3119,13 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B89" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C89" s="3">
-        <v>28.07</v>
+        <v>25.4</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>366</v>
@@ -3127,13 +3133,13 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>384</v>
+        <v>43</v>
       </c>
       <c r="B90" s="3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C90" s="3">
-        <v>23.33</v>
+        <v>28.07</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>366</v>
@@ -3141,41 +3147,41 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>44</v>
+        <v>384</v>
       </c>
       <c r="B91" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C91" s="3">
-        <v>34.630000000000003</v>
+        <v>23.33</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B92" s="3">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="C92" s="3">
-        <v>18.37</v>
+        <v>34.630000000000003</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B93" s="3">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="C93" s="3">
-        <v>82.88</v>
+        <v>18.37</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>369</v>
@@ -3183,13 +3189,13 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B94" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C94" s="3">
-        <v>161.01</v>
+        <v>82.88</v>
       </c>
       <c r="D94" s="4" t="s">
         <v>369</v>
@@ -3197,13 +3203,13 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B95" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C95" s="3">
-        <v>50.23</v>
+        <v>161.01</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>369</v>
@@ -3211,55 +3217,55 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B96" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C96" s="3">
-        <v>65.83</v>
+        <v>50.23</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B97" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C97" s="3">
-        <v>46.76</v>
+        <v>65.83</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B98" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C98" s="3">
-        <v>62.11</v>
+        <v>46.76</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B99" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C99" s="3">
-        <v>47.61</v>
+        <v>62.11</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>367</v>
@@ -3267,13 +3273,13 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B100" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C100" s="3">
-        <v>63.76</v>
+        <v>47.61</v>
       </c>
       <c r="D100" s="4" t="s">
         <v>367</v>
@@ -3281,13 +3287,13 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B101" s="3">
         <v>1</v>
       </c>
       <c r="C101" s="3">
-        <v>1159.2</v>
+        <v>63.76</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>367</v>
@@ -3295,13 +3301,13 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B102" s="3">
         <v>1</v>
       </c>
       <c r="C102" s="3">
-        <v>255</v>
+        <v>1159.2</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>367</v>
@@ -3309,13 +3315,13 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B103" s="3">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C103" s="3">
-        <v>69.55</v>
+        <v>255</v>
       </c>
       <c r="D103" s="4" t="s">
         <v>367</v>
@@ -3323,13 +3329,13 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B104" s="3">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C104" s="3">
-        <v>1391.04</v>
+        <v>69.55</v>
       </c>
       <c r="D104" s="4" t="s">
         <v>367</v>
@@ -3337,13 +3343,13 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B105" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C105" s="3">
-        <v>87.1</v>
+        <v>1391.04</v>
       </c>
       <c r="D105" s="4" t="s">
         <v>367</v>
@@ -3351,13 +3357,13 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B106" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C106" s="3">
-        <v>40.54</v>
+        <v>87.1</v>
       </c>
       <c r="D106" s="4" t="s">
         <v>367</v>
@@ -3365,13 +3371,13 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B107" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C107" s="3">
-        <v>460.01</v>
+        <v>40.54</v>
       </c>
       <c r="D107" s="4" t="s">
         <v>367</v>
@@ -3385,7 +3391,7 @@
         <v>1</v>
       </c>
       <c r="C108" s="3">
-        <v>639.4</v>
+        <v>460.01</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>367</v>
@@ -3393,13 +3399,13 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B109" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C109" s="3">
-        <v>103.89</v>
+        <v>639.4</v>
       </c>
       <c r="D109" s="4" t="s">
         <v>367</v>
@@ -3407,13 +3413,13 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B110" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C110" s="3">
-        <v>58.48</v>
+        <v>103.89</v>
       </c>
       <c r="D110" s="4" t="s">
         <v>367</v>
@@ -3421,13 +3427,13 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B111" s="3">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="C111" s="3">
-        <v>56.93</v>
+        <v>58.48</v>
       </c>
       <c r="D111" s="4" t="s">
         <v>367</v>
@@ -3438,10 +3444,10 @@
         <v>63</v>
       </c>
       <c r="B112" s="3">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C112" s="3">
-        <v>63.76</v>
+        <v>56.93</v>
       </c>
       <c r="D112" s="4" t="s">
         <v>367</v>
@@ -3449,13 +3455,13 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B113" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C113" s="3">
-        <v>61.92</v>
+        <v>63.76</v>
       </c>
       <c r="D113" s="4" t="s">
         <v>367</v>
@@ -3463,13 +3469,13 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B114" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C114" s="3">
-        <v>63.76</v>
+        <v>61.92</v>
       </c>
       <c r="D114" s="4" t="s">
         <v>367</v>
@@ -3477,13 +3483,13 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B115" s="3">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C115" s="3">
-        <v>69.56</v>
+        <v>63.76</v>
       </c>
       <c r="D115" s="4" t="s">
         <v>367</v>
@@ -3491,13 +3497,13 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B116" s="3">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C116" s="3">
-        <v>59.68</v>
+        <v>69.56</v>
       </c>
       <c r="D116" s="4" t="s">
         <v>367</v>
@@ -3505,13 +3511,13 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B117" s="3">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C117" s="3">
-        <v>56.93</v>
+        <v>59.68</v>
       </c>
       <c r="D117" s="4" t="s">
         <v>367</v>
@@ -3519,13 +3525,13 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B118" s="3">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="C118" s="3">
-        <v>80.73</v>
+        <v>56.93</v>
       </c>
       <c r="D118" s="4" t="s">
         <v>367</v>
@@ -3533,13 +3539,13 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B119" s="3">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C119" s="3">
-        <v>103.09</v>
+        <v>80.73</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>367</v>
@@ -3547,13 +3553,13 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B120" s="3">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C120" s="3">
-        <v>119.03</v>
+        <v>103.09</v>
       </c>
       <c r="D120" s="4" t="s">
         <v>367</v>
@@ -3561,13 +3567,13 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B121" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C121" s="3">
-        <v>63.76</v>
+        <v>119.03</v>
       </c>
       <c r="D121" s="4" t="s">
         <v>367</v>
@@ -3575,10 +3581,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B122" s="3">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C122" s="3">
         <v>63.76</v>
@@ -3589,13 +3595,13 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B123" s="3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C123" s="3">
-        <v>81.150000000000006</v>
+        <v>63.76</v>
       </c>
       <c r="D123" s="4" t="s">
         <v>367</v>
@@ -3603,13 +3609,13 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B124" s="3">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C124" s="3">
-        <v>63.76</v>
+        <v>81.150000000000006</v>
       </c>
       <c r="D124" s="4" t="s">
         <v>367</v>
@@ -3617,13 +3623,13 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B125" s="3">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C125" s="3">
-        <v>69.87</v>
+        <v>63.76</v>
       </c>
       <c r="D125" s="4" t="s">
         <v>367</v>
@@ -3631,13 +3637,13 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B126" s="3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C126" s="3">
-        <v>63.76</v>
+        <v>69.87</v>
       </c>
       <c r="D126" s="4" t="s">
         <v>367</v>
@@ -3645,13 +3651,13 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B127" s="3">
-        <v>6</v>
-      </c>
-      <c r="C127" s="8">
-        <v>79.91</v>
+        <v>14</v>
+      </c>
+      <c r="C127" s="3">
+        <v>63.76</v>
       </c>
       <c r="D127" s="4" t="s">
         <v>367</v>
@@ -3659,13 +3665,13 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B128" s="3">
         <v>6</v>
       </c>
-      <c r="C128" s="3">
-        <v>69.56</v>
+      <c r="C128" s="8">
+        <v>79.91</v>
       </c>
       <c r="D128" s="4" t="s">
         <v>367</v>
@@ -3673,13 +3679,13 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B129" s="3">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="C129" s="3">
-        <v>52.17</v>
+        <v>69.56</v>
       </c>
       <c r="D129" s="4" t="s">
         <v>367</v>
@@ -3687,13 +3693,13 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B130" s="3">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="C130" s="3">
-        <v>208.66</v>
+        <v>52.17</v>
       </c>
       <c r="D130" s="4" t="s">
         <v>367</v>
@@ -3701,13 +3707,13 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B131" s="3">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C131" s="3">
-        <v>88.87</v>
+        <v>208.66</v>
       </c>
       <c r="D131" s="4" t="s">
         <v>367</v>
@@ -3715,13 +3721,13 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B132" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C132" s="3">
-        <v>67.27</v>
+        <v>88.87</v>
       </c>
       <c r="D132" s="4" t="s">
         <v>367</v>
@@ -3729,13 +3735,13 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B133" s="3">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C133" s="3">
-        <v>69.55</v>
+        <v>67.27</v>
       </c>
       <c r="D133" s="4" t="s">
         <v>367</v>
@@ -3743,13 +3749,13 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B134" s="3">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="C134" s="3">
-        <v>78.84</v>
+        <v>69.55</v>
       </c>
       <c r="D134" s="4" t="s">
         <v>367</v>
@@ -3757,13 +3763,13 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B135" s="3">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="C135" s="3">
-        <v>149.91</v>
+        <v>78.84</v>
       </c>
       <c r="D135" s="4" t="s">
         <v>367</v>
@@ -3771,13 +3777,13 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B136" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C136" s="3">
-        <v>38.57</v>
+        <v>149.91</v>
       </c>
       <c r="D136" s="4" t="s">
         <v>367</v>
@@ -3785,13 +3791,13 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B137" s="3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C137" s="3">
-        <v>299</v>
+        <v>38.57</v>
       </c>
       <c r="D137" s="4" t="s">
         <v>367</v>
@@ -3799,16 +3805,16 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B138" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C138" s="3">
-        <v>58.24</v>
+        <v>299</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3816,10 +3822,10 @@
         <v>89</v>
       </c>
       <c r="B139" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C139" s="3">
-        <v>65.23</v>
+        <v>58.24</v>
       </c>
       <c r="D139" s="4" t="s">
         <v>364</v>
@@ -3827,13 +3833,13 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B140" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C140" s="3">
-        <v>290.95</v>
+        <v>65.23</v>
       </c>
       <c r="D140" s="4" t="s">
         <v>364</v>
@@ -3844,10 +3850,10 @@
         <v>90</v>
       </c>
       <c r="B141" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C141" s="3">
-        <v>325.87</v>
+        <v>290.95</v>
       </c>
       <c r="D141" s="4" t="s">
         <v>364</v>
@@ -3855,27 +3861,27 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B142" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C142" s="3">
-        <v>5165.8</v>
+        <v>325.87</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="143" spans="1:4">
       <c r="A143" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B143" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C143" s="3">
-        <v>511.75</v>
+        <v>5165.8</v>
       </c>
       <c r="D143" s="4" t="s">
         <v>367</v>
@@ -3883,13 +3889,13 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B144" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C144" s="3">
-        <v>572.70000000000005</v>
+        <v>511.75</v>
       </c>
       <c r="D144" s="4" t="s">
         <v>367</v>
@@ -3897,55 +3903,55 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B145" s="3">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="C145" s="3">
-        <v>66.98</v>
+        <v>572.70000000000005</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B146" s="3">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="C146" s="3">
-        <v>367.42</v>
+        <v>66.98</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B147" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C147" s="3">
-        <v>51.52</v>
+        <v>367.42</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B148" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C148" s="3">
-        <v>23.19</v>
+        <v>51.52</v>
       </c>
       <c r="D148" s="4" t="s">
         <v>366</v>
@@ -3953,10 +3959,10 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B149" s="3">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C149" s="3">
         <v>23.19</v>
@@ -3967,27 +3973,27 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B150" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C150" s="3">
-        <v>69.55</v>
+        <v>23.19</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B151" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C151" s="3">
-        <v>3169.7</v>
+        <v>69.55</v>
       </c>
       <c r="D151" s="4" t="s">
         <v>367</v>
@@ -3995,13 +4001,13 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B152" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C152" s="3">
-        <v>81.14</v>
+        <v>3169.7</v>
       </c>
       <c r="D152" s="4" t="s">
         <v>367</v>
@@ -4009,10 +4015,10 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B153" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C153" s="3">
         <v>81.14</v>
@@ -4023,41 +4029,41 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B154" s="3">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C154" s="3">
-        <v>66.98</v>
+        <v>81.14</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B155" s="3">
-        <v>30</v>
-      </c>
-      <c r="C155" s="8">
-        <v>77.63</v>
+        <v>58</v>
+      </c>
+      <c r="C155" s="3">
+        <v>66.98</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B156" s="3">
-        <v>26</v>
-      </c>
-      <c r="C156" s="3">
-        <v>93.35</v>
+        <v>30</v>
+      </c>
+      <c r="C156" s="8">
+        <v>77.63</v>
       </c>
       <c r="D156" s="4" t="s">
         <v>367</v>
@@ -4065,13 +4071,13 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C157" s="3">
-        <v>1217.1600000000001</v>
+        <v>93.35</v>
       </c>
       <c r="D157" s="4" t="s">
         <v>367</v>
@@ -4079,13 +4085,13 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B158" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C158" s="3">
-        <v>3079</v>
+        <v>1217.1600000000001</v>
       </c>
       <c r="D158" s="4" t="s">
         <v>367</v>
@@ -4093,16 +4099,16 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B159" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C159" s="3">
-        <v>43.7</v>
+        <v>3079</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4110,10 +4116,10 @@
         <v>108</v>
       </c>
       <c r="B160" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C160" s="3">
-        <v>48.95</v>
+        <v>43.7</v>
       </c>
       <c r="D160" s="4" t="s">
         <v>366</v>
@@ -4121,27 +4127,27 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B161" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C161" s="3">
-        <v>72.33</v>
+        <v>48.95</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="162" spans="1:4">
       <c r="A162" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B162" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C162" s="3">
-        <v>284.19</v>
+        <v>72.33</v>
       </c>
       <c r="D162" s="4" t="s">
         <v>364</v>
@@ -4149,38 +4155,38 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B163" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C163" s="3">
-        <v>101.5</v>
+        <v>284.19</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B164" s="3">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C164" s="3">
-        <v>32.200000000000003</v>
+        <v>101.5</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B165" s="3">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="C165" s="3">
         <v>32.200000000000003</v>
@@ -4191,13 +4197,13 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B166" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C166" s="3">
-        <v>37.43</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D166" s="4" t="s">
         <v>354</v>
@@ -4205,13 +4211,13 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B167" s="3">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C167" s="3">
-        <v>32.200000000000003</v>
+        <v>37.43</v>
       </c>
       <c r="D167" s="4" t="s">
         <v>354</v>
@@ -4219,41 +4225,41 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B168" s="3">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C168" s="3">
-        <v>115.01</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
     </row>
     <row r="169" spans="1:4">
       <c r="A169" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B169" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C169" s="3">
-        <v>38.39</v>
+        <v>115.01</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B170" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C170" s="3">
-        <v>151.47999999999999</v>
+        <v>38.39</v>
       </c>
       <c r="D170" s="4" t="s">
         <v>364</v>
@@ -4261,13 +4267,13 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B171" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C171" s="3">
-        <v>181.68</v>
+        <v>151.47999999999999</v>
       </c>
       <c r="D171" s="4" t="s">
         <v>364</v>
@@ -4275,27 +4281,27 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B172" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C172" s="3">
-        <v>20.059999999999999</v>
+        <v>181.68</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
     </row>
     <row r="173" spans="1:4">
       <c r="A173" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B173" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C173" s="3">
-        <v>12.88</v>
+        <v>20.059999999999999</v>
       </c>
       <c r="D173" s="4" t="s">
         <v>355</v>
@@ -4303,13 +4309,13 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B174" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C174" s="3">
-        <v>26.73</v>
+        <v>12.88</v>
       </c>
       <c r="D174" s="4" t="s">
         <v>355</v>
@@ -4317,13 +4323,13 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B175" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C175" s="3">
-        <v>29.95</v>
+        <v>26.73</v>
       </c>
       <c r="D175" s="4" t="s">
         <v>355</v>
@@ -4331,13 +4337,13 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B176" s="3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C176" s="3">
-        <v>58.68</v>
+        <v>29.95</v>
       </c>
       <c r="D176" s="4" t="s">
         <v>355</v>
@@ -4345,13 +4351,13 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B177" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C177" s="3">
-        <v>79.98</v>
+        <v>58.68</v>
       </c>
       <c r="D177" s="4" t="s">
         <v>355</v>
@@ -4359,55 +4365,55 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B178" s="3">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C178" s="3">
-        <v>38.770000000000003</v>
+        <v>79.98</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="179" spans="1:4">
       <c r="A179" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B179" s="3">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C179" s="3">
-        <v>107.35</v>
+        <v>38.770000000000003</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
     </row>
     <row r="180" spans="1:4">
       <c r="A180" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B180" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C180" s="3">
-        <v>61.83</v>
+        <v>107.35</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="181" spans="1:4">
       <c r="A181" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B181" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C181" s="3">
-        <v>243.16</v>
+        <v>61.83</v>
       </c>
       <c r="D181" s="4" t="s">
         <v>364</v>
@@ -4415,41 +4421,41 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B182" s="3">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C182" s="3">
-        <v>63.78</v>
+        <v>243.16</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="183" spans="1:4">
       <c r="A183" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B183" s="3">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C183" s="3">
-        <v>75.989999999999995</v>
+        <v>63.78</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="184" spans="1:4">
       <c r="A184" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B184" s="3">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C184" s="3">
-        <v>297.64999999999998</v>
+        <v>75.989999999999995</v>
       </c>
       <c r="D184" s="4" t="s">
         <v>364</v>
@@ -4457,13 +4463,13 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B185" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C185" s="3">
-        <v>77.28</v>
+        <v>297.64999999999998</v>
       </c>
       <c r="D185" s="4" t="s">
         <v>364</v>
@@ -4471,13 +4477,13 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B186" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C186" s="3">
-        <v>75.989999999999995</v>
+        <v>77.28</v>
       </c>
       <c r="D186" s="4" t="s">
         <v>364</v>
@@ -4485,13 +4491,13 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B187" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C187" s="3">
-        <v>342.24</v>
+        <v>75.989999999999995</v>
       </c>
       <c r="D187" s="4" t="s">
         <v>364</v>
@@ -4499,27 +4505,27 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B188" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C188" s="3">
-        <v>633.75</v>
+        <v>342.24</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="189" spans="1:4">
       <c r="A189" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B189" s="3">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="C189" s="3">
-        <v>50.51</v>
+        <v>633.75</v>
       </c>
       <c r="D189" s="4" t="s">
         <v>367</v>
@@ -4527,13 +4533,13 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" t="s">
-        <v>430</v>
+        <v>137</v>
       </c>
       <c r="B190" s="3">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="C190" s="3">
-        <v>581.9</v>
+        <v>50.51</v>
       </c>
       <c r="D190" s="4" t="s">
         <v>367</v>
@@ -4541,13 +4547,13 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" t="s">
-        <v>138</v>
+        <v>430</v>
       </c>
       <c r="B191" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C191" s="3">
-        <v>579.13</v>
+        <v>581.9</v>
       </c>
       <c r="D191" s="4" t="s">
         <v>367</v>
@@ -4555,55 +4561,55 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B192" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C192" s="3">
-        <v>122.36</v>
+        <v>579.13</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="193" spans="1:4">
       <c r="A193" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B193" s="3">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C193" s="3">
-        <v>35.81</v>
+        <v>122.36</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
     </row>
     <row r="194" spans="1:4">
       <c r="A194" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B194" s="3">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C194" s="3">
-        <v>59.25</v>
+        <v>35.81</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="195" spans="1:4">
       <c r="A195" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B195" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C195" s="3">
-        <v>260.33</v>
+        <v>59.25</v>
       </c>
       <c r="D195" s="4" t="s">
         <v>364</v>
@@ -4611,13 +4617,13 @@
     </row>
     <row r="196" spans="1:4">
       <c r="A196" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B196" s="3">
-        <v>15</v>
-      </c>
-      <c r="C196" s="7">
-        <v>59.62</v>
+        <v>7</v>
+      </c>
+      <c r="C196" s="3">
+        <v>260.33</v>
       </c>
       <c r="D196" s="4" t="s">
         <v>364</v>
@@ -4625,13 +4631,13 @@
     </row>
     <row r="197" spans="1:4">
       <c r="A197" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B197" s="3">
-        <v>4</v>
-      </c>
-      <c r="C197" s="3">
-        <v>248.77</v>
+        <v>15</v>
+      </c>
+      <c r="C197" s="7">
+        <v>59.62</v>
       </c>
       <c r="D197" s="4" t="s">
         <v>364</v>
@@ -4639,13 +4645,13 @@
     </row>
     <row r="198" spans="1:4">
       <c r="A198" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B198" s="3">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C198" s="3">
-        <v>74.7</v>
+        <v>248.77</v>
       </c>
       <c r="D198" s="4" t="s">
         <v>364</v>
@@ -4653,13 +4659,13 @@
     </row>
     <row r="199" spans="1:4">
       <c r="A199" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B199" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C199" s="3">
-        <v>296.3</v>
+        <v>74.7</v>
       </c>
       <c r="D199" s="4" t="s">
         <v>364</v>
@@ -4667,13 +4673,13 @@
     </row>
     <row r="200" spans="1:4">
       <c r="A200" t="s">
-        <v>385</v>
+        <v>146</v>
       </c>
       <c r="B200" s="3">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C200" s="3">
-        <v>168.7</v>
+        <v>296.3</v>
       </c>
       <c r="D200" s="4" t="s">
         <v>364</v>
@@ -4681,13 +4687,13 @@
     </row>
     <row r="201" spans="1:4">
       <c r="A201" t="s">
-        <v>147</v>
+        <v>385</v>
       </c>
       <c r="B201" s="3">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="C201" s="3">
-        <v>44.5</v>
+        <v>168.7</v>
       </c>
       <c r="D201" s="4" t="s">
         <v>364</v>
@@ -4695,13 +4701,13 @@
     </row>
     <row r="202" spans="1:4">
       <c r="A202" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B202" s="3">
-        <v>7</v>
-      </c>
-      <c r="C202" s="10">
-        <v>210.88</v>
+        <v>26</v>
+      </c>
+      <c r="C202" s="3">
+        <v>44.5</v>
       </c>
       <c r="D202" s="4" t="s">
         <v>364</v>
@@ -4709,13 +4715,13 @@
     </row>
     <row r="203" spans="1:4">
       <c r="A203" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B203" s="3">
-        <v>2</v>
-      </c>
-      <c r="C203" s="3">
-        <v>2189.02</v>
+        <v>7</v>
+      </c>
+      <c r="C203" s="10">
+        <v>210.88</v>
       </c>
       <c r="D203" s="4" t="s">
         <v>364</v>
@@ -4723,13 +4729,13 @@
     </row>
     <row r="204" spans="1:4">
       <c r="A204" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B204" s="3">
         <v>2</v>
       </c>
       <c r="C204" s="3">
-        <v>453.22</v>
+        <v>2189.02</v>
       </c>
       <c r="D204" s="4" t="s">
         <v>364</v>
@@ -4737,13 +4743,13 @@
     </row>
     <row r="205" spans="1:4">
       <c r="A205" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B205" s="3">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C205" s="3">
-        <v>48.64</v>
+        <v>453.22</v>
       </c>
       <c r="D205" s="4" t="s">
         <v>364</v>
@@ -4751,13 +4757,13 @@
     </row>
     <row r="206" spans="1:4">
       <c r="A206" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B206" s="3">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C206" s="3">
-        <v>126.63</v>
+        <v>48.64</v>
       </c>
       <c r="D206" s="4" t="s">
         <v>364</v>
@@ -4765,41 +4771,41 @@
     </row>
     <row r="207" spans="1:4">
       <c r="A207" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B207" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C207" s="3">
-        <v>69.56</v>
+        <v>126.63</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="208" spans="1:4">
       <c r="A208" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B208" s="3">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C208" s="3">
-        <v>44.51</v>
+        <v>69.56</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="209" spans="1:4">
       <c r="A209" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B209" s="3">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C209" s="3">
-        <v>145.94</v>
+        <v>44.51</v>
       </c>
       <c r="D209" s="4" t="s">
         <v>364</v>
@@ -4807,13 +4813,13 @@
     </row>
     <row r="210" spans="1:4">
       <c r="A210" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B210" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C210" s="3">
-        <v>199.77</v>
+        <v>145.94</v>
       </c>
       <c r="D210" s="4" t="s">
         <v>364</v>
@@ -4821,13 +4827,13 @@
     </row>
     <row r="211" spans="1:4">
       <c r="A211" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B211" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C211" s="3">
-        <v>2060</v>
+        <v>199.77</v>
       </c>
       <c r="D211" s="4" t="s">
         <v>364</v>
@@ -4835,13 +4841,13 @@
     </row>
     <row r="212" spans="1:4">
       <c r="A212" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B212" s="3">
-        <v>34</v>
-      </c>
-      <c r="C212" s="8">
-        <v>58.32</v>
+        <v>0</v>
+      </c>
+      <c r="C212" s="3">
+        <v>2060</v>
       </c>
       <c r="D212" s="4" t="s">
         <v>364</v>
@@ -4849,13 +4855,13 @@
     </row>
     <row r="213" spans="1:4">
       <c r="A213" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B213" s="3">
-        <v>2</v>
-      </c>
-      <c r="C213" s="3">
-        <v>183.41</v>
+        <v>34</v>
+      </c>
+      <c r="C213" s="8">
+        <v>58.32</v>
       </c>
       <c r="D213" s="4" t="s">
         <v>364</v>
@@ -4863,13 +4869,13 @@
     </row>
     <row r="214" spans="1:4">
       <c r="A214" t="s">
-        <v>352</v>
+        <v>159</v>
       </c>
       <c r="B214" s="3">
-        <v>7</v>
-      </c>
-      <c r="C214" s="8">
-        <v>257.70999999999998</v>
+        <v>2</v>
+      </c>
+      <c r="C214" s="3">
+        <v>183.41</v>
       </c>
       <c r="D214" s="4" t="s">
         <v>364</v>
@@ -4877,41 +4883,41 @@
     </row>
     <row r="215" spans="1:4">
       <c r="A215" t="s">
-        <v>160</v>
+        <v>352</v>
       </c>
       <c r="B215" s="3">
-        <v>27</v>
-      </c>
-      <c r="C215" s="3">
-        <v>33.479999999999997</v>
+        <v>7</v>
+      </c>
+      <c r="C215" s="8">
+        <v>257.70999999999998</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="216" spans="1:4">
       <c r="A216" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B216" s="3">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C216" s="3">
-        <v>48.13</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="217" spans="1:4">
       <c r="A217" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B217" s="3">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C217" s="3">
-        <v>5400</v>
+        <v>48.13</v>
       </c>
       <c r="D217" s="4" t="s">
         <v>364</v>
@@ -4919,13 +4925,13 @@
     </row>
     <row r="218" spans="1:4">
       <c r="A218" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B218" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C218" s="3">
-        <v>170.78</v>
+        <v>5400</v>
       </c>
       <c r="D218" s="4" t="s">
         <v>364</v>
@@ -4933,13 +4939,13 @@
     </row>
     <row r="219" spans="1:4">
       <c r="A219" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B219" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C219" s="3">
-        <v>216.3</v>
+        <v>170.78</v>
       </c>
       <c r="D219" s="4" t="s">
         <v>364</v>
@@ -4947,13 +4953,13 @@
     </row>
     <row r="220" spans="1:4">
       <c r="A220" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B220" s="3">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C220" s="3">
-        <v>59.7</v>
+        <v>216.3</v>
       </c>
       <c r="D220" s="4" t="s">
         <v>364</v>
@@ -4961,13 +4967,13 @@
     </row>
     <row r="221" spans="1:4">
       <c r="A221" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B221" s="3">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C221" s="3">
-        <v>265.05</v>
+        <v>59.7</v>
       </c>
       <c r="D221" s="4" t="s">
         <v>364</v>
@@ -4975,97 +4981,97 @@
     </row>
     <row r="222" spans="1:4">
       <c r="A222" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B222" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C222" s="3">
-        <v>36.799999999999997</v>
+        <v>265.05</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="223" spans="1:4">
       <c r="A223" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B223" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C223" s="3">
-        <v>103.04</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
     </row>
     <row r="224" spans="1:4">
       <c r="A224" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B224" s="3">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="C224" s="3">
-        <v>36.75</v>
+        <v>103.04</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
     </row>
     <row r="225" spans="1:4">
       <c r="A225" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B225" s="3">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="C225" s="3">
-        <v>47.16</v>
+        <v>36.75</v>
       </c>
       <c r="D225" s="4" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
     </row>
     <row r="226" spans="1:4">
       <c r="A226" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B226" s="3">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C226" s="3">
-        <v>16.809999999999999</v>
+        <v>47.16</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="227" spans="1:4">
       <c r="A227" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B227" s="3">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C227" s="3">
-        <v>37.299999999999997</v>
+        <v>16.809999999999999</v>
       </c>
       <c r="D227" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="228" spans="1:4">
       <c r="A228" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B228" s="3">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="C228" s="3">
-        <v>126.24</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="D228" s="4" t="s">
         <v>364</v>
@@ -5073,13 +5079,13 @@
     </row>
     <row r="229" spans="1:4">
       <c r="A229" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B229" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C229" s="3">
-        <v>154.62</v>
+        <v>126.24</v>
       </c>
       <c r="D229" s="4" t="s">
         <v>364</v>
@@ -5087,13 +5093,13 @@
     </row>
     <row r="230" spans="1:4">
       <c r="A230" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B230" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C230" s="3">
-        <v>508.2</v>
+        <v>154.62</v>
       </c>
       <c r="D230" s="4" t="s">
         <v>364</v>
@@ -5101,13 +5107,13 @@
     </row>
     <row r="231" spans="1:4">
       <c r="A231" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B231" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C231" s="3">
-        <v>5069</v>
+        <v>508.2</v>
       </c>
       <c r="D231" s="4" t="s">
         <v>364</v>
@@ -5115,13 +5121,13 @@
     </row>
     <row r="232" spans="1:4">
       <c r="A232" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B232" s="3">
         <v>0</v>
       </c>
       <c r="C232" s="3">
-        <v>466.78</v>
+        <v>5069</v>
       </c>
       <c r="D232" s="4" t="s">
         <v>364</v>
@@ -5129,27 +5135,27 @@
     </row>
     <row r="233" spans="1:4">
       <c r="A233" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B233" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C233" s="3">
-        <v>57.5</v>
+        <v>466.78</v>
       </c>
       <c r="D233" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="234" spans="1:4">
       <c r="A234" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B234" s="3">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C234" s="3">
-        <v>63.13</v>
+        <v>57.5</v>
       </c>
       <c r="D234" s="4" t="s">
         <v>367</v>
@@ -5157,13 +5163,13 @@
     </row>
     <row r="235" spans="1:4">
       <c r="A235" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B235" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C235" s="3">
-        <v>20789.41</v>
+        <v>63.13</v>
       </c>
       <c r="D235" s="4" t="s">
         <v>367</v>
@@ -5177,7 +5183,7 @@
         <v>1</v>
       </c>
       <c r="C236" s="3">
-        <v>33057.85</v>
+        <v>20789.41</v>
       </c>
       <c r="D236" s="4" t="s">
         <v>367</v>
@@ -5185,13 +5191,13 @@
     </row>
     <row r="237" spans="1:4">
       <c r="A237" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B237" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C237" s="3">
-        <v>83.5</v>
+        <v>33057.85</v>
       </c>
       <c r="D237" s="4" t="s">
         <v>367</v>
@@ -5199,16 +5205,16 @@
     </row>
     <row r="238" spans="1:4">
       <c r="A238" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B238" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C238" s="3">
-        <v>45.72</v>
+        <v>83.5</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5216,10 +5222,10 @@
         <v>182</v>
       </c>
       <c r="B239" s="3">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C239" s="3">
-        <v>81.650000000000006</v>
+        <v>45.72</v>
       </c>
       <c r="D239" s="4" t="s">
         <v>419</v>
@@ -5227,13 +5233,13 @@
     </row>
     <row r="240" spans="1:4">
       <c r="A240" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B240" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C240" s="3">
-        <v>50.71</v>
+        <v>81.650000000000006</v>
       </c>
       <c r="D240" s="4" t="s">
         <v>419</v>
@@ -5241,13 +5247,13 @@
     </row>
     <row r="241" spans="1:4">
       <c r="A241" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B241" s="3">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C241" s="3">
-        <v>51.75</v>
+        <v>50.71</v>
       </c>
       <c r="D241" s="4" t="s">
         <v>419</v>
@@ -5255,13 +5261,13 @@
     </row>
     <row r="242" spans="1:4">
       <c r="A242" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B242" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C242" s="3">
-        <v>36.94</v>
+        <v>51.75</v>
       </c>
       <c r="D242" s="4" t="s">
         <v>419</v>
@@ -5269,13 +5275,13 @@
     </row>
     <row r="243" spans="1:4">
       <c r="A243" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B243" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C243" s="3">
-        <v>36.799999999999997</v>
+        <v>36.94</v>
       </c>
       <c r="D243" s="4" t="s">
         <v>419</v>
@@ -5289,7 +5295,7 @@
         <v>12</v>
       </c>
       <c r="C244" s="3">
-        <v>79.58</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D244" s="4" t="s">
         <v>419</v>
@@ -5297,27 +5303,27 @@
     </row>
     <row r="245" spans="1:4">
       <c r="A245" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B245" s="3">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C245" s="3">
-        <v>67.28</v>
+        <v>79.58</v>
       </c>
       <c r="D245" s="4" t="s">
-        <v>367</v>
+        <v>419</v>
       </c>
     </row>
     <row r="246" spans="1:4">
       <c r="A246" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B246" s="3">
-        <v>21</v>
-      </c>
-      <c r="C246" s="8">
-        <v>79.599999999999994</v>
+        <v>23</v>
+      </c>
+      <c r="C246" s="3">
+        <v>67.28</v>
       </c>
       <c r="D246" s="4" t="s">
         <v>367</v>
@@ -5325,13 +5331,13 @@
     </row>
     <row r="247" spans="1:4">
       <c r="A247" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B247" s="3">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C247" s="8">
-        <v>75.88</v>
+        <v>79.599999999999994</v>
       </c>
       <c r="D247" s="4" t="s">
         <v>367</v>
@@ -5339,13 +5345,13 @@
     </row>
     <row r="248" spans="1:4">
       <c r="A248" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B248" s="3">
-        <v>17</v>
-      </c>
-      <c r="C248" s="3">
-        <v>109.08</v>
+        <v>25</v>
+      </c>
+      <c r="C248" s="8">
+        <v>75.88</v>
       </c>
       <c r="D248" s="4" t="s">
         <v>367</v>
@@ -5353,27 +5359,27 @@
     </row>
     <row r="249" spans="1:4">
       <c r="A249" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B249" s="3">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="C249" s="3">
-        <v>33.479999999999997</v>
+        <v>109.08</v>
       </c>
       <c r="D249" s="4" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
     </row>
     <row r="250" spans="1:4">
       <c r="A250" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B250" s="3">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="C250" s="3">
-        <v>422.09</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D250" s="4" t="s">
         <v>356</v>
@@ -5381,13 +5387,13 @@
     </row>
     <row r="251" spans="1:4">
       <c r="A251" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B251" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C251" s="3">
-        <v>1277.7</v>
+        <v>422.09</v>
       </c>
       <c r="D251" s="4" t="s">
         <v>356</v>
@@ -5395,27 +5401,27 @@
     </row>
     <row r="252" spans="1:4">
       <c r="A252" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B252" s="3">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C252" s="3">
-        <v>6.44</v>
+        <v>1277.7</v>
       </c>
       <c r="D252" s="4" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
     </row>
     <row r="253" spans="1:4">
       <c r="A253" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B253" s="3">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C253" s="3">
-        <v>108.2</v>
+        <v>6.44</v>
       </c>
       <c r="D253" s="4" t="s">
         <v>366</v>
@@ -5423,16 +5429,16 @@
     </row>
     <row r="254" spans="1:4">
       <c r="A254" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B254" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C254" s="3">
-        <v>4456.4799999999996</v>
+        <v>108.2</v>
       </c>
       <c r="D254" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5440,10 +5446,10 @@
         <v>196</v>
       </c>
       <c r="B255" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C255" s="3">
-        <v>7429</v>
+        <v>4456.4799999999996</v>
       </c>
       <c r="D255" s="4" t="s">
         <v>364</v>
@@ -5451,13 +5457,13 @@
     </row>
     <row r="256" spans="1:4">
       <c r="A256" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B256" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C256" s="3">
-        <v>609.5</v>
+        <v>7429</v>
       </c>
       <c r="D256" s="4" t="s">
         <v>364</v>
@@ -5465,24 +5471,24 @@
     </row>
     <row r="257" spans="1:4">
       <c r="A257" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B257" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C257" s="3">
-        <v>32.200000000000003</v>
+        <v>609.5</v>
       </c>
       <c r="D257" s="4" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
     </row>
     <row r="258" spans="1:4">
       <c r="A258" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B258" s="3">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C258" s="3">
         <v>32.200000000000003</v>
@@ -5493,10 +5499,10 @@
     </row>
     <row r="259" spans="1:4">
       <c r="A259" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B259" s="3">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C259" s="3">
         <v>32.200000000000003</v>
@@ -5507,10 +5513,10 @@
     </row>
     <row r="260" spans="1:4">
       <c r="A260" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B260" s="3">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="C260" s="3">
         <v>32.200000000000003</v>
@@ -5521,13 +5527,13 @@
     </row>
     <row r="261" spans="1:4">
       <c r="A261" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B261" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C261" s="3">
-        <v>40.4</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D261" s="4" t="s">
         <v>354</v>
@@ -5535,13 +5541,13 @@
     </row>
     <row r="262" spans="1:4">
       <c r="A262" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B262" s="3">
-        <v>173</v>
+        <v>3</v>
       </c>
       <c r="C262" s="3">
-        <v>36.06</v>
+        <v>40.4</v>
       </c>
       <c r="D262" s="4" t="s">
         <v>354</v>
@@ -5549,27 +5555,27 @@
     </row>
     <row r="263" spans="1:4">
       <c r="A263" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B263" s="3">
-        <v>1</v>
+        <v>173</v>
       </c>
       <c r="C263" s="3">
-        <v>56</v>
+        <v>36.06</v>
       </c>
       <c r="D263" s="4" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
     </row>
     <row r="264" spans="1:4">
       <c r="A264" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B264" s="3">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C264" s="3">
-        <v>57.63</v>
+        <v>56</v>
       </c>
       <c r="D264" s="4" t="s">
         <v>367</v>
@@ -5577,13 +5583,13 @@
     </row>
     <row r="265" spans="1:4">
       <c r="A265" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B265" s="3">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C265" s="3">
-        <v>60.78</v>
+        <v>57.63</v>
       </c>
       <c r="D265" s="4" t="s">
         <v>367</v>
@@ -5591,69 +5597,69 @@
     </row>
     <row r="266" spans="1:4">
       <c r="A266" t="s">
-        <v>420</v>
+        <v>206</v>
       </c>
       <c r="B266" s="3">
         <v>4</v>
       </c>
       <c r="C266" s="3">
-        <v>65</v>
+        <v>60.78</v>
       </c>
       <c r="D266" s="4" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
     </row>
     <row r="267" spans="1:4">
       <c r="A267" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B267" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C267" s="3">
-        <v>29.63</v>
+        <v>65</v>
       </c>
       <c r="D267" s="4" t="s">
-        <v>354</v>
+        <v>419</v>
       </c>
     </row>
     <row r="268" spans="1:4">
       <c r="A268" t="s">
-        <v>207</v>
+        <v>421</v>
       </c>
       <c r="B268" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C268" s="3">
-        <v>42.49</v>
+        <v>29.63</v>
       </c>
       <c r="D268" s="4" t="s">
-        <v>419</v>
+        <v>354</v>
       </c>
     </row>
     <row r="269" spans="1:4">
       <c r="A269" t="s">
-        <v>208</v>
-      </c>
-      <c r="B269" s="4">
-        <v>18</v>
-      </c>
-      <c r="C269" s="8">
-        <v>86.95</v>
+        <v>207</v>
+      </c>
+      <c r="B269" s="3">
+        <v>0</v>
+      </c>
+      <c r="C269" s="3">
+        <v>42.49</v>
       </c>
       <c r="D269" s="4" t="s">
-        <v>364</v>
+        <v>419</v>
       </c>
     </row>
     <row r="270" spans="1:4">
       <c r="A270" t="s">
-        <v>209</v>
-      </c>
-      <c r="B270" s="3">
-        <v>2</v>
+        <v>208</v>
+      </c>
+      <c r="B270" s="4">
+        <v>18</v>
       </c>
       <c r="C270" s="8">
-        <v>312.57</v>
+        <v>86.95</v>
       </c>
       <c r="D270" s="4" t="s">
         <v>364</v>
@@ -5661,13 +5667,13 @@
     </row>
     <row r="271" spans="1:4">
       <c r="A271" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B271" s="3">
-        <v>14</v>
-      </c>
-      <c r="C271" s="3">
-        <v>71.709999999999994</v>
+        <v>2</v>
+      </c>
+      <c r="C271" s="8">
+        <v>312.57</v>
       </c>
       <c r="D271" s="4" t="s">
         <v>364</v>
@@ -5675,41 +5681,41 @@
     </row>
     <row r="272" spans="1:4">
       <c r="A272" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B272" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C272" s="3">
-        <v>77.760000000000005</v>
+        <v>71.709999999999994</v>
       </c>
       <c r="D272" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="273" spans="1:4">
       <c r="A273" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B273" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C273" s="3">
-        <v>54.7</v>
+        <v>77.760000000000005</v>
       </c>
       <c r="D273" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="274" spans="1:4">
       <c r="A274" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B274" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C274" s="3">
-        <v>67.28</v>
+        <v>54.7</v>
       </c>
       <c r="D274" s="4" t="s">
         <v>364</v>
@@ -5717,13 +5723,13 @@
     </row>
     <row r="275" spans="1:4">
       <c r="A275" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B275" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C275" s="3">
-        <v>334.36</v>
+        <v>67.28</v>
       </c>
       <c r="D275" s="4" t="s">
         <v>364</v>
@@ -5731,13 +5737,13 @@
     </row>
     <row r="276" spans="1:4">
       <c r="A276" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B276" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C276" s="3">
-        <v>78.87</v>
+        <v>334.36</v>
       </c>
       <c r="D276" s="4" t="s">
         <v>364</v>
@@ -5745,13 +5751,13 @@
     </row>
     <row r="277" spans="1:4">
       <c r="A277" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B277" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C277" s="3">
-        <v>83.84</v>
+        <v>78.87</v>
       </c>
       <c r="D277" s="4" t="s">
         <v>364</v>
@@ -5759,13 +5765,13 @@
     </row>
     <row r="278" spans="1:4">
       <c r="A278" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B278" s="3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C278" s="3">
-        <v>331.2</v>
+        <v>83.84</v>
       </c>
       <c r="D278" s="4" t="s">
         <v>364</v>
@@ -5773,13 +5779,13 @@
     </row>
     <row r="279" spans="1:4">
       <c r="A279" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B279" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C279" s="3">
-        <v>79.75</v>
+        <v>331.2</v>
       </c>
       <c r="D279" s="4" t="s">
         <v>364</v>
@@ -5787,13 +5793,13 @@
     </row>
     <row r="280" spans="1:4">
       <c r="A280" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B280" s="3">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="C280" s="3">
-        <v>83.84</v>
+        <v>79.75</v>
       </c>
       <c r="D280" s="4" t="s">
         <v>364</v>
@@ -5801,13 +5807,13 @@
     </row>
     <row r="281" spans="1:4">
       <c r="A281" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B281" s="3">
-        <v>2</v>
-      </c>
-      <c r="C281" s="8">
-        <v>347.3</v>
+        <v>29</v>
+      </c>
+      <c r="C281" s="3">
+        <v>83.84</v>
       </c>
       <c r="D281" s="4" t="s">
         <v>364</v>
@@ -5820,8 +5826,8 @@
       <c r="B282" s="3">
         <v>2</v>
       </c>
-      <c r="C282" s="3">
-        <v>284</v>
+      <c r="C282" s="8">
+        <v>347.3</v>
       </c>
       <c r="D282" s="4" t="s">
         <v>364</v>
@@ -5829,27 +5835,27 @@
     </row>
     <row r="283" spans="1:4">
       <c r="A283" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B283" s="3">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C283" s="3">
-        <v>28.15</v>
+        <v>284</v>
       </c>
       <c r="D283" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="284" spans="1:4">
       <c r="A284" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B284" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C284" s="3">
-        <v>45.08</v>
+        <v>28.15</v>
       </c>
       <c r="D284" s="4" t="s">
         <v>366</v>
@@ -5857,13 +5863,13 @@
     </row>
     <row r="285" spans="1:4">
       <c r="A285" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B285" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C285" s="3">
-        <v>51.52</v>
+        <v>45.08</v>
       </c>
       <c r="D285" s="4" t="s">
         <v>366</v>
@@ -5871,27 +5877,27 @@
     </row>
     <row r="286" spans="1:4">
       <c r="A286" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B286" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C286" s="3">
-        <v>40.57</v>
+        <v>51.52</v>
       </c>
       <c r="D286" s="4" t="s">
-        <v>419</v>
+        <v>366</v>
       </c>
     </row>
     <row r="287" spans="1:4">
       <c r="A287" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B287" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C287" s="3">
-        <v>36.229999999999997</v>
+        <v>40.57</v>
       </c>
       <c r="D287" s="4" t="s">
         <v>419</v>
@@ -5899,41 +5905,41 @@
     </row>
     <row r="288" spans="1:4">
       <c r="A288" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B288" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C288" s="3">
-        <v>54.12</v>
+        <v>36.229999999999997</v>
       </c>
       <c r="D288" s="4" t="s">
-        <v>366</v>
+        <v>419</v>
       </c>
     </row>
     <row r="289" spans="1:4">
       <c r="A289" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B289" s="3">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C289" s="3">
-        <v>69.55</v>
+        <v>54.12</v>
       </c>
       <c r="D289" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="290" spans="1:4">
       <c r="A290" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B290" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C290" s="3">
-        <v>295.14999999999998</v>
+        <v>69.55</v>
       </c>
       <c r="D290" s="4" t="s">
         <v>364</v>
@@ -5941,41 +5947,41 @@
     </row>
     <row r="291" spans="1:4">
       <c r="A291" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B291" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C291" s="3">
-        <v>38.56</v>
+        <v>295.14999999999998</v>
       </c>
       <c r="D291" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="292" spans="1:4">
       <c r="A292" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B292" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C292" s="3">
-        <v>60.95</v>
+        <v>38.56</v>
       </c>
       <c r="D292" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="293" spans="1:4">
       <c r="A293" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B293" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C293" s="3">
-        <v>78.209999999999994</v>
+        <v>60.95</v>
       </c>
       <c r="D293" s="4" t="s">
         <v>367</v>
@@ -5983,27 +5989,27 @@
     </row>
     <row r="294" spans="1:4">
       <c r="A294" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B294" s="3">
-        <v>174</v>
+        <v>10</v>
       </c>
       <c r="C294" s="3">
-        <v>51.15</v>
+        <v>78.209999999999994</v>
       </c>
       <c r="D294" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="295" spans="1:4">
       <c r="A295" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B295" s="3">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="C295" s="3">
-        <v>6591.8</v>
+        <v>51.15</v>
       </c>
       <c r="D295" s="4" t="s">
         <v>364</v>
@@ -6011,13 +6017,13 @@
     </row>
     <row r="296" spans="1:4">
       <c r="A296" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B296" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C296" s="3">
-        <v>182.42</v>
+        <v>6591.8</v>
       </c>
       <c r="D296" s="4" t="s">
         <v>364</v>
@@ -6025,13 +6031,13 @@
     </row>
     <row r="297" spans="1:4">
       <c r="A297" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B297" s="3">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="C297" s="3">
-        <v>222.62</v>
+        <v>182.42</v>
       </c>
       <c r="D297" s="4" t="s">
         <v>364</v>
@@ -6039,13 +6045,13 @@
     </row>
     <row r="298" spans="1:4">
       <c r="A298" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B298" s="3">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="C298" s="3">
-        <v>2314.8000000000002</v>
+        <v>222.62</v>
       </c>
       <c r="D298" s="4" t="s">
         <v>364</v>
@@ -6053,13 +6059,13 @@
     </row>
     <row r="299" spans="1:4">
       <c r="A299" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B299" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C299" s="3">
-        <v>894.8</v>
+        <v>2314.8000000000002</v>
       </c>
       <c r="D299" s="4" t="s">
         <v>364</v>
@@ -6067,27 +6073,27 @@
     </row>
     <row r="300" spans="1:4">
       <c r="A300" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B300" s="3">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="C300" s="3">
-        <v>31.6</v>
+        <v>894.8</v>
       </c>
       <c r="D300" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="301" spans="1:4">
       <c r="A301" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B301" s="3">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C301" s="3">
-        <v>77.28</v>
+        <v>31.6</v>
       </c>
       <c r="D301" s="4" t="s">
         <v>366</v>
@@ -6095,13 +6101,13 @@
     </row>
     <row r="302" spans="1:4">
       <c r="A302" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B302" s="3">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="C302" s="3">
-        <v>43.8</v>
+        <v>77.28</v>
       </c>
       <c r="D302" s="4" t="s">
         <v>366</v>
@@ -6109,13 +6115,13 @@
     </row>
     <row r="303" spans="1:4">
       <c r="A303" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B303" s="3">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C303" s="3">
-        <v>21.9</v>
+        <v>43.8</v>
       </c>
       <c r="D303" s="4" t="s">
         <v>366</v>
@@ -6123,13 +6129,13 @@
     </row>
     <row r="304" spans="1:4">
       <c r="A304" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B304" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C304" s="3">
-        <v>798.6</v>
+        <v>21.9</v>
       </c>
       <c r="D304" s="4" t="s">
         <v>366</v>
@@ -6137,13 +6143,13 @@
     </row>
     <row r="305" spans="1:4">
       <c r="A305" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B305" s="3">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="C305" s="3">
-        <v>23.19</v>
+        <v>798.6</v>
       </c>
       <c r="D305" s="4" t="s">
         <v>366</v>
@@ -6151,13 +6157,13 @@
     </row>
     <row r="306" spans="1:4">
       <c r="A306" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B306" s="3">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="C306" s="3">
-        <v>8.24</v>
+        <v>23.19</v>
       </c>
       <c r="D306" s="4" t="s">
         <v>366</v>
@@ -6165,13 +6171,13 @@
     </row>
     <row r="307" spans="1:4">
       <c r="A307" t="s">
-        <v>455</v>
+        <v>244</v>
       </c>
       <c r="B307" s="3">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="C307" s="3">
-        <v>13.72</v>
+        <v>8.24</v>
       </c>
       <c r="D307" s="4" t="s">
         <v>366</v>
@@ -6179,10 +6185,10 @@
     </row>
     <row r="308" spans="1:4">
       <c r="A308" t="s">
-        <v>245</v>
+        <v>455</v>
       </c>
       <c r="B308" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C308" s="3">
         <v>13.72</v>
@@ -6193,13 +6199,13 @@
     </row>
     <row r="309" spans="1:4">
       <c r="A309" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B309" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C309" s="3">
-        <v>31.95</v>
+        <v>13.72</v>
       </c>
       <c r="D309" s="4" t="s">
         <v>366</v>
@@ -6207,13 +6213,13 @@
     </row>
     <row r="310" spans="1:4">
       <c r="A310" t="s">
-        <v>370</v>
+        <v>246</v>
       </c>
       <c r="B310" s="3">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="C310" s="3">
-        <v>16.2</v>
+        <v>31.95</v>
       </c>
       <c r="D310" s="4" t="s">
         <v>366</v>
@@ -6221,13 +6227,13 @@
     </row>
     <row r="311" spans="1:4">
       <c r="A311" t="s">
-        <v>247</v>
+        <v>370</v>
       </c>
       <c r="B311" s="3">
-        <v>5</v>
+        <v>103</v>
       </c>
       <c r="C311" s="3">
-        <v>36.869999999999997</v>
+        <v>16.2</v>
       </c>
       <c r="D311" s="4" t="s">
         <v>366</v>
@@ -6235,13 +6241,13 @@
     </row>
     <row r="312" spans="1:4">
       <c r="A312" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B312" s="3">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C312" s="3">
-        <v>31.48</v>
+        <v>36.869999999999997</v>
       </c>
       <c r="D312" s="4" t="s">
         <v>366</v>
@@ -6249,13 +6255,13 @@
     </row>
     <row r="313" spans="1:4">
       <c r="A313" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B313" s="3">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C313" s="3">
-        <v>21.9</v>
+        <v>31.48</v>
       </c>
       <c r="D313" s="4" t="s">
         <v>366</v>
@@ -6263,13 +6269,13 @@
     </row>
     <row r="314" spans="1:4">
       <c r="A314" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B314" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C314" s="3">
-        <v>23.19</v>
+        <v>21.9</v>
       </c>
       <c r="D314" s="4" t="s">
         <v>366</v>
@@ -6277,13 +6283,13 @@
     </row>
     <row r="315" spans="1:4">
       <c r="A315" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B315" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C315" s="3">
-        <v>19.55</v>
+        <v>23.19</v>
       </c>
       <c r="D315" s="4" t="s">
         <v>366</v>
@@ -6291,13 +6297,13 @@
     </row>
     <row r="316" spans="1:4">
       <c r="A316" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B316" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C316" s="3">
-        <v>19.07</v>
+        <v>19.55</v>
       </c>
       <c r="D316" s="4" t="s">
         <v>366</v>
@@ -6305,13 +6311,13 @@
     </row>
     <row r="317" spans="1:4">
       <c r="A317" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B317" s="3">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C317" s="3">
-        <v>21.9</v>
+        <v>19.07</v>
       </c>
       <c r="D317" s="4" t="s">
         <v>366</v>
@@ -6319,27 +6325,27 @@
     </row>
     <row r="318" spans="1:4">
       <c r="A318" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B318" s="3">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C318" s="3">
-        <v>79.349999999999994</v>
+        <v>21.9</v>
       </c>
       <c r="D318" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="319" spans="1:4">
       <c r="A319" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B319" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C319" s="3">
-        <v>862.7</v>
+        <v>79.349999999999994</v>
       </c>
       <c r="D319" s="4" t="s">
         <v>367</v>
@@ -6347,13 +6353,13 @@
     </row>
     <row r="320" spans="1:4">
       <c r="A320" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B320" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C320" s="3">
-        <v>56.93</v>
+        <v>862.7</v>
       </c>
       <c r="D320" s="4" t="s">
         <v>367</v>
@@ -6361,13 +6367,13 @@
     </row>
     <row r="321" spans="1:4">
       <c r="A321" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B321" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C321" s="3">
-        <v>1265</v>
+        <v>56.93</v>
       </c>
       <c r="D321" s="4" t="s">
         <v>367</v>
@@ -6375,27 +6381,27 @@
     </row>
     <row r="322" spans="1:4">
       <c r="A322" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B322" s="3">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="C322" s="3">
-        <v>76</v>
+        <v>1265</v>
       </c>
       <c r="D322" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="323" spans="1:4">
       <c r="A323" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B323" s="3">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C323" s="3">
-        <v>267.85000000000002</v>
+        <v>76</v>
       </c>
       <c r="D323" s="4" t="s">
         <v>364</v>
@@ -6403,13 +6409,13 @@
     </row>
     <row r="324" spans="1:4">
       <c r="A324" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B324" s="3">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C324" s="3">
-        <v>74.7</v>
+        <v>267.85000000000002</v>
       </c>
       <c r="D324" s="4" t="s">
         <v>364</v>
@@ -6417,13 +6423,13 @@
     </row>
     <row r="325" spans="1:4">
       <c r="A325" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B325" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C325" s="3">
-        <v>327.3</v>
+        <v>74.7</v>
       </c>
       <c r="D325" s="4" t="s">
         <v>364</v>
@@ -6431,13 +6437,13 @@
     </row>
     <row r="326" spans="1:4">
       <c r="A326" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B326" s="3">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C326" s="3">
-        <v>72.13</v>
+        <v>327.3</v>
       </c>
       <c r="D326" s="4" t="s">
         <v>364</v>
@@ -6445,13 +6451,13 @@
     </row>
     <row r="327" spans="1:4">
       <c r="A327" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B327" s="3">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="C327" s="3">
-        <v>302.39999999999998</v>
+        <v>72.13</v>
       </c>
       <c r="D327" s="4" t="s">
         <v>364</v>
@@ -6459,41 +6465,41 @@
     </row>
     <row r="328" spans="1:4">
       <c r="A328" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B328" s="3">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C328" s="3">
-        <v>36.799999999999997</v>
+        <v>302.39999999999998</v>
       </c>
       <c r="D328" s="4" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="329" spans="1:4">
       <c r="A329" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B329" s="3">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C329" s="3">
-        <v>428.5</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D329" s="4" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="330" spans="1:4">
       <c r="A330" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B330" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C330" s="3">
-        <v>450.22</v>
+        <v>428.5</v>
       </c>
       <c r="D330" s="4" t="s">
         <v>364</v>
@@ -6501,13 +6507,13 @@
     </row>
     <row r="331" spans="1:4">
       <c r="A331" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B331" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C331" s="3">
-        <v>465.7</v>
+        <v>450.22</v>
       </c>
       <c r="D331" s="4" t="s">
         <v>364</v>
@@ -6515,13 +6521,13 @@
     </row>
     <row r="332" spans="1:4">
       <c r="A332" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B332" s="3">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C332" s="3">
-        <v>38.25</v>
+        <v>465.7</v>
       </c>
       <c r="D332" s="4" t="s">
         <v>364</v>
@@ -6529,27 +6535,27 @@
     </row>
     <row r="333" spans="1:4">
       <c r="A333" t="s">
-        <v>269</v>
+        <v>472</v>
       </c>
       <c r="B333" s="3">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="C333" s="3">
-        <v>87.49</v>
+        <v>0</v>
       </c>
       <c r="D333" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="334" spans="1:4">
       <c r="A334" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B334" s="3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C334" s="3">
-        <v>63.13</v>
+        <v>38.25</v>
       </c>
       <c r="D334" s="4" t="s">
         <v>364</v>
@@ -6557,41 +6563,41 @@
     </row>
     <row r="335" spans="1:4">
       <c r="A335" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B335" s="3">
         <v>2</v>
       </c>
       <c r="C335" s="3">
-        <v>377.78</v>
+        <v>87.49</v>
       </c>
       <c r="D335" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="336" spans="1:4">
       <c r="A336" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B336" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C336" s="3">
-        <v>3333.85</v>
+        <v>63.13</v>
       </c>
       <c r="D336" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="337" spans="1:4">
       <c r="A337" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B337" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C337" s="3">
-        <v>374.67</v>
+        <v>377.78</v>
       </c>
       <c r="D337" s="4" t="s">
         <v>368</v>
@@ -6599,13 +6605,13 @@
     </row>
     <row r="338" spans="1:4">
       <c r="A338" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B338" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C338" s="3">
-        <v>120.06</v>
+        <v>3333.85</v>
       </c>
       <c r="D338" s="4" t="s">
         <v>368</v>
@@ -6613,55 +6619,55 @@
     </row>
     <row r="339" spans="1:4">
       <c r="A339" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B339" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C339" s="3">
-        <v>54.2</v>
+        <v>374.67</v>
       </c>
       <c r="D339" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="340" spans="1:4">
       <c r="A340" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B340" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C340" s="3">
-        <v>31.5</v>
+        <v>120.06</v>
       </c>
       <c r="D340" s="4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="341" spans="1:4">
       <c r="A341" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B341" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C341" s="3">
-        <v>114.09</v>
+        <v>54.2</v>
       </c>
       <c r="D341" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="342" spans="1:4">
       <c r="A342" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B342" s="3">
         <v>0</v>
       </c>
       <c r="C342" s="3">
-        <v>139.9</v>
+        <v>31.5</v>
       </c>
       <c r="D342" s="4" t="s">
         <v>364</v>
@@ -6669,13 +6675,13 @@
     </row>
     <row r="343" spans="1:4">
       <c r="A343" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B343" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C343" s="3">
-        <v>50.13</v>
+        <v>114.09</v>
       </c>
       <c r="D343" s="4" t="s">
         <v>364</v>
@@ -6683,13 +6689,13 @@
     </row>
     <row r="344" spans="1:4">
       <c r="A344" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B344" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C344" s="3">
-        <v>140.26</v>
+        <v>139.9</v>
       </c>
       <c r="D344" s="4" t="s">
         <v>364</v>
@@ -6697,69 +6703,69 @@
     </row>
     <row r="345" spans="1:4">
       <c r="A345" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B345" s="3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C345" s="3">
-        <v>370.53</v>
+        <v>50.13</v>
       </c>
       <c r="D345" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="346" spans="1:4">
       <c r="A346" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B346" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C346" s="3">
-        <v>30.9</v>
+        <v>140.26</v>
       </c>
       <c r="D346" s="4" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="347" spans="1:4">
       <c r="A347" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B347" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C347" s="3">
-        <v>5746.5</v>
+        <v>370.53</v>
       </c>
       <c r="D347" s="4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="348" spans="1:4">
       <c r="A348" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B348" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C348" s="3">
-        <v>516.46</v>
+        <v>30.9</v>
       </c>
       <c r="D348" s="4" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="349" spans="1:4">
       <c r="A349" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B349" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C349" s="3">
-        <v>185.15</v>
+        <v>5746.5</v>
       </c>
       <c r="D349" s="4" t="s">
         <v>364</v>
@@ -6767,27 +6773,27 @@
     </row>
     <row r="350" spans="1:4">
       <c r="A350" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B350" s="3">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="C350" s="3">
-        <v>11.5</v>
+        <v>516.46</v>
       </c>
       <c r="D350" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="351" spans="1:4">
       <c r="A351" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B351" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C351" s="3">
-        <v>724.5</v>
+        <v>185.15</v>
       </c>
       <c r="D351" s="4" t="s">
         <v>364</v>
@@ -6795,13 +6801,13 @@
     </row>
     <row r="352" spans="1:4">
       <c r="A352" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B352" s="3">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="C352" s="3">
-        <v>450.22</v>
+        <v>11.5</v>
       </c>
       <c r="D352" s="4" t="s">
         <v>367</v>
@@ -6809,41 +6815,41 @@
     </row>
     <row r="353" spans="1:4">
       <c r="A353" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B353" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C353" s="3">
-        <v>461.23</v>
+        <v>724.5</v>
       </c>
       <c r="D353" s="4" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
     </row>
     <row r="354" spans="1:4">
       <c r="A354" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B354" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C354" s="3">
-        <v>518.41999999999996</v>
+        <v>450.22</v>
       </c>
       <c r="D354" s="4" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
     </row>
     <row r="355" spans="1:4">
       <c r="A355" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B355" s="3">
         <v>1</v>
       </c>
       <c r="C355" s="3">
-        <v>348.08</v>
+        <v>461.23</v>
       </c>
       <c r="D355" s="4" t="s">
         <v>357</v>
@@ -6851,13 +6857,13 @@
     </row>
     <row r="356" spans="1:4">
       <c r="A356" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B356" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C356" s="3">
-        <v>33.479999999999997</v>
+        <v>518.41999999999996</v>
       </c>
       <c r="D356" s="4" t="s">
         <v>357</v>
@@ -6865,13 +6871,13 @@
     </row>
     <row r="357" spans="1:4">
       <c r="A357" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B357" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C357" s="3">
-        <v>35.79</v>
+        <v>348.08</v>
       </c>
       <c r="D357" s="4" t="s">
         <v>357</v>
@@ -6879,13 +6885,13 @@
     </row>
     <row r="358" spans="1:4">
       <c r="A358" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B358" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C358" s="3">
-        <v>377.7</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>357</v>
@@ -6893,13 +6899,13 @@
     </row>
     <row r="359" spans="1:4">
       <c r="A359" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B359" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C359" s="3">
-        <v>33.21</v>
+        <v>35.79</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>357</v>
@@ -6907,13 +6913,13 @@
     </row>
     <row r="360" spans="1:4">
       <c r="A360" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B360" s="3">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="C360" s="3">
-        <v>27.16</v>
+        <v>377.7</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>357</v>
@@ -6921,13 +6927,13 @@
     </row>
     <row r="361" spans="1:4">
       <c r="A361" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B361" s="3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C361" s="3">
-        <v>361.41</v>
+        <v>33.21</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>357</v>
@@ -6935,13 +6941,13 @@
     </row>
     <row r="362" spans="1:4">
       <c r="A362" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B362" s="3">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="C362" s="3">
-        <v>29.25</v>
+        <v>27.16</v>
       </c>
       <c r="D362" s="4" t="s">
         <v>357</v>
@@ -6949,13 +6955,13 @@
     </row>
     <row r="363" spans="1:4">
       <c r="A363" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B363" s="3">
         <v>1</v>
       </c>
       <c r="C363" s="3">
-        <v>304.54000000000002</v>
+        <v>361.41</v>
       </c>
       <c r="D363" s="4" t="s">
         <v>357</v>
@@ -6963,13 +6969,13 @@
     </row>
     <row r="364" spans="1:4">
       <c r="A364" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B364" s="3">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="C364" s="3">
-        <v>34.049999999999997</v>
+        <v>29.25</v>
       </c>
       <c r="D364" s="4" t="s">
         <v>357</v>
@@ -6977,41 +6983,41 @@
     </row>
     <row r="365" spans="1:4">
       <c r="A365" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B365" s="3">
         <v>1</v>
       </c>
       <c r="C365" s="3">
-        <v>57.7</v>
+        <v>304.54000000000002</v>
       </c>
       <c r="D365" s="4" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
     </row>
     <row r="366" spans="1:4">
       <c r="A366" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B366" s="3">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C366" s="3">
-        <v>90.9</v>
+        <v>34.049999999999997</v>
       </c>
       <c r="D366" s="4" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
     </row>
     <row r="367" spans="1:4">
       <c r="A367" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B367" s="3">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c r="C367" s="3">
-        <v>47.62</v>
+        <v>57.7</v>
       </c>
       <c r="D367" s="4" t="s">
         <v>364</v>
@@ -7019,27 +7025,27 @@
     </row>
     <row r="368" spans="1:4">
       <c r="A368" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B368" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C368" s="3">
-        <v>7173.59</v>
+        <v>90.9</v>
       </c>
       <c r="D368" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="369" spans="1:4">
       <c r="A369" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B369" s="3">
-        <v>1</v>
+        <v>169</v>
       </c>
       <c r="C369" s="3">
-        <v>677.79</v>
+        <v>47.62</v>
       </c>
       <c r="D369" s="4" t="s">
         <v>364</v>
@@ -7047,13 +7053,13 @@
     </row>
     <row r="370" spans="1:4">
       <c r="A370" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B370" s="3">
-        <v>20</v>
-      </c>
-      <c r="C370" s="8">
-        <v>171.47</v>
+        <v>0</v>
+      </c>
+      <c r="C370" s="3">
+        <v>7173.59</v>
       </c>
       <c r="D370" s="4" t="s">
         <v>364</v>
@@ -7061,13 +7067,13 @@
     </row>
     <row r="371" spans="1:4">
       <c r="A371" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B371" s="3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C371" s="3">
-        <v>212.75</v>
+        <v>677.79</v>
       </c>
       <c r="D371" s="4" t="s">
         <v>364</v>
@@ -7075,13 +7081,13 @@
     </row>
     <row r="372" spans="1:4">
       <c r="A372" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B372" s="3">
-        <v>4</v>
-      </c>
-      <c r="C372" s="3">
-        <v>2335.67</v>
+        <v>19</v>
+      </c>
+      <c r="C372" s="8">
+        <v>171.47</v>
       </c>
       <c r="D372" s="4" t="s">
         <v>364</v>
@@ -7089,13 +7095,13 @@
     </row>
     <row r="373" spans="1:4">
       <c r="A373" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B373" s="3">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C373" s="3">
-        <v>66.180000000000007</v>
+        <v>212.75</v>
       </c>
       <c r="D373" s="4" t="s">
         <v>364</v>
@@ -7103,13 +7109,13 @@
     </row>
     <row r="374" spans="1:4">
       <c r="A374" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B374" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C374" s="3">
-        <v>8139.6</v>
+        <v>2335.67</v>
       </c>
       <c r="D374" s="4" t="s">
         <v>364</v>
@@ -7117,13 +7123,13 @@
     </row>
     <row r="375" spans="1:4">
       <c r="A375" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B375" s="3">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C375" s="3">
-        <v>259.81</v>
+        <v>66.180000000000007</v>
       </c>
       <c r="D375" s="4" t="s">
         <v>364</v>
@@ -7131,13 +7137,13 @@
     </row>
     <row r="376" spans="1:4">
       <c r="A376" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B376" s="3">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="C376" s="3">
-        <v>259.8</v>
+        <v>8139.6</v>
       </c>
       <c r="D376" s="4" t="s">
         <v>364</v>
@@ -7145,13 +7151,13 @@
     </row>
     <row r="377" spans="1:4">
       <c r="A377" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B377" s="3">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="C377" s="3">
-        <v>310.2</v>
+        <v>259.81</v>
       </c>
       <c r="D377" s="4" t="s">
         <v>364</v>
@@ -7159,13 +7165,13 @@
     </row>
     <row r="378" spans="1:4">
       <c r="A378" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B378" s="3">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C378" s="3">
-        <v>36.43</v>
+        <v>259.8</v>
       </c>
       <c r="D378" s="4" t="s">
         <v>364</v>
@@ -7173,13 +7179,13 @@
     </row>
     <row r="379" spans="1:4">
       <c r="A379" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B379" s="3">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="C379" s="3">
-        <v>87.22</v>
+        <v>310.2</v>
       </c>
       <c r="D379" s="4" t="s">
         <v>364</v>
@@ -7187,13 +7193,13 @@
     </row>
     <row r="380" spans="1:4">
       <c r="A380" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B380" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C380" s="3">
-        <v>319.60000000000002</v>
+        <v>36.43</v>
       </c>
       <c r="D380" s="4" t="s">
         <v>364</v>
@@ -7201,13 +7207,13 @@
     </row>
     <row r="381" spans="1:4">
       <c r="A381" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B381" s="3">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C381" s="3">
-        <v>62.6</v>
+        <v>87.22</v>
       </c>
       <c r="D381" s="4" t="s">
         <v>364</v>
@@ -7215,13 +7221,13 @@
     </row>
     <row r="382" spans="1:4">
       <c r="A382" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B382" s="3">
-        <v>8</v>
-      </c>
-      <c r="C382" s="8">
-        <v>385.25</v>
+        <v>0</v>
+      </c>
+      <c r="C382" s="3">
+        <v>319.60000000000002</v>
       </c>
       <c r="D382" s="4" t="s">
         <v>364</v>
@@ -7229,69 +7235,69 @@
     </row>
     <row r="383" spans="1:4">
       <c r="A383" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B383" s="3">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C383" s="3">
-        <v>81.760000000000005</v>
+        <v>62.6</v>
       </c>
       <c r="D383" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="384" spans="1:4">
       <c r="A384" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B384" s="3">
-        <v>4</v>
-      </c>
-      <c r="C384" s="3">
-        <v>1138.5</v>
+        <v>8</v>
+      </c>
+      <c r="C384" s="8">
+        <v>385.25</v>
       </c>
       <c r="D384" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="385" spans="1:4">
       <c r="A385" t="s">
-        <v>350</v>
+        <v>318</v>
       </c>
       <c r="B385" s="3">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C385" s="3">
-        <v>58.69</v>
+        <v>81.760000000000005</v>
       </c>
       <c r="D385" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="386" spans="1:4">
       <c r="A386" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="B386" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C386" s="3">
-        <v>289.33999999999997</v>
+        <v>1138.5</v>
       </c>
       <c r="D386" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="387" spans="1:4">
       <c r="A387" t="s">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="B387" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C387" s="3">
-        <v>48.76</v>
+        <v>58.69</v>
       </c>
       <c r="D387" s="4" t="s">
         <v>364</v>
@@ -7299,13 +7305,13 @@
     </row>
     <row r="388" spans="1:4">
       <c r="A388" t="s">
-        <v>321</v>
+        <v>351</v>
       </c>
       <c r="B388" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C388" s="3">
-        <v>242.34</v>
+        <v>289.33999999999997</v>
       </c>
       <c r="D388" s="4" t="s">
         <v>364</v>
@@ -7313,13 +7319,13 @@
     </row>
     <row r="389" spans="1:4">
       <c r="A389" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B389" s="3">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="C389" s="3">
-        <v>65.599999999999994</v>
+        <v>48.76</v>
       </c>
       <c r="D389" s="4" t="s">
         <v>364</v>
@@ -7327,13 +7333,13 @@
     </row>
     <row r="390" spans="1:4">
       <c r="A390" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B390" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C390" s="3">
-        <v>255.03</v>
+        <v>242.34</v>
       </c>
       <c r="D390" s="4" t="s">
         <v>364</v>
@@ -7341,13 +7347,13 @@
     </row>
     <row r="391" spans="1:4">
       <c r="A391" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B391" s="3">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C391" s="3">
-        <v>220.8</v>
+        <v>65.599999999999994</v>
       </c>
       <c r="D391" s="4" t="s">
         <v>364</v>
@@ -7355,13 +7361,13 @@
     </row>
     <row r="392" spans="1:4">
       <c r="A392" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B392" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C392" s="3">
-        <v>255.02</v>
+        <v>255.03</v>
       </c>
       <c r="D392" s="4" t="s">
         <v>364</v>
@@ -7369,13 +7375,13 @@
     </row>
     <row r="393" spans="1:4">
       <c r="A393" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B393" s="3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C393" s="3">
-        <v>68.86</v>
+        <v>220.8</v>
       </c>
       <c r="D393" s="4" t="s">
         <v>364</v>
@@ -7383,13 +7389,13 @@
     </row>
     <row r="394" spans="1:4">
       <c r="A394" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B394" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C394" s="3">
-        <v>344.28</v>
+        <v>255.02</v>
       </c>
       <c r="D394" s="4" t="s">
         <v>364</v>
@@ -7397,13 +7403,13 @@
     </row>
     <row r="395" spans="1:4">
       <c r="A395" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B395" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C395" s="3">
-        <v>60.29</v>
+        <v>68.86</v>
       </c>
       <c r="D395" s="4" t="s">
         <v>364</v>
@@ -7411,13 +7417,13 @@
     </row>
     <row r="396" spans="1:4">
       <c r="A396" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B396" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C396" s="3">
-        <v>261.8</v>
+        <v>344.28</v>
       </c>
       <c r="D396" s="4" t="s">
         <v>364</v>
@@ -7425,69 +7431,69 @@
     </row>
     <row r="397" spans="1:4">
       <c r="A397" t="s">
-        <v>382</v>
+        <v>328</v>
       </c>
       <c r="B397" s="3">
         <v>2</v>
       </c>
       <c r="C397" s="3">
-        <v>30.58</v>
+        <v>60.29</v>
       </c>
       <c r="D397" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="398" spans="1:4">
       <c r="A398" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B398" s="3">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="C398" s="3">
-        <v>16.95</v>
+        <v>261.8</v>
       </c>
       <c r="D398" s="4" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="399" spans="1:4">
       <c r="A399" t="s">
-        <v>331</v>
+        <v>382</v>
       </c>
       <c r="B399" s="3">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C399" s="3">
-        <v>24.95</v>
+        <v>30.58</v>
       </c>
       <c r="D399" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="400" spans="1:4">
       <c r="A400" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B400" s="3">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="C400" s="3">
-        <v>641.49</v>
+        <v>16.95</v>
       </c>
       <c r="D400" s="4" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
     </row>
     <row r="401" spans="1:4">
       <c r="A401" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B401" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C401" s="3">
-        <v>39.57</v>
+        <v>24.95</v>
       </c>
       <c r="D401" s="4" t="s">
         <v>367</v>
@@ -7495,13 +7501,13 @@
     </row>
     <row r="402" spans="1:4">
       <c r="A402" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B402" s="3">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="C402" s="3">
-        <v>51.83</v>
+        <v>641.49</v>
       </c>
       <c r="D402" s="4" t="s">
         <v>367</v>
@@ -7509,41 +7515,41 @@
     </row>
     <row r="403" spans="1:4">
       <c r="A403" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B403" s="3">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C403" s="3">
-        <v>33.840000000000003</v>
+        <v>39.57</v>
       </c>
       <c r="D403" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="404" spans="1:4">
       <c r="A404" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B404" s="3">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C404" s="3">
-        <v>150.15</v>
+        <v>51.83</v>
       </c>
       <c r="D404" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="405" spans="1:4">
       <c r="A405" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B405" s="3">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C405" s="3">
-        <v>144.5</v>
+        <v>33.840000000000003</v>
       </c>
       <c r="D405" s="4" t="s">
         <v>364</v>
@@ -7551,13 +7557,13 @@
     </row>
     <row r="406" spans="1:4">
       <c r="A406" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B406" s="3">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C406" s="3">
-        <v>100.93</v>
+        <v>150.15</v>
       </c>
       <c r="D406" s="4" t="s">
         <v>364</v>
@@ -7565,13 +7571,13 @@
     </row>
     <row r="407" spans="1:4">
       <c r="A407" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B407" s="3">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C407" s="3">
-        <v>124.5</v>
+        <v>144.5</v>
       </c>
       <c r="D407" s="4" t="s">
         <v>364</v>
@@ -7579,13 +7585,13 @@
     </row>
     <row r="408" spans="1:4">
       <c r="A408" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B408" s="3">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C408" s="3">
-        <v>27.21</v>
+        <v>100.93</v>
       </c>
       <c r="D408" s="4" t="s">
         <v>364</v>
@@ -7593,27 +7599,27 @@
     </row>
     <row r="409" spans="1:4">
       <c r="A409" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B409" s="3">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="C409" s="3">
-        <v>24.79</v>
+        <v>124.5</v>
       </c>
       <c r="D409" s="4" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
     </row>
     <row r="410" spans="1:4">
       <c r="A410" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B410" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C410" s="3">
-        <v>37.1</v>
+        <v>27.21</v>
       </c>
       <c r="D410" s="4" t="s">
         <v>364</v>
@@ -7621,41 +7627,41 @@
     </row>
     <row r="411" spans="1:4">
       <c r="A411" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B411" s="3">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="C411" s="3">
-        <v>178.04</v>
+        <v>24.79</v>
       </c>
       <c r="D411" s="4" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
     </row>
     <row r="412" spans="1:4">
       <c r="A412" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B412" s="3">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="C412" s="3">
-        <v>23.88</v>
+        <v>37.1</v>
       </c>
       <c r="D412" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="413" spans="1:4">
       <c r="A413" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B413" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C413" s="3">
-        <v>20.68</v>
+        <v>178.04</v>
       </c>
       <c r="D413" s="4" t="s">
         <v>364</v>
@@ -7663,27 +7669,27 @@
     </row>
     <row r="414" spans="1:4">
       <c r="A414" t="s">
-        <v>372</v>
+        <v>344</v>
       </c>
       <c r="B414" s="3">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="C414" s="3">
-        <v>97.54</v>
+        <v>23.88</v>
       </c>
       <c r="D414" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="415" spans="1:4">
       <c r="A415" t="s">
-        <v>373</v>
+        <v>345</v>
       </c>
       <c r="B415" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C415" s="3">
-        <v>304.02999999999997</v>
+        <v>20.68</v>
       </c>
       <c r="D415" s="4" t="s">
         <v>364</v>
@@ -7691,97 +7697,97 @@
     </row>
     <row r="416" spans="1:4">
       <c r="A416" t="s">
-        <v>346</v>
+        <v>372</v>
       </c>
       <c r="B416" s="3">
         <v>0</v>
       </c>
       <c r="C416" s="3">
-        <v>1934.56</v>
+        <v>97.54</v>
       </c>
       <c r="D416" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="417" spans="1:4">
       <c r="A417" t="s">
-        <v>347</v>
+        <v>373</v>
       </c>
       <c r="B417" s="3">
         <v>0</v>
       </c>
       <c r="C417" s="3">
-        <v>230.99</v>
+        <v>304.02999999999997</v>
       </c>
       <c r="D417" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="418" spans="1:4">
       <c r="A418" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B418" s="3">
         <v>0</v>
       </c>
       <c r="C418" s="3">
-        <v>33.39</v>
+        <v>1934.56</v>
       </c>
       <c r="D418" s="4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="419" spans="1:4">
       <c r="A419" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B419" s="3">
         <v>0</v>
       </c>
       <c r="C419" s="3">
-        <v>20.66</v>
+        <v>230.99</v>
       </c>
       <c r="D419" s="4" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="420" spans="1:4">
       <c r="A420" t="s">
-        <v>375</v>
+        <v>348</v>
       </c>
       <c r="B420" s="3">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="C420" s="3">
-        <v>97.5</v>
+        <v>33.39</v>
       </c>
       <c r="D420" s="4" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
     </row>
     <row r="421" spans="1:4">
       <c r="A421" t="s">
-        <v>376</v>
+        <v>349</v>
       </c>
       <c r="B421" s="3">
-        <v>302</v>
+        <v>0</v>
       </c>
       <c r="C421" s="3">
-        <v>24.7</v>
+        <v>20.66</v>
       </c>
       <c r="D421" s="4" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
     </row>
     <row r="422" spans="1:4">
       <c r="A422" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B422" s="3">
-        <v>305</v>
+        <v>24</v>
       </c>
       <c r="C422" s="3">
-        <v>35.75</v>
+        <v>97.5</v>
       </c>
       <c r="D422" s="4" t="s">
         <v>374</v>
@@ -7789,13 +7795,13 @@
     </row>
     <row r="423" spans="1:4">
       <c r="A423" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B423" s="3">
-        <v>93</v>
+        <v>302</v>
       </c>
       <c r="C423" s="3">
-        <v>9.1</v>
+        <v>24.7</v>
       </c>
       <c r="D423" s="4" t="s">
         <v>374</v>
@@ -7803,13 +7809,13 @@
     </row>
     <row r="424" spans="1:4">
       <c r="A424" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B424" s="3">
-        <v>152</v>
+        <v>305</v>
       </c>
       <c r="C424" s="3">
-        <v>5.43</v>
+        <v>35.75</v>
       </c>
       <c r="D424" s="4" t="s">
         <v>374</v>
@@ -7817,13 +7823,13 @@
     </row>
     <row r="425" spans="1:4">
       <c r="A425" t="s">
-        <v>432</v>
+        <v>378</v>
       </c>
       <c r="B425" s="3">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="C425" s="3">
-        <v>11.99</v>
+        <v>9.1</v>
       </c>
       <c r="D425" s="4" t="s">
         <v>374</v>
@@ -7831,41 +7837,41 @@
     </row>
     <row r="426" spans="1:4">
       <c r="A426" t="s">
-        <v>414</v>
+        <v>379</v>
       </c>
       <c r="B426" s="3">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="C426" s="3">
-        <v>9.75</v>
+        <v>5.43</v>
       </c>
       <c r="D426" s="4" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="427" spans="1:4">
       <c r="A427" t="s">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="B427" s="3">
-        <v>11</v>
+        <v>125</v>
       </c>
       <c r="C427" s="3">
-        <v>6.37</v>
+        <v>11.99</v>
       </c>
       <c r="D427" s="4" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="428" spans="1:4">
       <c r="A428" t="s">
-        <v>433</v>
+        <v>414</v>
       </c>
       <c r="B428" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C428" s="3">
-        <v>10.53</v>
+        <v>9.75</v>
       </c>
       <c r="D428" s="4" t="s">
         <v>380</v>
@@ -7873,41 +7879,41 @@
     </row>
     <row r="429" spans="1:4">
       <c r="A429" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B429" s="3">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C429" s="3">
-        <v>11.59</v>
+        <v>6.37</v>
       </c>
       <c r="D429" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="430" spans="1:4">
       <c r="A430" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B430" s="3">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C430" s="3">
-        <v>12.09</v>
+        <v>10.53</v>
       </c>
       <c r="D430" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="431" spans="1:4">
       <c r="A431" t="s">
-        <v>435</v>
+        <v>416</v>
       </c>
       <c r="B431" s="3">
-        <v>182</v>
+        <v>18</v>
       </c>
       <c r="C431" s="3">
-        <v>12.09</v>
+        <v>11.59</v>
       </c>
       <c r="D431" s="4" t="s">
         <v>381</v>
@@ -7915,13 +7921,13 @@
     </row>
     <row r="432" spans="1:4">
       <c r="A432" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B432" s="3">
-        <v>184</v>
+        <v>36</v>
       </c>
       <c r="C432" s="3">
-        <v>6.5</v>
+        <v>12.09</v>
       </c>
       <c r="D432" s="4" t="s">
         <v>381</v>
@@ -7929,13 +7935,13 @@
     </row>
     <row r="433" spans="1:4">
       <c r="A433" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B433" s="3">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="C433" s="3">
-        <v>6.5</v>
+        <v>12.09</v>
       </c>
       <c r="D433" s="4" t="s">
         <v>381</v>
@@ -7943,41 +7949,41 @@
     </row>
     <row r="434" spans="1:4">
       <c r="A434" t="s">
-        <v>451</v>
+        <v>436</v>
       </c>
       <c r="B434" s="3">
-        <v>2</v>
+        <v>184</v>
       </c>
       <c r="C434" s="3">
-        <v>5017</v>
+        <v>6.5</v>
       </c>
       <c r="D434" s="4" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
     </row>
     <row r="435" spans="1:4">
       <c r="A435" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="B435" s="3">
-        <v>7</v>
+        <v>174</v>
       </c>
       <c r="C435" s="3">
-        <v>4437.1499999999996</v>
+        <v>6.5</v>
       </c>
       <c r="D435" s="4" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
     </row>
     <row r="436" spans="1:4">
       <c r="A436" t="s">
-        <v>429</v>
+        <v>451</v>
       </c>
       <c r="B436" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C436" s="3">
-        <v>6239.83</v>
+        <v>5017</v>
       </c>
       <c r="D436" s="4" t="s">
         <v>364</v>
@@ -7985,13 +7991,13 @@
     </row>
     <row r="437" spans="1:4">
       <c r="A437" t="s">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="B437" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C437" s="3">
-        <v>5980</v>
+        <v>4437.1499999999996</v>
       </c>
       <c r="D437" s="4" t="s">
         <v>364</v>
@@ -7999,13 +8005,13 @@
     </row>
     <row r="438" spans="1:4">
       <c r="A438" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B438" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C438" s="3">
-        <v>3556.4</v>
+        <v>6239.83</v>
       </c>
       <c r="D438" s="4" t="s">
         <v>364</v>
@@ -8013,13 +8019,13 @@
     </row>
     <row r="439" spans="1:4">
       <c r="A439" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="B439" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C439" s="3">
-        <v>6463</v>
+        <v>5980</v>
       </c>
       <c r="D439" s="4" t="s">
         <v>364</v>
@@ -8027,13 +8033,13 @@
     </row>
     <row r="440" spans="1:4">
       <c r="A440" t="s">
-        <v>450</v>
+        <v>428</v>
       </c>
       <c r="B440" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C440" s="3">
-        <v>5199</v>
+        <v>3556.4</v>
       </c>
       <c r="D440" s="4" t="s">
         <v>364</v>
@@ -8041,55 +8047,55 @@
     </row>
     <row r="441" spans="1:4">
       <c r="A441" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="B441" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C441" s="3">
-        <v>45</v>
+        <v>6463</v>
       </c>
       <c r="D441" s="4" t="s">
-        <v>453</v>
+        <v>364</v>
       </c>
     </row>
     <row r="442" spans="1:4">
       <c r="A442" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="B442" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C442" s="3">
-        <v>70.25</v>
+        <v>5199</v>
       </c>
       <c r="D442" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="443" spans="1:4">
       <c r="A443" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B443" s="3">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="C443" s="3">
-        <v>58.9</v>
+        <v>45</v>
       </c>
       <c r="D443" s="4" t="s">
-        <v>367</v>
+        <v>453</v>
       </c>
     </row>
     <row r="444" spans="1:4">
       <c r="A444" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B444" s="3">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="C444" s="3">
-        <v>89.21</v>
+        <v>70.25</v>
       </c>
       <c r="D444" s="4" t="s">
         <v>367</v>
@@ -8097,13 +8103,13 @@
     </row>
     <row r="445" spans="1:4">
       <c r="A445" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B445" s="3">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="C445" s="3">
-        <v>59.18</v>
+        <v>58.9</v>
       </c>
       <c r="D445" s="4" t="s">
         <v>367</v>
@@ -8111,13 +8117,13 @@
     </row>
     <row r="446" spans="1:4">
       <c r="A446" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B446" s="3">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C446" s="3">
-        <v>60.62</v>
+        <v>89.21</v>
       </c>
       <c r="D446" s="4" t="s">
         <v>367</v>
@@ -8125,13 +8131,13 @@
     </row>
     <row r="447" spans="1:4">
       <c r="A447" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B447" s="3">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="C447" s="3">
-        <v>3431.7</v>
+        <v>59.18</v>
       </c>
       <c r="D447" s="4" t="s">
         <v>367</v>
@@ -8139,13 +8145,13 @@
     </row>
     <row r="448" spans="1:4">
       <c r="A448" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B448" s="3">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="C448" s="3">
-        <v>1260.2</v>
+        <v>60.62</v>
       </c>
       <c r="D448" s="4" t="s">
         <v>367</v>
@@ -8153,13 +8159,13 @@
     </row>
     <row r="449" spans="1:4">
       <c r="A449" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B449" s="3">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="C449" s="3">
-        <v>47.2</v>
+        <v>3431.7</v>
       </c>
       <c r="D449" s="4" t="s">
         <v>367</v>
@@ -8167,13 +8173,13 @@
     </row>
     <row r="450" spans="1:4">
       <c r="A450" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="B450" s="3">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="C450" s="3">
-        <v>71.760000000000005</v>
+        <v>1260.2</v>
       </c>
       <c r="D450" s="4" t="s">
         <v>367</v>
@@ -8181,15 +8187,43 @@
     </row>
     <row r="451" spans="1:4">
       <c r="A451" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B451" s="3">
         <v>34</v>
       </c>
       <c r="C451" s="3">
+        <v>47.2</v>
+      </c>
+      <c r="D451" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4">
+      <c r="A452" t="s">
+        <v>467</v>
+      </c>
+      <c r="B452" s="3">
+        <v>60</v>
+      </c>
+      <c r="C452" s="3">
+        <v>71.760000000000005</v>
+      </c>
+      <c r="D452" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4">
+      <c r="A453" t="s">
+        <v>469</v>
+      </c>
+      <c r="B453" s="3">
+        <v>34</v>
+      </c>
+      <c r="C453" s="3">
         <v>45</v>
       </c>
-      <c r="D451" s="4" t="s">
+      <c r="D453" s="4" t="s">
         <v>453</v>
       </c>
     </row>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="474">
   <si>
     <t>Denumire produs</t>
   </si>
@@ -1433,6 +1433,9 @@
   </si>
   <si>
     <t>RAV Spuma activa de curatare 0.5L PROMO</t>
+  </si>
+  <si>
+    <t>CYC PRO V1 5W30 LL CART 5L</t>
   </si>
 </sst>
 </file>
@@ -1877,7 +1880,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D453"/>
+  <dimension ref="A1:D454"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="49.85546875" customWidth="1"/>
@@ -1960,7 +1963,7 @@
         <v>392</v>
       </c>
       <c r="B6" s="3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C6" s="9">
         <v>269.10000000000002</v>
@@ -1988,7 +1991,7 @@
         <v>406</v>
       </c>
       <c r="B8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" s="3">
         <v>635.11</v>
@@ -2226,7 +2229,7 @@
         <v>401</v>
       </c>
       <c r="B25" s="3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C25" s="3">
         <v>381.54</v>
@@ -2366,7 +2369,7 @@
         <v>425</v>
       </c>
       <c r="B35" s="3">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C35" s="3">
         <v>42.7</v>
@@ -2954,7 +2957,7 @@
         <v>38</v>
       </c>
       <c r="B77" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C77" s="3">
         <v>103.51</v>
@@ -3091,27 +3094,27 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>40</v>
+        <v>473</v>
       </c>
       <c r="B87" s="3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C87" s="3">
-        <v>25.4</v>
+        <v>137.16</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>366</v>
+        <v>389</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B88" s="3">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C88" s="3">
-        <v>40.92</v>
+        <v>25.4</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>366</v>
@@ -3119,13 +3122,13 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B89" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C89" s="3">
-        <v>25.4</v>
+        <v>40.92</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>366</v>
@@ -3133,13 +3136,13 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B90" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C90" s="3">
-        <v>28.07</v>
+        <v>25.4</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>366</v>
@@ -3147,13 +3150,13 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>384</v>
+        <v>43</v>
       </c>
       <c r="B91" s="3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C91" s="3">
-        <v>23.33</v>
+        <v>28.07</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>366</v>
@@ -3161,41 +3164,41 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>44</v>
+        <v>384</v>
       </c>
       <c r="B92" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C92" s="3">
-        <v>34.630000000000003</v>
+        <v>23.33</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B93" s="3">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="C93" s="3">
-        <v>18.37</v>
+        <v>34.630000000000003</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B94" s="3">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="C94" s="3">
-        <v>82.88</v>
+        <v>18.37</v>
       </c>
       <c r="D94" s="4" t="s">
         <v>369</v>
@@ -3203,13 +3206,13 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B95" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C95" s="3">
-        <v>161.01</v>
+        <v>82.88</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>369</v>
@@ -3217,13 +3220,13 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B96" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C96" s="3">
-        <v>50.23</v>
+        <v>161.01</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>369</v>
@@ -3231,55 +3234,55 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B97" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C97" s="3">
-        <v>65.83</v>
+        <v>50.23</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B98" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C98" s="3">
-        <v>46.76</v>
+        <v>65.83</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B99" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C99" s="3">
-        <v>62.11</v>
+        <v>46.76</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B100" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C100" s="3">
-        <v>47.61</v>
+        <v>62.11</v>
       </c>
       <c r="D100" s="4" t="s">
         <v>367</v>
@@ -3287,13 +3290,13 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B101" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C101" s="3">
-        <v>63.76</v>
+        <v>47.61</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>367</v>
@@ -3301,13 +3304,13 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B102" s="3">
         <v>1</v>
       </c>
       <c r="C102" s="3">
-        <v>1159.2</v>
+        <v>63.76</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>367</v>
@@ -3315,13 +3318,13 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B103" s="3">
         <v>1</v>
       </c>
       <c r="C103" s="3">
-        <v>255</v>
+        <v>1159.2</v>
       </c>
       <c r="D103" s="4" t="s">
         <v>367</v>
@@ -3329,13 +3332,13 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B104" s="3">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C104" s="3">
-        <v>69.55</v>
+        <v>255</v>
       </c>
       <c r="D104" s="4" t="s">
         <v>367</v>
@@ -3343,13 +3346,13 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B105" s="3">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C105" s="3">
-        <v>1391.04</v>
+        <v>69.55</v>
       </c>
       <c r="D105" s="4" t="s">
         <v>367</v>
@@ -3357,13 +3360,13 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B106" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C106" s="3">
-        <v>87.1</v>
+        <v>1391.04</v>
       </c>
       <c r="D106" s="4" t="s">
         <v>367</v>
@@ -3371,13 +3374,13 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B107" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C107" s="3">
-        <v>40.54</v>
+        <v>87.1</v>
       </c>
       <c r="D107" s="4" t="s">
         <v>367</v>
@@ -3385,13 +3388,13 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B108" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C108" s="3">
-        <v>460.01</v>
+        <v>40.54</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>367</v>
@@ -3405,7 +3408,7 @@
         <v>1</v>
       </c>
       <c r="C109" s="3">
-        <v>639.4</v>
+        <v>460.01</v>
       </c>
       <c r="D109" s="4" t="s">
         <v>367</v>
@@ -3413,13 +3416,13 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B110" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C110" s="3">
-        <v>103.89</v>
+        <v>639.4</v>
       </c>
       <c r="D110" s="4" t="s">
         <v>367</v>
@@ -3427,13 +3430,13 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B111" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C111" s="3">
-        <v>58.48</v>
+        <v>103.89</v>
       </c>
       <c r="D111" s="4" t="s">
         <v>367</v>
@@ -3441,13 +3444,13 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B112" s="3">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="C112" s="3">
-        <v>56.93</v>
+        <v>58.48</v>
       </c>
       <c r="D112" s="4" t="s">
         <v>367</v>
@@ -3458,10 +3461,10 @@
         <v>63</v>
       </c>
       <c r="B113" s="3">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C113" s="3">
-        <v>63.76</v>
+        <v>56.93</v>
       </c>
       <c r="D113" s="4" t="s">
         <v>367</v>
@@ -3469,13 +3472,13 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B114" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C114" s="3">
-        <v>61.92</v>
+        <v>63.76</v>
       </c>
       <c r="D114" s="4" t="s">
         <v>367</v>
@@ -3483,13 +3486,13 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B115" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C115" s="3">
-        <v>63.76</v>
+        <v>61.92</v>
       </c>
       <c r="D115" s="4" t="s">
         <v>367</v>
@@ -3497,13 +3500,13 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B116" s="3">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C116" s="3">
-        <v>69.56</v>
+        <v>63.76</v>
       </c>
       <c r="D116" s="4" t="s">
         <v>367</v>
@@ -3511,13 +3514,13 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B117" s="3">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C117" s="3">
-        <v>59.68</v>
+        <v>69.56</v>
       </c>
       <c r="D117" s="4" t="s">
         <v>367</v>
@@ -3525,13 +3528,13 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B118" s="3">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C118" s="3">
-        <v>56.93</v>
+        <v>59.68</v>
       </c>
       <c r="D118" s="4" t="s">
         <v>367</v>
@@ -3539,13 +3542,13 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B119" s="3">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="C119" s="3">
-        <v>80.73</v>
+        <v>56.93</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>367</v>
@@ -3553,13 +3556,13 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B120" s="3">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C120" s="3">
-        <v>103.09</v>
+        <v>80.73</v>
       </c>
       <c r="D120" s="4" t="s">
         <v>367</v>
@@ -3567,13 +3570,13 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B121" s="3">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C121" s="3">
-        <v>119.03</v>
+        <v>103.09</v>
       </c>
       <c r="D121" s="4" t="s">
         <v>367</v>
@@ -3581,13 +3584,13 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B122" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C122" s="3">
-        <v>63.76</v>
+        <v>119.03</v>
       </c>
       <c r="D122" s="4" t="s">
         <v>367</v>
@@ -3595,10 +3598,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B123" s="3">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C123" s="3">
         <v>63.76</v>
@@ -3609,13 +3612,13 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B124" s="3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C124" s="3">
-        <v>81.150000000000006</v>
+        <v>63.76</v>
       </c>
       <c r="D124" s="4" t="s">
         <v>367</v>
@@ -3623,13 +3626,13 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B125" s="3">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C125" s="3">
-        <v>63.76</v>
+        <v>81.150000000000006</v>
       </c>
       <c r="D125" s="4" t="s">
         <v>367</v>
@@ -3637,13 +3640,13 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B126" s="3">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C126" s="3">
-        <v>69.87</v>
+        <v>63.76</v>
       </c>
       <c r="D126" s="4" t="s">
         <v>367</v>
@@ -3651,13 +3654,13 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B127" s="3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C127" s="3">
-        <v>63.76</v>
+        <v>69.87</v>
       </c>
       <c r="D127" s="4" t="s">
         <v>367</v>
@@ -3665,13 +3668,13 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B128" s="3">
-        <v>6</v>
-      </c>
-      <c r="C128" s="8">
-        <v>79.91</v>
+        <v>14</v>
+      </c>
+      <c r="C128" s="3">
+        <v>63.76</v>
       </c>
       <c r="D128" s="4" t="s">
         <v>367</v>
@@ -3679,13 +3682,13 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B129" s="3">
         <v>6</v>
       </c>
-      <c r="C129" s="3">
-        <v>69.56</v>
+      <c r="C129" s="8">
+        <v>79.91</v>
       </c>
       <c r="D129" s="4" t="s">
         <v>367</v>
@@ -3693,13 +3696,13 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B130" s="3">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="C130" s="3">
-        <v>52.17</v>
+        <v>69.56</v>
       </c>
       <c r="D130" s="4" t="s">
         <v>367</v>
@@ -3707,13 +3710,13 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B131" s="3">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="C131" s="3">
-        <v>208.66</v>
+        <v>52.17</v>
       </c>
       <c r="D131" s="4" t="s">
         <v>367</v>
@@ -3721,13 +3724,13 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B132" s="3">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C132" s="3">
-        <v>88.87</v>
+        <v>208.66</v>
       </c>
       <c r="D132" s="4" t="s">
         <v>367</v>
@@ -3735,13 +3738,13 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B133" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C133" s="3">
-        <v>67.27</v>
+        <v>88.87</v>
       </c>
       <c r="D133" s="4" t="s">
         <v>367</v>
@@ -3749,13 +3752,13 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B134" s="3">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C134" s="3">
-        <v>69.55</v>
+        <v>67.27</v>
       </c>
       <c r="D134" s="4" t="s">
         <v>367</v>
@@ -3763,13 +3766,13 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B135" s="3">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="C135" s="3">
-        <v>78.84</v>
+        <v>69.55</v>
       </c>
       <c r="D135" s="4" t="s">
         <v>367</v>
@@ -3777,13 +3780,13 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B136" s="3">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="C136" s="3">
-        <v>149.91</v>
+        <v>78.84</v>
       </c>
       <c r="D136" s="4" t="s">
         <v>367</v>
@@ -3791,13 +3794,13 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B137" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C137" s="3">
-        <v>38.57</v>
+        <v>149.91</v>
       </c>
       <c r="D137" s="4" t="s">
         <v>367</v>
@@ -3805,13 +3808,13 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B138" s="3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C138" s="3">
-        <v>299</v>
+        <v>38.57</v>
       </c>
       <c r="D138" s="4" t="s">
         <v>367</v>
@@ -3819,16 +3822,16 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B139" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C139" s="3">
-        <v>58.24</v>
+        <v>299</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3836,10 +3839,10 @@
         <v>89</v>
       </c>
       <c r="B140" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C140" s="3">
-        <v>65.23</v>
+        <v>58.24</v>
       </c>
       <c r="D140" s="4" t="s">
         <v>364</v>
@@ -3847,13 +3850,13 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B141" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C141" s="3">
-        <v>290.95</v>
+        <v>65.23</v>
       </c>
       <c r="D141" s="4" t="s">
         <v>364</v>
@@ -3864,10 +3867,10 @@
         <v>90</v>
       </c>
       <c r="B142" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C142" s="3">
-        <v>325.87</v>
+        <v>290.95</v>
       </c>
       <c r="D142" s="4" t="s">
         <v>364</v>
@@ -3875,27 +3878,27 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B143" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C143" s="3">
-        <v>5165.8</v>
+        <v>325.87</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B144" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C144" s="3">
-        <v>511.75</v>
+        <v>5165.8</v>
       </c>
       <c r="D144" s="4" t="s">
         <v>367</v>
@@ -3903,13 +3906,13 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B145" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C145" s="3">
-        <v>572.70000000000005</v>
+        <v>511.75</v>
       </c>
       <c r="D145" s="4" t="s">
         <v>367</v>
@@ -3917,55 +3920,55 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B146" s="3">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="C146" s="3">
-        <v>66.98</v>
+        <v>572.70000000000005</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B147" s="3">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="C147" s="3">
-        <v>367.42</v>
+        <v>66.98</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B148" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C148" s="3">
-        <v>51.52</v>
+        <v>367.42</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B149" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C149" s="3">
-        <v>23.19</v>
+        <v>51.52</v>
       </c>
       <c r="D149" s="4" t="s">
         <v>366</v>
@@ -3973,10 +3976,10 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B150" s="3">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C150" s="3">
         <v>23.19</v>
@@ -3987,27 +3990,27 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B151" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C151" s="3">
-        <v>69.55</v>
+        <v>23.19</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B152" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C152" s="3">
-        <v>3169.7</v>
+        <v>69.55</v>
       </c>
       <c r="D152" s="4" t="s">
         <v>367</v>
@@ -4015,13 +4018,13 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B153" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C153" s="3">
-        <v>81.14</v>
+        <v>3169.7</v>
       </c>
       <c r="D153" s="4" t="s">
         <v>367</v>
@@ -4029,10 +4032,10 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B154" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C154" s="3">
         <v>81.14</v>
@@ -4043,41 +4046,41 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B155" s="3">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C155" s="3">
-        <v>66.98</v>
+        <v>81.14</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B156" s="3">
-        <v>30</v>
-      </c>
-      <c r="C156" s="8">
-        <v>77.63</v>
+        <v>58</v>
+      </c>
+      <c r="C156" s="3">
+        <v>66.98</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B157" s="3">
-        <v>26</v>
-      </c>
-      <c r="C157" s="3">
-        <v>93.35</v>
+        <v>30</v>
+      </c>
+      <c r="C157" s="8">
+        <v>77.63</v>
       </c>
       <c r="D157" s="4" t="s">
         <v>367</v>
@@ -4085,13 +4088,13 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C158" s="3">
-        <v>1217.1600000000001</v>
+        <v>93.35</v>
       </c>
       <c r="D158" s="4" t="s">
         <v>367</v>
@@ -4099,13 +4102,13 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B159" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C159" s="3">
-        <v>3079</v>
+        <v>1217.1600000000001</v>
       </c>
       <c r="D159" s="4" t="s">
         <v>367</v>
@@ -4113,16 +4116,16 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B160" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C160" s="3">
-        <v>43.7</v>
+        <v>3079</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4130,10 +4133,10 @@
         <v>108</v>
       </c>
       <c r="B161" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C161" s="3">
-        <v>48.95</v>
+        <v>43.7</v>
       </c>
       <c r="D161" s="4" t="s">
         <v>366</v>
@@ -4141,27 +4144,27 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B162" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C162" s="3">
-        <v>72.33</v>
+        <v>48.95</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B163" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C163" s="3">
-        <v>284.19</v>
+        <v>72.33</v>
       </c>
       <c r="D163" s="4" t="s">
         <v>364</v>
@@ -4169,38 +4172,38 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B164" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C164" s="3">
-        <v>101.5</v>
+        <v>284.19</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B165" s="3">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C165" s="3">
-        <v>32.200000000000003</v>
+        <v>101.5</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B166" s="3">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="C166" s="3">
         <v>32.200000000000003</v>
@@ -4211,13 +4214,13 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B167" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C167" s="3">
-        <v>37.43</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D167" s="4" t="s">
         <v>354</v>
@@ -4225,13 +4228,13 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B168" s="3">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C168" s="3">
-        <v>32.200000000000003</v>
+        <v>37.43</v>
       </c>
       <c r="D168" s="4" t="s">
         <v>354</v>
@@ -4239,41 +4242,41 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B169" s="3">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C169" s="3">
-        <v>115.01</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B170" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C170" s="3">
-        <v>38.39</v>
+        <v>115.01</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="171" spans="1:4">
       <c r="A171" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B171" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C171" s="3">
-        <v>151.47999999999999</v>
+        <v>38.39</v>
       </c>
       <c r="D171" s="4" t="s">
         <v>364</v>
@@ -4281,13 +4284,13 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B172" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C172" s="3">
-        <v>181.68</v>
+        <v>151.47999999999999</v>
       </c>
       <c r="D172" s="4" t="s">
         <v>364</v>
@@ -4295,27 +4298,27 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B173" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C173" s="3">
-        <v>20.059999999999999</v>
+        <v>181.68</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
     </row>
     <row r="174" spans="1:4">
       <c r="A174" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B174" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C174" s="3">
-        <v>12.88</v>
+        <v>20.059999999999999</v>
       </c>
       <c r="D174" s="4" t="s">
         <v>355</v>
@@ -4323,13 +4326,13 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B175" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C175" s="3">
-        <v>26.73</v>
+        <v>12.88</v>
       </c>
       <c r="D175" s="4" t="s">
         <v>355</v>
@@ -4337,13 +4340,13 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B176" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C176" s="3">
-        <v>29.95</v>
+        <v>26.73</v>
       </c>
       <c r="D176" s="4" t="s">
         <v>355</v>
@@ -4351,13 +4354,13 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B177" s="3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C177" s="3">
-        <v>58.68</v>
+        <v>29.95</v>
       </c>
       <c r="D177" s="4" t="s">
         <v>355</v>
@@ -4365,13 +4368,13 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B178" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C178" s="3">
-        <v>79.98</v>
+        <v>58.68</v>
       </c>
       <c r="D178" s="4" t="s">
         <v>355</v>
@@ -4379,55 +4382,55 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B179" s="3">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C179" s="3">
-        <v>38.770000000000003</v>
+        <v>79.98</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="180" spans="1:4">
       <c r="A180" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B180" s="3">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C180" s="3">
-        <v>107.35</v>
+        <v>38.770000000000003</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
     </row>
     <row r="181" spans="1:4">
       <c r="A181" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B181" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C181" s="3">
-        <v>61.83</v>
+        <v>107.35</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="182" spans="1:4">
       <c r="A182" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B182" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C182" s="3">
-        <v>243.16</v>
+        <v>61.83</v>
       </c>
       <c r="D182" s="4" t="s">
         <v>364</v>
@@ -4435,41 +4438,41 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B183" s="3">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C183" s="3">
-        <v>63.78</v>
+        <v>243.16</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="184" spans="1:4">
       <c r="A184" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B184" s="3">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C184" s="3">
-        <v>75.989999999999995</v>
+        <v>63.78</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="185" spans="1:4">
       <c r="A185" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B185" s="3">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C185" s="3">
-        <v>297.64999999999998</v>
+        <v>75.989999999999995</v>
       </c>
       <c r="D185" s="4" t="s">
         <v>364</v>
@@ -4477,13 +4480,13 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B186" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C186" s="3">
-        <v>77.28</v>
+        <v>297.64999999999998</v>
       </c>
       <c r="D186" s="4" t="s">
         <v>364</v>
@@ -4491,13 +4494,13 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B187" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C187" s="3">
-        <v>75.989999999999995</v>
+        <v>77.28</v>
       </c>
       <c r="D187" s="4" t="s">
         <v>364</v>
@@ -4505,13 +4508,13 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B188" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C188" s="3">
-        <v>342.24</v>
+        <v>75.989999999999995</v>
       </c>
       <c r="D188" s="4" t="s">
         <v>364</v>
@@ -4519,27 +4522,27 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B189" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C189" s="3">
-        <v>633.75</v>
+        <v>342.24</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="190" spans="1:4">
       <c r="A190" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B190" s="3">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="C190" s="3">
-        <v>50.51</v>
+        <v>633.75</v>
       </c>
       <c r="D190" s="4" t="s">
         <v>367</v>
@@ -4547,13 +4550,13 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" t="s">
-        <v>430</v>
+        <v>137</v>
       </c>
       <c r="B191" s="3">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="C191" s="3">
-        <v>581.9</v>
+        <v>50.51</v>
       </c>
       <c r="D191" s="4" t="s">
         <v>367</v>
@@ -4561,13 +4564,13 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" t="s">
-        <v>138</v>
+        <v>430</v>
       </c>
       <c r="B192" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C192" s="3">
-        <v>579.13</v>
+        <v>581.9</v>
       </c>
       <c r="D192" s="4" t="s">
         <v>367</v>
@@ -4575,55 +4578,55 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B193" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C193" s="3">
-        <v>122.36</v>
+        <v>579.13</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="194" spans="1:4">
       <c r="A194" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B194" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C194" s="3">
-        <v>35.81</v>
+        <v>122.36</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
     </row>
     <row r="195" spans="1:4">
       <c r="A195" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B195" s="3">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C195" s="3">
-        <v>59.25</v>
+        <v>35.81</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="196" spans="1:4">
       <c r="A196" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B196" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C196" s="3">
-        <v>260.33</v>
+        <v>59.25</v>
       </c>
       <c r="D196" s="4" t="s">
         <v>364</v>
@@ -4631,13 +4634,13 @@
     </row>
     <row r="197" spans="1:4">
       <c r="A197" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B197" s="3">
-        <v>15</v>
-      </c>
-      <c r="C197" s="7">
-        <v>59.62</v>
+        <v>7</v>
+      </c>
+      <c r="C197" s="3">
+        <v>260.33</v>
       </c>
       <c r="D197" s="4" t="s">
         <v>364</v>
@@ -4645,13 +4648,13 @@
     </row>
     <row r="198" spans="1:4">
       <c r="A198" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B198" s="3">
-        <v>4</v>
-      </c>
-      <c r="C198" s="3">
-        <v>248.77</v>
+        <v>12</v>
+      </c>
+      <c r="C198" s="7">
+        <v>59.62</v>
       </c>
       <c r="D198" s="4" t="s">
         <v>364</v>
@@ -4659,13 +4662,13 @@
     </row>
     <row r="199" spans="1:4">
       <c r="A199" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B199" s="3">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C199" s="3">
-        <v>74.7</v>
+        <v>248.77</v>
       </c>
       <c r="D199" s="4" t="s">
         <v>364</v>
@@ -4673,13 +4676,13 @@
     </row>
     <row r="200" spans="1:4">
       <c r="A200" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B200" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C200" s="3">
-        <v>296.3</v>
+        <v>74.7</v>
       </c>
       <c r="D200" s="4" t="s">
         <v>364</v>
@@ -4687,13 +4690,13 @@
     </row>
     <row r="201" spans="1:4">
       <c r="A201" t="s">
-        <v>385</v>
+        <v>146</v>
       </c>
       <c r="B201" s="3">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C201" s="3">
-        <v>168.7</v>
+        <v>296.3</v>
       </c>
       <c r="D201" s="4" t="s">
         <v>364</v>
@@ -4701,13 +4704,13 @@
     </row>
     <row r="202" spans="1:4">
       <c r="A202" t="s">
-        <v>147</v>
+        <v>385</v>
       </c>
       <c r="B202" s="3">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="C202" s="3">
-        <v>44.5</v>
+        <v>168.7</v>
       </c>
       <c r="D202" s="4" t="s">
         <v>364</v>
@@ -4715,13 +4718,13 @@
     </row>
     <row r="203" spans="1:4">
       <c r="A203" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B203" s="3">
-        <v>7</v>
-      </c>
-      <c r="C203" s="10">
-        <v>210.88</v>
+        <v>26</v>
+      </c>
+      <c r="C203" s="3">
+        <v>44.5</v>
       </c>
       <c r="D203" s="4" t="s">
         <v>364</v>
@@ -4729,13 +4732,13 @@
     </row>
     <row r="204" spans="1:4">
       <c r="A204" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B204" s="3">
-        <v>2</v>
-      </c>
-      <c r="C204" s="3">
-        <v>2189.02</v>
+        <v>7</v>
+      </c>
+      <c r="C204" s="10">
+        <v>210.88</v>
       </c>
       <c r="D204" s="4" t="s">
         <v>364</v>
@@ -4743,13 +4746,13 @@
     </row>
     <row r="205" spans="1:4">
       <c r="A205" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B205" s="3">
         <v>2</v>
       </c>
       <c r="C205" s="3">
-        <v>453.22</v>
+        <v>2189.02</v>
       </c>
       <c r="D205" s="4" t="s">
         <v>364</v>
@@ -4757,13 +4760,13 @@
     </row>
     <row r="206" spans="1:4">
       <c r="A206" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B206" s="3">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C206" s="3">
-        <v>48.64</v>
+        <v>453.22</v>
       </c>
       <c r="D206" s="4" t="s">
         <v>364</v>
@@ -4771,13 +4774,13 @@
     </row>
     <row r="207" spans="1:4">
       <c r="A207" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B207" s="3">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C207" s="3">
-        <v>126.63</v>
+        <v>48.64</v>
       </c>
       <c r="D207" s="4" t="s">
         <v>364</v>
@@ -4785,41 +4788,41 @@
     </row>
     <row r="208" spans="1:4">
       <c r="A208" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B208" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C208" s="3">
-        <v>69.56</v>
+        <v>126.63</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="209" spans="1:4">
       <c r="A209" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B209" s="3">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C209" s="3">
-        <v>44.51</v>
+        <v>69.56</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="210" spans="1:4">
       <c r="A210" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B210" s="3">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C210" s="3">
-        <v>145.94</v>
+        <v>44.51</v>
       </c>
       <c r="D210" s="4" t="s">
         <v>364</v>
@@ -4827,13 +4830,13 @@
     </row>
     <row r="211" spans="1:4">
       <c r="A211" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B211" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C211" s="3">
-        <v>199.77</v>
+        <v>145.94</v>
       </c>
       <c r="D211" s="4" t="s">
         <v>364</v>
@@ -4841,13 +4844,13 @@
     </row>
     <row r="212" spans="1:4">
       <c r="A212" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B212" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C212" s="3">
-        <v>2060</v>
+        <v>199.77</v>
       </c>
       <c r="D212" s="4" t="s">
         <v>364</v>
@@ -4855,13 +4858,13 @@
     </row>
     <row r="213" spans="1:4">
       <c r="A213" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B213" s="3">
-        <v>34</v>
-      </c>
-      <c r="C213" s="8">
-        <v>58.32</v>
+        <v>0</v>
+      </c>
+      <c r="C213" s="3">
+        <v>2060</v>
       </c>
       <c r="D213" s="4" t="s">
         <v>364</v>
@@ -4869,13 +4872,13 @@
     </row>
     <row r="214" spans="1:4">
       <c r="A214" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B214" s="3">
-        <v>2</v>
-      </c>
-      <c r="C214" s="3">
-        <v>183.41</v>
+        <v>34</v>
+      </c>
+      <c r="C214" s="8">
+        <v>58.32</v>
       </c>
       <c r="D214" s="4" t="s">
         <v>364</v>
@@ -4883,13 +4886,13 @@
     </row>
     <row r="215" spans="1:4">
       <c r="A215" t="s">
-        <v>352</v>
+        <v>159</v>
       </c>
       <c r="B215" s="3">
-        <v>7</v>
-      </c>
-      <c r="C215" s="8">
-        <v>257.70999999999998</v>
+        <v>2</v>
+      </c>
+      <c r="C215" s="3">
+        <v>183.41</v>
       </c>
       <c r="D215" s="4" t="s">
         <v>364</v>
@@ -4897,41 +4900,41 @@
     </row>
     <row r="216" spans="1:4">
       <c r="A216" t="s">
-        <v>160</v>
+        <v>352</v>
       </c>
       <c r="B216" s="3">
-        <v>27</v>
-      </c>
-      <c r="C216" s="3">
-        <v>33.479999999999997</v>
+        <v>7</v>
+      </c>
+      <c r="C216" s="8">
+        <v>257.70999999999998</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="217" spans="1:4">
       <c r="A217" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B217" s="3">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C217" s="3">
-        <v>48.13</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="218" spans="1:4">
       <c r="A218" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B218" s="3">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C218" s="3">
-        <v>5400</v>
+        <v>48.13</v>
       </c>
       <c r="D218" s="4" t="s">
         <v>364</v>
@@ -4939,13 +4942,13 @@
     </row>
     <row r="219" spans="1:4">
       <c r="A219" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B219" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C219" s="3">
-        <v>170.78</v>
+        <v>5400</v>
       </c>
       <c r="D219" s="4" t="s">
         <v>364</v>
@@ -4953,13 +4956,13 @@
     </row>
     <row r="220" spans="1:4">
       <c r="A220" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B220" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C220" s="3">
-        <v>216.3</v>
+        <v>170.78</v>
       </c>
       <c r="D220" s="4" t="s">
         <v>364</v>
@@ -4967,13 +4970,13 @@
     </row>
     <row r="221" spans="1:4">
       <c r="A221" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B221" s="3">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C221" s="3">
-        <v>59.7</v>
+        <v>216.3</v>
       </c>
       <c r="D221" s="4" t="s">
         <v>364</v>
@@ -4981,13 +4984,13 @@
     </row>
     <row r="222" spans="1:4">
       <c r="A222" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B222" s="3">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C222" s="3">
-        <v>265.05</v>
+        <v>59.7</v>
       </c>
       <c r="D222" s="4" t="s">
         <v>364</v>
@@ -4995,97 +4998,97 @@
     </row>
     <row r="223" spans="1:4">
       <c r="A223" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B223" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C223" s="3">
-        <v>36.799999999999997</v>
+        <v>265.05</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="224" spans="1:4">
       <c r="A224" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B224" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C224" s="3">
-        <v>103.04</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
     </row>
     <row r="225" spans="1:4">
       <c r="A225" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B225" s="3">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="C225" s="3">
-        <v>36.75</v>
+        <v>103.04</v>
       </c>
       <c r="D225" s="4" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
     </row>
     <row r="226" spans="1:4">
       <c r="A226" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B226" s="3">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="C226" s="3">
-        <v>47.16</v>
+        <v>36.75</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
     </row>
     <row r="227" spans="1:4">
       <c r="A227" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B227" s="3">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C227" s="3">
-        <v>16.809999999999999</v>
+        <v>47.16</v>
       </c>
       <c r="D227" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="228" spans="1:4">
       <c r="A228" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B228" s="3">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C228" s="3">
-        <v>37.299999999999997</v>
+        <v>16.809999999999999</v>
       </c>
       <c r="D228" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="229" spans="1:4">
       <c r="A229" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B229" s="3">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="C229" s="3">
-        <v>126.24</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="D229" s="4" t="s">
         <v>364</v>
@@ -5093,13 +5096,13 @@
     </row>
     <row r="230" spans="1:4">
       <c r="A230" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B230" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C230" s="3">
-        <v>154.62</v>
+        <v>126.24</v>
       </c>
       <c r="D230" s="4" t="s">
         <v>364</v>
@@ -5107,13 +5110,13 @@
     </row>
     <row r="231" spans="1:4">
       <c r="A231" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B231" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C231" s="3">
-        <v>508.2</v>
+        <v>154.62</v>
       </c>
       <c r="D231" s="4" t="s">
         <v>364</v>
@@ -5121,13 +5124,13 @@
     </row>
     <row r="232" spans="1:4">
       <c r="A232" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B232" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C232" s="3">
-        <v>5069</v>
+        <v>508.2</v>
       </c>
       <c r="D232" s="4" t="s">
         <v>364</v>
@@ -5135,13 +5138,13 @@
     </row>
     <row r="233" spans="1:4">
       <c r="A233" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B233" s="3">
         <v>0</v>
       </c>
       <c r="C233" s="3">
-        <v>466.78</v>
+        <v>5069</v>
       </c>
       <c r="D233" s="4" t="s">
         <v>364</v>
@@ -5149,27 +5152,27 @@
     </row>
     <row r="234" spans="1:4">
       <c r="A234" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B234" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C234" s="3">
-        <v>57.5</v>
+        <v>466.78</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="235" spans="1:4">
       <c r="A235" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B235" s="3">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C235" s="3">
-        <v>63.13</v>
+        <v>57.5</v>
       </c>
       <c r="D235" s="4" t="s">
         <v>367</v>
@@ -5177,13 +5180,13 @@
     </row>
     <row r="236" spans="1:4">
       <c r="A236" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B236" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C236" s="3">
-        <v>20789.41</v>
+        <v>63.13</v>
       </c>
       <c r="D236" s="4" t="s">
         <v>367</v>
@@ -5197,7 +5200,7 @@
         <v>1</v>
       </c>
       <c r="C237" s="3">
-        <v>33057.85</v>
+        <v>20789.41</v>
       </c>
       <c r="D237" s="4" t="s">
         <v>367</v>
@@ -5205,13 +5208,13 @@
     </row>
     <row r="238" spans="1:4">
       <c r="A238" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B238" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C238" s="3">
-        <v>83.5</v>
+        <v>33057.85</v>
       </c>
       <c r="D238" s="4" t="s">
         <v>367</v>
@@ -5219,16 +5222,16 @@
     </row>
     <row r="239" spans="1:4">
       <c r="A239" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B239" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C239" s="3">
-        <v>45.72</v>
+        <v>83.5</v>
       </c>
       <c r="D239" s="4" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5236,10 +5239,10 @@
         <v>182</v>
       </c>
       <c r="B240" s="3">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C240" s="3">
-        <v>81.650000000000006</v>
+        <v>45.72</v>
       </c>
       <c r="D240" s="4" t="s">
         <v>419</v>
@@ -5247,13 +5250,13 @@
     </row>
     <row r="241" spans="1:4">
       <c r="A241" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B241" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C241" s="3">
-        <v>50.71</v>
+        <v>81.650000000000006</v>
       </c>
       <c r="D241" s="4" t="s">
         <v>419</v>
@@ -5261,13 +5264,13 @@
     </row>
     <row r="242" spans="1:4">
       <c r="A242" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B242" s="3">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C242" s="3">
-        <v>51.75</v>
+        <v>50.71</v>
       </c>
       <c r="D242" s="4" t="s">
         <v>419</v>
@@ -5275,13 +5278,13 @@
     </row>
     <row r="243" spans="1:4">
       <c r="A243" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B243" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C243" s="3">
-        <v>36.94</v>
+        <v>51.75</v>
       </c>
       <c r="D243" s="4" t="s">
         <v>419</v>
@@ -5289,13 +5292,13 @@
     </row>
     <row r="244" spans="1:4">
       <c r="A244" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B244" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C244" s="3">
-        <v>36.799999999999997</v>
+        <v>36.94</v>
       </c>
       <c r="D244" s="4" t="s">
         <v>419</v>
@@ -5309,7 +5312,7 @@
         <v>12</v>
       </c>
       <c r="C245" s="3">
-        <v>79.58</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D245" s="4" t="s">
         <v>419</v>
@@ -5317,27 +5320,27 @@
     </row>
     <row r="246" spans="1:4">
       <c r="A246" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B246" s="3">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C246" s="3">
-        <v>67.28</v>
+        <v>79.58</v>
       </c>
       <c r="D246" s="4" t="s">
-        <v>367</v>
+        <v>419</v>
       </c>
     </row>
     <row r="247" spans="1:4">
       <c r="A247" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B247" s="3">
-        <v>21</v>
-      </c>
-      <c r="C247" s="8">
-        <v>79.599999999999994</v>
+        <v>23</v>
+      </c>
+      <c r="C247" s="3">
+        <v>67.28</v>
       </c>
       <c r="D247" s="4" t="s">
         <v>367</v>
@@ -5345,13 +5348,13 @@
     </row>
     <row r="248" spans="1:4">
       <c r="A248" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B248" s="3">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C248" s="8">
-        <v>75.88</v>
+        <v>79.599999999999994</v>
       </c>
       <c r="D248" s="4" t="s">
         <v>367</v>
@@ -5359,13 +5362,13 @@
     </row>
     <row r="249" spans="1:4">
       <c r="A249" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B249" s="3">
-        <v>17</v>
-      </c>
-      <c r="C249" s="3">
-        <v>109.08</v>
+        <v>25</v>
+      </c>
+      <c r="C249" s="8">
+        <v>75.88</v>
       </c>
       <c r="D249" s="4" t="s">
         <v>367</v>
@@ -5373,27 +5376,27 @@
     </row>
     <row r="250" spans="1:4">
       <c r="A250" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B250" s="3">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C250" s="3">
-        <v>33.479999999999997</v>
+        <v>109.08</v>
       </c>
       <c r="D250" s="4" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
     </row>
     <row r="251" spans="1:4">
       <c r="A251" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B251" s="3">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="C251" s="3">
-        <v>422.09</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D251" s="4" t="s">
         <v>356</v>
@@ -5401,13 +5404,13 @@
     </row>
     <row r="252" spans="1:4">
       <c r="A252" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B252" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C252" s="3">
-        <v>1277.7</v>
+        <v>422.09</v>
       </c>
       <c r="D252" s="4" t="s">
         <v>356</v>
@@ -5415,27 +5418,27 @@
     </row>
     <row r="253" spans="1:4">
       <c r="A253" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B253" s="3">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C253" s="3">
-        <v>6.44</v>
+        <v>1277.7</v>
       </c>
       <c r="D253" s="4" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
     </row>
     <row r="254" spans="1:4">
       <c r="A254" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B254" s="3">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C254" s="3">
-        <v>108.2</v>
+        <v>6.44</v>
       </c>
       <c r="D254" s="4" t="s">
         <v>366</v>
@@ -5443,16 +5446,16 @@
     </row>
     <row r="255" spans="1:4">
       <c r="A255" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B255" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C255" s="3">
-        <v>4456.4799999999996</v>
+        <v>108.2</v>
       </c>
       <c r="D255" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5460,10 +5463,10 @@
         <v>196</v>
       </c>
       <c r="B256" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C256" s="3">
-        <v>7429</v>
+        <v>4456.4799999999996</v>
       </c>
       <c r="D256" s="4" t="s">
         <v>364</v>
@@ -5471,13 +5474,13 @@
     </row>
     <row r="257" spans="1:4">
       <c r="A257" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B257" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C257" s="3">
-        <v>609.5</v>
+        <v>7429</v>
       </c>
       <c r="D257" s="4" t="s">
         <v>364</v>
@@ -5485,24 +5488,24 @@
     </row>
     <row r="258" spans="1:4">
       <c r="A258" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B258" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C258" s="3">
-        <v>32.200000000000003</v>
+        <v>609.5</v>
       </c>
       <c r="D258" s="4" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
     </row>
     <row r="259" spans="1:4">
       <c r="A259" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B259" s="3">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C259" s="3">
         <v>32.200000000000003</v>
@@ -5513,10 +5516,10 @@
     </row>
     <row r="260" spans="1:4">
       <c r="A260" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B260" s="3">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C260" s="3">
         <v>32.200000000000003</v>
@@ -5527,10 +5530,10 @@
     </row>
     <row r="261" spans="1:4">
       <c r="A261" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B261" s="3">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="C261" s="3">
         <v>32.200000000000003</v>
@@ -5541,13 +5544,13 @@
     </row>
     <row r="262" spans="1:4">
       <c r="A262" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B262" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C262" s="3">
-        <v>40.4</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D262" s="4" t="s">
         <v>354</v>
@@ -5555,13 +5558,13 @@
     </row>
     <row r="263" spans="1:4">
       <c r="A263" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B263" s="3">
-        <v>173</v>
+        <v>3</v>
       </c>
       <c r="C263" s="3">
-        <v>36.06</v>
+        <v>40.4</v>
       </c>
       <c r="D263" s="4" t="s">
         <v>354</v>
@@ -5569,27 +5572,27 @@
     </row>
     <row r="264" spans="1:4">
       <c r="A264" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B264" s="3">
-        <v>1</v>
+        <v>173</v>
       </c>
       <c r="C264" s="3">
-        <v>56</v>
+        <v>36.06</v>
       </c>
       <c r="D264" s="4" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
     </row>
     <row r="265" spans="1:4">
       <c r="A265" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B265" s="3">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C265" s="3">
-        <v>57.63</v>
+        <v>56</v>
       </c>
       <c r="D265" s="4" t="s">
         <v>367</v>
@@ -5597,13 +5600,13 @@
     </row>
     <row r="266" spans="1:4">
       <c r="A266" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B266" s="3">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C266" s="3">
-        <v>60.78</v>
+        <v>57.63</v>
       </c>
       <c r="D266" s="4" t="s">
         <v>367</v>
@@ -5611,69 +5614,69 @@
     </row>
     <row r="267" spans="1:4">
       <c r="A267" t="s">
-        <v>420</v>
+        <v>206</v>
       </c>
       <c r="B267" s="3">
         <v>4</v>
       </c>
       <c r="C267" s="3">
-        <v>65</v>
+        <v>60.78</v>
       </c>
       <c r="D267" s="4" t="s">
-        <v>419</v>
+        <v>367</v>
       </c>
     </row>
     <row r="268" spans="1:4">
       <c r="A268" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B268" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C268" s="3">
-        <v>29.63</v>
+        <v>65</v>
       </c>
       <c r="D268" s="4" t="s">
-        <v>354</v>
+        <v>419</v>
       </c>
     </row>
     <row r="269" spans="1:4">
       <c r="A269" t="s">
-        <v>207</v>
+        <v>421</v>
       </c>
       <c r="B269" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C269" s="3">
-        <v>42.49</v>
+        <v>29.63</v>
       </c>
       <c r="D269" s="4" t="s">
-        <v>419</v>
+        <v>354</v>
       </c>
     </row>
     <row r="270" spans="1:4">
       <c r="A270" t="s">
-        <v>208</v>
-      </c>
-      <c r="B270" s="4">
-        <v>18</v>
-      </c>
-      <c r="C270" s="8">
-        <v>86.95</v>
+        <v>207</v>
+      </c>
+      <c r="B270" s="3">
+        <v>0</v>
+      </c>
+      <c r="C270" s="3">
+        <v>42.49</v>
       </c>
       <c r="D270" s="4" t="s">
-        <v>364</v>
+        <v>419</v>
       </c>
     </row>
     <row r="271" spans="1:4">
       <c r="A271" t="s">
-        <v>209</v>
-      </c>
-      <c r="B271" s="3">
-        <v>2</v>
+        <v>208</v>
+      </c>
+      <c r="B271" s="4">
+        <v>18</v>
       </c>
       <c r="C271" s="8">
-        <v>312.57</v>
+        <v>86.95</v>
       </c>
       <c r="D271" s="4" t="s">
         <v>364</v>
@@ -5681,13 +5684,13 @@
     </row>
     <row r="272" spans="1:4">
       <c r="A272" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B272" s="3">
-        <v>14</v>
-      </c>
-      <c r="C272" s="3">
-        <v>71.709999999999994</v>
+        <v>2</v>
+      </c>
+      <c r="C272" s="8">
+        <v>312.57</v>
       </c>
       <c r="D272" s="4" t="s">
         <v>364</v>
@@ -5695,41 +5698,41 @@
     </row>
     <row r="273" spans="1:4">
       <c r="A273" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B273" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C273" s="3">
-        <v>77.760000000000005</v>
+        <v>71.709999999999994</v>
       </c>
       <c r="D273" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="274" spans="1:4">
       <c r="A274" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B274" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C274" s="3">
-        <v>54.7</v>
+        <v>77.760000000000005</v>
       </c>
       <c r="D274" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="275" spans="1:4">
       <c r="A275" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B275" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C275" s="3">
-        <v>67.28</v>
+        <v>54.7</v>
       </c>
       <c r="D275" s="4" t="s">
         <v>364</v>
@@ -5737,13 +5740,13 @@
     </row>
     <row r="276" spans="1:4">
       <c r="A276" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B276" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C276" s="3">
-        <v>334.36</v>
+        <v>67.28</v>
       </c>
       <c r="D276" s="4" t="s">
         <v>364</v>
@@ -5751,13 +5754,13 @@
     </row>
     <row r="277" spans="1:4">
       <c r="A277" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B277" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C277" s="3">
-        <v>78.87</v>
+        <v>334.36</v>
       </c>
       <c r="D277" s="4" t="s">
         <v>364</v>
@@ -5765,13 +5768,13 @@
     </row>
     <row r="278" spans="1:4">
       <c r="A278" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B278" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C278" s="3">
-        <v>83.84</v>
+        <v>78.87</v>
       </c>
       <c r="D278" s="4" t="s">
         <v>364</v>
@@ -5779,13 +5782,13 @@
     </row>
     <row r="279" spans="1:4">
       <c r="A279" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B279" s="3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C279" s="3">
-        <v>331.2</v>
+        <v>83.84</v>
       </c>
       <c r="D279" s="4" t="s">
         <v>364</v>
@@ -5793,13 +5796,13 @@
     </row>
     <row r="280" spans="1:4">
       <c r="A280" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B280" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C280" s="3">
-        <v>79.75</v>
+        <v>331.2</v>
       </c>
       <c r="D280" s="4" t="s">
         <v>364</v>
@@ -5807,13 +5810,13 @@
     </row>
     <row r="281" spans="1:4">
       <c r="A281" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B281" s="3">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="C281" s="3">
-        <v>83.84</v>
+        <v>79.75</v>
       </c>
       <c r="D281" s="4" t="s">
         <v>364</v>
@@ -5821,13 +5824,13 @@
     </row>
     <row r="282" spans="1:4">
       <c r="A282" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B282" s="3">
-        <v>2</v>
-      </c>
-      <c r="C282" s="8">
-        <v>347.3</v>
+        <v>29</v>
+      </c>
+      <c r="C282" s="3">
+        <v>83.84</v>
       </c>
       <c r="D282" s="4" t="s">
         <v>364</v>
@@ -5840,8 +5843,8 @@
       <c r="B283" s="3">
         <v>2</v>
       </c>
-      <c r="C283" s="3">
-        <v>284</v>
+      <c r="C283" s="8">
+        <v>347.3</v>
       </c>
       <c r="D283" s="4" t="s">
         <v>364</v>
@@ -5849,27 +5852,27 @@
     </row>
     <row r="284" spans="1:4">
       <c r="A284" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B284" s="3">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C284" s="3">
-        <v>28.15</v>
+        <v>284</v>
       </c>
       <c r="D284" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="285" spans="1:4">
       <c r="A285" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B285" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C285" s="3">
-        <v>45.08</v>
+        <v>28.15</v>
       </c>
       <c r="D285" s="4" t="s">
         <v>366</v>
@@ -5877,13 +5880,13 @@
     </row>
     <row r="286" spans="1:4">
       <c r="A286" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B286" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C286" s="3">
-        <v>51.52</v>
+        <v>45.08</v>
       </c>
       <c r="D286" s="4" t="s">
         <v>366</v>
@@ -5891,27 +5894,27 @@
     </row>
     <row r="287" spans="1:4">
       <c r="A287" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B287" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C287" s="3">
-        <v>40.57</v>
+        <v>51.52</v>
       </c>
       <c r="D287" s="4" t="s">
-        <v>419</v>
+        <v>366</v>
       </c>
     </row>
     <row r="288" spans="1:4">
       <c r="A288" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B288" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C288" s="3">
-        <v>36.229999999999997</v>
+        <v>40.57</v>
       </c>
       <c r="D288" s="4" t="s">
         <v>419</v>
@@ -5919,41 +5922,41 @@
     </row>
     <row r="289" spans="1:4">
       <c r="A289" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B289" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C289" s="3">
-        <v>54.12</v>
+        <v>36.229999999999997</v>
       </c>
       <c r="D289" s="4" t="s">
-        <v>366</v>
+        <v>419</v>
       </c>
     </row>
     <row r="290" spans="1:4">
       <c r="A290" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B290" s="3">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C290" s="3">
-        <v>69.55</v>
+        <v>54.12</v>
       </c>
       <c r="D290" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="291" spans="1:4">
       <c r="A291" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B291" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C291" s="3">
-        <v>295.14999999999998</v>
+        <v>69.55</v>
       </c>
       <c r="D291" s="4" t="s">
         <v>364</v>
@@ -5961,41 +5964,41 @@
     </row>
     <row r="292" spans="1:4">
       <c r="A292" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B292" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C292" s="3">
-        <v>38.56</v>
+        <v>295.14999999999998</v>
       </c>
       <c r="D292" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="293" spans="1:4">
       <c r="A293" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B293" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C293" s="3">
-        <v>60.95</v>
+        <v>38.56</v>
       </c>
       <c r="D293" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="294" spans="1:4">
       <c r="A294" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B294" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C294" s="3">
-        <v>78.209999999999994</v>
+        <v>60.95</v>
       </c>
       <c r="D294" s="4" t="s">
         <v>367</v>
@@ -6003,27 +6006,27 @@
     </row>
     <row r="295" spans="1:4">
       <c r="A295" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B295" s="3">
-        <v>173</v>
+        <v>10</v>
       </c>
       <c r="C295" s="3">
-        <v>51.15</v>
+        <v>78.209999999999994</v>
       </c>
       <c r="D295" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="296" spans="1:4">
       <c r="A296" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B296" s="3">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="C296" s="3">
-        <v>6591.8</v>
+        <v>51.15</v>
       </c>
       <c r="D296" s="4" t="s">
         <v>364</v>
@@ -6031,13 +6034,13 @@
     </row>
     <row r="297" spans="1:4">
       <c r="A297" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B297" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C297" s="3">
-        <v>182.42</v>
+        <v>6591.8</v>
       </c>
       <c r="D297" s="4" t="s">
         <v>364</v>
@@ -6045,13 +6048,13 @@
     </row>
     <row r="298" spans="1:4">
       <c r="A298" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B298" s="3">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="C298" s="3">
-        <v>222.62</v>
+        <v>182.42</v>
       </c>
       <c r="D298" s="4" t="s">
         <v>364</v>
@@ -6059,13 +6062,13 @@
     </row>
     <row r="299" spans="1:4">
       <c r="A299" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B299" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C299" s="3">
-        <v>2314.8000000000002</v>
+        <v>222.62</v>
       </c>
       <c r="D299" s="4" t="s">
         <v>364</v>
@@ -6073,13 +6076,13 @@
     </row>
     <row r="300" spans="1:4">
       <c r="A300" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B300" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C300" s="3">
-        <v>894.8</v>
+        <v>2314.8000000000002</v>
       </c>
       <c r="D300" s="4" t="s">
         <v>364</v>
@@ -6087,27 +6090,27 @@
     </row>
     <row r="301" spans="1:4">
       <c r="A301" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B301" s="3">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="C301" s="3">
-        <v>31.6</v>
+        <v>894.8</v>
       </c>
       <c r="D301" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="302" spans="1:4">
       <c r="A302" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B302" s="3">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C302" s="3">
-        <v>77.28</v>
+        <v>31.6</v>
       </c>
       <c r="D302" s="4" t="s">
         <v>366</v>
@@ -6115,13 +6118,13 @@
     </row>
     <row r="303" spans="1:4">
       <c r="A303" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B303" s="3">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="C303" s="3">
-        <v>43.8</v>
+        <v>77.28</v>
       </c>
       <c r="D303" s="4" t="s">
         <v>366</v>
@@ -6129,13 +6132,13 @@
     </row>
     <row r="304" spans="1:4">
       <c r="A304" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B304" s="3">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C304" s="3">
-        <v>21.9</v>
+        <v>43.8</v>
       </c>
       <c r="D304" s="4" t="s">
         <v>366</v>
@@ -6143,13 +6146,13 @@
     </row>
     <row r="305" spans="1:4">
       <c r="A305" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B305" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C305" s="3">
-        <v>798.6</v>
+        <v>21.9</v>
       </c>
       <c r="D305" s="4" t="s">
         <v>366</v>
@@ -6157,13 +6160,13 @@
     </row>
     <row r="306" spans="1:4">
       <c r="A306" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B306" s="3">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="C306" s="3">
-        <v>23.19</v>
+        <v>798.6</v>
       </c>
       <c r="D306" s="4" t="s">
         <v>366</v>
@@ -6171,13 +6174,13 @@
     </row>
     <row r="307" spans="1:4">
       <c r="A307" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B307" s="3">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="C307" s="3">
-        <v>8.24</v>
+        <v>23.19</v>
       </c>
       <c r="D307" s="4" t="s">
         <v>366</v>
@@ -6185,13 +6188,13 @@
     </row>
     <row r="308" spans="1:4">
       <c r="A308" t="s">
-        <v>455</v>
+        <v>244</v>
       </c>
       <c r="B308" s="3">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="C308" s="3">
-        <v>13.72</v>
+        <v>8.24</v>
       </c>
       <c r="D308" s="4" t="s">
         <v>366</v>
@@ -6199,10 +6202,10 @@
     </row>
     <row r="309" spans="1:4">
       <c r="A309" t="s">
-        <v>245</v>
+        <v>455</v>
       </c>
       <c r="B309" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C309" s="3">
         <v>13.72</v>
@@ -6213,13 +6216,13 @@
     </row>
     <row r="310" spans="1:4">
       <c r="A310" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B310" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C310" s="3">
-        <v>31.95</v>
+        <v>13.72</v>
       </c>
       <c r="D310" s="4" t="s">
         <v>366</v>
@@ -6227,13 +6230,13 @@
     </row>
     <row r="311" spans="1:4">
       <c r="A311" t="s">
-        <v>370</v>
+        <v>246</v>
       </c>
       <c r="B311" s="3">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="C311" s="3">
-        <v>16.2</v>
+        <v>31.95</v>
       </c>
       <c r="D311" s="4" t="s">
         <v>366</v>
@@ -6241,13 +6244,13 @@
     </row>
     <row r="312" spans="1:4">
       <c r="A312" t="s">
-        <v>247</v>
+        <v>370</v>
       </c>
       <c r="B312" s="3">
-        <v>5</v>
+        <v>103</v>
       </c>
       <c r="C312" s="3">
-        <v>36.869999999999997</v>
+        <v>16.2</v>
       </c>
       <c r="D312" s="4" t="s">
         <v>366</v>
@@ -6255,13 +6258,13 @@
     </row>
     <row r="313" spans="1:4">
       <c r="A313" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B313" s="3">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C313" s="3">
-        <v>31.48</v>
+        <v>36.869999999999997</v>
       </c>
       <c r="D313" s="4" t="s">
         <v>366</v>
@@ -6269,13 +6272,13 @@
     </row>
     <row r="314" spans="1:4">
       <c r="A314" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B314" s="3">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C314" s="3">
-        <v>21.9</v>
+        <v>31.48</v>
       </c>
       <c r="D314" s="4" t="s">
         <v>366</v>
@@ -6283,13 +6286,13 @@
     </row>
     <row r="315" spans="1:4">
       <c r="A315" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B315" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C315" s="3">
-        <v>23.19</v>
+        <v>21.9</v>
       </c>
       <c r="D315" s="4" t="s">
         <v>366</v>
@@ -6297,13 +6300,13 @@
     </row>
     <row r="316" spans="1:4">
       <c r="A316" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B316" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C316" s="3">
-        <v>19.55</v>
+        <v>23.19</v>
       </c>
       <c r="D316" s="4" t="s">
         <v>366</v>
@@ -6311,13 +6314,13 @@
     </row>
     <row r="317" spans="1:4">
       <c r="A317" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B317" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C317" s="3">
-        <v>19.07</v>
+        <v>19.55</v>
       </c>
       <c r="D317" s="4" t="s">
         <v>366</v>
@@ -6325,13 +6328,13 @@
     </row>
     <row r="318" spans="1:4">
       <c r="A318" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B318" s="3">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C318" s="3">
-        <v>21.9</v>
+        <v>19.07</v>
       </c>
       <c r="D318" s="4" t="s">
         <v>366</v>
@@ -6339,27 +6342,27 @@
     </row>
     <row r="319" spans="1:4">
       <c r="A319" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B319" s="3">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C319" s="3">
-        <v>79.349999999999994</v>
+        <v>21.9</v>
       </c>
       <c r="D319" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="320" spans="1:4">
       <c r="A320" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B320" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C320" s="3">
-        <v>862.7</v>
+        <v>79.349999999999994</v>
       </c>
       <c r="D320" s="4" t="s">
         <v>367</v>
@@ -6367,13 +6370,13 @@
     </row>
     <row r="321" spans="1:4">
       <c r="A321" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B321" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C321" s="3">
-        <v>56.93</v>
+        <v>862.7</v>
       </c>
       <c r="D321" s="4" t="s">
         <v>367</v>
@@ -6381,13 +6384,13 @@
     </row>
     <row r="322" spans="1:4">
       <c r="A322" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B322" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C322" s="3">
-        <v>1265</v>
+        <v>56.93</v>
       </c>
       <c r="D322" s="4" t="s">
         <v>367</v>
@@ -6395,27 +6398,27 @@
     </row>
     <row r="323" spans="1:4">
       <c r="A323" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B323" s="3">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="C323" s="3">
-        <v>76</v>
+        <v>1265</v>
       </c>
       <c r="D323" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="324" spans="1:4">
       <c r="A324" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B324" s="3">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C324" s="3">
-        <v>267.85000000000002</v>
+        <v>76</v>
       </c>
       <c r="D324" s="4" t="s">
         <v>364</v>
@@ -6423,13 +6426,13 @@
     </row>
     <row r="325" spans="1:4">
       <c r="A325" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B325" s="3">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C325" s="3">
-        <v>74.7</v>
+        <v>267.85000000000002</v>
       </c>
       <c r="D325" s="4" t="s">
         <v>364</v>
@@ -6437,13 +6440,13 @@
     </row>
     <row r="326" spans="1:4">
       <c r="A326" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B326" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C326" s="3">
-        <v>327.3</v>
+        <v>74.7</v>
       </c>
       <c r="D326" s="4" t="s">
         <v>364</v>
@@ -6451,13 +6454,13 @@
     </row>
     <row r="327" spans="1:4">
       <c r="A327" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B327" s="3">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C327" s="3">
-        <v>72.13</v>
+        <v>327.3</v>
       </c>
       <c r="D327" s="4" t="s">
         <v>364</v>
@@ -6465,13 +6468,13 @@
     </row>
     <row r="328" spans="1:4">
       <c r="A328" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B328" s="3">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="C328" s="3">
-        <v>302.39999999999998</v>
+        <v>72.13</v>
       </c>
       <c r="D328" s="4" t="s">
         <v>364</v>
@@ -6479,41 +6482,41 @@
     </row>
     <row r="329" spans="1:4">
       <c r="A329" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B329" s="3">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C329" s="3">
-        <v>36.799999999999997</v>
+        <v>302.39999999999998</v>
       </c>
       <c r="D329" s="4" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="330" spans="1:4">
       <c r="A330" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B330" s="3">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C330" s="3">
-        <v>428.5</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="D330" s="4" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="331" spans="1:4">
       <c r="A331" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B331" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C331" s="3">
-        <v>450.22</v>
+        <v>428.5</v>
       </c>
       <c r="D331" s="4" t="s">
         <v>364</v>
@@ -6521,13 +6524,13 @@
     </row>
     <row r="332" spans="1:4">
       <c r="A332" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B332" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C332" s="3">
-        <v>465.7</v>
+        <v>450.22</v>
       </c>
       <c r="D332" s="4" t="s">
         <v>364</v>
@@ -6535,41 +6538,41 @@
     </row>
     <row r="333" spans="1:4">
       <c r="A333" t="s">
-        <v>472</v>
+        <v>267</v>
       </c>
       <c r="B333" s="3">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="C333" s="3">
-        <v>0</v>
+        <v>465.7</v>
       </c>
       <c r="D333" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="334" spans="1:4">
       <c r="A334" t="s">
-        <v>268</v>
+        <v>472</v>
       </c>
       <c r="B334" s="3">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="C334" s="3">
-        <v>38.25</v>
+        <v>0</v>
       </c>
       <c r="D334" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="335" spans="1:4">
       <c r="A335" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B335" s="3">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C335" s="3">
-        <v>87.49</v>
+        <v>38.25</v>
       </c>
       <c r="D335" s="4" t="s">
         <v>364</v>
@@ -6577,13 +6580,13 @@
     </row>
     <row r="336" spans="1:4">
       <c r="A336" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B336" s="3">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C336" s="3">
-        <v>63.13</v>
+        <v>87.49</v>
       </c>
       <c r="D336" s="4" t="s">
         <v>364</v>
@@ -6591,27 +6594,27 @@
     </row>
     <row r="337" spans="1:4">
       <c r="A337" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B337" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C337" s="3">
-        <v>377.78</v>
+        <v>63.13</v>
       </c>
       <c r="D337" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="338" spans="1:4">
       <c r="A338" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B338" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C338" s="3">
-        <v>3333.85</v>
+        <v>377.78</v>
       </c>
       <c r="D338" s="4" t="s">
         <v>368</v>
@@ -6619,13 +6622,13 @@
     </row>
     <row r="339" spans="1:4">
       <c r="A339" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B339" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C339" s="3">
-        <v>374.67</v>
+        <v>3333.85</v>
       </c>
       <c r="D339" s="4" t="s">
         <v>368</v>
@@ -6633,13 +6636,13 @@
     </row>
     <row r="340" spans="1:4">
       <c r="A340" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B340" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C340" s="3">
-        <v>120.06</v>
+        <v>374.67</v>
       </c>
       <c r="D340" s="4" t="s">
         <v>368</v>
@@ -6647,41 +6650,41 @@
     </row>
     <row r="341" spans="1:4">
       <c r="A341" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B341" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C341" s="3">
-        <v>54.2</v>
+        <v>120.06</v>
       </c>
       <c r="D341" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="342" spans="1:4">
       <c r="A342" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B342" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C342" s="3">
-        <v>31.5</v>
+        <v>54.2</v>
       </c>
       <c r="D342" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="343" spans="1:4">
       <c r="A343" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B343" s="3">
         <v>0</v>
       </c>
       <c r="C343" s="3">
-        <v>114.09</v>
+        <v>31.5</v>
       </c>
       <c r="D343" s="4" t="s">
         <v>364</v>
@@ -6689,13 +6692,13 @@
     </row>
     <row r="344" spans="1:4">
       <c r="A344" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B344" s="3">
         <v>0</v>
       </c>
       <c r="C344" s="3">
-        <v>139.9</v>
+        <v>114.09</v>
       </c>
       <c r="D344" s="4" t="s">
         <v>364</v>
@@ -6703,13 +6706,13 @@
     </row>
     <row r="345" spans="1:4">
       <c r="A345" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B345" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C345" s="3">
-        <v>50.13</v>
+        <v>139.9</v>
       </c>
       <c r="D345" s="4" t="s">
         <v>364</v>
@@ -6717,13 +6720,13 @@
     </row>
     <row r="346" spans="1:4">
       <c r="A346" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B346" s="3">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C346" s="3">
-        <v>140.26</v>
+        <v>50.13</v>
       </c>
       <c r="D346" s="4" t="s">
         <v>364</v>
@@ -6731,55 +6734,55 @@
     </row>
     <row r="347" spans="1:4">
       <c r="A347" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B347" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C347" s="3">
-        <v>370.53</v>
+        <v>140.26</v>
       </c>
       <c r="D347" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="348" spans="1:4">
       <c r="A348" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B348" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C348" s="3">
-        <v>30.9</v>
+        <v>370.53</v>
       </c>
       <c r="D348" s="4" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
     </row>
     <row r="349" spans="1:4">
       <c r="A349" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B349" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C349" s="3">
-        <v>5746.5</v>
+        <v>30.9</v>
       </c>
       <c r="D349" s="4" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="350" spans="1:4">
       <c r="A350" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B350" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C350" s="3">
-        <v>516.46</v>
+        <v>5746.5</v>
       </c>
       <c r="D350" s="4" t="s">
         <v>364</v>
@@ -6787,13 +6790,13 @@
     </row>
     <row r="351" spans="1:4">
       <c r="A351" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B351" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C351" s="3">
-        <v>185.15</v>
+        <v>516.46</v>
       </c>
       <c r="D351" s="4" t="s">
         <v>364</v>
@@ -6801,58 +6804,58 @@
     </row>
     <row r="352" spans="1:4">
       <c r="A352" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B352" s="3">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="C352" s="3">
-        <v>11.5</v>
+        <v>185.15</v>
       </c>
       <c r="D352" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="353" spans="1:4">
       <c r="A353" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B353" s="3">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C353" s="3">
-        <v>724.5</v>
+        <v>11.5</v>
       </c>
       <c r="D353" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="354" spans="1:4">
       <c r="A354" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B354" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C354" s="3">
-        <v>450.22</v>
+        <v>724.5</v>
       </c>
       <c r="D354" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="355" spans="1:4">
       <c r="A355" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B355" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C355" s="3">
-        <v>461.23</v>
+        <v>450.22</v>
       </c>
       <c r="D355" s="4" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -6863,7 +6866,7 @@
         <v>1</v>
       </c>
       <c r="C356" s="3">
-        <v>518.41999999999996</v>
+        <v>461.23</v>
       </c>
       <c r="D356" s="4" t="s">
         <v>357</v>
@@ -6871,13 +6874,13 @@
     </row>
     <row r="357" spans="1:4">
       <c r="A357" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B357" s="3">
         <v>1</v>
       </c>
       <c r="C357" s="3">
-        <v>348.08</v>
+        <v>518.41999999999996</v>
       </c>
       <c r="D357" s="4" t="s">
         <v>357</v>
@@ -6885,13 +6888,13 @@
     </row>
     <row r="358" spans="1:4">
       <c r="A358" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B358" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C358" s="3">
-        <v>33.479999999999997</v>
+        <v>348.08</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>357</v>
@@ -6899,13 +6902,13 @@
     </row>
     <row r="359" spans="1:4">
       <c r="A359" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B359" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C359" s="3">
-        <v>35.79</v>
+        <v>33.479999999999997</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>357</v>
@@ -6913,13 +6916,13 @@
     </row>
     <row r="360" spans="1:4">
       <c r="A360" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B360" s="3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C360" s="3">
-        <v>377.7</v>
+        <v>35.79</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>357</v>
@@ -6927,13 +6930,13 @@
     </row>
     <row r="361" spans="1:4">
       <c r="A361" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B361" s="3">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C361" s="3">
-        <v>33.21</v>
+        <v>377.7</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>357</v>
@@ -6941,13 +6944,13 @@
     </row>
     <row r="362" spans="1:4">
       <c r="A362" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B362" s="3">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C362" s="3">
-        <v>27.16</v>
+        <v>33.21</v>
       </c>
       <c r="D362" s="4" t="s">
         <v>357</v>
@@ -6955,13 +6958,13 @@
     </row>
     <row r="363" spans="1:4">
       <c r="A363" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B363" s="3">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="C363" s="3">
-        <v>361.41</v>
+        <v>27.16</v>
       </c>
       <c r="D363" s="4" t="s">
         <v>357</v>
@@ -6969,13 +6972,13 @@
     </row>
     <row r="364" spans="1:4">
       <c r="A364" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B364" s="3">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="C364" s="3">
-        <v>29.25</v>
+        <v>361.41</v>
       </c>
       <c r="D364" s="4" t="s">
         <v>357</v>
@@ -6983,13 +6986,13 @@
     </row>
     <row r="365" spans="1:4">
       <c r="A365" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B365" s="3">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="C365" s="3">
-        <v>304.54000000000002</v>
+        <v>29.25</v>
       </c>
       <c r="D365" s="4" t="s">
         <v>357</v>
@@ -6997,13 +7000,13 @@
     </row>
     <row r="366" spans="1:4">
       <c r="A366" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B366" s="3">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C366" s="3">
-        <v>34.049999999999997</v>
+        <v>304.54000000000002</v>
       </c>
       <c r="D366" s="4" t="s">
         <v>357</v>
@@ -7011,55 +7014,55 @@
     </row>
     <row r="367" spans="1:4">
       <c r="A367" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B367" s="3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C367" s="3">
-        <v>57.7</v>
+        <v>34.049999999999997</v>
       </c>
       <c r="D367" s="4" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
     </row>
     <row r="368" spans="1:4">
       <c r="A368" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B368" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C368" s="3">
-        <v>90.9</v>
+        <v>57.7</v>
       </c>
       <c r="D368" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="369" spans="1:4">
       <c r="A369" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B369" s="3">
-        <v>169</v>
+        <v>10</v>
       </c>
       <c r="C369" s="3">
-        <v>47.62</v>
+        <v>90.9</v>
       </c>
       <c r="D369" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="370" spans="1:4">
       <c r="A370" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B370" s="3">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="C370" s="3">
-        <v>7173.59</v>
+        <v>47.62</v>
       </c>
       <c r="D370" s="4" t="s">
         <v>364</v>
@@ -7067,13 +7070,13 @@
     </row>
     <row r="371" spans="1:4">
       <c r="A371" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B371" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C371" s="3">
-        <v>677.79</v>
+        <v>7173.59</v>
       </c>
       <c r="D371" s="4" t="s">
         <v>364</v>
@@ -7081,13 +7084,13 @@
     </row>
     <row r="372" spans="1:4">
       <c r="A372" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B372" s="3">
-        <v>19</v>
-      </c>
-      <c r="C372" s="8">
-        <v>171.47</v>
+        <v>1</v>
+      </c>
+      <c r="C372" s="3">
+        <v>677.79</v>
       </c>
       <c r="D372" s="4" t="s">
         <v>364</v>
@@ -7095,13 +7098,13 @@
     </row>
     <row r="373" spans="1:4">
       <c r="A373" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B373" s="3">
-        <v>11</v>
-      </c>
-      <c r="C373" s="3">
-        <v>212.75</v>
+        <v>18</v>
+      </c>
+      <c r="C373" s="8">
+        <v>171.47</v>
       </c>
       <c r="D373" s="4" t="s">
         <v>364</v>
@@ -7109,13 +7112,13 @@
     </row>
     <row r="374" spans="1:4">
       <c r="A374" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B374" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C374" s="3">
-        <v>2335.67</v>
+        <v>212.75</v>
       </c>
       <c r="D374" s="4" t="s">
         <v>364</v>
@@ -7123,13 +7126,13 @@
     </row>
     <row r="375" spans="1:4">
       <c r="A375" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B375" s="3">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C375" s="3">
-        <v>66.180000000000007</v>
+        <v>2335.67</v>
       </c>
       <c r="D375" s="4" t="s">
         <v>364</v>
@@ -7137,13 +7140,13 @@
     </row>
     <row r="376" spans="1:4">
       <c r="A376" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B376" s="3">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C376" s="3">
-        <v>8139.6</v>
+        <v>66.180000000000007</v>
       </c>
       <c r="D376" s="4" t="s">
         <v>364</v>
@@ -7151,13 +7154,13 @@
     </row>
     <row r="377" spans="1:4">
       <c r="A377" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B377" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C377" s="3">
-        <v>259.81</v>
+        <v>8139.6</v>
       </c>
       <c r="D377" s="4" t="s">
         <v>364</v>
@@ -7165,13 +7168,13 @@
     </row>
     <row r="378" spans="1:4">
       <c r="A378" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B378" s="3">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="C378" s="3">
-        <v>259.8</v>
+        <v>259.81</v>
       </c>
       <c r="D378" s="4" t="s">
         <v>364</v>
@@ -7179,13 +7182,13 @@
     </row>
     <row r="379" spans="1:4">
       <c r="A379" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B379" s="3">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C379" s="3">
-        <v>310.2</v>
+        <v>259.8</v>
       </c>
       <c r="D379" s="4" t="s">
         <v>364</v>
@@ -7193,13 +7196,13 @@
     </row>
     <row r="380" spans="1:4">
       <c r="A380" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B380" s="3">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="C380" s="3">
-        <v>36.43</v>
+        <v>310.2</v>
       </c>
       <c r="D380" s="4" t="s">
         <v>364</v>
@@ -7207,13 +7210,13 @@
     </row>
     <row r="381" spans="1:4">
       <c r="A381" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B381" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C381" s="3">
-        <v>87.22</v>
+        <v>36.43</v>
       </c>
       <c r="D381" s="4" t="s">
         <v>364</v>
@@ -7221,13 +7224,13 @@
     </row>
     <row r="382" spans="1:4">
       <c r="A382" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B382" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C382" s="3">
-        <v>319.60000000000002</v>
+        <v>87.22</v>
       </c>
       <c r="D382" s="4" t="s">
         <v>364</v>
@@ -7235,13 +7238,13 @@
     </row>
     <row r="383" spans="1:4">
       <c r="A383" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B383" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C383" s="3">
-        <v>62.6</v>
+        <v>319.60000000000002</v>
       </c>
       <c r="D383" s="4" t="s">
         <v>364</v>
@@ -7249,13 +7252,13 @@
     </row>
     <row r="384" spans="1:4">
       <c r="A384" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B384" s="3">
-        <v>8</v>
-      </c>
-      <c r="C384" s="8">
-        <v>385.25</v>
+        <v>14</v>
+      </c>
+      <c r="C384" s="3">
+        <v>62.6</v>
       </c>
       <c r="D384" s="4" t="s">
         <v>364</v>
@@ -7263,27 +7266,27 @@
     </row>
     <row r="385" spans="1:4">
       <c r="A385" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B385" s="3">
-        <v>19</v>
-      </c>
-      <c r="C385" s="3">
-        <v>81.760000000000005</v>
+        <v>8</v>
+      </c>
+      <c r="C385" s="8">
+        <v>385.25</v>
       </c>
       <c r="D385" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="386" spans="1:4">
       <c r="A386" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B386" s="3">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C386" s="3">
-        <v>1138.5</v>
+        <v>81.760000000000005</v>
       </c>
       <c r="D386" s="4" t="s">
         <v>367</v>
@@ -7291,27 +7294,27 @@
     </row>
     <row r="387" spans="1:4">
       <c r="A387" t="s">
-        <v>350</v>
+        <v>319</v>
       </c>
       <c r="B387" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C387" s="3">
-        <v>58.69</v>
+        <v>1138.5</v>
       </c>
       <c r="D387" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="388" spans="1:4">
       <c r="A388" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B388" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C388" s="3">
-        <v>289.33999999999997</v>
+        <v>58.69</v>
       </c>
       <c r="D388" s="4" t="s">
         <v>364</v>
@@ -7319,13 +7322,13 @@
     </row>
     <row r="389" spans="1:4">
       <c r="A389" t="s">
-        <v>320</v>
+        <v>351</v>
       </c>
       <c r="B389" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C389" s="3">
-        <v>48.76</v>
+        <v>289.33999999999997</v>
       </c>
       <c r="D389" s="4" t="s">
         <v>364</v>
@@ -7333,13 +7336,13 @@
     </row>
     <row r="390" spans="1:4">
       <c r="A390" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B390" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C390" s="3">
-        <v>242.34</v>
+        <v>48.76</v>
       </c>
       <c r="D390" s="4" t="s">
         <v>364</v>
@@ -7347,13 +7350,13 @@
     </row>
     <row r="391" spans="1:4">
       <c r="A391" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B391" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C391" s="3">
-        <v>65.599999999999994</v>
+        <v>242.34</v>
       </c>
       <c r="D391" s="4" t="s">
         <v>364</v>
@@ -7361,13 +7364,13 @@
     </row>
     <row r="392" spans="1:4">
       <c r="A392" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B392" s="3">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C392" s="3">
-        <v>255.03</v>
+        <v>65.599999999999994</v>
       </c>
       <c r="D392" s="4" t="s">
         <v>364</v>
@@ -7375,13 +7378,13 @@
     </row>
     <row r="393" spans="1:4">
       <c r="A393" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B393" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C393" s="3">
-        <v>220.8</v>
+        <v>255.03</v>
       </c>
       <c r="D393" s="4" t="s">
         <v>364</v>
@@ -7389,13 +7392,13 @@
     </row>
     <row r="394" spans="1:4">
       <c r="A394" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B394" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C394" s="3">
-        <v>255.02</v>
+        <v>220.8</v>
       </c>
       <c r="D394" s="4" t="s">
         <v>364</v>
@@ -7403,13 +7406,13 @@
     </row>
     <row r="395" spans="1:4">
       <c r="A395" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B395" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C395" s="3">
-        <v>68.86</v>
+        <v>255.02</v>
       </c>
       <c r="D395" s="4" t="s">
         <v>364</v>
@@ -7417,13 +7420,13 @@
     </row>
     <row r="396" spans="1:4">
       <c r="A396" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B396" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C396" s="3">
-        <v>344.28</v>
+        <v>68.86</v>
       </c>
       <c r="D396" s="4" t="s">
         <v>364</v>
@@ -7431,13 +7434,13 @@
     </row>
     <row r="397" spans="1:4">
       <c r="A397" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B397" s="3">
         <v>2</v>
       </c>
       <c r="C397" s="3">
-        <v>60.29</v>
+        <v>344.28</v>
       </c>
       <c r="D397" s="4" t="s">
         <v>364</v>
@@ -7445,13 +7448,13 @@
     </row>
     <row r="398" spans="1:4">
       <c r="A398" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B398" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C398" s="3">
-        <v>261.8</v>
+        <v>60.29</v>
       </c>
       <c r="D398" s="4" t="s">
         <v>364</v>
@@ -7459,55 +7462,55 @@
     </row>
     <row r="399" spans="1:4">
       <c r="A399" t="s">
-        <v>382</v>
+        <v>329</v>
       </c>
       <c r="B399" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C399" s="3">
-        <v>30.58</v>
+        <v>261.8</v>
       </c>
       <c r="D399" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="400" spans="1:4">
       <c r="A400" t="s">
-        <v>330</v>
+        <v>382</v>
       </c>
       <c r="B400" s="3">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="C400" s="3">
-        <v>16.95</v>
+        <v>30.58</v>
       </c>
       <c r="D400" s="4" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
     </row>
     <row r="401" spans="1:4">
       <c r="A401" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B401" s="3">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="C401" s="3">
-        <v>24.95</v>
+        <v>16.95</v>
       </c>
       <c r="D401" s="4" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
     </row>
     <row r="402" spans="1:4">
       <c r="A402" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B402" s="3">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C402" s="3">
-        <v>641.49</v>
+        <v>24.95</v>
       </c>
       <c r="D402" s="4" t="s">
         <v>367</v>
@@ -7515,13 +7518,13 @@
     </row>
     <row r="403" spans="1:4">
       <c r="A403" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B403" s="3">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C403" s="3">
-        <v>39.57</v>
+        <v>641.49</v>
       </c>
       <c r="D403" s="4" t="s">
         <v>367</v>
@@ -7529,13 +7532,13 @@
     </row>
     <row r="404" spans="1:4">
       <c r="A404" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B404" s="3">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C404" s="3">
-        <v>51.83</v>
+        <v>39.57</v>
       </c>
       <c r="D404" s="4" t="s">
         <v>367</v>
@@ -7543,27 +7546,27 @@
     </row>
     <row r="405" spans="1:4">
       <c r="A405" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B405" s="3">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C405" s="3">
-        <v>33.840000000000003</v>
+        <v>51.83</v>
       </c>
       <c r="D405" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="406" spans="1:4">
       <c r="A406" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B406" s="3">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="C406" s="3">
-        <v>150.15</v>
+        <v>33.840000000000003</v>
       </c>
       <c r="D406" s="4" t="s">
         <v>364</v>
@@ -7571,13 +7574,13 @@
     </row>
     <row r="407" spans="1:4">
       <c r="A407" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B407" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C407" s="3">
-        <v>144.5</v>
+        <v>150.15</v>
       </c>
       <c r="D407" s="4" t="s">
         <v>364</v>
@@ -7585,13 +7588,13 @@
     </row>
     <row r="408" spans="1:4">
       <c r="A408" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B408" s="3">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C408" s="3">
-        <v>100.93</v>
+        <v>144.5</v>
       </c>
       <c r="D408" s="4" t="s">
         <v>364</v>
@@ -7599,13 +7602,13 @@
     </row>
     <row r="409" spans="1:4">
       <c r="A409" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B409" s="3">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C409" s="3">
-        <v>124.5</v>
+        <v>100.93</v>
       </c>
       <c r="D409" s="4" t="s">
         <v>364</v>
@@ -7613,13 +7616,13 @@
     </row>
     <row r="410" spans="1:4">
       <c r="A410" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B410" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C410" s="3">
-        <v>27.21</v>
+        <v>124.5</v>
       </c>
       <c r="D410" s="4" t="s">
         <v>364</v>
@@ -7627,41 +7630,41 @@
     </row>
     <row r="411" spans="1:4">
       <c r="A411" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B411" s="3">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="C411" s="3">
-        <v>24.79</v>
+        <v>27.21</v>
       </c>
       <c r="D411" s="4" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
     </row>
     <row r="412" spans="1:4">
       <c r="A412" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B412" s="3">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="C412" s="3">
-        <v>37.1</v>
+        <v>24.79</v>
       </c>
       <c r="D412" s="4" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
     </row>
     <row r="413" spans="1:4">
       <c r="A413" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B413" s="3">
         <v>0</v>
       </c>
       <c r="C413" s="3">
-        <v>178.04</v>
+        <v>37.1</v>
       </c>
       <c r="D413" s="4" t="s">
         <v>364</v>
@@ -7669,41 +7672,41 @@
     </row>
     <row r="414" spans="1:4">
       <c r="A414" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B414" s="3">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="C414" s="3">
-        <v>23.88</v>
+        <v>178.04</v>
       </c>
       <c r="D414" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="415" spans="1:4">
       <c r="A415" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B415" s="3">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="C415" s="3">
-        <v>20.68</v>
+        <v>23.88</v>
       </c>
       <c r="D415" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="416" spans="1:4">
       <c r="A416" t="s">
-        <v>372</v>
+        <v>345</v>
       </c>
       <c r="B416" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C416" s="3">
-        <v>97.54</v>
+        <v>20.68</v>
       </c>
       <c r="D416" s="4" t="s">
         <v>364</v>
@@ -7711,13 +7714,13 @@
     </row>
     <row r="417" spans="1:4">
       <c r="A417" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B417" s="3">
         <v>0</v>
       </c>
       <c r="C417" s="3">
-        <v>304.02999999999997</v>
+        <v>97.54</v>
       </c>
       <c r="D417" s="4" t="s">
         <v>364</v>
@@ -7725,27 +7728,27 @@
     </row>
     <row r="418" spans="1:4">
       <c r="A418" t="s">
-        <v>346</v>
+        <v>373</v>
       </c>
       <c r="B418" s="3">
         <v>0</v>
       </c>
       <c r="C418" s="3">
-        <v>1934.56</v>
+        <v>304.02999999999997</v>
       </c>
       <c r="D418" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="419" spans="1:4">
       <c r="A419" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B419" s="3">
         <v>0</v>
       </c>
       <c r="C419" s="3">
-        <v>230.99</v>
+        <v>1934.56</v>
       </c>
       <c r="D419" s="4" t="s">
         <v>368</v>
@@ -7753,55 +7756,55 @@
     </row>
     <row r="420" spans="1:4">
       <c r="A420" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B420" s="3">
         <v>0</v>
       </c>
       <c r="C420" s="3">
-        <v>33.39</v>
+        <v>230.99</v>
       </c>
       <c r="D420" s="4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="421" spans="1:4">
       <c r="A421" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B421" s="3">
         <v>0</v>
       </c>
       <c r="C421" s="3">
-        <v>20.66</v>
+        <v>33.39</v>
       </c>
       <c r="D421" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="422" spans="1:4">
       <c r="A422" t="s">
-        <v>375</v>
+        <v>349</v>
       </c>
       <c r="B422" s="3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C422" s="3">
-        <v>97.5</v>
+        <v>20.66</v>
       </c>
       <c r="D422" s="4" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
     </row>
     <row r="423" spans="1:4">
       <c r="A423" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B423" s="3">
-        <v>302</v>
+        <v>24</v>
       </c>
       <c r="C423" s="3">
-        <v>24.7</v>
+        <v>97.5</v>
       </c>
       <c r="D423" s="4" t="s">
         <v>374</v>
@@ -7809,13 +7812,13 @@
     </row>
     <row r="424" spans="1:4">
       <c r="A424" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B424" s="3">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C424" s="3">
-        <v>35.75</v>
+        <v>24.7</v>
       </c>
       <c r="D424" s="4" t="s">
         <v>374</v>
@@ -7823,13 +7826,13 @@
     </row>
     <row r="425" spans="1:4">
       <c r="A425" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B425" s="3">
-        <v>93</v>
+        <v>305</v>
       </c>
       <c r="C425" s="3">
-        <v>9.1</v>
+        <v>35.75</v>
       </c>
       <c r="D425" s="4" t="s">
         <v>374</v>
@@ -7837,13 +7840,13 @@
     </row>
     <row r="426" spans="1:4">
       <c r="A426" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B426" s="3">
-        <v>152</v>
+        <v>93</v>
       </c>
       <c r="C426" s="3">
-        <v>5.43</v>
+        <v>9.1</v>
       </c>
       <c r="D426" s="4" t="s">
         <v>374</v>
@@ -7851,13 +7854,13 @@
     </row>
     <row r="427" spans="1:4">
       <c r="A427" t="s">
-        <v>432</v>
+        <v>379</v>
       </c>
       <c r="B427" s="3">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="C427" s="3">
-        <v>11.99</v>
+        <v>5.43</v>
       </c>
       <c r="D427" s="4" t="s">
         <v>374</v>
@@ -7865,27 +7868,27 @@
     </row>
     <row r="428" spans="1:4">
       <c r="A428" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
       <c r="B428" s="3">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="C428" s="3">
-        <v>9.75</v>
+        <v>11.99</v>
       </c>
       <c r="D428" s="4" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="429" spans="1:4">
       <c r="A429" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B429" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C429" s="3">
-        <v>6.37</v>
+        <v>9.75</v>
       </c>
       <c r="D429" s="4" t="s">
         <v>380</v>
@@ -7893,13 +7896,13 @@
     </row>
     <row r="430" spans="1:4">
       <c r="A430" t="s">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="B430" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C430" s="3">
-        <v>10.53</v>
+        <v>6.37</v>
       </c>
       <c r="D430" s="4" t="s">
         <v>380</v>
@@ -7907,27 +7910,27 @@
     </row>
     <row r="431" spans="1:4">
       <c r="A431" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="B431" s="3">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C431" s="3">
-        <v>11.59</v>
+        <v>10.53</v>
       </c>
       <c r="D431" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="432" spans="1:4">
       <c r="A432" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="B432" s="3">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="C432" s="3">
-        <v>12.09</v>
+        <v>11.59</v>
       </c>
       <c r="D432" s="4" t="s">
         <v>381</v>
@@ -7935,10 +7938,10 @@
     </row>
     <row r="433" spans="1:4">
       <c r="A433" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B433" s="3">
-        <v>182</v>
+        <v>36</v>
       </c>
       <c r="C433" s="3">
         <v>12.09</v>
@@ -7949,13 +7952,13 @@
     </row>
     <row r="434" spans="1:4">
       <c r="A434" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B434" s="3">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C434" s="3">
-        <v>6.5</v>
+        <v>12.09</v>
       </c>
       <c r="D434" s="4" t="s">
         <v>381</v>
@@ -7963,10 +7966,10 @@
     </row>
     <row r="435" spans="1:4">
       <c r="A435" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B435" s="3">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="C435" s="3">
         <v>6.5</v>
@@ -7977,27 +7980,27 @@
     </row>
     <row r="436" spans="1:4">
       <c r="A436" t="s">
-        <v>451</v>
+        <v>437</v>
       </c>
       <c r="B436" s="3">
-        <v>2</v>
+        <v>174</v>
       </c>
       <c r="C436" s="3">
-        <v>5017</v>
+        <v>6.5</v>
       </c>
       <c r="D436" s="4" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
     </row>
     <row r="437" spans="1:4">
       <c r="A437" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B437" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C437" s="3">
-        <v>4437.1499999999996</v>
+        <v>5017</v>
       </c>
       <c r="D437" s="4" t="s">
         <v>364</v>
@@ -8005,13 +8008,13 @@
     </row>
     <row r="438" spans="1:4">
       <c r="A438" t="s">
-        <v>429</v>
+        <v>452</v>
       </c>
       <c r="B438" s="3">
         <v>7</v>
       </c>
       <c r="C438" s="3">
-        <v>6239.83</v>
+        <v>4437.1499999999996</v>
       </c>
       <c r="D438" s="4" t="s">
         <v>364</v>
@@ -8019,13 +8022,13 @@
     </row>
     <row r="439" spans="1:4">
       <c r="A439" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="B439" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C439" s="3">
-        <v>5980</v>
+        <v>6239.83</v>
       </c>
       <c r="D439" s="4" t="s">
         <v>364</v>
@@ -8033,13 +8036,13 @@
     </row>
     <row r="440" spans="1:4">
       <c r="A440" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="B440" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C440" s="3">
-        <v>3556.4</v>
+        <v>5980</v>
       </c>
       <c r="D440" s="4" t="s">
         <v>364</v>
@@ -8047,13 +8050,13 @@
     </row>
     <row r="441" spans="1:4">
       <c r="A441" t="s">
-        <v>449</v>
+        <v>428</v>
       </c>
       <c r="B441" s="3">
         <v>2</v>
       </c>
       <c r="C441" s="3">
-        <v>6463</v>
+        <v>3556.4</v>
       </c>
       <c r="D441" s="4" t="s">
         <v>364</v>
@@ -8061,13 +8064,13 @@
     </row>
     <row r="442" spans="1:4">
       <c r="A442" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B442" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C442" s="3">
-        <v>5199</v>
+        <v>6463</v>
       </c>
       <c r="D442" s="4" t="s">
         <v>364</v>
@@ -8075,41 +8078,41 @@
     </row>
     <row r="443" spans="1:4">
       <c r="A443" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="B443" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C443" s="3">
-        <v>45</v>
+        <v>5199</v>
       </c>
       <c r="D443" s="4" t="s">
-        <v>453</v>
+        <v>364</v>
       </c>
     </row>
     <row r="444" spans="1:4">
       <c r="A444" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B444" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C444" s="3">
-        <v>70.25</v>
+        <v>45</v>
       </c>
       <c r="D444" s="4" t="s">
-        <v>367</v>
+        <v>453</v>
       </c>
     </row>
     <row r="445" spans="1:4">
       <c r="A445" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B445" s="3">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C445" s="3">
-        <v>58.9</v>
+        <v>70.25</v>
       </c>
       <c r="D445" s="4" t="s">
         <v>367</v>
@@ -8117,13 +8120,13 @@
     </row>
     <row r="446" spans="1:4">
       <c r="A446" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B446" s="3">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="C446" s="3">
-        <v>89.21</v>
+        <v>58.9</v>
       </c>
       <c r="D446" s="4" t="s">
         <v>367</v>
@@ -8131,13 +8134,13 @@
     </row>
     <row r="447" spans="1:4">
       <c r="A447" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B447" s="3">
         <v>60</v>
       </c>
       <c r="C447" s="3">
-        <v>59.18</v>
+        <v>89.21</v>
       </c>
       <c r="D447" s="4" t="s">
         <v>367</v>
@@ -8145,13 +8148,13 @@
     </row>
     <row r="448" spans="1:4">
       <c r="A448" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B448" s="3">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C448" s="3">
-        <v>60.62</v>
+        <v>59.18</v>
       </c>
       <c r="D448" s="4" t="s">
         <v>367</v>
@@ -8159,13 +8162,13 @@
     </row>
     <row r="449" spans="1:4">
       <c r="A449" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B449" s="3">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="C449" s="3">
-        <v>3431.7</v>
+        <v>60.62</v>
       </c>
       <c r="D449" s="4" t="s">
         <v>367</v>
@@ -8173,13 +8176,13 @@
     </row>
     <row r="450" spans="1:4">
       <c r="A450" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B450" s="3">
         <v>3</v>
       </c>
       <c r="C450" s="3">
-        <v>1260.2</v>
+        <v>3431.7</v>
       </c>
       <c r="D450" s="4" t="s">
         <v>367</v>
@@ -8187,13 +8190,13 @@
     </row>
     <row r="451" spans="1:4">
       <c r="A451" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B451" s="3">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="C451" s="3">
-        <v>47.2</v>
+        <v>1260.2</v>
       </c>
       <c r="D451" s="4" t="s">
         <v>367</v>
@@ -8201,13 +8204,13 @@
     </row>
     <row r="452" spans="1:4">
       <c r="A452" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="B452" s="3">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="C452" s="3">
-        <v>71.760000000000005</v>
+        <v>47.2</v>
       </c>
       <c r="D452" s="4" t="s">
         <v>367</v>
@@ -8215,15 +8218,29 @@
     </row>
     <row r="453" spans="1:4">
       <c r="A453" t="s">
+        <v>467</v>
+      </c>
+      <c r="B453" s="3">
+        <v>60</v>
+      </c>
+      <c r="C453" s="3">
+        <v>71.760000000000005</v>
+      </c>
+      <c r="D453" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4">
+      <c r="A454" t="s">
         <v>469</v>
       </c>
-      <c r="B453" s="3">
+      <c r="B454" s="3">
         <v>34</v>
       </c>
-      <c r="C453" s="3">
+      <c r="C454" s="3">
         <v>45</v>
       </c>
-      <c r="D453" s="4" t="s">
+      <c r="D454" s="4" t="s">
         <v>453</v>
       </c>
     </row>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -2299,7 +2299,7 @@
         <v>422</v>
       </c>
       <c r="B30" s="3">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="C30" s="3">
         <v>45.19</v>
@@ -2341,7 +2341,7 @@
         <v>423</v>
       </c>
       <c r="B33" s="3">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C33" s="3">
         <v>207.95</v>
@@ -2523,7 +2523,7 @@
         <v>13</v>
       </c>
       <c r="B46" s="3">
-        <v>1449</v>
+        <v>1437</v>
       </c>
       <c r="C46" s="3">
         <v>13</v>
@@ -2733,7 +2733,7 @@
         <v>440</v>
       </c>
       <c r="B61" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C61" s="3">
         <v>135.29</v>
@@ -2859,7 +2859,7 @@
         <v>32</v>
       </c>
       <c r="B70" s="3">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C70" s="3">
         <v>88.33</v>
@@ -2999,7 +2999,7 @@
         <v>443</v>
       </c>
       <c r="B80" s="3">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C80" s="3">
         <v>19.48</v>
@@ -3195,7 +3195,7 @@
         <v>45</v>
       </c>
       <c r="B94" s="3">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C94" s="3">
         <v>18.37</v>
@@ -3209,7 +3209,7 @@
         <v>46</v>
       </c>
       <c r="B95" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C95" s="3">
         <v>82.88</v>
@@ -3237,7 +3237,7 @@
         <v>48</v>
       </c>
       <c r="B97" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C97" s="3">
         <v>50.23</v>
@@ -4721,7 +4721,7 @@
         <v>147</v>
       </c>
       <c r="B203" s="3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C203" s="3">
         <v>44.5</v>
@@ -4735,7 +4735,7 @@
         <v>148</v>
       </c>
       <c r="B204" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C204" s="10">
         <v>210.88</v>
@@ -4917,7 +4917,7 @@
         <v>160</v>
       </c>
       <c r="B217" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C217" s="3">
         <v>33.479999999999997</v>
@@ -5393,7 +5393,7 @@
         <v>191</v>
       </c>
       <c r="B251" s="3">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C251" s="3">
         <v>33.479999999999997</v>
@@ -5645,7 +5645,7 @@
         <v>421</v>
       </c>
       <c r="B269" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C269" s="3">
         <v>29.63</v>
@@ -5813,7 +5813,7 @@
         <v>218</v>
       </c>
       <c r="B281" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C281" s="3">
         <v>79.75</v>
@@ -6023,7 +6023,7 @@
         <v>232</v>
       </c>
       <c r="B296" s="3">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C296" s="3">
         <v>51.15</v>
@@ -6065,7 +6065,7 @@
         <v>235</v>
       </c>
       <c r="B299" s="3">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C299" s="3">
         <v>222.62</v>
@@ -6723,7 +6723,7 @@
         <v>279</v>
       </c>
       <c r="B346" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C346" s="3">
         <v>50.13</v>
@@ -6737,7 +6737,7 @@
         <v>280</v>
       </c>
       <c r="B347" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C347" s="3">
         <v>140.26</v>
@@ -7115,7 +7115,7 @@
         <v>306</v>
       </c>
       <c r="B374" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C374" s="3">
         <v>212.75</v>
@@ -7171,7 +7171,7 @@
         <v>310</v>
       </c>
       <c r="B378" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C378" s="3">
         <v>259.81</v>
@@ -7577,7 +7577,7 @@
         <v>336</v>
       </c>
       <c r="B407" s="3">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C407" s="3">
         <v>150.15</v>
@@ -7801,7 +7801,7 @@
         <v>375</v>
       </c>
       <c r="B423" s="3">
-        <v>24</v>
+        <v>217</v>
       </c>
       <c r="C423" s="3">
         <v>97.5</v>
@@ -7815,7 +7815,7 @@
         <v>376</v>
       </c>
       <c r="B424" s="3">
-        <v>302</v>
+        <v>499</v>
       </c>
       <c r="C424" s="3">
         <v>24.7</v>
@@ -7829,7 +7829,7 @@
         <v>377</v>
       </c>
       <c r="B425" s="3">
-        <v>305</v>
+        <v>598</v>
       </c>
       <c r="C425" s="3">
         <v>35.75</v>
@@ -7843,7 +7843,7 @@
         <v>378</v>
       </c>
       <c r="B426" s="3">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C426" s="3">
         <v>9.1</v>
@@ -8095,7 +8095,7 @@
         <v>454</v>
       </c>
       <c r="B444" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C444" s="3">
         <v>45</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -5155,10 +5155,10 @@
         <v>177</v>
       </c>
       <c r="B234" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C234" s="3">
-        <v>466.78</v>
+        <v>615.9</v>
       </c>
       <c r="D234" s="4" t="s">
         <v>364</v>
@@ -7115,7 +7115,7 @@
         <v>306</v>
       </c>
       <c r="B374" s="3">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="C374" s="3">
         <v>212.75</v>
@@ -7241,7 +7241,7 @@
         <v>315</v>
       </c>
       <c r="B383" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C383" s="3">
         <v>319.60000000000002</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -1907,7 +1907,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="3">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C2" s="3">
         <v>12.4</v>
@@ -1949,7 +1949,7 @@
         <v>391</v>
       </c>
       <c r="B5" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C5" s="9">
         <v>245.7</v>
@@ -1963,7 +1963,7 @@
         <v>392</v>
       </c>
       <c r="B6" s="3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C6" s="9">
         <v>269.10000000000002</v>
@@ -1991,7 +1991,7 @@
         <v>406</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" s="3">
         <v>635.11</v>
@@ -2005,7 +2005,7 @@
         <v>394</v>
       </c>
       <c r="B9" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C9" s="3">
         <v>320</v>
@@ -2033,7 +2033,7 @@
         <v>412</v>
       </c>
       <c r="B11" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3">
         <v>476.85</v>
@@ -2047,7 +2047,7 @@
         <v>413</v>
       </c>
       <c r="B12" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" s="3">
         <v>545.9</v>
@@ -2075,7 +2075,7 @@
         <v>407</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14" s="3">
         <v>825.42</v>
@@ -2159,7 +2159,7 @@
         <v>396</v>
       </c>
       <c r="B20" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C20" s="3">
         <v>534.95000000000005</v>
@@ -2229,7 +2229,7 @@
         <v>401</v>
       </c>
       <c r="B25" s="3">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C25" s="3">
         <v>381.54</v>
@@ -2243,7 +2243,7 @@
         <v>402</v>
       </c>
       <c r="B26" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C26" s="3">
         <v>417.6</v>
@@ -2257,7 +2257,7 @@
         <v>403</v>
       </c>
       <c r="B27" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C27" s="3">
         <v>442.81</v>
@@ -2299,7 +2299,7 @@
         <v>422</v>
       </c>
       <c r="B30" s="3">
-        <v>231</v>
+        <v>183</v>
       </c>
       <c r="C30" s="3">
         <v>45.19</v>
@@ -2341,7 +2341,7 @@
         <v>423</v>
       </c>
       <c r="B33" s="3">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="C33" s="3">
         <v>207.95</v>
@@ -2411,7 +2411,7 @@
         <v>11</v>
       </c>
       <c r="B38" s="3">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C38" s="3">
         <v>189</v>
@@ -2453,7 +2453,7 @@
         <v>427</v>
       </c>
       <c r="B41" s="3">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C41" s="3">
         <v>120.32</v>
@@ -2677,7 +2677,7 @@
         <v>417</v>
       </c>
       <c r="B57" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C57" s="3">
         <v>144.84</v>
@@ -2705,7 +2705,7 @@
         <v>23</v>
       </c>
       <c r="B59" s="3">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C59" s="3">
         <v>255</v>
@@ -2957,7 +2957,7 @@
         <v>38</v>
       </c>
       <c r="B77" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C77" s="3">
         <v>103.51</v>
@@ -2999,7 +2999,7 @@
         <v>443</v>
       </c>
       <c r="B80" s="3">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="C80" s="3">
         <v>19.48</v>
@@ -3013,7 +3013,7 @@
         <v>444</v>
       </c>
       <c r="B81" s="3">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C81" s="3">
         <v>70.72</v>
@@ -3055,7 +3055,7 @@
         <v>468</v>
       </c>
       <c r="B84" s="3">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="C84" s="3">
         <v>14.42</v>
@@ -3937,7 +3937,7 @@
         <v>94</v>
       </c>
       <c r="B147" s="3">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C147" s="3">
         <v>66.98</v>
@@ -4189,7 +4189,7 @@
         <v>111</v>
       </c>
       <c r="B165" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C165" s="3">
         <v>101.5</v>
@@ -4245,7 +4245,7 @@
         <v>115</v>
       </c>
       <c r="B169" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C169" s="3">
         <v>32.200000000000003</v>
@@ -4651,7 +4651,7 @@
         <v>143</v>
       </c>
       <c r="B198" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C198" s="7">
         <v>59.62</v>
@@ -4665,7 +4665,7 @@
         <v>144</v>
       </c>
       <c r="B199" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C199" s="3">
         <v>248.77</v>
@@ -4777,7 +4777,7 @@
         <v>151</v>
       </c>
       <c r="B207" s="3">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C207" s="3">
         <v>48.64</v>
@@ -4791,7 +4791,7 @@
         <v>152</v>
       </c>
       <c r="B208" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C208" s="3">
         <v>126.63</v>
@@ -5085,7 +5085,7 @@
         <v>172</v>
       </c>
       <c r="B229" s="3">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C229" s="3">
         <v>37.299999999999997</v>
@@ -5113,7 +5113,7 @@
         <v>174</v>
       </c>
       <c r="B231" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C231" s="3">
         <v>154.62</v>
@@ -5533,7 +5533,7 @@
         <v>200</v>
       </c>
       <c r="B261" s="3">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C261" s="3">
         <v>32.200000000000003</v>
@@ -6023,7 +6023,7 @@
         <v>232</v>
       </c>
       <c r="B296" s="3">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C296" s="3">
         <v>51.15</v>
@@ -6051,7 +6051,7 @@
         <v>234</v>
       </c>
       <c r="B298" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C298" s="3">
         <v>182.42</v>
@@ -6065,7 +6065,7 @@
         <v>235</v>
       </c>
       <c r="B299" s="3">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C299" s="3">
         <v>222.62</v>
@@ -6093,7 +6093,7 @@
         <v>237</v>
       </c>
       <c r="B301" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C301" s="3">
         <v>894.8</v>
@@ -7115,7 +7115,7 @@
         <v>306</v>
       </c>
       <c r="B374" s="3">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C374" s="3">
         <v>212.75</v>
@@ -7143,7 +7143,7 @@
         <v>308</v>
       </c>
       <c r="B376" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C376" s="3">
         <v>66.180000000000007</v>
@@ -7199,7 +7199,7 @@
         <v>312</v>
       </c>
       <c r="B380" s="3">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C380" s="3">
         <v>310.2</v>
@@ -7381,7 +7381,7 @@
         <v>323</v>
       </c>
       <c r="B393" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C393" s="3">
         <v>255.03</v>
@@ -7801,7 +7801,7 @@
         <v>375</v>
       </c>
       <c r="B423" s="3">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="C423" s="3">
         <v>97.5</v>
@@ -7829,7 +7829,7 @@
         <v>377</v>
       </c>
       <c r="B425" s="3">
-        <v>598</v>
+        <v>578</v>
       </c>
       <c r="C425" s="3">
         <v>35.75</v>
@@ -7843,7 +7843,7 @@
         <v>378</v>
       </c>
       <c r="B426" s="3">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="C426" s="3">
         <v>9.1</v>
@@ -7927,7 +7927,7 @@
         <v>416</v>
       </c>
       <c r="B432" s="3">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C432" s="3">
         <v>11.59</v>
@@ -8151,7 +8151,7 @@
         <v>459</v>
       </c>
       <c r="B448" s="3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C448" s="3">
         <v>59.18</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -1907,7 +1907,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="3">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="C2" s="3">
         <v>12.4</v>
@@ -2341,7 +2341,7 @@
         <v>423</v>
       </c>
       <c r="B33" s="3">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C33" s="3">
         <v>207.95</v>
@@ -2369,7 +2369,7 @@
         <v>425</v>
       </c>
       <c r="B35" s="3">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="C35" s="3">
         <v>42.7</v>
@@ -2411,7 +2411,7 @@
         <v>11</v>
       </c>
       <c r="B38" s="3">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="C38" s="3">
         <v>189</v>
@@ -2523,7 +2523,7 @@
         <v>13</v>
       </c>
       <c r="B46" s="3">
-        <v>1437</v>
+        <v>1425</v>
       </c>
       <c r="C46" s="3">
         <v>13</v>
@@ -2859,7 +2859,7 @@
         <v>32</v>
       </c>
       <c r="B70" s="3">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C70" s="3">
         <v>88.33</v>
@@ -2887,7 +2887,7 @@
         <v>33</v>
       </c>
       <c r="B72" s="3">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C72" s="3">
         <v>18.96</v>
@@ -2915,7 +2915,7 @@
         <v>35</v>
       </c>
       <c r="B74" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C74" s="3">
         <v>89.38</v>
@@ -2999,7 +2999,7 @@
         <v>443</v>
       </c>
       <c r="B80" s="3">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="C80" s="3">
         <v>19.48</v>
@@ -3083,7 +3083,7 @@
         <v>446</v>
       </c>
       <c r="B86" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C86" s="3">
         <v>22.21</v>
@@ -3153,7 +3153,7 @@
         <v>43</v>
       </c>
       <c r="B91" s="3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C91" s="3">
         <v>28.07</v>
@@ -3167,7 +3167,7 @@
         <v>384</v>
       </c>
       <c r="B92" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C92" s="3">
         <v>23.33</v>
@@ -3209,7 +3209,7 @@
         <v>46</v>
       </c>
       <c r="B95" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C95" s="3">
         <v>82.88</v>
@@ -3755,7 +3755,7 @@
         <v>83</v>
       </c>
       <c r="B134" s="3">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C134" s="3">
         <v>67.27</v>
@@ -4427,7 +4427,7 @@
         <v>128</v>
       </c>
       <c r="B182" s="3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C182" s="3">
         <v>61.83</v>
@@ -4707,7 +4707,7 @@
         <v>385</v>
       </c>
       <c r="B202" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C202" s="3">
         <v>168.7</v>
@@ -4735,7 +4735,7 @@
         <v>148</v>
       </c>
       <c r="B204" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C204" s="10">
         <v>210.88</v>
@@ -4903,7 +4903,7 @@
         <v>352</v>
       </c>
       <c r="B216" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C216" s="8">
         <v>257.70999999999998</v>
@@ -4973,7 +4973,7 @@
         <v>164</v>
       </c>
       <c r="B221" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C221" s="3">
         <v>216.3</v>
@@ -5015,7 +5015,7 @@
         <v>167</v>
       </c>
       <c r="B224" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C224" s="3">
         <v>36.799999999999997</v>
@@ -5085,7 +5085,7 @@
         <v>172</v>
       </c>
       <c r="B229" s="3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C229" s="3">
         <v>37.299999999999997</v>
@@ -5393,7 +5393,7 @@
         <v>191</v>
       </c>
       <c r="B251" s="3">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C251" s="3">
         <v>33.479999999999997</v>
@@ -6023,7 +6023,7 @@
         <v>232</v>
       </c>
       <c r="B296" s="3">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C296" s="3">
         <v>51.15</v>
@@ -6065,7 +6065,7 @@
         <v>235</v>
       </c>
       <c r="B299" s="3">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C299" s="3">
         <v>222.62</v>
@@ -6639,7 +6639,7 @@
         <v>273</v>
       </c>
       <c r="B340" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C340" s="3">
         <v>374.67</v>
@@ -7101,7 +7101,7 @@
         <v>305</v>
       </c>
       <c r="B373" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C373" s="8">
         <v>171.47</v>
@@ -7115,7 +7115,7 @@
         <v>306</v>
       </c>
       <c r="B374" s="3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C374" s="3">
         <v>212.75</v>
@@ -7143,7 +7143,7 @@
         <v>308</v>
       </c>
       <c r="B376" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C376" s="3">
         <v>66.180000000000007</v>
@@ -7199,7 +7199,7 @@
         <v>312</v>
       </c>
       <c r="B380" s="3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C380" s="3">
         <v>310.2</v>
@@ -7815,7 +7815,7 @@
         <v>376</v>
       </c>
       <c r="B424" s="3">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C424" s="3">
         <v>24.7</v>
@@ -7829,7 +7829,7 @@
         <v>377</v>
       </c>
       <c r="B425" s="3">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="C425" s="3">
         <v>35.75</v>
@@ -7843,7 +7843,7 @@
         <v>378</v>
       </c>
       <c r="B426" s="3">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="C426" s="3">
         <v>9.1</v>
@@ -7857,7 +7857,7 @@
         <v>379</v>
       </c>
       <c r="B427" s="3">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C427" s="3">
         <v>5.43</v>
@@ -8235,7 +8235,7 @@
         <v>469</v>
       </c>
       <c r="B454" s="3">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C454" s="3">
         <v>45</v>

--- a/STOCEGIUNIE.xlsx
+++ b/STOCEGIUNIE.xlsx
@@ -2159,7 +2159,7 @@
         <v>396</v>
       </c>
       <c r="B20" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C20" s="3">
         <v>534.95000000000005</v>
@@ -2229,7 +2229,7 @@
         <v>401</v>
       </c>
       <c r="B25" s="3">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C25" s="3">
         <v>381.54</v>
@@ -2411,7 +2411,7 @@
         <v>11</v>
       </c>
       <c r="B38" s="3">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C38" s="3">
         <v>189</v>
@@ -2887,7 +2887,7 @@
         <v>33</v>
       </c>
       <c r="B72" s="3">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C72" s="3">
         <v>18.96</v>
@@ -2901,7 +2901,7 @@
         <v>34</v>
       </c>
       <c r="B73" s="3">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C73" s="3">
         <v>73.13</v>
@@ -2915,7 +2915,7 @@
         <v>35</v>
       </c>
       <c r="B74" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C74" s="3">
         <v>89.38</v>
@@ -2999,7 +2999,7 @@
         <v>443</v>
       </c>
       <c r="B80" s="3">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="C80" s="3">
         <v>19.48</v>
@@ -3013,7 +3013,7 @@
         <v>444</v>
       </c>
       <c r="B81" s="3">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C81" s="3">
         <v>70.72</v>
@@ -3797,7 +3797,7 @@
         <v>86</v>
       </c>
       <c r="B137" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C137" s="3">
         <v>149.91</v>
@@ -3937,7 +3937,7 @@
         <v>94</v>
       </c>
       <c r="B147" s="3">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C147" s="3">
         <v>66.98</v>
@@ -4189,7 +4189,7 @@
         <v>111</v>
       </c>
       <c r="B165" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C165" s="3">
         <v>101.5</v>
@@ -4973,7 +4973,7 @@
         <v>164</v>
       </c>
       <c r="B221" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C221" s="3">
         <v>216.3</v>
@@ -5337,7 +5337,7 @@
         <v>187</v>
       </c>
       <c r="B247" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C247" s="3">
         <v>67.28</v>
@@ -5365,7 +5365,7 @@
         <v>189</v>
       </c>
       <c r="B249" s="3">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C249" s="8">
         <v>75.88</v>
@@ -6023,7 +6023,7 @@
         <v>232</v>
       </c>
       <c r="B296" s="3">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C296" s="3">
         <v>51.15</v>
@@ -6065,7 +6065,7 @@
         <v>235</v>
       </c>
       <c r="B299" s="3">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C299" s="3">
         <v>222.62</v>
@@ -6667,7 +6667,7 @@
         <v>275</v>
       </c>
       <c r="B342" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C342" s="3">
         <v>54.2</v>
@@ -7059,7 +7059,7 @@
         <v>302</v>
       </c>
       <c r="B370" s="3">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C370" s="3">
         <v>47.62</v>
@@ -7101,7 +7101,7 @@
         <v>305</v>
       </c>
       <c r="B373" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C373" s="8">
         <v>171.47</v>
@@ -7115,7 +7115,7 @@
         <v>306</v>
       </c>
       <c r="B374" s="3">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C374" s="3">
         <v>212.75</v>
@@ -7143,7 +7143,7 @@
         <v>308</v>
       </c>
       <c r="B376" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C376" s="3">
         <v>66.180000000000007</v>
@@ -7199,7 +7199,7 @@
         <v>312</v>
       </c>
       <c r="B380" s="3">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C380" s="3">
         <v>310.2</v>
@@ -7283,7 +7283,7 @@
         <v>318</v>
       </c>
       <c r="B386" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C386" s="3">
         <v>81.760000000000005</v>
@@ -7801,7 +7801,7 @@
         <v>375</v>
       </c>
       <c r="B423" s="3">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C423" s="3">
         <v>97.5</v>
@@ -7815,7 +7815,7 @@
         <v>376</v>
       </c>
       <c r="B424" s="3">
-        <v>496</v>
+        <v>482</v>
       </c>
       <c r="C424" s="3">
         <v>24.7</v>
@@ -7829,7 +7829,7 @@
         <v>377</v>
       </c>
       <c r="B425" s="3">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="C425" s="3">
         <v>35.75</v>
@@ -7843,7 +7843,7 @@
         <v>378</v>
       </c>
       <c r="B426" s="3">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C426" s="3">
         <v>9.1</v>
@@ -7941,7 +7941,7 @@
         <v>434</v>
       </c>
       <c r="B433" s="3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C433" s="3">
         <v>12.09</v>
@@ -7955,7 +7955,7 @@
         <v>435</v>
       </c>
       <c r="B434" s="3">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C434" s="3">
         <v>12.09</v>
@@ -7969,7 +7969,7 @@
         <v>436</v>
       </c>
       <c r="B435" s="3">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C435" s="3">
         <v>6.5</v>
@@ -7983,7 +7983,7 @@
         <v>437</v>
       </c>
       <c r="B436" s="3">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C436" s="3">
         <v>6.5</v>
@@ -8095,7 +8095,7 @@
         <v>454</v>
       </c>
       <c r="B444" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C444" s="3">
         <v>45</v>
@@ -8151,7 +8151,7 @@
         <v>459</v>
       </c>
       <c r="B448" s="3">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C448" s="3">
         <v>59.18</v>
@@ -8207,7 +8207,7 @@
         <v>463</v>
       </c>
       <c r="B452" s="3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C452" s="3">
         <v>47.2</v>
@@ -8235,7 +8235,7 @@
         <v>469</v>
       </c>
       <c r="B454" s="3">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C454" s="3">
         <v>45</v>
